--- a/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
+++ b/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sourcing_Candidates" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sourcing_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sourcing_Candidates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verified_Partners" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sourcing_History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,67 +419,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>국가 (Country)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>데이터 수집일</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>EDA 데이터 근거 (HS Code별 순위/수입액/물량)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>후보 HS Code 수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>최고 순위</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>우선순위 점수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>조사 상태</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>후보 파트너/에이전트명</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>회사 이메일</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>웹사이트 / LinkedIn</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Messenger</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>본사 위치</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>비고/메모</t>
         </is>
@@ -504,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +567,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,7 +604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -660,7 +649,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -697,7 +686,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -734,7 +723,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -771,7 +760,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -808,7 +797,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -845,7 +834,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -882,7 +871,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -919,7 +908,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -956,7 +945,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -993,7 +982,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1030,7 +1019,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1067,7 +1056,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1104,7 +1093,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1141,7 +1130,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1178,7 +1167,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1215,7 +1204,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1252,7 +1241,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1289,7 +1278,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-31 11:28:57</t>
+          <t>2026-07-31 21:06:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1329,44 +1318,356 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>수집 구동 시기 (Execution Timestamp)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>참조 HS Code 표 수</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>이번 실행 발견 국가 수</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>신규 후보국 수 (New)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>누적 총 후보국 수 (Total Accumulated)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>상태 (Status)</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>조사일 (Research Date)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>국가 (Country)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>회사명/에이전트명</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>구분 (법인/개인 에이전트)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>이메일</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>웹사이트 / LinkedIn URL</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Messenger/연락처</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>조사 범위 (HS Code 표)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>본사 위치 (상세)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>주요 취급 품목 및 특징</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>잠재적 협력 포인트</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>출처 URL (검증 근거)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-07-31 14:58:21</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pesca K &amp; M Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>pescauno@nifty.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>표2 (HS 160557)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-31 14:58:21</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>True World Japan Inc.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>표1 (HS 030781)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-31 14:58:21</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tsukuino Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tukuino@heart.ocn.ne.jp</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.tsukuino.com/english.html</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>표1 (HS 030781)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://www.tsukuino.com/english.html</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>수집 구동 시기 (Execution Timestamp)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>참조 HS Code 표 수</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>이번 실행 발견 국가 수</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>신규 후보국 수 (New)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>누적 총 후보국 수 (Total Accumulated)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>상태 (Status)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>2026-07-31 13:55:51</t>
         </is>
       </c>
@@ -1407,6 +1708,30 @@
         <v>22</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>정상 완료 (Success)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:06:19</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>정상 완료 (Success)</t>
         </is>

--- a/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
+++ b/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sourcing_Candidates" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verified_Partners" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sourcing_History" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sourcing_Candidates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Verified_Partners" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sourcing_History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,67 +431,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>국가 (Country)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>데이터 수집일</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>EDA 데이터 근거 (HS Code별 순위/수입액/물량)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>후보 HS Code 수</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>최고 순위</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>우선순위 점수</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>조사 상태</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>후보 파트너/에이전트명</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>회사 이메일</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>웹사이트 / LinkedIn</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Messenger</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>본사 위치</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>비고/메모</t>
         </is>
@@ -493,7 +505,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -530,7 +542,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,7 +579,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -604,7 +616,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -649,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -686,7 +698,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -723,7 +735,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -760,7 +772,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -797,7 +809,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -834,7 +846,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -871,7 +883,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -908,7 +920,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -945,7 +957,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -982,7 +994,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1019,7 +1031,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1056,7 +1068,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1093,7 +1105,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1130,7 +1142,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1167,7 +1179,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1204,7 +1216,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1241,7 +1253,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1278,7 +1290,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-31 21:06:19</t>
+          <t>2026-07-31 12:08:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1630,36 +1642,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>수집 구동 시기 (Execution Timestamp)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>참조 HS Code 표 수</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>이번 실행 발견 국가 수</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>신규 후보국 수 (New)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>누적 총 후보국 수 (Total Accumulated)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>상태 (Status)</t>
         </is>
@@ -1732,6 +1744,30 @@
         <v>22</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>정상 완료 (Success)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:08:43</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>정상 완료 (Success)</t>
         </is>

--- a/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
+++ b/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
@@ -524,15 +524,23 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>🔍 조사 완료 (1개사 발견)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yu Cheong Trading</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -561,15 +569,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd, UlifeFoods 외 1개사</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -598,15 +614,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Monterey Abalone Company, Ocean Floor Inc. 외 1개사</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1330,81 +1354,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>조사일 (Research Date)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>국가 (Country)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>회사명/에이전트명</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>구분 (법인/개인 에이전트)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>이메일</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>웹사이트 / LinkedIn URL</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Messenger/연락처</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>조사 범위 (HS Code 표)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>본사 위치 (상세)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>주요 취급 품목 및 특징</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>잠재적 협력 포인트</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>출처 URL (검증 근거)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1413,17 +1437,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pesca K &amp; M Co., Ltd.</t>
+          <t>Yu Cheong Trading</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1433,74 +1457,74 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>pescauno@nifty.com</t>
+          <t>yucheongtrading@hotmail.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEQe3eqzzyUiuv_BD8g2CnXbYj_yINvZWddKhuXl_6WeFAgDM33gA8N_CCXh8KRXiVuURa9buw9b_YcNjoGves1pX5rOGPsOleu9SJ1025RfCkFu5j1N1jue7S2YTxxrgYZvl4=</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
+          <t>WeChat (contact for appointments)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>표2 (HS 160557)</t>
+          <t>Wholesale supplier and processor of Australian wild abalone, and wholesaler of premium, local and imported seafood products, including imported canned and dried goods.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Melbourne</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
+          <t>Braeside, Victoria (Factory outlet address: 2 Canterbury Rd Braeside 3195)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
+          <t>Fresh, live wild-caught Australian abalone; IQF frozen abalone; locally processed canned abalone; imported canned and dried seafood products (including abalone).</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
+          <t>Explicitly states they have 'a range of imported canned and dried goods', making them a direct target for importing abalone. They welcome various buyers including restaurants, caterers, fish shops, fish markets, grocery and supermarkets, group buyers/on sellers and distributors and also the general public.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEQe3eqzzyUiuv_BD8g2CnXbYj_yINvZWddKhuXl_6WeFAgDM33gA8N_CCXh8KRXiVuURa9buw9b_YcNjoGves1pX5rOGPsOleu9SJ1025RfCkFu5j1N1jue7S2YTxxrgYZvl4=</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
+          <t>They are also a processor and supplier of Australian wild abalone. Email and WeChat are listed as contact methods. Phone number is +61 427 955 952.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>True World Japan Inc.</t>
+          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1508,126 +1532,607 @@
           <t>법인</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>marketing@vegfoodgroup.com</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+          <t>http://www.vegfoodgroup.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
+          <t>+86-17706396685 (WhatsApp)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>Professional supplier of frozen, fresh, dehydrated vegetables, fruit and mushroom. Also lists 'Seafood' including 'canned abalone' among its products. Engages in import and export.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
+          <t>No.79 Jinzhong Road, Licang District, Qingdao City, China</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
+          <t>One import and export company, five own factories and more than 15 factories in China through mutual shareholding, joint ventures. Diverse product range beyond abalone.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
+          <t>An import and export company explicitly dealing with 'canned abalone' as part of their seafood offerings, indicating direct involvement in abalone distribution within China.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+          <t>http://www.vegfoodgroup.com/contact-us.html</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
+          <t>The company lists 'canned abalone' as a product, confirming their involvement with abalone.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UlifeFoods</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>info@ulifefoods.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.ulifefoods.com</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>IQF Abalone wholesale supplier, frozen seafood, raw abalone, cooked abalone, canned abalone, dried abalone. Specializing in research, production, and sales of frozen processed foods.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fuzhou</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No. 10 Xiamei Road, Meixin Village, Meihua Town, Changle District, Fuzhou City, Fujian Province, China</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Over 30 years in the industry, own breeding base and factory, HACCP, BRC, ISO, ASC, FSPCA certified. Exports to USA, Canada, South Korea, Japan, Southeast Asia. Annual production capacity of 15,000 tons of quick-frozen prepared food.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Direct wholesale supplier with extensive product range (raw, cooked, canned, dried abalone) and international export experience. Certifications indicate high quality and safety standards.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://www.ulifefoods.com/about-us.html</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>They are a manufacturer and wholesale supplier, implying distribution and import capabilities for their own products, and potentially for others given their 'wholesale supplier' designation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Xiamen Binqi Import &amp; Export Co., Ltd</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tom@binqi-china.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Aquaculture producers, processors, importers and exporters of abalones (our own farm) and shrimps, crabs, squids, octopus, mackerel fish, hairtail, bamboo leaf fish, sardine and other frozen aquatic products. Also acts as an importer and distributor for various seafood products.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Xiamen</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Xiamen, Fujian, China</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Professional import and export company with strong capital strength, owned production factory (Zhangzhou Minzheng Food Co.,Ltd), 20 years farming and marketing experience. Strictly carries out 'Export food production regulations' and 'PRC food security law'.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Explicitly states 'importers of abalones' and 'Importer, Distributor'. Their integrated approach from farming to import/export makes them a comprehensive partner.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>https://www.sea-ex.com/seafood-companies/china/xiamen-binqi-import-export-co-ltd.htm</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Email found on Sea-Ex directory. Website not explicitly found in search results, but 'binqi-china.com' is part of the email domain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>2026-07-31 14:58:21</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pesca K &amp; M Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>pescauno@nifty.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>표2 (HS 160557)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-31 14:58:21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>True World Japan Inc.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>표1 (HS 030781)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-31 14:58:21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Tsukuino Co. Ltd.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>법인</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>tukuino@heart.ocn.ne.jp</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>https://www.tsukuino.com/english.html</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>표1 (HS 030781)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Toyosu Market, store 1065-1068, Koto-ku</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://www.tsukuino.com/english.html</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>이메일만 공개, 전화번호/문의폼 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Monterey Abalone Company</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://montereyabalone.com</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Monterey</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Email not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ocean Floor Inc.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>City, email, and website not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Seafarers Inc.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>City, email, and website not found in provided snippets.</t>
         </is>
       </c>
     </row>

--- a/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
+++ b/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
@@ -852,15 +852,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>OceanTaste Canada, Seacore Seafood Inc. 외 1개사</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -963,15 +971,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Goh Joo Hin Pte Ltd, Oceanus Group Limited 외 1개사</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1111,15 +1127,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Harmony Marine Products Sdn. Bhd., Ocean Pacific Seafood &amp; Meat Sdn Bhd 외 1개사</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1259,15 +1283,23 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>🔍 조사 완료 (2개사 발견)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD, Thai Abalone Co.,Ltd.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1354,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1514,17 +1546,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd</t>
+          <t>OceanTaste Canada</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1532,76 +1564,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>marketing@vegfoodgroup.com</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>http://www.vegfoodgroup.com</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>+86-17706396685 (WhatsApp)</t>
-        </is>
-      </c>
+          <t>https://oceantaste.ca</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Professional supplier of frozen, fresh, dehydrated vegetables, fruit and mushroom. Also lists 'Seafood' including 'canned abalone' among its products. Engages in import and export.</t>
+          <t>Online retailer of premium frozen seafood, including abalone. Offers local delivery in the Greater Toronto Area (GTA). Likely imports and distributes.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>No.79 Jinzhong Road, Licang District, Qingdao City, China</t>
+          <t>Unit 22, 140 Milner Ave., Scarborough, ON, M1S 3R3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>One import and export company, five own factories and more than 15 factories in China through mutual shareholding, joint ventures. Diverse product range beyond abalone.</t>
+          <t>Frozen Abalone Whole Clean, Vacuum Packed (160g). Specializes in premium frozen seafood for Chinese and Asian fine dining culture.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>An import and export company explicitly dealing with 'canned abalone' as part of their seafood offerings, indicating direct involvement in abalone distribution within China.</t>
+          <t>Directly sells frozen abalone to consumers, indicating an active market and direct import/distribution channels.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>http://www.vegfoodgroup.com/contact-us.html</t>
+          <t>https://oceantaste.ca/products/frozen-abalone-whole-clean-160g</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>The company lists 'canned abalone' as a product, confirming their involvement with abalone.</t>
+          <t>Email not directly published; a contact form is available on their website.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UlifeFoods</t>
+          <t>Seacore Seafood Inc.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1609,72 +1633,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>info@ulifefoods.com</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.ulifefoods.com</t>
+          <t>https://www.seacoreseafood.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>IQF Abalone wholesale supplier, frozen seafood, raw abalone, cooked abalone, canned abalone, dried abalone. Specializing in research, production, and sales of frozen processed foods.</t>
+          <t>Wholesaler, importer, exporter, foodservice, retail, traders, and distributors of IQF Frozen Abalone Products.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Vaughan</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>No. 10 Xiamei Road, Meixin Village, Meihua Town, Changle District, Fuzhou City, Fujian Province, China</t>
+          <t>81 Aviva Park Drive Vaughan, ON Canada L4L 9C1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Over 30 years in the industry, own breeding base and factory, HACCP, BRC, ISO, ASC, FSPCA certified. Exports to USA, Canada, South Korea, Japan, Southeast Asia. Annual production capacity of 15,000 tons of quick-frozen prepared food.</t>
+          <t>Abalone (Haliotis kamtschatkana), available in shell or meat, fresh and frozen, wild.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Direct wholesale supplier with extensive product range (raw, cooked, canned, dried abalone) and international export experience. Certifications indicate high quality and safety standards.</t>
+          <t>A large, established wholesaler and importer with explicit mention of handling fresh and frozen abalone.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.ulifefoods.com/about-us.html</t>
+          <t>https://www.seacoreseafood.com/abalone</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>They are a manufacturer and wholesale supplier, implying distribution and import capabilities for their own products, and potentially for others given their 'wholesale supplier' designation.</t>
+          <t>Email not directly published on the website. Phone numbers are 905-856-6222 and toll-free 1-800-563-6222.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xiamen Binqi Import &amp; Export Co., Ltd</t>
+          <t>Seafood Depot</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1682,68 +1702,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>tom@binqi-china.com</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.seafooddepot.ca</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Aquaculture producers, processors, importers and exporters of abalones (our own farm) and shrimps, crabs, squids, octopus, mackerel fish, hairtail, bamboo leaf fish, sardine and other frozen aquatic products. Also acts as an importer and distributor for various seafood products.</t>
+          <t>Wholesaler of fresh and frozen seafood, including abalone. Part of the Seacore Seafood Inc. group.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Xiamen</t>
+          <t>Vaughan</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Xiamen, Fujian, China</t>
+          <t>81 Aviva Park Drive Vaughan, ON Canada L4L 9C1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Professional import and export company with strong capital strength, owned production factory (Zhangzhou Minzheng Food Co.,Ltd), 20 years farming and marketing experience. Strictly carries out 'Export food production regulations' and 'PRC food security law'.</t>
+          <t>Abalone (Haliotis kamtschatkana), available in shell or meat, fresh and frozen, wild.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Explicitly states 'importers of abalones' and 'Importer, Distributor'. Their integrated approach from farming to import/export makes them a comprehensive partner.</t>
+          <t>As an affiliate of Seacore Seafood, they also deal with abalone and represent another distribution channel within the same major group.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.sea-ex.com/seafood-companies/china/xiamen-binqi-import-export-co-ltd.htm</t>
+          <t>https://www.seafooddepot.ca/abalone</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Email found on Sea-Ex directory. Website not explicitly found in search results, but 'binqi-china.com' is part of the email domain.</t>
+          <t>Email not directly published on the website. Phone numbers are 905-856-2770 and toll-free 1-855-563-2770.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pesca K &amp; M Co., Ltd.</t>
+          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1753,74 +1773,74 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>pescauno@nifty.com</t>
+          <t>marketing@vegfoodgroup.com</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+          <t>http://www.vegfoodgroup.com</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
+          <t>+86-17706396685 (WhatsApp)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>표2 (HS 160557)</t>
+          <t>Professional supplier of frozen, fresh, dehydrated vegetables, fruit and mushroom. Also lists 'Seafood' including 'canned abalone' among its products. Engages in import and export.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
+          <t>No.79 Jinzhong Road, Licang District, Qingdao City, China</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
+          <t>One import and export company, five own factories and more than 15 factories in China through mutual shareholding, joint ventures. Diverse product range beyond abalone.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
+          <t>An import and export company explicitly dealing with 'canned abalone' as part of their seafood offerings, indicating direct involvement in abalone distribution within China.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+          <t>http://www.vegfoodgroup.com/contact-us.html</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
+          <t>The company lists 'canned abalone' as a product, confirming their involvement with abalone.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>True World Japan Inc.</t>
+          <t>UlifeFoods</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1828,72 +1848,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>info@ulifefoods.com</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
-        </is>
-      </c>
+          <t>https://www.ulifefoods.com</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>IQF Abalone wholesale supplier, frozen seafood, raw abalone, cooked abalone, canned abalone, dried abalone. Specializing in research, production, and sales of frozen processed foods.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
+          <t>No. 10 Xiamei Road, Meixin Village, Meihua Town, Changle District, Fuzhou City, Fujian Province, China</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
+          <t>Over 30 years in the industry, own breeding base and factory, HACCP, BRC, ISO, ASC, FSPCA certified. Exports to USA, Canada, South Korea, Japan, Southeast Asia. Annual production capacity of 15,000 tons of quick-frozen prepared food.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
+          <t>Direct wholesale supplier with extensive product range (raw, cooked, canned, dried abalone) and international export experience. Certifications indicate high quality and safety standards.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+          <t>https://www.ulifefoods.com/about-us.html</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
+          <t>They are a manufacturer and wholesale supplier, implying distribution and import capabilities for their own products, and potentially for others given their 'wholesale supplier' designation.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tsukuino Co. Ltd.</t>
+          <t>Xiamen Binqi Import &amp; Export Co., Ltd</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1903,70 +1923,66 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tukuino@heart.ocn.ne.jp</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://www.tsukuino.com/english.html</t>
-        </is>
-      </c>
+          <t>tom@binqi-china.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>Aquaculture producers, processors, importers and exporters of abalones (our own farm) and shrimps, crabs, squids, octopus, mackerel fish, hairtail, bamboo leaf fish, sardine and other frozen aquatic products. Also acts as an importer and distributor for various seafood products.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Xiamen</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
+          <t>Xiamen, Fujian, China</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
+          <t>Professional import and export company with strong capital strength, owned production factory (Zhangzhou Minzheng Food Co.,Ltd), 20 years farming and marketing experience. Strictly carries out 'Export food production regulations' and 'PRC food security law'.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
+          <t>Explicitly states 'importers of abalones' and 'Importer, Distributor'. Their integrated approach from farming to import/export makes them a comprehensive partner.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.tsukuino.com/english.html</t>
+          <t>https://www.sea-ex.com/seafood-companies/china/xiamen-binqi-import-export-co-ltd.htm</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
+          <t>Email found on Sea-Ex directory. Website not explicitly found in search results, but 'binqi-china.com' is part of the email domain.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monterey Abalone Company</t>
+          <t>Bin Auf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1975,67 +1991,55 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://montereyabalone.com</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Monterey</t>
-        </is>
-      </c>
+          <t>인도네시아 수출업체, 수입업체, 해산물 무역업체. 제품에는 말린 해삼, 전복, 전갱이, 산호 송어, 말린 오징어, 황다랑어 등이 포함됩니다. 소량/대량 공급 가능.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
-        </is>
-      </c>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
+          <t>전복을 포함한 다양한 해산물 거래, 소량/대량 공급 가능.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
+          <t>명시적으로 '수입업체' 역할을 명시, 다양한 제품 범위, 유연한 공급량.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
+          <t>https://www.trade-seafood.com/seafood-indonesia.htm</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Email not found in provided snippets.</t>
+          <t>스니펫에서 직접적인 웹사이트나 이메일을 찾을 수 없지만, 회사는 수입업체로 등재되어 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ocean Floor Inc.</t>
+          <t>CV Langgeng Sentosa Trade Indo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2048,51 +2052,59 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>인도네시아 동부 자바의 냉동 해산물 수출업체, 조달업체 및 가공업체. 주요 생산품은 롤리고 오징어, 전복 고기, 문어, 갑오징어, 저서어류입니다. 냉동 삶은 전복 고기 'mata 7' 재고 보유.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>East Java</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>East Java - Indonesia.</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
+          <t>냉동 삶은 전복 고기, 즉시 선적 가능.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
+          <t>전복 고기의 직접 조달 및 가공업체, 즉시 선적 가능한 재고 보유. 주로 수출업체이지만, 조달 및 가공 역할은 국내에서 제품을 취급하며 수입을 위한 연락처가 될 수 있음을 시사합니다.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+          <t>https://www.go4worldbusiness.com/find/products/frozen-abalone/indonesia.html</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>City, email, and website not found in provided snippets.</t>
+          <t>연락 담당자 Tonny Santoso가 언급되었습니다. 스니펫에서 직접적인 이메일이나 웹사이트를 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seafarers Inc.</t>
+          <t>PT CITA KARYA AGUNG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2101,38 +2113,1231 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://variouseafood.com/</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
+          <t>인도네시아의 선도적인 신선 및 냉동 해산물 가공업체, 공급업체 및 수출업체. 전복과 같은 냉동 복족류를 포함하여 35가지 이상의 다양한 제품을 제공합니다. 어부 및 양식 전문가로부터 조달.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Belawan</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Belawan, Indonesia.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>달팽이 및 전복과 같은 프리미엄 냉동 복족류, 최적의 신선도를 유지하기 위해 신중하게 가공. GMP 표준 및 HACCP 인증.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>확고한 가공업체 및 공급업체, 지속 가능성 및 품질에 대한 약속, 광범위한 제품. 주로 수출업체이지만, 조달 및 가공 활동은 인도네시아 내 전복 공급망에서 관련 플레이어임을 나타냅니다.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>https://variouseafood.com/</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>스니펫에서 직접적인 이메일을 찾을 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-31 14:58:21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pesca K &amp; M Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>pescauno@nifty.com</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>표2 (HS 160557)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-31 14:58:21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>True World Japan Inc.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>표1 (HS 030781)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-31 14:58:21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tsukuino Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tukuino@heart.ocn.ne.jp</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.tsukuino.com/english.html</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>표1 (HS 030781)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>https://www.tsukuino.com/english.html</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Harmony Marine Products Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.harmonymarine.com.my/</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>전복, 해삼, 어류 부레를 포함한 프리미엄 해산물 진미 공급업체. 아시아 태평양, 남미 및 아프리카에서 제품 및 재료를 조달합니다.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>본사는 현대적인 시설(전용 건조실, 3,000평방피트 냉동고, 5,000평방피트 보관 공간)을 갖추고 있으며 HACCP 인증을 받았습니다.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>프리미엄 전복, 엄격한 품질 관리, 지속 가능한 조달, 30년 이상의 경험.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>광범위한 경험을 가진 확고한 공급업체, 국제적으로 조달, HACCP 인증.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>https://www.harmonymarine.com.my/abalone-supplier-malaysia</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>주로 공급업체이지만, 다양한 지역에서 조달하는 것은 수입 활동을 의미합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://oceanpacificonline.com/</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>전복을 포함한 다양한 해산물 및 냉동 식품을 도매 및 공급합니다.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Johor Bahru</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>전복, 조개, 게, 생선, 고기, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 공급합니다. 해산물 및 냉동 식품의 선두 공급업체입니다.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>다양한 국내 브랜드, 지속적인 트렌드 분석, 최고의 서비스와 제품 제공에 전념.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>https://oceanpacificonline.com/abalone</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>웹사이트에 전화번호가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>V Top Frozen Food Sdn Bhd</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Vtopff@gmail.com</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://vtopfrozenfood.com/</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>https://vtopfrozenfood.com/abalone-slices</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>웹사이트에 전화번호가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Goh Joo Hin Pte Ltd</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>food@gjh.com.sg</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>http://www.gjh.com.sg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Importer, Exporter, Wholesaler, Distributor</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oceanus Group Limited</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>contact@oceanus.com.sg</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>http://www.oceanus.com.sg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Teck Sang Pte Ltd</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>local@tecksang.com</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.tecksang.com</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>11 Hongkong Street, Singapore 059654</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>info@ruifuoilfood.com</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://ruifuoilfood.com/</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Si Maha Phot, Prachin Buri</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Thai Abalone Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Pathiu, Chumphon</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Monterey Abalone Company</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://montereyabalone.com</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Monterey</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Email not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ocean Floor Inc.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>City, email, and website not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Seafarers Inc.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>City, email, and website not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FGC JOINT STOCK COMPANY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>fgc.seafoods@gmail.com</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.fgc-foods.com/</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>전복(살아있는, 열처리 및 냉동)을 포함한 고품질의 안전한 수입 식품을 제조 및 공급합니다.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>수입 전복(살아있는, 열처리 및 냉동), 1kg/봉지, 10kg/상자, -18°C 보관, 24개월 유통기한.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>수입 전복 공급업체, 품질 및 안전에 중점, 다양한 맛과 스타일.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://www.fgc-foods.com/san-pham/thuc-pham-chat-luong-cho-kenh-nha-hang-va-ban-le/bao-ngu-nhap-khau</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>전화 및 Zalo 핫라인도 이용 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fishy Vietnam Co., Ltd</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Fishy.vn@gmail.com</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>베트남에서 전복(냉동 전복(Loco) 고기, 냉동 호주산 그린립 전복 포함)을 포함한 최고급 해산물을 수입 및 유통합니다.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>최고급 해산물 수입 및 유통 전문, 헌신과 명성, 고객 만족 중시, 고품질 제품, 최고의 서비스.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>프리미엄 해산물 수입 및 유통 선두 기업, 다양한 전복 제품, 품질 및 고객 서비스에 중점.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/san-pham/bao-ngu</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>세금 ID 및 핫라인도 이용 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Trọng Đức Seafood</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://trongduc.vn/</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>한국, 일본 및 인근 국가에서 전복을 수입하여 도매업체, 에이전트 및 유통업체에 공급합니다.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>수입 전복 (한국, 일본 및 인근 국가산), 다양한 크기, 도매업체/에이전트/유통업체에 좋은 가격, 품질 명성, 완전한 문서 및 바코드.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>직접 수입업체이며, 도매업체/에이전트/유통업체에 좋은 가격을 제공하고, 품질 및 문서화에 중점을 둡니다.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://trongduc.vn/san-pham/bao-ngu-nhap-khau/</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>이메일/전화번호는 스니펫에 명시되어 있지 않지만 웹사이트가 제공됩니다.</t>
         </is>
       </c>
     </row>

--- a/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
+++ b/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
@@ -704,15 +704,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kiwi Fish, Northern Waters Marine Limited 외 1개사</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1386,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1546,17 +1554,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OceanTaste Canada</t>
+          <t>ABC Communication (BD) Ltd.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1565,119 +1573,99 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://oceantaste.ca</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Online retailer of premium frozen seafood, including abalone. Offers local delivery in the Greater Toronto Area (GTA). Likely imports and distributes.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Scarborough</t>
-        </is>
-      </c>
+          <t>Live, Fresh &amp; Frozen Fish &amp; Shellfish Importer, Exporter and Wholesale Supplier</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Unit 22, 140 Milner Ave., Scarborough, ON, M1S 3R3</t>
-        </is>
-      </c>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Frozen Abalone Whole Clean, Vacuum Packed (160g). Specializes in premium frozen seafood for Chinese and Asian fine dining culture.</t>
+          <t>Various sea water and freshwater shrimps, lobsters, sea fish (grouper, pomfret, snapper, mackerel, tuna, sole, ribbonfish, yellow croaker, kingfish, queenfish, catfish, eel), crab, river fish (pangasius, tilapia), squid, cuttlefish, octopus. The broad range of molluscs and shellfish suggests potential for abalone import.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Directly sells frozen abalone to consumers, indicating an active market and direct import/distribution channels.</t>
+          <t>다양한 해산물, 특히 연체동물 및 조개류를 수입 및 도매하는 업체로, 전복 취급 가능성이 높습니다. 수출입 경험이 풍부합니다.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://oceantaste.ca/products/frozen-abalone-whole-clean-160g</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH2recWw77LodLAqieXnaM19i_QlUbz_GlfXiltSp4ImQ9ZToY192qgqeXp1PBqKOWBnmjOGq4lcuLpDTFAbU8f3IVf_E-hubC1ImotUiBh4A_0sJEYxk3_1wacYfHzQa6ClAdRNjH0zCK-YUHABEYGZNmjwIgn7NPfBdDUd0fhftM=</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Email not directly published; a contact form is available on their website.</t>
+          <t>이메일/웹사이트/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다. 다양한 조개류 및 연체동물을 취급하므로 전복 수입 가능성이 높다고 판단됩니다.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seacore Seafood Inc.</t>
+          <t>Sea Source Foods International</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>법인</t>
+          <t>개인 에이전트</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.seacoreseafood.com</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Wholesaler, importer, exporter, foodservice, retail, traders, and distributors of IQF Frozen Abalone Products.</t>
+          <t>Seafood Sourcing and Supplying Organization, Seafood Trading and Buying Agency</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Vaughan</t>
+          <t>Khulna</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>81 Aviva Park Drive Vaughan, ON Canada L4L 9C1</t>
-        </is>
-      </c>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Abalone (Haliotis kamtschatkana), available in shell or meat, fresh and frozen, wild.</t>
+          <t>Best-quality, sustainable and traceable seafood. Meets international approvals from EEC and FDA with HACCP, BRCGS, ISO, IFS, BAP standards. Specializes in sourcing and supplying supreme quality seafood to global clients.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>A large, established wholesaler and importer with explicit mention of handling fresh and frozen abalone.</t>
+          <t>방글라데시의 주요 해산물 소싱 및 공급 기관이자 구매 에이전시로, 국제 표준을 충족하며 다양한 해산물을 취급합니다. 전복 수입을 위한 파트너십 구축 가능성이 있습니다.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.seacoreseafood.com/abalone</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEdB9N6kAWV52i-o8j_ES0kpl_UGL87D3BcCFt1EMhegOHmGFRdZ9QpXdWz7tlCS0kJLdz87hnAd30JFFTpn7FbTes5KinaKz8OVbCkwFfswdo-GmOmvzVc8g=</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Email not directly published on the website. Phone numbers are 905-856-6222 and toll-free 1-800-563-6222.</t>
+          <t>이메일/웹사이트/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다. 'buying agency'로 명시되어 있어 에이전트 역할도 수행하는 것으로 판단됩니다.</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1682,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seafood Depot</t>
+          <t>OceanTaste Canada</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1705,18 +1693,18 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.seafooddepot.ca</t>
+          <t>https://oceantaste.ca</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Wholesaler of fresh and frozen seafood, including abalone. Part of the Seacore Seafood Inc. group.</t>
+          <t>Online retailer of premium frozen seafood, including abalone. Offers local delivery in the Greater Toronto Area (GTA). Likely imports and distributes.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Vaughan</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1726,44 +1714,44 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>81 Aviva Park Drive Vaughan, ON Canada L4L 9C1</t>
+          <t>Unit 22, 140 Milner Ave., Scarborough, ON, M1S 3R3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Abalone (Haliotis kamtschatkana), available in shell or meat, fresh and frozen, wild.</t>
+          <t>Frozen Abalone Whole Clean, Vacuum Packed (160g). Specializes in premium frozen seafood for Chinese and Asian fine dining culture.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>As an affiliate of Seacore Seafood, they also deal with abalone and represent another distribution channel within the same major group.</t>
+          <t>Directly sells frozen abalone to consumers, indicating an active market and direct import/distribution channels.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.seafooddepot.ca/abalone</t>
+          <t>https://oceantaste.ca/products/frozen-abalone-whole-clean-160g</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Email not directly published on the website. Phone numbers are 905-856-2770 and toll-free 1-855-563-2770.</t>
+          <t>Email not directly published; a contact form is available on their website.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd</t>
+          <t>Seacore Seafood Inc.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1771,76 +1759,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>marketing@vegfoodgroup.com</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>http://www.vegfoodgroup.com</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>+86-17706396685 (WhatsApp)</t>
-        </is>
-      </c>
+          <t>https://www.seacoreseafood.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Professional supplier of frozen, fresh, dehydrated vegetables, fruit and mushroom. Also lists 'Seafood' including 'canned abalone' among its products. Engages in import and export.</t>
+          <t>Wholesaler, importer, exporter, foodservice, retail, traders, and distributors of IQF Frozen Abalone Products.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Vaughan</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>No.79 Jinzhong Road, Licang District, Qingdao City, China</t>
+          <t>81 Aviva Park Drive Vaughan, ON Canada L4L 9C1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>One import and export company, five own factories and more than 15 factories in China through mutual shareholding, joint ventures. Diverse product range beyond abalone.</t>
+          <t>Abalone (Haliotis kamtschatkana), available in shell or meat, fresh and frozen, wild.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>An import and export company explicitly dealing with 'canned abalone' as part of their seafood offerings, indicating direct involvement in abalone distribution within China.</t>
+          <t>A large, established wholesaler and importer with explicit mention of handling fresh and frozen abalone.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>http://www.vegfoodgroup.com/contact-us.html</t>
+          <t>https://www.seacoreseafood.com/abalone</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>The company lists 'canned abalone' as a product, confirming their involvement with abalone.</t>
+          <t>Email not directly published on the website. Phone numbers are 905-856-6222 and toll-free 1-800-563-6222.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UlifeFoods</t>
+          <t>Seafood Depot</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1848,55 +1828,51 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>info@ulifefoods.com</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.ulifefoods.com</t>
+          <t>https://www.seafooddepot.ca</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>IQF Abalone wholesale supplier, frozen seafood, raw abalone, cooked abalone, canned abalone, dried abalone. Specializing in research, production, and sales of frozen processed foods.</t>
+          <t>Wholesaler of fresh and frozen seafood, including abalone. Part of the Seacore Seafood Inc. group.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Vaughan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>No. 10 Xiamei Road, Meixin Village, Meihua Town, Changle District, Fuzhou City, Fujian Province, China</t>
+          <t>81 Aviva Park Drive Vaughan, ON Canada L4L 9C1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Over 30 years in the industry, own breeding base and factory, HACCP, BRC, ISO, ASC, FSPCA certified. Exports to USA, Canada, South Korea, Japan, Southeast Asia. Annual production capacity of 15,000 tons of quick-frozen prepared food.</t>
+          <t>Abalone (Haliotis kamtschatkana), available in shell or meat, fresh and frozen, wild.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Direct wholesale supplier with extensive product range (raw, cooked, canned, dried abalone) and international export experience. Certifications indicate high quality and safety standards.</t>
+          <t>As an affiliate of Seacore Seafood, they also deal with abalone and represent another distribution channel within the same major group.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.ulifefoods.com/about-us.html</t>
+          <t>https://www.seafooddepot.ca/abalone</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>They are a manufacturer and wholesale supplier, implying distribution and import capabilities for their own products, and potentially for others given their 'wholesale supplier' designation.</t>
+          <t>Email not directly published on the website. Phone numbers are 905-856-2770 and toll-free 1-855-563-2770.</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1889,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xiamen Binqi Import &amp; Export Co., Ltd</t>
+          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1923,19 +1899,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tom@binqi-china.com</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>marketing@vegfoodgroup.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>http://www.vegfoodgroup.com</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>+86-17706396685 (WhatsApp)</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Aquaculture producers, processors, importers and exporters of abalones (our own farm) and shrimps, crabs, squids, octopus, mackerel fish, hairtail, bamboo leaf fish, sardine and other frozen aquatic products. Also acts as an importer and distributor for various seafood products.</t>
+          <t>Professional supplier of frozen, fresh, dehydrated vegetables, fruit and mushroom. Also lists 'Seafood' including 'canned abalone' among its products. Engages in import and export.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Xiamen</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1945,44 +1929,44 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Xiamen, Fujian, China</t>
+          <t>No.79 Jinzhong Road, Licang District, Qingdao City, China</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Professional import and export company with strong capital strength, owned production factory (Zhangzhou Minzheng Food Co.,Ltd), 20 years farming and marketing experience. Strictly carries out 'Export food production regulations' and 'PRC food security law'.</t>
+          <t>One import and export company, five own factories and more than 15 factories in China through mutual shareholding, joint ventures. Diverse product range beyond abalone.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Explicitly states 'importers of abalones' and 'Importer, Distributor'. Their integrated approach from farming to import/export makes them a comprehensive partner.</t>
+          <t>An import and export company explicitly dealing with 'canned abalone' as part of their seafood offerings, indicating direct involvement in abalone distribution within China.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.sea-ex.com/seafood-companies/china/xiamen-binqi-import-export-co-ltd.htm</t>
+          <t>http://www.vegfoodgroup.com/contact-us.html</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Email found on Sea-Ex directory. Website not explicitly found in search results, but 'binqi-china.com' is part of the email domain.</t>
+          <t>The company lists 'canned abalone' as a product, confirming their involvement with abalone.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bin Auf</t>
+          <t>UlifeFoods</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1990,56 +1974,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>info@ulifefoods.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.ulifefoods.com</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>인도네시아 수출업체, 수입업체, 해산물 무역업체. 제품에는 말린 해삼, 전복, 전갱이, 산호 송어, 말린 오징어, 황다랑어 등이 포함됩니다. 소량/대량 공급 가능.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>IQF Abalone wholesale supplier, frozen seafood, raw abalone, cooked abalone, canned abalone, dried abalone. Specializing in research, production, and sales of frozen processed foods.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Fuzhou</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>No. 10 Xiamei Road, Meixin Village, Meihua Town, Changle District, Fuzhou City, Fujian Province, China</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 해산물 거래, 소량/대량 공급 가능.</t>
+          <t>Over 30 years in the industry, own breeding base and factory, HACCP, BRC, ISO, ASC, FSPCA certified. Exports to USA, Canada, South Korea, Japan, Southeast Asia. Annual production capacity of 15,000 tons of quick-frozen prepared food.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>명시적으로 '수입업체' 역할을 명시, 다양한 제품 범위, 유연한 공급량.</t>
+          <t>Direct wholesale supplier with extensive product range (raw, cooked, canned, dried abalone) and international export experience. Certifications indicate high quality and safety standards.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/seafood-indonesia.htm</t>
+          <t>https://www.ulifefoods.com/about-us.html</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>스니펫에서 직접적인 웹사이트나 이메일을 찾을 수 없지만, 회사는 수입업체로 등재되어 있습니다.</t>
+          <t>They are a manufacturer and wholesale supplier, implying distribution and import capabilities for their own products, and potentially for others given their 'wholesale supplier' designation.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CV Langgeng Sentosa Trade Indo</t>
+          <t>Xiamen Binqi Import &amp; Export Co., Ltd</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2047,47 +2047,51 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tom@binqi-china.com</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>인도네시아 동부 자바의 냉동 해산물 수출업체, 조달업체 및 가공업체. 주요 생산품은 롤리고 오징어, 전복 고기, 문어, 갑오징어, 저서어류입니다. 냉동 삶은 전복 고기 'mata 7' 재고 보유.</t>
+          <t>Aquaculture producers, processors, importers and exporters of abalones (our own farm) and shrimps, crabs, squids, octopus, mackerel fish, hairtail, bamboo leaf fish, sardine and other frozen aquatic products. Also acts as an importer and distributor for various seafood products.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>East Java</t>
+          <t>Xiamen</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>East Java - Indonesia.</t>
+          <t>Xiamen, Fujian, China</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>냉동 삶은 전복 고기, 즉시 선적 가능.</t>
+          <t>Professional import and export company with strong capital strength, owned production factory (Zhangzhou Minzheng Food Co.,Ltd), 20 years farming and marketing experience. Strictly carries out 'Export food production regulations' and 'PRC food security law'.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>전복 고기의 직접 조달 및 가공업체, 즉시 선적 가능한 재고 보유. 주로 수출업체이지만, 조달 및 가공 역할은 국내에서 제품을 취급하며 수입을 위한 연락처가 될 수 있음을 시사합니다.</t>
+          <t>Explicitly states 'importers of abalones' and 'Importer, Distributor'. Their integrated approach from farming to import/export makes them a comprehensive partner.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.go4worldbusiness.com/find/products/frozen-abalone/indonesia.html</t>
+          <t>https://www.sea-ex.com/seafood-companies/china/xiamen-binqi-import-export-co-ltd.htm</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>연락 담당자 Tonny Santoso가 언급되었습니다. 스니펫에서 직접적인 이메일이나 웹사이트를 찾을 수 없습니다.</t>
+          <t>Email found on Sea-Ex directory. Website not explicitly found in search results, but 'binqi-china.com' is part of the email domain.</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2108,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PT CITA KARYA AGUNG</t>
+          <t>Bin Auf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2113,67 +2117,55 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://variouseafood.com/</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>인도네시아의 선도적인 신선 및 냉동 해산물 가공업체, 공급업체 및 수출업체. 전복과 같은 냉동 복족류를 포함하여 35가지 이상의 다양한 제품을 제공합니다. 어부 및 양식 전문가로부터 조달.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Belawan</t>
-        </is>
-      </c>
+          <t>인도네시아 수출업체, 수입업체, 해산물 무역업체. 제품에는 말린 해삼, 전복, 전갱이, 산호 송어, 말린 오징어, 황다랑어 등이 포함됩니다. 소량/대량 공급 가능.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Belawan, Indonesia.</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>달팽이 및 전복과 같은 프리미엄 냉동 복족류, 최적의 신선도를 유지하기 위해 신중하게 가공. GMP 표준 및 HACCP 인증.</t>
+          <t>전복을 포함한 다양한 해산물 거래, 소량/대량 공급 가능.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>확고한 가공업체 및 공급업체, 지속 가능성 및 품질에 대한 약속, 광범위한 제품. 주로 수출업체이지만, 조달 및 가공 활동은 인도네시아 내 전복 공급망에서 관련 플레이어임을 나타냅니다.</t>
+          <t>명시적으로 '수입업체' 역할을 명시, 다양한 제품 범위, 유연한 공급량.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://variouseafood.com/</t>
+          <t>https://www.trade-seafood.com/seafood-indonesia.htm</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>스니펫에서 직접적인 이메일을 찾을 수 없습니다.</t>
+          <t>스니펫에서 직접적인 웹사이트나 이메일을 찾을 수 없지만, 회사는 수입업체로 등재되어 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pesca K &amp; M Co., Ltd.</t>
+          <t>CV Langgeng Sentosa Trade Indo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2181,76 +2173,64 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>pescauno@nifty.com</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>표2 (HS 160557)</t>
+          <t>인도네시아 동부 자바의 냉동 해산물 수출업체, 조달업체 및 가공업체. 주요 생산품은 롤리고 오징어, 전복 고기, 문어, 갑오징어, 저서어류입니다. 냉동 삶은 전복 고기 'mata 7' 재고 보유.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>East Java</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
+          <t>East Java - Indonesia.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
+          <t>냉동 삶은 전복 고기, 즉시 선적 가능.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
+          <t>전복 고기의 직접 조달 및 가공업체, 즉시 선적 가능한 재고 보유. 주로 수출업체이지만, 조달 및 가공 역할은 국내에서 제품을 취급하며 수입을 위한 연락처가 될 수 있음을 시사합니다.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+          <t>https://www.go4worldbusiness.com/find/products/frozen-abalone/indonesia.html</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
+          <t>연락 담당자 Tonny Santoso가 언급되었습니다. 스니펫에서 직접적인 이메일이나 웹사이트를 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>True World Japan Inc.</t>
+          <t>PT CITA KARYA AGUNG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2261,52 +2241,48 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
-        </is>
-      </c>
+          <t>https://variouseafood.com/</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>인도네시아의 선도적인 신선 및 냉동 해산물 가공업체, 공급업체 및 수출업체. 전복과 같은 냉동 복족류를 포함하여 35가지 이상의 다양한 제품을 제공합니다. 어부 및 양식 전문가로부터 조달.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Belawan</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
+          <t>Belawan, Indonesia.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
+          <t>달팽이 및 전복과 같은 프리미엄 냉동 복족류, 최적의 신선도를 유지하기 위해 신중하게 가공. GMP 표준 및 HACCP 인증.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
+          <t>확고한 가공업체 및 공급업체, 지속 가능성 및 품질에 대한 약속, 광범위한 제품. 주로 수출업체이지만, 조달 및 가공 활동은 인도네시아 내 전복 공급망에서 관련 플레이어임을 나타냅니다.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+          <t>https://variouseafood.com/</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
+          <t>스니펫에서 직접적인 이메일을 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2299,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tsukuino Co. Ltd.</t>
+          <t>Pesca K &amp; M Co., Ltd.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2333,18 +2309,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tukuino@heart.ocn.ne.jp</t>
+          <t>pescauno@nifty.com</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.tsukuino.com/english.html</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>표2 (HS 160557)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2359,44 +2339,44 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
+          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
+          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
+          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.tsukuino.com/english.html</t>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
+          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-07-31 14:58:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Harmony Marine Products Sdn. Bhd.</t>
+          <t>True World Japan Inc.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2407,61 +2387,69 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.harmonymarine.com.my/</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>전복, 해삼, 어류 부레를 포함한 프리미엄 해산물 진미 공급업체. 아시아 태평양, 남미 및 아프리카에서 제품 및 재료를 조달합니다.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>표1 (HS 030781)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>본사는 현대적인 시설(전용 건조실, 3,000평방피트 냉동고, 5,000평방피트 보관 공간)을 갖추고 있으며 HACCP 인증을 받았습니다.</t>
+          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>프리미엄 전복, 엄격한 품질 관리, 지속 가능한 조달, 30년 이상의 경험.</t>
+          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>광범위한 경험을 가진 확고한 공급업체, 국제적으로 조달, HACCP 인증.</t>
+          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.harmonymarine.com.my/abalone-supplier-malaysia</t>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>주로 공급업체이지만, 다양한 지역에서 조달하는 것은 수입 활동을 의미합니다.</t>
+          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-07-31 14:58:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
+          <t>Tsukuino Co. Ltd.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2469,51 +2457,55 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tukuino@heart.ocn.ne.jp</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://oceanpacificonline.com/</t>
+          <t>https://www.tsukuino.com/english.html</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 해산물 및 냉동 식품을 도매 및 공급합니다.</t>
+          <t>표1 (HS 030781)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Johor Bahru</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia.</t>
+          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>전복, 조개, 게, 생선, 고기, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 공급합니다. 해산물 및 냉동 식품의 선두 공급업체입니다.</t>
+          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>다양한 국내 브랜드, 지속적인 트렌드 분석, 최고의 서비스와 제품 제공에 전념.</t>
+          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://oceanpacificonline.com/abalone</t>
+          <t>https://www.tsukuino.com/english.html</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>웹사이트에 전화번호가 있습니다.</t>
+          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2522,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>V Top Frozen Food Sdn Bhd</t>
+          <t>Harmony Marine Products Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2538,27 +2530,19 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Vtopff@gmail.com</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://vtopfrozenfood.com/</t>
+          <t>https://www.harmonymarine.com.my/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Kuala Lumpur</t>
-        </is>
-      </c>
+          <t>전복, 해삼, 어류 부레를 포함한 프리미엄 해산물 진미 공급업체. 아시아 태평양, 남미 및 아프리카에서 제품 및 재료를 조달합니다.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Malaysia</t>
@@ -2566,27 +2550,27 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
+          <t>본사는 현대적인 시설(전용 건조실, 3,000평방피트 냉동고, 5,000평방피트 보관 공간)을 갖추고 있으며 HACCP 인증을 받았습니다.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
+          <t>프리미엄 전복, 엄격한 품질 관리, 지속 가능한 조달, 30년 이상의 경험.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
+          <t>광범위한 경험을 가진 확고한 공급업체, 국제적으로 조달, HACCP 인증.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://vtopfrozenfood.com/abalone-slices</t>
+          <t>https://www.harmonymarine.com.my/abalone-supplier-malaysia</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>웹사이트에 전화번호가 있습니다.</t>
+          <t>주로 공급업체이지만, 다양한 지역에서 조달하는 것은 수입 활동을 의미합니다.</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2582,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goh Joo Hin Pte Ltd</t>
+          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2611,55 +2595,51 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>food@gjh.com.sg</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>http://www.gjh.com.sg</t>
+          <t>https://oceanpacificonline.com/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Wholesaler, Distributor</t>
+          <t>전복을 포함한 다양한 해산물 및 냉동 식품을 도매 및 공급합니다.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
+          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
+          <t>전복, 조개, 게, 생선, 고기, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 공급합니다. 해산물 및 냉동 식품의 선두 공급업체입니다.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
+          <t>다양한 국내 브랜드, 지속적인 트렌드 분석, 최고의 서비스와 제품 제공에 전념.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
+          <t>https://oceanpacificonline.com/abalone</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
+          <t>웹사이트에 전화번호가 있습니다.</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2651,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oceanus Group Limited</t>
+          <t>V Top Frozen Food Sdn Bhd</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2686,70 +2666,70 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>contact@oceanus.com.sg</t>
+          <t>Vtopff@gmail.com</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>http://www.oceanus.com.sg</t>
+          <t>https://vtopfrozenfood.com/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
+          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
+          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
+          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
+          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
+          <t>https://vtopfrozenfood.com/abalone-slices</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
+          <t>웹사이트에 전화번호가 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teck Sang Pte Ltd</t>
+          <t>Kiwi Fish</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2757,72 +2737,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>local@tecksang.com</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.tecksang.com</t>
+          <t>https://kiwifish.co.nz</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
+          <t>Premium seafood wholesaler, supplying an extensive range of live, chilled, and frozen shellfish, including pāua (abalone), to various markets including superyachts.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11 Hongkong Street, Singapore 059654</t>
+          <t>Central Auckland</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
+          <t>Offers the best of New Zealand's sustainably caught seafood harvest, custom processed and delivered. Operates a Risk Management Programme (RMP) approved and audited by the Ministry for Primary Industries (MPI).</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
+          <t>Established premium seafood wholesaler with a wide range of products and strong quality control, suggesting capability for distributing abalone within New Zealand.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQET8rm6pD2fyT7blQHzUlDu1ArhqNzw8L5XOkDHPt6BbyoKTCVauxe6Oxsjy7ctVUvrR8vDBXtaw4VbGut7tDCnC3Pj4-1Xvaq0HCMnqW3hIuF82K8ePbg==</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
+          <t>Distributes New Zealand-sourced abalone (pāua).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
+          <t>Northern Waters Marine Limited</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2832,70 +2808,74 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>info@ruifuoilfood.com</t>
+          <t>hello@northernwaters.co.nz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://ruifuoilfood.com/</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>https://northernwaters.co.nz</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Facebook, TikTok, Instagram</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
+          <t>Sells whole pāua (abalone) for wholesale and retail.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Si Maha Phot, Prachin Buri</t>
+          <t>Warkworth</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
+          <t>182 State Highway 1, Warkworth 0981, New Zealand (AUK Dome Valley)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
+          <t>Sustainably harvested whole pāua (abalone) from the waters of Wairarapa and the South Island, offering authentic New Zealand flavor. Available for pickup or delivery.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
+          <t>Direct supplier and wholesaler of whole abalone, with clear contact information and a focus on sustainably harvested local product for the New Zealand market.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUTHdE_OizUFY_wnDheiVjs5gz8f6C2bi2M-kQnU8AHGUWDyfJfhJEeNJt5ZarxJzqydgApFymnTwOlFD3rW2VhMd-tPSVGo3JAsYEGcp40Nc3oTgS5tR5neHphsqorpRO59dq267d84rNGLqV6wH6d8HO7QE==</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
+          <t>Distributes New Zealand-sourced abalone (pāua).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thai Abalone Co.,Ltd.</t>
+          <t>Sunz Seafood</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2906,65 +2886,65 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://m.ec21.com/company/thaiabalone/</t>
+          <t>https://sunzseafood.co.nz</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
+          <t>Wholesale and foodservice distribution of New Zealand minced pāua (abalone).</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Pathiu, Chumphon</t>
+          <t>Whitianga</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
+          <t>269 South Highway West Whitianga 3510</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
+          <t>Premium New Zealand minced pāua (abalone), wild-caught and hand-harvested from Wairarapa and South Island, processed to export standards and frozen fresh. Offers meat-only pāua, ideal for patties, fritters, and commercial kitchen use.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
+          <t>Established wholesaler and foodservice supplier of abalone meat within New Zealand, indicating a strong distribution network for locally sourced product.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://m.ec21.com/company/thaiabalone/</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6XLTPVgpag7xKK9QzbM_253BrUulevcWOCSV-khxpvqieFX7K7bO3HslNSPhfSIJySeYWXSDhgResGgoCJy1BNk6USQXQpWs7QU9S16CwXnw3H-JmFBse6B2Q6YReNBZXV8pjWQbq-KKVPcA-Zat9UCHvP7N6mtg50x-AO6e4Da1VnfLE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
+          <t>Primarily distributes New Zealand-sourced abalone (pāua).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monterey Abalone Company</t>
+          <t>Goh Joo Hin Pte Ltd</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2972,68 +2952,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>food@gjh.com.sg</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://montereyabalone.com</t>
+          <t>http://www.gjh.com.sg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
+          <t>Importer, Exporter, Wholesaler, Distributor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Monterey</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
+          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
+          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
+          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Email not found in provided snippets.</t>
+          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ocean Floor Inc.</t>
+          <t>Oceanus Group Limited</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3041,56 +3025,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>contact@oceanus.com.sg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>http://www.oceanus.com.sg</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
+          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
+          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>City, email, and website not found in provided snippets.</t>
+          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seafarers Inc.</t>
+          <t>Teck Sang Pte Ltd</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3098,56 +3098,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>local@tecksang.com</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.tecksang.com</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>11 Hongkong Street, Singapore 059654</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
+          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
+          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>City, email, and website not found in provided snippets.</t>
+          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FGC JOINT STOCK COMPANY</t>
+          <t>Fresh Harvest (Pvt) Ltd</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3155,55 +3171,43 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>fgc.seafoods@gmail.com</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.fgc-foods.com/</t>
+          <t>https://freshharvest.lk/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>전복(살아있는, 열처리 및 냉동)을 포함한 고품질의 안전한 수입 식품을 제조 및 공급합니다.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Hanoi</t>
-        </is>
-      </c>
+          <t>Seafood Importer and Distributor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi.</t>
-        </is>
-      </c>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>수입 전복(살아있는, 열처리 및 냉동), 1kg/봉지, 10kg/상자, -18°C 보관, 24개월 유통기한.</t>
+          <t>Leading seafood company in Sri Lanka, delivers high quality ready-to-cook seafood products. Caters to local market, supplies to top-class hotel chains, leading restaurants, and expanding in local retail market. Acts as an importer of high quality seafood.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>수입 전복 공급업체, 품질 및 안전에 중점, 다양한 맛과 스타일.</t>
+          <t>스리랑카 현지 시장에 고품질 해산물을 수입하여 호텔, 레스토랑 및 소매점에 공급하는 선도적인 회사입니다. 전복 수입 및 유통에 대한 협력 가능성이 높습니다.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://www.fgc-foods.com/san-pham/thuc-pham-chat-luong-cho-kenh-nha-hang-va-ban-le/bao-ngu-nhap-khau</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcQYNWYOJvFZ5465KMss_BHieKPxvrhT-oNHOi2KKwePbAueaXewTLSRdFvyC53bKsJB9SxBoH5hsVkTNWMHCaabHTVCeR0iPYsraHevFcJpFSX0n9</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>전화 및 Zalo 핫라인도 이용 가능합니다.</t>
+          <t>이메일/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다.</t>
         </is>
       </c>
     </row>
@@ -3215,12 +3219,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fishy Vietnam Co., Ltd</t>
+          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3230,53 +3234,53 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fishy.vn@gmail.com</t>
+          <t>info@ruifuoilfood.com</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://fishy.vn/</t>
+          <t>https://ruifuoilfood.com/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>베트남에서 전복(냉동 전복(Loco) 고기, 냉동 호주산 그린립 전복 포함)을 포함한 최고급 해산물을 수입 및 유통합니다.</t>
+          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Si Maha Phot, Prachin Buri</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City.</t>
+          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>최고급 해산물 수입 및 유통 전문, 헌신과 명성, 고객 만족 중시, 고품질 제품, 최고의 서비스.</t>
+          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>프리미엄 해산물 수입 및 유통 선두 기업, 다양한 전복 제품, 품질 및 고객 서비스에 중점.</t>
+          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://fishy.vn/san-pham/bao-ngu</t>
+          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>세금 ID 및 핫라인도 이용 가능합니다.</t>
+          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
         </is>
       </c>
     </row>
@@ -3288,12 +3292,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trọng Đức Seafood</t>
+          <t>Thai Abalone Co.,Ltd.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3304,38 +3308,436 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://trongduc.vn/</t>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
+          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pathiu, Chumphon</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Monterey Abalone Company</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://montereyabalone.com</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Monterey</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Email not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ocean Floor Inc.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>City, email, and website not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Seafarers Inc.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>City, email, and website not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FGC JOINT STOCK COMPANY</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>fgc.seafoods@gmail.com</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.fgc-foods.com/</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>전복(살아있는, 열처리 및 냉동)을 포함한 고품질의 안전한 수입 식품을 제조 및 공급합니다.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>수입 전복(살아있는, 열처리 및 냉동), 1kg/봉지, 10kg/상자, -18°C 보관, 24개월 유통기한.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>수입 전복 공급업체, 품질 및 안전에 중점, 다양한 맛과 스타일.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://www.fgc-foods.com/san-pham/thuc-pham-chat-luong-cho-kenh-nha-hang-va-ban-le/bao-ngu-nhap-khau</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>전화 및 Zalo 핫라인도 이용 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fishy Vietnam Co., Ltd</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Fishy.vn@gmail.com</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>베트남에서 전복(냉동 전복(Loco) 고기, 냉동 호주산 그린립 전복 포함)을 포함한 최고급 해산물을 수입 및 유통합니다.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>최고급 해산물 수입 및 유통 전문, 헌신과 명성, 고객 만족 중시, 고품질 제품, 최고의 서비스.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>프리미엄 해산물 수입 및 유통 선두 기업, 다양한 전복 제품, 품질 및 고객 서비스에 중점.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/san-pham/bao-ngu</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>세금 ID 및 핫라인도 이용 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Trọng Đức Seafood</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://trongduc.vn/</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>한국, 일본 및 인근 국가에서 전복을 수입하여 도매업체, 에이전트 및 유통업체에 공급합니다.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>수입 전복 (한국, 일본 및 인근 국가산), 다양한 크기, 도매업체/에이전트/유통업체에 좋은 가격, 품질 명성, 완전한 문서 및 바코드.</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>직접 수입업체이며, 도매업체/에이전트/유통업체에 좋은 가격을 제공하고, 품질 및 문서화에 중점을 둡니다.</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://trongduc.vn/san-pham/bao-ngu-nhap-khau/</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>이메일/전화번호는 스니펫에 명시되어 있지 않지만 웹사이트가 제공됩니다.</t>
         </is>

--- a/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
+++ b/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
@@ -786,15 +786,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>🔍 조사 완료 (2개사 발견)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Atlantis Foods, Greenfish</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -823,15 +831,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Fishy Vietnam Co., Ltd., Sai Thanh Foods 외 1개사</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -905,15 +921,23 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FoodPhil Corporation, Pancoastal International 외 1개사</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -942,15 +966,23 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Comercial Oceano, Fish and Fishes SPA 외 1개사</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1024,15 +1056,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>㈜제이에스코리아, ㈜청산바다 외 1개사</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1061,15 +1101,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bajamar Trading Group, GlobalPezk 외 1개사</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1098,15 +1146,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>🔍 조사 완료 (2개사 발견)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Adri &amp; Zoon Schaal- en Schelpdierenhandel B.V., Starco Foodstuff</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1180,15 +1236,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>FRESHCADO RECIEN PESCADO SL, Globalimar Europa, SL 외 1개사</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1254,15 +1318,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Abalone Fish Processing LLC, Dior Fresh Fish 외 1개사</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1336,15 +1408,23 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>🔍 조사 완료 (1개사 발견)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Dakar Ice</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1373,15 +1453,23 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>🆕 신규 후보 (미착수)</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>🔍 조사 완료 (3개사 발견)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Direct Seafoods, Fine Food Specialist 외 1개사</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>상세 내역은 'Verified_Partners' 시트 참고</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1394,7 +1482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1879,17 +1967,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd</t>
+          <t>Comercial Oceano</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1899,74 +1987,70 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>marketing@vegfoodgroup.com</t>
+          <t>ventas@comercialoceano.cl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>http://www.vegfoodgroup.com</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>+86-17706396685 (WhatsApp)</t>
-        </is>
-      </c>
+          <t>https://www.comercialoceano.cl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Professional supplier of frozen, fresh, dehydrated vegetables, fruit and mushroom. Also lists 'Seafood' including 'canned abalone' among its products. Engages in import and export.</t>
+          <t>Importation, commercialization, and distribution of shrimp from Ecuador, fish, and seafood in Chile.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>No.79 Jinzhong Road, Licang District, Qingdao City, China</t>
+          <t>Fresia 1240, Peñalolén, Santiago.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>One import and export company, five own factories and more than 15 factories in China through mutual shareholding, joint ventures. Diverse product range beyond abalone.</t>
+          <t>Specializes in shrimp, fish, and general seafood. They have over 20 years of experience in the business.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>An import and export company explicitly dealing with 'canned abalone' as part of their seafood offerings, indicating direct involvement in abalone distribution within China.</t>
+          <t>Explicitly states their role in the 'Importación, Comercialización y distribución' of 'Pescados y Mariscos' (Fish and Seafood) in Chile, which would include abalone.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>http://www.vegfoodgroup.com/contact-us.html</t>
+          <t>https://www.comercialoceano.cl/contacto</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>The company lists 'canned abalone' as a product, confirming their involvement with abalone.</t>
+          <t>Abalone is not explicitly listed on their contact page, but it falls under their general 'Mariscos' (seafood) category.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UlifeFoods</t>
+          <t>Fish and Fishes SPA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1976,70 +2060,66 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>info@ulifefoods.com</t>
+          <t>comercial@fishandfishes.cl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.ulifefoods.com</t>
+          <t>https://www.fishandfishes.cl</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>IQF Abalone wholesale supplier, frozen seafood, raw abalone, cooked abalone, canned abalone, dried abalone. Specializing in research, production, and sales of frozen processed foods.</t>
+          <t>Online sale and distribution of seafood products, including abalone, to consumers and potentially smaller businesses in the Metropolitan Region of Chile.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>No. 10 Xiamei Road, Meixin Village, Meihua Town, Changle District, Fuzhou City, Fujian Province, China</t>
+          <t>Av. Manuel Montt 1740, Providencia, Región Metropolitana, Santiago.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Over 30 years in the industry, own breeding base and factory, HACCP, BRC, ISO, ASC, FSPCA certified. Exports to USA, Canada, South Korea, Japan, Southeast Asia. Annual production capacity of 15,000 tons of quick-frozen prepared food.</t>
+          <t>Offers 'Abulón Cocido 180 gr neto - Producto Premium Natural desde Chile' as part of their seafood product range, alongside other fish and seafood items.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Direct wholesale supplier with extensive product range (raw, cooked, canned, dried abalone) and international export experience. Certifications indicate high quality and safety standards.</t>
+          <t>Directly sells and distributes abalone products within Chile, acting as a retailer/distributor for the local market.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.ulifefoods.com/about-us.html</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>They are a manufacturer and wholesale supplier, implying distribution and import capabilities for their own products, and potentially for others given their 'wholesale supplier' designation.</t>
-        </is>
-      </c>
+          <t>https://www.fishandfishes.cl/products/abalon-180-gr</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xiamen Binqi Import &amp; Export Co., Ltd</t>
+          <t>Seagarden</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2049,66 +2129,70 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tom@binqi-china.com</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>info@seagarden.cl</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.seagarden.cl</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Aquaculture producers, processors, importers and exporters of abalones (our own farm) and shrimps, crabs, squids, octopus, mackerel fish, hairtail, bamboo leaf fish, sardine and other frozen aquatic products. Also acts as an importer and distributor for various seafood products.</t>
+          <t>Import and supply of seafood products in Chile for various channels including Distributor, Retail, Food Service, Institutional, Industrial, and Export. They import from various global origins, including Chile.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Xiamen</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Xiamen, Fujian, China</t>
+          <t>Los Maitenes poniente #1332, Pudahuel – Santiago. Also has offices in Concepción, Temuco, and Puerto Varas.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Professional import and export company with strong capital strength, owned production factory (Zhangzhou Minzheng Food Co.,Ltd), 20 years farming and marketing experience. Strictly carries out 'Export food production regulations' and 'PRC food security law'.</t>
+          <t>Largest importer and supplier of seafood products in Chile, offering over 600 products across six categories, including 'Locos' (Chilean Abalone) under their 'MARISCOS' category. They process and export various seafood products.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Explicitly states 'importers of abalones' and 'Importer, Distributor'. Their integrated approach from farming to import/export makes them a comprehensive partner.</t>
+          <t>Explicitly states being the largest importer and supplier of seafood in Chile and lists 'Locos' (Chilean Abalone) among their products, indicating a clear role in abalone distribution within the country.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.sea-ex.com/seafood-companies/china/xiamen-binqi-import-export-co-ltd.htm</t>
+          <t>https://www.seagarden.cl/contacto</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Email found on Sea-Ex directory. Website not explicitly found in search results, but 'binqi-china.com' is part of the email domain.</t>
+          <t>Email provided is for their Santiago office. They have multiple branches across Chile.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bin Auf</t>
+          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2116,56 +2200,76 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>marketing@vegfoodgroup.com</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>http://www.vegfoodgroup.com</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>+86-17706396685 (WhatsApp)</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>인도네시아 수출업체, 수입업체, 해산물 무역업체. 제품에는 말린 해삼, 전복, 전갱이, 산호 송어, 말린 오징어, 황다랑어 등이 포함됩니다. 소량/대량 공급 가능.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Professional supplier of frozen, fresh, dehydrated vegetables, fruit and mushroom. Also lists 'Seafood' including 'canned abalone' among its products. Engages in import and export.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Qingdao</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No.79 Jinzhong Road, Licang District, Qingdao City, China</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 해산물 거래, 소량/대량 공급 가능.</t>
+          <t>One import and export company, five own factories and more than 15 factories in China through mutual shareholding, joint ventures. Diverse product range beyond abalone.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>명시적으로 '수입업체' 역할을 명시, 다양한 제품 범위, 유연한 공급량.</t>
+          <t>An import and export company explicitly dealing with 'canned abalone' as part of their seafood offerings, indicating direct involvement in abalone distribution within China.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/seafood-indonesia.htm</t>
+          <t>http://www.vegfoodgroup.com/contact-us.html</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>스니펫에서 직접적인 웹사이트나 이메일을 찾을 수 없지만, 회사는 수입업체로 등재되어 있습니다.</t>
+          <t>The company lists 'canned abalone' as a product, confirming their involvement with abalone.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CV Langgeng Sentosa Trade Indo</t>
+          <t>UlifeFoods</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2173,64 +2277,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>info@ulifefoods.com</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.ulifefoods.com</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>인도네시아 동부 자바의 냉동 해산물 수출업체, 조달업체 및 가공업체. 주요 생산품은 롤리고 오징어, 전복 고기, 문어, 갑오징어, 저서어류입니다. 냉동 삶은 전복 고기 'mata 7' 재고 보유.</t>
+          <t>IQF Abalone wholesale supplier, frozen seafood, raw abalone, cooked abalone, canned abalone, dried abalone. Specializing in research, production, and sales of frozen processed foods.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>East Java</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>East Java - Indonesia.</t>
+          <t>No. 10 Xiamei Road, Meixin Village, Meihua Town, Changle District, Fuzhou City, Fujian Province, China</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>냉동 삶은 전복 고기, 즉시 선적 가능.</t>
+          <t>Over 30 years in the industry, own breeding base and factory, HACCP, BRC, ISO, ASC, FSPCA certified. Exports to USA, Canada, South Korea, Japan, Southeast Asia. Annual production capacity of 15,000 tons of quick-frozen prepared food.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>전복 고기의 직접 조달 및 가공업체, 즉시 선적 가능한 재고 보유. 주로 수출업체이지만, 조달 및 가공 역할은 국내에서 제품을 취급하며 수입을 위한 연락처가 될 수 있음을 시사합니다.</t>
+          <t>Direct wholesale supplier with extensive product range (raw, cooked, canned, dried abalone) and international export experience. Certifications indicate high quality and safety standards.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.go4worldbusiness.com/find/products/frozen-abalone/indonesia.html</t>
+          <t>https://www.ulifefoods.com/about-us.html</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>연락 담당자 Tonny Santoso가 언급되었습니다. 스니펫에서 직접적인 이메일이나 웹사이트를 찾을 수 없습니다.</t>
+          <t>They are a manufacturer and wholesale supplier, implying distribution and import capabilities for their own products, and potentially for others given their 'wholesale supplier' designation.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PT CITA KARYA AGUNG</t>
+          <t>Xiamen Binqi Import &amp; Export Co., Ltd</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2238,68 +2350,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://variouseafood.com/</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tom@binqi-china.com</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>인도네시아의 선도적인 신선 및 냉동 해산물 가공업체, 공급업체 및 수출업체. 전복과 같은 냉동 복족류를 포함하여 35가지 이상의 다양한 제품을 제공합니다. 어부 및 양식 전문가로부터 조달.</t>
+          <t>Aquaculture producers, processors, importers and exporters of abalones (our own farm) and shrimps, crabs, squids, octopus, mackerel fish, hairtail, bamboo leaf fish, sardine and other frozen aquatic products. Also acts as an importer and distributor for various seafood products.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Belawan</t>
+          <t>Xiamen</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Belawan, Indonesia.</t>
+          <t>Xiamen, Fujian, China</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>달팽이 및 전복과 같은 프리미엄 냉동 복족류, 최적의 신선도를 유지하기 위해 신중하게 가공. GMP 표준 및 HACCP 인증.</t>
+          <t>Professional import and export company with strong capital strength, owned production factory (Zhangzhou Minzheng Food Co.,Ltd), 20 years farming and marketing experience. Strictly carries out 'Export food production regulations' and 'PRC food security law'.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>확고한 가공업체 및 공급업체, 지속 가능성 및 품질에 대한 약속, 광범위한 제품. 주로 수출업체이지만, 조달 및 가공 활동은 인도네시아 내 전복 공급망에서 관련 플레이어임을 나타냅니다.</t>
+          <t>Explicitly states 'importers of abalones' and 'Importer, Distributor'. Their integrated approach from farming to import/export makes them a comprehensive partner.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://variouseafood.com/</t>
+          <t>https://www.sea-ex.com/seafood-companies/china/xiamen-binqi-import-export-co-ltd.htm</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>스니펫에서 직접적인 이메일을 찾을 수 없습니다.</t>
+          <t>Email found on Sea-Ex directory. Website not explicitly found in search results, but 'binqi-china.com' is part of the email domain.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pesca K &amp; M Co., Ltd.</t>
+          <t>Halbmond Company HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2307,76 +2419,60 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>pescauno@nifty.com</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
-        </is>
-      </c>
+          <t>https://www.halbmondco.com</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>표2 (HS 160557)</t>
+          <t>Wholesaler and importer of dried seafood, including dried abalone, dried sea cucumber, fish maws, shark fins. Actively looking for high-quality dried seafood products.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
-        </is>
-      </c>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
+          <t>Specializes in quality dry seafood products, purchases from Middle-East, Indian ocean and Africa, partners in 14 countries. Buys finest quality of dried Abalone in large volume.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
+          <t>Specialized in dried abalone, actively seeking new suppliers, and has an established global purchasing network for high-quality dried seafood.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
-        </is>
-      </c>
+          <t>https://www.halbmondco.com/abalone</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>True World Japan Inc.</t>
+          <t>I.FISH Company Limited</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2387,69 +2483,61 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
-        </is>
-      </c>
+          <t>https://www.ifish.com.hk</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>Leading seafood importer in Hong Kong. Supplies farm-raised and wild-caught abalone from South Africa. Provides a wide range of premium seafood products for Hong Kong hotels and restaurants.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Yau Tong</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
+          <t>Unit D, 8/F, Wah Shun Industrial Building 4 Cho Yuen Street; Yau Tong, Hong Kong</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
+          <t>Committed to sustainable practices, sources world's finest quality seafood, supplies to hotels and restaurants. Specializes in shellfish and prawns, including abalone.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
+          <t>Focus on premium quality and sustainable sourcing, strong network with hotels and restaurants in Hong Kong, and direct supply of abalone from South Africa.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
-        </is>
-      </c>
+          <t>https://www.ifish.com.hk/product/abalone</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tsukuino Co. Ltd.</t>
+          <t>Seabo International Limited</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2459,70 +2547,66 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tukuino@heart.ocn.ne.jp</t>
+          <t>enquiry@seabo.co</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.tsukuino.com/english.html</t>
+          <t>https://www.seabo.co</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>Leading Hong Kong-based company in the seafood industry, importer, wholesaler. Deals with frozen abalone, frozen molluscs, frozen fish, frozen pork.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Kwai Chung</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
+          <t>116-122 Kwok Shui Road, Kwai Chung, Hong Kong</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
+          <t>Over 40 years of international reputation, global seafood network (sources from over 30 countries), offers Seabo brand line products, reliable and timely delivery.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
+          <t>Established company with extensive sourcing and distribution capabilities in Hong Kong, specializing in frozen seafood including abalone.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.tsukuino.com/english.html</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
-        </is>
-      </c>
+          <t>https://www.seabo.co/contact-us</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Harmony Marine Products Sdn. Bhd.</t>
+          <t>Hai Sang Hong Marine Foodstuffs Limited</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2533,61 +2617,61 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.harmonymarine.com.my/</t>
+          <t>https://hshhongkong.com/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>전복, 해삼, 어류 부레를 포함한 프리미엄 해산물 진미 공급업체. 아시아 태평양, 남미 및 아프리카에서 제품 및 재료를 조달합니다.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Importer, Wholesaler, Retailer of seafood and frozen products</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>본사는 현대적인 시설(전용 건조실, 3,000평방피트 냉동고, 5,000평방피트 보관 공간)을 갖추고 있으며 HACCP 인증을 받았습니다.</t>
+          <t>Physical store in the heart of the seafood district</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>프리미엄 전복, 엄격한 품질 관리, 지속 가능한 조달, 30년 이상의 경험.</t>
+          <t>Offers a diverse selection of high-quality seafood and frozen products, including premium abalone, imported from various countries.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>광범위한 경험을 가진 확고한 공급업체, 국제적으로 조달, HACCP 인증.</t>
+          <t>A long-standing company (50 years) with a strong presence in the seafood industry, acting as an importer, wholesaler, and retailer of abalone.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.harmonymarine.com.my/abalone-supplier-malaysia</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>주로 공급업체이지만, 다양한 지역에서 조달하는 것은 수입 활동을 의미합니다.</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGh6uStIBzLzAsQPFttX2GJZLjvdVhH_j6rNKY276Ws2aWnpTeepN3EbgMK5BDoqO-GcGdJxey9ZeE9xX409tT0l8nU_OMwCKb9Vctc1_8aFZzyEGdax3nndXci66nbTGN3AdDft4iDqZWF9BH4B_whX8xfT1P2tvVG6SQ0hqAuR4bHumg_La8w==</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
+          <t>I.FISH Company Limited</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2598,65 +2682,65 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://oceanpacificonline.com/</t>
+          <t>https://ifish.com.hk/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 해산물 및 냉동 식품을 도매 및 공급합니다.</t>
+          <t>Seafood importer and supplier for hotels and restaurants</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Johor Bahru</t>
+          <t>Yau Tong</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia.</t>
+          <t>Unit D, 8/F, Wah Shun Industrial Building 4 Cho Yuen Street; Yau Tong, Hong Kong</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>전복, 조개, 게, 생선, 고기, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 공급합니다. 해산물 및 냉동 식품의 선두 공급업체입니다.</t>
+          <t>Supplies farm-raised and wild-caught abalone from South Africa, along with a wide range of premium seafood products.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>다양한 국내 브랜드, 지속적인 트렌드 분석, 최고의 서비스와 제품 제공에 전념.</t>
+          <t>Explicitly states they are a leading seafood importer in Hong Kong and supply abalone, targeting hotels and restaurants, suggesting a strong distribution network.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://oceanpacificonline.com/abalone</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGtI-nmTK4njbRY2vG7POki0OZpPdXFRWnkI3Gz1qUh0rFzIJvfNJn9ZnDvOA6OKvciXsN8kXgc9qvoRnPpUstOg1juycMC5z2OmBS4jBc-TLkNamM5L1yX46syAg==</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>웹사이트에 전화번호가 있습니다.</t>
+          <t>Tel: +852 2775-9118, Fax: +852 2775-1118 are available on the source page but not requested in the schema.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>V Top Frozen Food Sdn Bhd</t>
+          <t>Wing Tai Hong Marine Products Limited</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2664,72 +2748,60 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Vtopff@gmail.com</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://vtopfrozenfood.com/</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
+          <t>Importing, wholesaling, retailing and exporting of dried marine products</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
-        </is>
-      </c>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
+          <t>Dried marine products, including abalone and scallop.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
+          <t>A well-established company involved in importing and wholesaling dried abalone, indicating a direct channel for distribution.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://vtopfrozenfood.com/abalone-slices</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGJ1L2bIzrk2yA85itKs-Ijnva2yxVj9WV1_DK8czhqTtfES3ukaA7PcRVAQPil20Pjf9_BmyMTol0b1me42dKM_pGn7L3GCecfevtyZR-V_ptb6x1ux-wy20gy3jahAAyZ_cGrx9koIh-YEkg4h0UqNkI=</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>웹사이트에 전화번호가 있습니다.</t>
+          <t>Phone number +852 28150381 is available on the source page but not requested in the schema.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kiwi Fish</t>
+          <t>Bin Auf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2738,67 +2810,55 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://kiwifish.co.nz</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Premium seafood wholesaler, supplying an extensive range of live, chilled, and frozen shellfish, including pāua (abalone), to various markets including superyachts.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Auckland</t>
-        </is>
-      </c>
+          <t>인도네시아 수출업체, 수입업체, 해산물 무역업체. 제품에는 말린 해삼, 전복, 전갱이, 산호 송어, 말린 오징어, 황다랑어 등이 포함됩니다. 소량/대량 공급 가능.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Central Auckland</t>
-        </is>
-      </c>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Offers the best of New Zealand's sustainably caught seafood harvest, custom processed and delivered. Operates a Risk Management Programme (RMP) approved and audited by the Ministry for Primary Industries (MPI).</t>
+          <t>전복을 포함한 다양한 해산물 거래, 소량/대량 공급 가능.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Established premium seafood wholesaler with a wide range of products and strong quality control, suggesting capability for distributing abalone within New Zealand.</t>
+          <t>명시적으로 '수입업체' 역할을 명시, 다양한 제품 범위, 유연한 공급량.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQET8rm6pD2fyT7blQHzUlDu1ArhqNzw8L5XOkDHPt6BbyoKTCVauxe6Oxsjy7ctVUvrR8vDBXtaw4VbGut7tDCnC3Pj4-1Xvaq0HCMnqW3hIuF82K8ePbg==</t>
+          <t>https://www.trade-seafood.com/seafood-indonesia.htm</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Distributes New Zealand-sourced abalone (pāua).</t>
+          <t>스니펫에서 직접적인 웹사이트나 이메일을 찾을 수 없지만, 회사는 수입업체로 등재되어 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Waters Marine Limited</t>
+          <t>CV Langgeng Sentosa Trade Indo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2806,76 +2866,64 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>hello@northernwaters.co.nz</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://northernwaters.co.nz</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Facebook, TikTok, Instagram</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sells whole pāua (abalone) for wholesale and retail.</t>
+          <t>인도네시아 동부 자바의 냉동 해산물 수출업체, 조달업체 및 가공업체. 주요 생산품은 롤리고 오징어, 전복 고기, 문어, 갑오징어, 저서어류입니다. 냉동 삶은 전복 고기 'mata 7' 재고 보유.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Warkworth</t>
+          <t>East Java</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>182 State Highway 1, Warkworth 0981, New Zealand (AUK Dome Valley)</t>
+          <t>East Java - Indonesia.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sustainably harvested whole pāua (abalone) from the waters of Wairarapa and the South Island, offering authentic New Zealand flavor. Available for pickup or delivery.</t>
+          <t>냉동 삶은 전복 고기, 즉시 선적 가능.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Direct supplier and wholesaler of whole abalone, with clear contact information and a focus on sustainably harvested local product for the New Zealand market.</t>
+          <t>전복 고기의 직접 조달 및 가공업체, 즉시 선적 가능한 재고 보유. 주로 수출업체이지만, 조달 및 가공 역할은 국내에서 제품을 취급하며 수입을 위한 연락처가 될 수 있음을 시사합니다.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUTHdE_OizUFY_wnDheiVjs5gz8f6C2bi2M-kQnU8AHGUWDyfJfhJEeNJt5ZarxJzqydgApFymnTwOlFD3rW2VhMd-tPSVGo3JAsYEGcp40Nc3oTgS5tR5neHphsqorpRO59dq267d84rNGLqV6wH6d8HO7QE==</t>
+          <t>https://www.go4worldbusiness.com/find/products/frozen-abalone/indonesia.html</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Distributes New Zealand-sourced abalone (pāua).</t>
+          <t>연락 담당자 Tonny Santoso가 언급되었습니다. 스니펫에서 직접적인 이메일이나 웹사이트를 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sunz Seafood</t>
+          <t>PT CITA KARYA AGUNG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2886,65 +2934,65 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://sunzseafood.co.nz</t>
+          <t>https://variouseafood.com/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Wholesale and foodservice distribution of New Zealand minced pāua (abalone).</t>
+          <t>인도네시아의 선도적인 신선 및 냉동 해산물 가공업체, 공급업체 및 수출업체. 전복과 같은 냉동 복족류를 포함하여 35가지 이상의 다양한 제품을 제공합니다. 어부 및 양식 전문가로부터 조달.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Whitianga</t>
+          <t>Belawan</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>269 South Highway West Whitianga 3510</t>
+          <t>Belawan, Indonesia.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Premium New Zealand minced pāua (abalone), wild-caught and hand-harvested from Wairarapa and South Island, processed to export standards and frozen fresh. Offers meat-only pāua, ideal for patties, fritters, and commercial kitchen use.</t>
+          <t>달팽이 및 전복과 같은 프리미엄 냉동 복족류, 최적의 신선도를 유지하기 위해 신중하게 가공. GMP 표준 및 HACCP 인증.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Established wholesaler and foodservice supplier of abalone meat within New Zealand, indicating a strong distribution network for locally sourced product.</t>
+          <t>확고한 가공업체 및 공급업체, 지속 가능성 및 품질에 대한 약속, 광범위한 제품. 주로 수출업체이지만, 조달 및 가공 활동은 인도네시아 내 전복 공급망에서 관련 플레이어임을 나타냅니다.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6XLTPVgpag7xKK9QzbM_253BrUulevcWOCSV-khxpvqieFX7K7bO3HslNSPhfSIJySeYWXSDhgResGgoCJy1BNk6USQXQpWs7QU9S16CwXnw3H-JmFBse6B2Q6YReNBZXV8pjWQbq-KKVPcA-Zat9UCHvP7N6mtg50x-AO6e4Da1VnfLE</t>
+          <t>https://variouseafood.com/</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Primarily distributes New Zealand-sourced abalone (pāua).</t>
+          <t>스니펫에서 직접적인 이메일을 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-07-31 14:58:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Goh Joo Hin Pte Ltd</t>
+          <t>Pesca K &amp; M Co., Ltd.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2954,70 +3002,74 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>food@gjh.com.sg</t>
+          <t>pescauno@nifty.com</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>http://www.gjh.com.sg</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Wholesaler, Distributor</t>
+          <t>표2 (HS 160557)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
+          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
+          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
+          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
+          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-07-31 14:58:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oceanus Group Limited</t>
+          <t>True World Japan Inc.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3025,72 +3077,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>contact@oceanus.com.sg</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>http://www.oceanus.com.sg</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
+          <t>표1 (HS 030781)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
+          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
+          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
+          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
+          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-07-31 14:58:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Teck Sang Pte Ltd</t>
+          <t>Tsukuino Co. Ltd.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3100,70 +3152,70 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>local@tecksang.com</t>
+          <t>tukuino@heart.ocn.ne.jp</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.tecksang.com</t>
+          <t>https://www.tsukuino.com/english.html</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
+          <t>표1 (HS 030781)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11 Hongkong Street, Singapore 059654</t>
+          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
+          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
+          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
+          <t>https://www.tsukuino.com/english.html</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
+          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fresh Harvest (Pvt) Ltd</t>
+          <t>Harmony Marine Products Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3174,40 +3226,44 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://freshharvest.lk/</t>
+          <t>https://www.harmonymarine.com.my/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Seafood Importer and Distributor</t>
+          <t>전복, 해삼, 어류 부레를 포함한 프리미엄 해산물 진미 공급업체. 아시아 태평양, 남미 및 아프리카에서 제품 및 재료를 조달합니다.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>본사는 현대적인 시설(전용 건조실, 3,000평방피트 냉동고, 5,000평방피트 보관 공간)을 갖추고 있으며 HACCP 인증을 받았습니다.</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Leading seafood company in Sri Lanka, delivers high quality ready-to-cook seafood products. Caters to local market, supplies to top-class hotel chains, leading restaurants, and expanding in local retail market. Acts as an importer of high quality seafood.</t>
+          <t>프리미엄 전복, 엄격한 품질 관리, 지속 가능한 조달, 30년 이상의 경험.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>스리랑카 현지 시장에 고품질 해산물을 수입하여 호텔, 레스토랑 및 소매점에 공급하는 선도적인 회사입니다. 전복 수입 및 유통에 대한 협력 가능성이 높습니다.</t>
+          <t>광범위한 경험을 가진 확고한 공급업체, 국제적으로 조달, HACCP 인증.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcQYNWYOJvFZ5465KMss_BHieKPxvrhT-oNHOi2KKwePbAueaXewTLSRdFvyC53bKsJB9SxBoH5hsVkTNWMHCaabHTVCeR0iPYsraHevFcJpFSX0n9</t>
+          <t>https://www.harmonymarine.com.my/abalone-supplier-malaysia</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>이메일/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다.</t>
+          <t>주로 공급업체이지만, 다양한 지역에서 조달하는 것은 수입 활동을 의미합니다.</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3275,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
+          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3232,55 +3288,51 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>info@ruifuoilfood.com</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://ruifuoilfood.com/</t>
+          <t>https://oceanpacificonline.com/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
+          <t>전복을 포함한 다양한 해산물 및 냉동 식품을 도매 및 공급합니다.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Si Maha Phot, Prachin Buri</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
+          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
+          <t>전복, 조개, 게, 생선, 고기, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 공급합니다. 해산물 및 냉동 식품의 선두 공급업체입니다.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
+          <t>다양한 국내 브랜드, 지속적인 트렌드 분석, 최고의 서비스와 제품 제공에 전념.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
+          <t>https://oceanpacificonline.com/abalone</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
+          <t>웹사이트에 전화번호가 있습니다.</t>
         </is>
       </c>
     </row>
@@ -3292,12 +3344,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thai Abalone Co.,Ltd.</t>
+          <t>V Top Frozen Food Sdn Bhd</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3305,137 +3357,137 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Vtopff@gmail.com</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://m.ec21.com/company/thaiabalone/</t>
+          <t>https://vtopfrozenfood.com/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
+          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Pathiu, Chumphon</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
+          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
+          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
+          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://m.ec21.com/company/thaiabalone/</t>
+          <t>https://vtopfrozenfood.com/abalone-slices</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
+          <t>웹사이트에 전화번호가 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Monterey Abalone Company</t>
+          <t>Bajamar Trading Group</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>법인</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://montereyabalone.com</t>
-        </is>
-      </c>
+          <t>개인 에이전트</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>artavilo@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
+          <t>Producers, exporters, importers, wholesalers and agents of various seafood products including live and canned abalone, geoduck, lobster, fish, squid, scallops, shrimp, tuna, octopus.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Monterey</t>
+          <t>Guerrero Negro</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
+          <t>Victoria Sanchez s/n, Col. Estado 30, Guerrero Negro, Baja California Sur, 23940</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
+          <t>Live Red Abalone, Cultured Live Red Abalone, Blue and Yellow Canned Abalone, Yellow and Blue Abalone (frozen).</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
+          <t>Explicitly imports and distributes abalone, acts as an agent, and deals with both live and canned abalone.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Email not found in provided snippets.</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEywKxEIyVlMNjfilH11VDswQqsLbyNCU7KB_sereg0oMd6MEBpTRLhahJSb5ITplmF-lGSCyPqmzVjEvIRUUGjTD8ks23jykrR0C5IlZx-us7Uhww1TkqIWDq3d_g75TtnWphZSRfxCKtdPR7qLt6KUMo6XIBaSHqS9NjgbTEworKmrpJVnpV6fm7Igv28sf0h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ocean Floor Inc.</t>
+          <t>GlobalPezk</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3443,56 +3495,76 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>info@globalpezk.com</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>globalpezk.com</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>+52 (669) 980 6440 (Whatsapp for Mazatlán)</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Import and commercialization of premium seafood and exclusive supplies for oriental cuisine from the USA, China, Japan, and Canada. Wholesale and retail with national coverage in Mexico.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Tijuana</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Blvd. Fundadores 6119 Int. 11. El Rubí, C.P 22626, Tijuana, B.C. (Also operates in Mazatlán, Los Mochis, Culiacán, Guadalajara, and Mexico City)</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
+          <t>Imported premium seafood, wagyu, and oriental cuisine supplies. Products mentioned include smoked eel, hamachi fillet, soft-shell crab, masago, langostino, tiger shrimp.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
+          <t>Explicitly imports seafood from various countries and specializes in supplies for oriental cuisine, where abalone is a key product. Possesses a strong distribution network across Mexico.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGZAJLAMkuIRT2SJZy4_LMCS0YEHBaLEV3uNNvyo_6qjuNukemFvTb2riRNlf6Y_eb0QOnBfUKIkNRGgwPQ0HRaFdsRwduGKkx8wQ2viuu2e4n2vMcwFmNdwBlZrdWJZg==</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>City, email, and website not found in provided snippets.</t>
+          <t>Abalone is not explicitly listed in their product examples, but their focus on imported seafood and oriental cuisine supplies makes it highly probable.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seafarers Inc.</t>
+          <t>Olanda Seafood Trading Inc.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3500,56 +3572,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ventas@olandaseafood.com</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>www.olandaseafood.com</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Commercialization of seafood products from different parts of the world, importing and distributing fresh and frozen seafood, including shellfish. Focus on quality and freshness, and supplies for the Oriental gastronomic sector.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Tijuana</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Boulevard Tercera Oeste 17503 Int 1 Garita de Otay, Otay, Tijuana, B.C., 22430</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
+          <t>Import and commercialization of seafood, including shellfish. Products mentioned include salmon, octopus, shrimp, frozen fish, frozen noodles.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
+          <t>Explicitly imports and distributes seafood. While abalone is not explicitly listed in their product snippets, 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNYFpQ3-O5BAGOJXp-8-1MXgnYuTONmz1IeuKZ8cjTcQDFTiUIliVDTOUiVv-9Pmlv-_yFfxQMX7171TKmxWaTj2u0Zkeu7QCZma2SACK8gvTa_I4BkXwS3dQs</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>City, email, and website not found in provided snippets.</t>
+          <t>Abalone is not explicitly listed in their product snippets, but 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FGC JOINT STOCK COMPANY</t>
+          <t>Adri &amp; Zoon Schaal- en Schelpdierenhandel B.V.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3559,70 +3647,66 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>fgc.seafoods@gmail.com</t>
+          <t>info@adrienzoon.nl</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.fgc-foods.com/</t>
+          <t>https://www.adrienzoon.com</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>전복(살아있는, 열처리 및 냉동)을 포함한 고품질의 안전한 수입 식품을 제조 및 공급합니다.</t>
+          <t>전 세계 25개 어시장에서 해산물을 조달하며, 생선, 조개류, 갑각류를 수입, 수출, 도매 및 유통합니다.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Yerseke</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi.</t>
+          <t>Krab 17, 4401 PA Yerseke</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>수입 전복(살아있는, 열처리 및 냉동), 1kg/봉지, 10kg/상자, -18°C 보관, 24개월 유통기한.</t>
+          <t>전복 (Abalone), 아만데스/도그 코클 (Amandes/Dog Cockles), 멸치 (Anchovies), 북극 곤들매기 (Arctic char), 홍합 (Blue Mussels), 갈색 게 (Brown Crab), 대구 (Cod), 가재 (Crayfish), 굴 (Oysters), 기타 조개류 및 갑각류, 신선 수입 생선, 북해 생선, 냉동 해산물, 해초, 비식품 품목. 맞춤형 필레 및 포장 서비스를 제공합니다.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>수입 전복 공급업체, 품질 및 안전에 중점, 다양한 맛과 스타일.</t>
+          <t>1983년부터 운영된 가족 기업으로, 고객, 공급업체 및 직원과의 장기적인 파트너십에 중점을 둡니다. 고품질의 맞춤형 서비스를 제공하며, 친환경 어업 방식과 전기 트레일러 사용 등 지속 가능한 관행을 추구합니다. 자체 운송 차량을 통해 전 세계로 배송합니다.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://www.fgc-foods.com/san-pham/thuc-pham-chat-luong-cho-kenh-nha-hang-va-ban-le/bao-ngu-nhap-khau</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>전화 및 Zalo 핫라인도 이용 가능합니다.</t>
-        </is>
-      </c>
+          <t>https://www.adrienzoon.com/contact</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fishy Vietnam Co., Ltd</t>
+          <t>Starco Foodstuff</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3630,72 +3714,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Fishy.vn@gmail.com</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://fishy.vn/</t>
+          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>베트남에서 전복(냉동 전복(Loco) 고기, 냉동 호주산 그린립 전복 포함)을 포함한 최고급 해산물을 수입 및 유통합니다.</t>
+          <t>냉동 전복 조개류를 포함한 다양한 제품의 공급업체 및 수출업체입니다. 보리, 목재 펠릿, 새우, 복사 용지, 금속 등도 취급합니다.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Heerlen</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City.</t>
+          <t>Hoofdstraat 208, Hoensbroek</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>최고급 해산물 수입 및 유통 전문, 헌신과 명성, 고객 만족 중시, 고품질 제품, 최고의 서비스.</t>
+          <t>냉동 전복 조개류 (Frozen Abalone Shellfish), 보리 (Barley), 목재 펠릿 (Wood Pellets), 새우 (Shrimps), 복사 용지 (Copy Paper), 폐철 (Used Rail Scrap), 구리 음극 (Copper Cathode), 아몬드 (Almond Nuts), 알루미늄 잉곳 (Aluminium Ingots), 냉동 닭고기 (Frozen Chicken), 양고기 (Lamb/Mutton Meat).</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>프리미엄 해산물 수입 및 유통 선두 기업, 다양한 전복 제품, 품질 및 고객 서비스에 중점.</t>
+          <t>B2B 플랫폼인 Tradewheel.com에 냉동 전복 조개류 공급업체로 등록되어 있습니다. 2019년에 설립되었습니다. 매우 다양한 제품군을 취급하는 일반 무역 회사일 수 있습니다.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://fishy.vn/san-pham/bao-ngu</t>
+          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>세금 ID 및 핫라인도 이용 가능합니다.</t>
+          <t>이메일 주소는 Tradewheel.com 프로필에 직접 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Trọng Đức Seafood</t>
+          <t>Kiwi Fish</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3706,38 +3786,2632 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://trongduc.vn/</t>
+          <t>https://kiwifish.co.nz</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
+          <t>Premium seafood wholesaler, supplying an extensive range of live, chilled, and frozen shellfish, including pāua (abalone), to various markets including superyachts.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Central Auckland</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Offers the best of New Zealand's sustainably caught seafood harvest, custom processed and delivered. Operates a Risk Management Programme (RMP) approved and audited by the Ministry for Primary Industries (MPI).</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Established premium seafood wholesaler with a wide range of products and strong quality control, suggesting capability for distributing abalone within New Zealand.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQET8rm6pD2fyT7blQHzUlDu1ArhqNzw8L5XOkDHPt6BbyoKTCVauxe6Oxsjy7ctVUvrR8vDBXtaw4VbGut7tDCnC3Pj4-1Xvaq0HCMnqW3hIuF82K8ePbg==</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Distributes New Zealand-sourced abalone (pāua).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-01 02:57:29</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Northern Waters Marine Limited</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>hello@northernwaters.co.nz</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://northernwaters.co.nz</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Facebook, TikTok, Instagram</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sells whole pāua (abalone) for wholesale and retail.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Warkworth</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>182 State Highway 1, Warkworth 0981, New Zealand (AUK Dome Valley)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Sustainably harvested whole pāua (abalone) from the waters of Wairarapa and the South Island, offering authentic New Zealand flavor. Available for pickup or delivery.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Direct supplier and wholesaler of whole abalone, with clear contact information and a focus on sustainably harvested local product for the New Zealand market.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUTHdE_OizUFY_wnDheiVjs5gz8f6C2bi2M-kQnU8AHGUWDyfJfhJEeNJt5ZarxJzqydgApFymnTwOlFD3rW2VhMd-tPSVGo3JAsYEGcp40Nc3oTgS5tR5neHphsqorpRO59dq267d84rNGLqV6wH6d8HO7QE==</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Distributes New Zealand-sourced abalone (pāua).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-01 02:57:29</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sunz Seafood</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://sunzseafood.co.nz</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Wholesale and foodservice distribution of New Zealand minced pāua (abalone).</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Whitianga</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>269 South Highway West Whitianga 3510</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Premium New Zealand minced pāua (abalone), wild-caught and hand-harvested from Wairarapa and South Island, processed to export standards and frozen fresh. Offers meat-only pāua, ideal for patties, fritters, and commercial kitchen use.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Established wholesaler and foodservice supplier of abalone meat within New Zealand, indicating a strong distribution network for locally sourced product.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6XLTPVgpag7xKK9QzbM_253BrUulevcWOCSV-khxpvqieFX7K7bO3HslNSPhfSIJySeYWXSDhgResGgoCJy1BNk6USQXQpWs7QU9S16CwXnw3H-JmFBse6B2Q6YReNBZXV8pjWQbq-KKVPcA-Zat9UCHvP7N6mtg50x-AO6e4Da1VnfLE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Primarily distributes New Zealand-sourced abalone (pāua).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FoodPhil Corporation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://foodphil.com/</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Frozen and fresh seafood, including abalone, scallop, shrimps, lobsters, crabs, crablets, crabmeat.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Cebu</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Proven trader of frozen and fresh seafood, supplying to several restaurants, distributors, and malls around the Philippines.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Established in 2007, they are a reliable supplier of frozen and fresh seafood to hotels, restaurants, and retailers.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://foodphil.com/</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pancoastal International</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://pancoastal.com/</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Importation, distribution, wholesale, and retail of premium frozen seafood. Product range includes Atlantic Salmon, Coho Salmon, Barramundi, Pompano, Chilean Seabass, Tuna.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Specializes in premium frozen seafood, sourcing globally from Canada, Chile, Norway, EU, China, Vietnam, and USA. Serves restaurants, hotels, supermarkets, wholesalers, and retailers.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Dedicated to offering a diverse range of top-quality imported seafood and leading the market in high-quality seafood distribution.</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://pancoastal.com/</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Abalone is not explicitly listed in their product examples, but their general scope as a 'premium frozen seafood importer' and distributor makes them a strong potential partner for abalone. Contact details like email/LinkedIn/messenger not explicitly listed on the homepage, but a 'Contact' page is available on their website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TC International Seafoods Provider Inc.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Manufacturing, import and export of Fresh Frozen Marine products, including Frozen Boiled Abalone Meat.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Actively trading in Taiwan, China, Hong Kong, Vietnam, USA and Canada.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Engaged in both import and export of fresh frozen marine products, indicating a strong supply chain and market presence.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHuXKC2Pza8RjFQF46dD1k1qjUsZOZYpuhqP_IeQ9NAgxgU5WN--XiuJAdSYdV639ettOP0E8pmoUv3ePW26aNr17kXVLhBdJmbwcr7SiA7-K-5MOvza_DQsawn51Im7X9ksC7MtyPAsNMpSMlBQfligeiYlwfRTvQbojapfK_uRtBC</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Specific city within the Philippines not found in the provided snippets. Contact details like email/website not explicitly listed in the search results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rep. of Korea</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>㈜제이에스코리아</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>js-korea.com</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>전복, 굴 등 어패류 가공 및 수출 전문. 활어, 냉동, 통조림 등 다양한 형태로 가공하여 홍콩, 싱가포르, 베트남, 캐나다 등 세계 각지에 수출.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>완도</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Rep. of Korea</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>완도에 본사 및 식품 가공 공장 위치.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>전복 가공식품 (통조림, 소스, 죽, 장 등), 굴 가공식품, 해외 수출. K·FISH 인증 보유.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>전복 가공 기술 및 수출 노하우가 뛰어나며, K·FISH 인증을 통해 품질 안정성을 확보하고 다양한 가공 제품으로 해외 시장에 진출하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvnf2Abv7NqaI1pbEBcXg5_-hi89lZ5556iuwdFyRctwjXwyaEYhM901eVExey6vZHCLG2nr3C1Ds3UgxRZBC2l7XMO0V9Hwe2dSiv9Eiln8VAsVxufluTjNuYHTksoBQK1LF7NASp5z_cPjB03gfmajsqvetdJ_MZQMDDQHE_kel2J0KkBfswaCR-M4EiTiX4uJYtFdg5QL47Zt8rQ4DJ7Hke9DdDqsWHLKoplDUi9hbzGTMsS37FIrEp1_O71yNFk4e8cwEwaSAIU9C-xfFqHRF_cTbnsDkL515JE3vwHY6A2yA36BPJZHGFFp1QPwcNMRBp7ltExYN9-pcsBO_T3RPaRjmUxAKC0G3FnWNyoXPT7et58evQA0Rcp1h2iJK22EkfH4CpCY1dkQuXFfkbgr6h6KCIA==</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rep. of Korea</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>㈜청산바다</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>cheongsanbada.com</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>전복 생산, 유통, 수출, 가공, 판매를 원스톱으로 진행하는 생산자 조합 회사. 일본, 홍콩, 유럽, 미국 등 해외 수출 및 국내 최고급 호텔, 백화점 거래.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>완도</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Rep. of Korea</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>전남 완도군 완도읍 농공단지4길 22-7</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>활전복, 전복 가공식품, 아시아 최초 ASC 인증 보유.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>전복 생산부터 수출까지 전 과정을 직접 관리하며, 아시아 최초 ASC 인증을 통해 품질과 지속가능성을 인정받았습니다. 해외 시장에 대한 높은 이해도와 유통망을 보유하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVkzRFigxKCfhziKW_fKDfhJoYijxhubjB5tnFMmsV-sW4Hy7O47UY7PSizNwgsH9ltf3nlA7J_PcfmA2VN8TcatJD25HrYqVUA4eEVj5_as7jOPqqp9X38PI99eMFTx96G1kBBqatrgJmAqFLEwSfcCW_l6aPl4a7ueV0NkLYLdFEZltKfZAJ0nJdrlEcxLNzCY4xx-4CVxPPNRSUu8OA6l9jflRKq5crSvp4aoZzg8LOXK_2P7byIJdl-QxIVlAA5QWCiUfuaUts400REyvusr10ZahsNebaiZTaok3EDYrSY0J10Sq-yuiN34IlTHLWVfNEWYCVxkzX4Ix3EAkZWzRvYeJkFLlH3lZi7Po_Ul7QhAwasnpX0fHZVEtJ</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>고객센터 전화번호는 061-553-5900이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rep. of Korea</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>완도전복주식회사</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>wakorea.kr</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>국내외 기업 및 개인 고객을 대상으로 활전복 및 가공전복 공급, 국내 최대 활전복 유통 및 가공전복 제품 생산, 롯데마트, 이마트, CJ프레시웨이 등 주요 거래처, 일본, 미국, 싱가포르 등 동남아 지역 수출.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>완도</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Rep. of Korea</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>전라남도 완도군</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>활전복, 가공전복 (통조림, 동결제품), 국내 대형 유통망 공급, 해외 수출.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>생산 어민과 완도군이 공동 출자하여 설립된 국내 최대 전복 전문 기업으로, 안정적인 공급망과 광범위한 국내외 유통망을 보유하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVUzQYPzka2YSdvtxrcdlEwnD9kMLBlEc0nUobdRmu7Sh6VCkqAI7XZdkeOmLwU4iXbob_FjOZxeI7_jSshQFyj4k2SrvUPYNeiS2umO4l</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>고객센터 전화번호는 1577-8855이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dakar Ice</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>contact@dakarice.com</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>http://www.dakarice.com</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>수입/유통 (Import/Distribution)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Dakar</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Hann plage, au km 5 boulevard de la commune de Dakar</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>다양한 어류 취급, 특히 전복(abalone)을 월 최소 1컨테이너 처리 가능.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>전복(abalone)을 월 최소 1컨테이너 규모로 취급하며, 수산물 전반에 대한 경험이 풍부하여 협력 가능성이 높습니다.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHyVlKRmRztQxojYk66kNXGxJrx8_JI93Lx6e0cD3eq6iNIdAXKWbzug3ERNopXTxQ4Xu-KFj5Nf0dusDVD1ygDla4N1Jmpqe5_Hq1joE8XvJ2ZD6iyhMQbnLgAWb_WAVShMpUIkg==</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Fijin.com에 'Dakar Ice'가 전복을 취급하며 월 최소 1컨테이너를 처리할 수 있다고 명시되어 있습니다. 공식 웹사이트는 검색 결과에서 직접 확인되지 않았으나, 이메일 주소를 통해 도메인을 추정했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Goh Joo Hin Pte Ltd</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>food@gjh.com.sg</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>http://www.gjh.com.sg</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Importer, Exporter, Wholesaler, Distributor</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Oceanus Group Limited</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>contact@oceanus.com.sg</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>http://www.oceanus.com.sg</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Teck Sang Pte Ltd</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>local@tecksang.com</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.tecksang.com</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>11 Hongkong Street, Singapore 059654</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Atlantis Foods</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>info@atlantisfoods.co.za</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.atlantisfoods.co.za/</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>South Africa의 주요 해산물 유통 회사 중 하나로, 도매업체, 식품 서비스 제공업체 및 소매업체에 고품질 해산물 제품을 소싱, 가공 및 유통합니다. 과거 전무이사가 전복(Abalone) 및 냉장 보관을 담당했습니다.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>8 Wessex Road Paarden Eiland Cape Town, South Africa, 7405 (Sales &amp; Marketing Office)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>다양한 신선, 냉동, 부가가치 및 즉석 해산물 제품을 취급하며, 전복을 포함한 해산물 유통 경험이 있습니다.</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>남아프리카 공화국 내에서 광범위한 유통망을 가진 대규모 해산물 유통업체로, 다양한 채널에 대량 공급이 가능합니다.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://www.atlantisfoods.co.za/contact-us/</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>BestFoodImporters.com에 따르면 'Importer, Distributor, Wholesaler, Supplier'로 분류됩니다. 이전 그룹 물류 관리자가 전복을 담당했다는 언급이 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Greenfish</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ops@greenfish.co.za, Sales1@greenfish.co.za</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://greenfish.co.za/</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>063 666 2802 (Whatsapp)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>온라인 및 도매 해산물 공급업체로, 양식 전복(perlemoen)을 포함한 신선한 해산물을 취급합니다.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>온라인 전용 (소매점 없음), Cape Town 및 주변 지역(CBD, Southern Suburbs, Houtbay, Plattekloof, Deep South, Table View, Blouberg, Melkbos, Durbanville, Stellenbosch, Somerset West, Franschhoek, Paarl) 배송 가능.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>6개들이 라이브 양식 전복(perlemoen)을 판매하며, 노르웨이산 연어, 대구, 참치, 킹클립, 홍합, 굴, 옐로우테일, 카벨조우 등 다양한 신선 해산물을 제공합니다.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>양식 전복을 직접 공급하며, 개인 소비자 및 도매 고객 모두에게 서비스를 제공합니다. 소규모 또는 전문적인 주문, 레스토랑 직거래에 적합합니다.</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://greenfish.co.za/products/abalone-perlemoen-live-box-cultivated-x6</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>온라인 전용 업체이며, 소매점은 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FRESHCADO RECIEN PESCADO SL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>contact@freshcado.es</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://freshcado.es</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Wholesale and retail of fresh and frozen fish and seafood, including premium seafood. Operates as an online fishmonger and supplies professionals across Spain, sourcing from Mercamadrid and international ports.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>C/ de la Diputació, 256, 08007 Barcelona</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Offers a wide selection of fresh and frozen seafood. Emphasizes maximum freshness, direct product from Mercamadrid, and 24/48h delivery. Committed to sustainability and responsible fishing.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>As a large seafood wholesaler and online retailer with a wide range of fresh and frozen seafood, including a 'Premium Seafood' category, Freshcado is a strong prospect for importing and distributing abalone.</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://freshcado.es/legal-notice/, https://freshcado.es/accessibility-statement/, https://freshcado.es/general-terms-and-conditions/, https://freshcado.es/en/fish-and-seafood-wholesaler-in-spain/, https://freshcado.es/en/online-fishmonger-buy-fresh-fish-and-seafood/, https://freshcado.es/en/comprar-smoked-and-canned-products-online/</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Globalimar Europa, SL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>info@globalimar.com</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.globalimar.com</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Frozen seafood import, production, and commercialization for mass-market, including bivalves, cephalopods, crustaceans, surimi, and prepared fish. Serves Spain, Europe, USA, and Maghreb region.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Llagostera</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>C/ Jaume I, 2A, 17240 Llagostera, Girona</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Specialists in frozen seafood products, with a focus on quality and sustainability. Offers a diversified range of frozen seafood. Explicitly states import and commercialization activities.</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Explicitly states 'import, produce and commercialize' frozen seafood. Their broad range of seafood products, including bivalves, makes them a highly probable candidate for importing abalone.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://www.globalimar.com/contact/, https://www.conxemar.com/en/asociados/globalimar-europa-sl, https://www.conxemar.com/en/exhibitor/globalimar-europa-sl-conxemar-2024, https://www.globalimar.com/en/company/specialists-in-frozen-seafood/, https://www.bestfoodimporters.com/importer/globalimar-europa</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>La Alondra Seafood (Pescados La Alondra Sl)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>hola@laalondraseafood.es</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.laalondraseafood.es</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Distribution of fresh and cryogenized seafood for retail, HORECA channel, and international markets. Focuses on premium seafood products from the best fishing grounds worldwide.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Avenida Euro núm. 24 Puesto 17 19 21, 47009 Valladolid, Castilla-león</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Specializes in high-quality, fresh, and cryogenized seafood. Offers a catalog of seafood products from the best fishing grounds globally. Strong presence in HORECA and retail, with international distribution capabilities.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Their focus on premium seafood, international distribution, and the HORECA channel makes them a good prospect for importing and distributing abalone. Their advanced cryogenic preservation technology could be a suitable fit for abalone products.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://www.laalondraseafood.es/en/distribution/, https://www.laalondraseafood.es/en/fresh-fish-and-seafood/, https://www.laalondraseafood.es/en/cryogenized-seafood/, https://www.laalondraseafood.es/en/innovation/, https://www.empresite.com/PESCADOS-LA-ALONDRA-SL.html, https://www.laalondraseafood.es/en/contact/</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-01 02:57:29</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Fresh Harvest (Pvt) Ltd</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://freshharvest.lk/</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Seafood Importer and Distributor</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Leading seafood company in Sri Lanka, delivers high quality ready-to-cook seafood products. Caters to local market, supplies to top-class hotel chains, leading restaurants, and expanding in local retail market. Acts as an importer of high quality seafood.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>스리랑카 현지 시장에 고품질 해산물을 수입하여 호텔, 레스토랑 및 소매점에 공급하는 선도적인 회사입니다. 전복 수입 및 유통에 대한 협력 가능성이 높습니다.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcQYNWYOJvFZ5465KMss_BHieKPxvrhT-oNHOi2KKwePbAueaXewTLSRdFvyC53bKsJB9SxBoH5hsVkTNWMHCaabHTVCeR0iPYsraHevFcJpFSX0n9</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>이메일/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Johnson Seafood Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.johnsonseafood.com.tw</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Leading seafood importer in Taiwan. Imports live, frozen, and freshly chilled seafood, including abalone &amp; scallop. Sources from over 40 countries.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Tainan</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Based in Qigu coastal areas around Tainan, aquaculture in Tainan's Jiali Township.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Wide range of seafood products (fish, shrimps, crabs, shellfish, mollusk, processed seafood), regular SGS inspection, provides safe and tasty food materials. Product range covers live seafood, frozen seafood, and freshly chilled seafood.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Over 50 years of operation, excellent reputation, sizeable procurement volume, trusted partner by overseas suppliers, and commitment to food safety with SGS inspection.</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>https://www.johnsonseafood.com.tw/about-us/company-profile</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ming Sheng Seafood Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.mingsheng.com.tw</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Importer of fresh frozen marine products, supplying diversified premium seafood to wholesalers across Taiwan. Imports over 300 premium frozen seafood products, sourcing from 4 oceans and 5 continents.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Kaohsiung City</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2F, 332 Zihyou 2nd Rd., Zuoying District, Kaohsiung City, Taiwan.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Over 30 years of experience, strong relationships with manufacturers and customers, world-class logistic system. Offers a set of diversified premium seafood.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Long-standing importer with a wide global sourcing network and a focus on timely delivery to wholesalers. Strong reputation and trust from domestic and international suppliers.</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>https://www.mingsheng.com.tw/about-ming-sheng</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>YEN &amp; Brothers Enterprise CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>service@mail.yens.com.tw</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.yens.com.tw</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Abalone importer and wholesaler, deals with frozen abalone meat, whole-cooked abalone, Australian abalone. Also handles other fish, crustacean, shellfish, mollusc, meat, soup, prepared foods.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>New Taipei City</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>14F, NO. 217,SEC. 2, NEW TAIPEI BLVD., XINZHUANG DIST., NEW TAIPEI CITY 242, TAIWAN (R.O.C.)</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Global purchasing, R&amp;D and production, food safety, logistic management. Importer and wholesaler of various seafood products, including abalone.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Established company with global purchasing capabilities and a strong focus on food safety and quality management. Handles a variety of abalone products (frozen, whole-cooked, Australian).</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>https://www.yens.com.tw/products/shellfish/abalone</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>info@ruifuoilfood.com</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://ruifuoilfood.com/</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Si Maha Phot, Prachin Buri</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Thai Abalone Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Pathiu, Chumphon</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Monterey Abalone Company</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://montereyabalone.com</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Monterey</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Email not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ocean Floor Inc.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>City, email, and website not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:22:35</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Seafarers Inc.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>City, email, and website not found in provided snippets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Abalone Fish Processing LLC</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Fish and Seafood Processors</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Ajman</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Near Factory Mart, New Ind Area, Ajman / 78a, Amman street, Ajman Industrial 2</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Fish and Seafood Processors. The company name suggests a focus on abalone.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>A seafood processing company, likely involved in the import and distribution of various seafood, potentially including abalone, given its name. They are listed as 'Fish And Seafood Processors'.</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHFN1ioKMvAABGXDTz-XA2FisFHogtokbmSflhk3jbvA8p7zaDQFSZwrI0hdELPSZmK4Wc-LYdVkfx9Icf2bIlxGcy5n-3UNZ38yb-YhBVFHE0QP_48m00iz7KofFmbKySqsSnnKW3nKI_I128GTUIQfv-FTBuOaPRMuJfMDST_</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Phone number: 06-7438606</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Dior Fresh Fish</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://diorfreshfish.com/</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Fresh and frozen seafood, including Whole Shell Abalone. Delivery across UAE (Dubai, Abu Dhabi, Sharjah).</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Waterfront market Deira, Dubai.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Sells 'Fresh Whole Shell Abalone' sourced from pristine cold-water regions (FAO Areas 27 and 81). Halal Compliant &amp; Hygienically Processed. Cold-Chain Delivery (0–4°C). Offers custom fish preparation and 2-hour/same-day delivery in Dubai, next-day across UAE.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Directly imports and distributes abalone, with a focus on quality and cold-chain logistics. They cater to households and high-end restaurants.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF1n6IrUDF_2UqEV1FcEcY_91lJj3LUZsTqcN2E-z6ynL2pmf6_SM1ymPQjnZMML_D3hhCHfVLVikDUjllk1QaU7pVCslFnbxRTPWXUF1y6MLjcD1m-IBi83-ovGxE8KZhXTNMo4yW_3PmnAFzpJ5O5jrf8_bcyfg==</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sea World Fish Processing Llc</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>+971564117152 (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Frozen Seafood, Shrimp, Salmon, Squid, Abalone, Lobster, Tuna, Trevally. Fish &amp; Seafood Importers, Exporters &amp; Processors.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Ajman</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Meena Rd, Nr Fish Market, Al Jurf Indl Area, Ajman. Also listed in Al Quoz Industrial 3, Dubai.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Supplier of Frozen Seafood including Abalone, Shrimp, Salmon, Squid, Lobster, Tuna, Trevally. Also lists Salmon, King Fish, Octopus.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Explicitly listed as a supplier of 'Frozen Abalone' and 'Frozen Seafood'. They are also 'Fish &amp; Seafood Importers, Exporters &amp; Processors'.</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHilrZwc_-sVdE6bxfa_EuTM77Z-w7QcSFQExMjw8zLaBemFs7vOrXa3yrDTsx-7YDW4t9Z8Al_fRoC7fqyqD0LgQWijBKAJOUkaCbOVcgwqY3UASq9uRKwk3Qd-ag7ux7mmxmf1e26daaZRNlDWEd_2ZaKnwEDtz5oxNbZCL9OEVnyaMgh0ArAZFmnkodMlaIL</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Phone number: +971-6-7444559</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Direct Seafoods</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>sales@directseafoods.co.uk</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.directseafoods.co.uk/</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Wholesale abalone, frozen wholesale abalone, supplying to restaurants, caterers, and distributors.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Colchester</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Crown Court Severalls Business Park, Clough road, Colchester CO4 9TZ</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Expertly sourced wholesale abalone, premium quality, range of pack sizes, sustainably sourced options, frozen abalone.</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Clearly states they are suppliers of wholesale abalone for businesses, including caterers and distributors, indicating they import or source in bulk.</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHUIYsQ2UBPSBJ867GFx9lsSGgOScseBoH5kgVzDM4Z9FqfpgCuJOckuXoixQJWbbT--kaUWwRR_UzXIpjbk7uvQF9L8O0c_NRa3jAnZIPK8qH5hk4lkW-WX7hkiJFFlIanM64gCt86Rui4ofRFzhQfr-MHgQRPuI-tVU0=</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Part of Bidfresh Limited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Fine Food Specialist</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>support@finefoodspecialist.co.uk</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.finefoodspecialist.co.uk/</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sells large Australian abalone online, offers wholesale.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Not explicitly stated beyond 'London and the UK'.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Large Australian abalone, frozen, sashimi grade, offers next day delivery.</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Explicitly states 'Wholesale available. Trusted UK fine food wholesaler,' indicating they are a distributor.</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGMjhqPJpEsff_zAS7zQT4UIck_UEpFMw36Ap14taYnEELyVa1mAKjWqtFFwvjKYoZ6_VuZ37CEImyilNnDqE0avI5M1E1YyngtytpAY67YhY8ts-aoTS1FWZ3AtkuSrw-UyioUx9MMvlc6lidPdRqiatFTdXzrMlinyaaYKh0gqQ==</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Offers both retail and wholesale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Seafood Australia</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://seafoodaustralia.co.uk/</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sells Premium Australian Canned Abalone and Wild Abalone, with 'Fast UK Shipping' and a 'Wholesale' section.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Delivers to anywhere in the UK.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Premium Australian wild and farmed abalone, canned abalone, direct from farm to door, sustainably farmed or caught.</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Has a 'Wholesale' section on their website and offers direct supply of Australian abalone, suggesting they are an importer/distributor.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHydvT7JMFhRuJb4p5iZBcaBABfGyX2tWoFEHuHnjJ_kqBq4Eb1I0ey6Ty7x2ua2-wI7FN6fuFx3syKl6sTP9xSL_oGe4JKYhCxMN3JZuetVzzTAo5vHoDUhwQt-44=</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Specializes in Australian abalone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Viet Nam</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Fishy Vietnam Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Fishy.vn@gmail.com</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Importing and distributing top-class seafood, including various types of abalone (Frozen Abalone (Loco) Meat, Frozen Australian Greenlip Abalone, Frozen Abalone, Braised Abalone In Oyster Sauce, Abalone Seafood Soup).</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Specializes in importing and distributing top-class seafood. Products include various types of abalone (frozen, Australian greenlip, loco meat, abalone seafood soup, braised abalone in oyster sauce). Focus on product quality, dedication, and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Direct importer and distributor, indicating a clear channel for cooperation. Emphasizes quality and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFnIbNcTSOzpm1rjxZKNdOXHZFHXPLvkR6w0O11uKwUJy88CBKHuqahAqg6N3_l-KqHBD9TlsdBOFLPPwARm092X_aBdYKa_w7CDxuB3MzJ4junbM6oKTpwaIgIt3W2fFE=</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Viet Nam</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Sai Thanh Foods</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>salesfreshfood@sacofoods.vn</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://saithanhfoods.com/</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Supplier of frozen abalone (Haliotis Diversicolor) from Vietnam. Also deals with other seafood like sea fish, river fish, octopus, squid, shellfish.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Lot III-22, Street 19/5A, Tan Binh Industrial Park, Tay Thanh Ward, Ho Chi Minh City, Vietnam</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Specializes in frozen abalone (Haliotis Diversicolor) of Vietnamese origin. They also offer other seafood products.</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Direct supplier of frozen abalone, indicating a potential for direct sourcing. They invite inquiries for specifications and pricing.</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdzZHAIL6EJepETfinawUNWPxz-8vXV951xIFxRs0HZB32IxHGNPOCJKb_txdlYe0VZWWpejeThan1R4sfd3Pj_eg_ZzTpeCR9cmBU_meF-izlTZCbpQTD124H_zWN5Fe1iuEj6bD5iqxCJW8af6yMk-s=</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Viet Nam</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Trọng Đức Seafood</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://trongduc.com/</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Imports abalone mainly from Korea, Japan, and neighboring countries. Also deals with other seafood like Japanese scallops, sea eel. Offers good prices for wholesalers, agents, and distributors.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Imports abalone from Korea, Japan, and neighboring countries. Offers various sizes of Korean abalone. Emphasizes product quality, reputation, and direct import for good prices for wholesalers/agents/distributors.</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Explicitly states good prices for wholesalers, agents, and distributors, making them a direct potential partner. They also offer returns if not satisfied.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFNhjSu_CUVmGlZe8ulZHnui_rrcb9z2Gm9Dk4aJlf3YHrn288thuxtw0ARGxmu3uLnFb-7BIWKI_KEffIQPvRk0m3fct_IGwngL1ebQV7ngD9mdbqcdBnMHvE7US-xDV1Y9SOFz--R_tY6SDR-u-90jvs=</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>City and location detail not explicitly mentioned in the provided source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FGC JOINT STOCK COMPANY</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>fgc.seafoods@gmail.com</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.fgc-foods.com/</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>전복(살아있는, 열처리 및 냉동)을 포함한 고품질의 안전한 수입 식품을 제조 및 공급합니다.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>수입 전복(살아있는, 열처리 및 냉동), 1kg/봉지, 10kg/상자, -18°C 보관, 24개월 유통기한.</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>수입 전복 공급업체, 품질 및 안전에 중점, 다양한 맛과 스타일.</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>https://www.fgc-foods.com/san-pham/thuc-pham-chat-luong-cho-kenh-nha-hang-va-ban-le/bao-ngu-nhap-khau</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>전화 및 Zalo 핫라인도 이용 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fishy Vietnam Co., Ltd</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Fishy.vn@gmail.com</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>베트남에서 전복(냉동 전복(Loco) 고기, 냉동 호주산 그린립 전복 포함)을 포함한 최고급 해산물을 수입 및 유통합니다.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>최고급 해산물 수입 및 유통 전문, 헌신과 명성, 고객 만족 중시, 고품질 제품, 최고의 서비스.</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>프리미엄 해산물 수입 및 유통 선두 기업, 다양한 전복 제품, 품질 및 고객 서비스에 중점.</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/san-pham/bao-ngu</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>세금 ID 및 핫라인도 이용 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Trọng Đức Seafood</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://trongduc.vn/</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>한국, 일본 및 인근 국가에서 전복을 수입하여 도매업체, 에이전트 및 유통업체에 공급합니다.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
         <is>
           <t>수입 전복 (한국, 일본 및 인근 국가산), 다양한 크기, 도매업체/에이전트/유통업체에 좋은 가격, 품질 명성, 완전한 문서 및 바코드.</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>직접 수입업체이며, 도매업체/에이전트/유통업체에 좋은 가격을 제공하고, 품질 및 문서화에 중점을 둡니다.</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>https://trongduc.vn/san-pham/bao-ngu-nhap-khau/</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>이메일/전화번호는 스니펫에 명시되어 있지 않지만 웹사이트가 제공됩니다.</t>
         </is>

--- a/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
+++ b/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
@@ -569,12 +569,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>🔍 조사 완료 (3개사 발견)</t>
+          <t>🔍 조사 완료 (6개사 발견)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd, UlifeFoods 외 1개사</t>
+          <t>Caharbor (Qingdao Caharbor Food Co., Ltd.), Dongshang Seafood Trading 외 4개사</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🔍 조사 완료 (3개사 발견)</t>
+          <t>🔍 조사 완료 (5개사 발견)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Goh Joo Hin Pte Ltd, Oceanus Group Limited 외 1개사</t>
+          <t>Goh Joo Hin Pte Ltd, Hosen Group Ltd. 외 3개사</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1482,7 +1482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,7 +2182,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd</t>
+          <t>Caharbor (Qingdao Caharbor Food Co., Ltd.)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2200,24 +2200,12 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>marketing@vegfoodgroup.com</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>http://www.vegfoodgroup.com</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>+86-17706396685 (WhatsApp)</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Professional supplier of frozen, fresh, dehydrated vegetables, fruit and mushroom. Also lists 'Seafood' including 'canned abalone' among its products. Engages in import and export.</t>
+          <t>Import and export of frozen seafood, wholesale</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2230,36 +2218,32 @@
           <t>China</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>No.79 Jinzhong Road, Licang District, Qingdao City, China</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>One import and export company, five own factories and more than 15 factories in China through mutual shareholding, joint ventures. Diverse product range beyond abalone.</t>
+          <t>30 years in processing fish, 10+ years in import/export. Deals with Frozen Abalone.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>An import and export company explicitly dealing with 'canned abalone' as part of their seafood offerings, indicating direct involvement in abalone distribution within China.</t>
+          <t>Explicitly states 'import and export' experience and deals with 'Frozen Abalone', indicating they are an active player in the abalone import market.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>http://www.vegfoodgroup.com/contact-us.html</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFpnu4QYK2ckMLX-qAE2TQsFPld1ud8vCkVid1tj18epRsD4f8SF9QlRSx2YHUMuNGU9SISm3Jwixlgv8Yi43NcJ_K50MYVum_N6Kq3Zga8AXE-4jGSSL0QaBbINZtTCujlcu5SoXa6s4-eT4o4kI0I14QFQPZA-AS-gg==</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>The company lists 'canned abalone' as a product, confirming their involvement with abalone.</t>
+          <t>The company name 'Qingdao Caharbor Food Co., Ltd.' suggests Qingdao as the city.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2269,7 +2253,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UlifeFoods</t>
+          <t>Dongshang Seafood Trading</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2277,55 +2261,39 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>info@ulifefoods.com</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://www.ulifefoods.com</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>IQF Abalone wholesale supplier, frozen seafood, raw abalone, cooked abalone, canned abalone, dried abalone. Specializing in research, production, and sales of frozen processed foods.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Fuzhou</t>
-        </is>
-      </c>
+          <t>Buyer/importer of various seafood</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>No. 10 Xiamei Road, Meixin Village, Meihua Town, Changle District, Fuzhou City, Fujian Province, China</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Over 30 years in the industry, own breeding base and factory, HACCP, BRC, ISO, ASC, FSPCA certified. Exports to USA, Canada, South Korea, Japan, Southeast Asia. Annual production capacity of 15,000 tons of quick-frozen prepared food.</t>
+          <t>Buys abalone, depurated jackknife clams, quahog clams, oysters, black/blood clams, peruvian scallops.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Direct wholesale supplier with extensive product range (raw, cooked, canned, dried abalone) and international export experience. Certifications indicate high quality and safety standards.</t>
+          <t>Explicitly identified as a 'Buyer' of abalone on a B2B platform, indicating direct interest in sourcing.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.ulifefoods.com/about-us.html</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHBozlwjYcQLdoU0_k3LQandS5PwGiP_Cfv1eeyftYZO5U3F2XBblTEqjf_vlqX2qQ0GKcwKNt8vF8SzExuoxb9KSBCa2XM5ma4xPugRSpcBfu1S0eQpLVFR7qL2BdemR75UPJ0Ul2f1c2vBhkjIaLVKC8I9zLd1jHhLw==</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>They are a manufacturer and wholesale supplier, implying distribution and import capabilities for their own products, and potentially for others given their 'wholesale supplier' designation.</t>
+          <t>Listed as 'Buyer From China' on go4WorldBusiness.com.</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2310,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xiamen Binqi Import &amp; Export Co., Ltd</t>
+          <t>Qingdao Veg Food Imp. &amp; Exp. Co.,Ltd</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2352,19 +2320,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tom@binqi-china.com</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>marketing@vegfoodgroup.com</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>http://www.vegfoodgroup.com</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>+86-17706396685 (WhatsApp)</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Aquaculture producers, processors, importers and exporters of abalones (our own farm) and shrimps, crabs, squids, octopus, mackerel fish, hairtail, bamboo leaf fish, sardine and other frozen aquatic products. Also acts as an importer and distributor for various seafood products.</t>
+          <t>Professional supplier of frozen, fresh, dehydrated vegetables, fruit and mushroom. Also lists 'Seafood' including 'canned abalone' among its products. Engages in import and export.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Xiamen</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2374,44 +2350,44 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Xiamen, Fujian, China</t>
+          <t>No.79 Jinzhong Road, Licang District, Qingdao City, China</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Professional import and export company with strong capital strength, owned production factory (Zhangzhou Minzheng Food Co.,Ltd), 20 years farming and marketing experience. Strictly carries out 'Export food production regulations' and 'PRC food security law'.</t>
+          <t>One import and export company, five own factories and more than 15 factories in China through mutual shareholding, joint ventures. Diverse product range beyond abalone.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Explicitly states 'importers of abalones' and 'Importer, Distributor'. Their integrated approach from farming to import/export makes them a comprehensive partner.</t>
+          <t>An import and export company explicitly dealing with 'canned abalone' as part of their seafood offerings, indicating direct involvement in abalone distribution within China.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.sea-ex.com/seafood-companies/china/xiamen-binqi-import-export-co-ltd.htm</t>
+          <t>http://www.vegfoodgroup.com/contact-us.html</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Email found on Sea-Ex directory. Website not explicitly found in search results, but 'binqi-china.com' is part of the email domain.</t>
+          <t>The company lists 'canned abalone' as a product, confirming their involvement with abalone.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Halbmond Company HK</t>
+          <t>UlifeFoods</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2419,60 +2395,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>info@ulifefoods.com</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.halbmondco.com</t>
+          <t>https://www.ulifefoods.com</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Wholesaler and importer of dried seafood, including dried abalone, dried sea cucumber, fish maws, shark fins. Actively looking for high-quality dried seafood products.</t>
+          <t>IQF Abalone wholesale supplier, frozen seafood, raw abalone, cooked abalone, canned abalone, dried abalone. Specializing in research, production, and sales of frozen processed foods.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>No. 10 Xiamei Road, Meixin Village, Meihua Town, Changle District, Fuzhou City, Fujian Province, China</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Specializes in quality dry seafood products, purchases from Middle-East, Indian ocean and Africa, partners in 14 countries. Buys finest quality of dried Abalone in large volume.</t>
+          <t>Over 30 years in the industry, own breeding base and factory, HACCP, BRC, ISO, ASC, FSPCA certified. Exports to USA, Canada, South Korea, Japan, Southeast Asia. Annual production capacity of 15,000 tons of quick-frozen prepared food.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Specialized in dried abalone, actively seeking new suppliers, and has an established global purchasing network for high-quality dried seafood.</t>
+          <t>Direct wholesale supplier with extensive product range (raw, cooked, canned, dried abalone) and international export experience. Certifications indicate high quality and safety standards.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.halbmondco.com/abalone</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>https://www.ulifefoods.com/about-us.html</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>They are a manufacturer and wholesale supplier, implying distribution and import capabilities for their own products, and potentially for others given their 'wholesale supplier' designation.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>I.FISH Company Limited</t>
+          <t>Xiamen Binqi Import &amp; Export Co., Ltd</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2480,64 +2468,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://www.ifish.com.hk</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tom@binqi-china.com</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Leading seafood importer in Hong Kong. Supplies farm-raised and wild-caught abalone from South Africa. Provides a wide range of premium seafood products for Hong Kong hotels and restaurants.</t>
+          <t>Aquaculture producers, processors, importers and exporters of abalones (our own farm) and shrimps, crabs, squids, octopus, mackerel fish, hairtail, bamboo leaf fish, sardine and other frozen aquatic products. Also acts as an importer and distributor for various seafood products.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yau Tong</t>
+          <t>Xiamen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>China</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Unit D, 8/F, Wah Shun Industrial Building 4 Cho Yuen Street; Yau Tong, Hong Kong</t>
+          <t>Xiamen, Fujian, China</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Committed to sustainable practices, sources world's finest quality seafood, supplies to hotels and restaurants. Specializes in shellfish and prawns, including abalone.</t>
+          <t>Professional import and export company with strong capital strength, owned production factory (Zhangzhou Minzheng Food Co.,Ltd), 20 years farming and marketing experience. Strictly carries out 'Export food production regulations' and 'PRC food security law'.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Focus on premium quality and sustainable sourcing, strong network with hotels and restaurants in Hong Kong, and direct supply of abalone from South Africa.</t>
+          <t>Explicitly states 'importers of abalones' and 'Importer, Distributor'. Their integrated approach from farming to import/export makes them a comprehensive partner.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.ifish.com.hk/product/abalone</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>https://www.sea-ex.com/seafood-companies/china/xiamen-binqi-import-export-co-ltd.htm</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Email found on Sea-Ex directory. Website not explicitly found in search results, but 'binqi-china.com' is part of the email domain.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seabo International Limited</t>
+          <t>Xiamen Binqi Import &amp; Export Co., Ltd.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2545,53 +2537,45 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>enquiry@seabo.co</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://www.seabo.co</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Leading Hong Kong-based company in the seafood industry, importer, wholesaler. Deals with frozen abalone, frozen molluscs, frozen fish, frozen pork.</t>
+          <t>Aquaculture producers, processors, importers and exporters of abalones and other aquatic products</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Kwai Chung</t>
+          <t>Xiamen</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>116-122 Kwok Shui Road, Kwai Chung, Hong Kong</t>
-        </is>
-      </c>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Over 40 years of international reputation, global seafood network (sources from over 30 countries), offers Seabo brand line products, reliable and timely delivery.</t>
+          <t>Own abalone farm, also deals with shrimps, crabs, squids, octopus, mackerel fish, hairtail, bamboo leaf fish, sardine and other frozen aquatic products.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Established company with extensive sourcing and distribution capabilities in Hong Kong, specializing in frozen seafood including abalone.</t>
+          <t>Explicitly states 'importers and exporters of abalones' and has their own farm, indicating a significant and direct involvement in the abalone trade.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.seabo.co/contact-us</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEJOtZKlCzaIAGGaZlSlgDB6D_vFWCaTgXVHFT2wDOI9oF5VFMKRBBiS8dr_Ipop02eu-_zul8LKnH9Dp4QzghyT-O-jndM7QWwVsIfsUv_rmywjZj8Qxhke_IwWsh8tOTvfr4hP2Qcxxp7OraETEOf9vvv6Pr4gyiHbqr4AWiT</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>The company name 'Xiamen Binqi Import &amp; Export Co., Ltd.' suggests Xiamen as the city.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2601,12 +2585,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hong Kong SAR</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hai Sang Hong Marine Foodstuffs Limited</t>
+          <t>Halbmond Company HK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2617,13 +2601,13 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://hshhongkong.com/</t>
+          <t>https://www.halbmondco.com</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Importer, Wholesaler, Retailer of seafood and frozen products</t>
+          <t>Wholesaler and importer of dried seafood, including dried abalone, dried sea cucumber, fish maws, shark fins. Actively looking for high-quality dried seafood products.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2633,27 +2617,23 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Hong Kong SAR</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Physical store in the heart of the seafood district</t>
-        </is>
-      </c>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Offers a diverse selection of high-quality seafood and frozen products, including premium abalone, imported from various countries.</t>
+          <t>Specializes in quality dry seafood products, purchases from Middle-East, Indian ocean and Africa, partners in 14 countries. Buys finest quality of dried Abalone in large volume.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A long-standing company (50 years) with a strong presence in the seafood industry, acting as an importer, wholesaler, and retailer of abalone.</t>
+          <t>Specialized in dried abalone, actively seeking new suppliers, and has an established global purchasing network for high-quality dried seafood.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGh6uStIBzLzAsQPFttX2GJZLjvdVhH_j6rNKY276Ws2aWnpTeepN3EbgMK5BDoqO-GcGdJxey9ZeE9xX409tT0l8nU_OMwCKb9Vctc1_8aFZzyEGdax3nndXci66nbTGN3AdDft4iDqZWF9BH4B_whX8xfT1P2tvVG6SQ0hqAuR4bHumg_La8w==</t>
+          <t>https://www.halbmondco.com/abalone</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -2666,7 +2646,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hong Kong SAR</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2682,13 +2662,13 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://ifish.com.hk/</t>
+          <t>https://www.ifish.com.hk</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Seafood importer and supplier for hotels and restaurants</t>
+          <t>Leading seafood importer in Hong Kong. Supplies farm-raised and wild-caught abalone from South Africa. Provides a wide range of premium seafood products for Hong Kong hotels and restaurants.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2698,7 +2678,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Hong Kong SAR</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2708,44 +2688,40 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Supplies farm-raised and wild-caught abalone from South Africa, along with a wide range of premium seafood products.</t>
+          <t>Committed to sustainable practices, sources world's finest quality seafood, supplies to hotels and restaurants. Specializes in shellfish and prawns, including abalone.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Explicitly states they are a leading seafood importer in Hong Kong and supply abalone, targeting hotels and restaurants, suggesting a strong distribution network.</t>
+          <t>Focus on premium quality and sustainable sourcing, strong network with hotels and restaurants in Hong Kong, and direct supply of abalone from South Africa.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGtI-nmTK4njbRY2vG7POki0OZpPdXFRWnkI3Gz1qUh0rFzIJvfNJn9ZnDvOA6OKvciXsN8kXgc9qvoRnPpUstOg1juycMC5z2OmBS4jBc-TLkNamM5L1yX46syAg==</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Tel: +852 2775-9118, Fax: +852 2775-1118 are available on the source page but not requested in the schema.</t>
-        </is>
-      </c>
+          <t>https://www.ifish.com.hk/product/abalone</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hong Kong SAR</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wing Tai Hong Marine Products Limited</t>
+          <t>Reign Abalone Limited</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>법인</t>
+          <t>개인 에이전트</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -2753,55 +2729,59 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Importing, wholesaling, retailing and exporting of dried marine products</t>
+          <t>Distributor, Import Agent, Importer, Retailer, Service Company, Wholesaler, e-tailer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Hong Kong SAR</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Unit 25, 16/F One Island South 2 Heung Yip Rd</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Dried marine products, including abalone and scallop.</t>
+          <t>Food, Food &amp; Beverage. Major markets include Chinese Mainland, Hong Kong, Japan, Other Asian Countries, Southeast Asia.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A well-established company involved in importing and wholesaling dried abalone, indicating a direct channel for distribution.</t>
+          <t>Explicitly listed as an Importer and Import Agent for food products, with a focus on Asian markets including 'Other Asian Countries' and Southeast Asia. Handles wholesale and distribution.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGJ1L2bIzrk2yA85itKs-Ijnva2yxVj9WV1_DK8czhqTtfES3ukaA7PcRVAQPil20Pjf9_BmyMTol0b1me42dKM_pGn7L3GCecfevtyZR-V_ptb6x1ux-wy20gy3jahAAyZ_cGrx9koIh-YEkg4h0UqNkI=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHs_UrjUiksMwMku5GxaRzu55tr9QYwMAOEcYCiPw30oxyfHgK5sfZtx3UKLELi2XcP5KEObX-z-4NhJkevT2vS4xG-YSmys9Pjpm9jYheokDR6dd4xEEpy_nu20WEoxqsU1xyGWmBFAMeINwttLkZxqSt3Lk0UDmWQ-MCFduSYpN5rchLVVd9cExTaIekJrdy8</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Phone number +852 28150381 is available on the source page but not requested in the schema.</t>
+          <t>Contact person: Mr Lawrence Kuoch, CEO. Email and website not publicly available in the snippet.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bin Auf</t>
+          <t>Seabo International Limited</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2809,56 +2789,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>enquiry@seabo.co</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.seabo.co</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>인도네시아 수출업체, 수입업체, 해산물 무역업체. 제품에는 말린 해삼, 전복, 전갱이, 산호 송어, 말린 오징어, 황다랑어 등이 포함됩니다. 소량/대량 공급 가능.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Leading Hong Kong-based company in the seafood industry, importer, wholesaler. Deals with frozen abalone, frozen molluscs, frozen fish, frozen pork.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>116-122 Kwok Shui Road, Kwai Chung, Hong Kong</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 해산물 거래, 소량/대량 공급 가능.</t>
+          <t>Over 40 years of international reputation, global seafood network (sources from over 30 countries), offers Seabo brand line products, reliable and timely delivery.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>명시적으로 '수입업체' 역할을 명시, 다양한 제품 범위, 유연한 공급량.</t>
+          <t>Established company with extensive sourcing and distribution capabilities in Hong Kong, specializing in frozen seafood including abalone.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/seafood-indonesia.htm</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>스니펫에서 직접적인 웹사이트나 이메일을 찾을 수 없지만, 회사는 수입업체로 등재되어 있습니다.</t>
-        </is>
-      </c>
+          <t>https://www.seabo.co/contact-us</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CV Langgeng Sentosa Trade Indo</t>
+          <t>Fat Kee Seafood Trading Limited</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2871,59 +2863,51 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>인도네시아 동부 자바의 냉동 해산물 수출업체, 조달업체 및 가공업체. 주요 생산품은 롤리고 오징어, 전복 고기, 문어, 갑오징어, 저서어류입니다. 냉동 삶은 전복 고기 'mata 7' 재고 보유.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>East Java</t>
-        </is>
-      </c>
+          <t>Import and sell live fish and shellfish, including abalone, to Hong Kong market</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>East Java - Indonesia.</t>
-        </is>
-      </c>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>냉동 삶은 전복 고기, 즉시 선적 가능.</t>
+          <t>Imports abalone, oysters, scallops, razor clams, geoduck, whelk, etc. from Europe, New Zealand, and Japan.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>전복 고기의 직접 조달 및 가공업체, 즉시 선적 가능한 재고 보유. 주로 수출업체이지만, 조달 및 가공 역할은 국내에서 제품을 취급하며 수입을 위한 연락처가 될 수 있음을 시사합니다.</t>
+          <t>Actively imports abalone from international suppliers for the Hong Kong market.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.go4worldbusiness.com/find/products/frozen-abalone/indonesia.html</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG2I-4A0qwPc-XJEKnrDCpINcE_jzbJFptJGUxEH6iGDGw8CkGniiIXq2ZhH31a4tPQ9uPAoWgv0t2pVxiOt60B7mFixUyiADUoQ95xsh49T_gl8Z2r9aj4R4WIEAmIkVCwhQ==</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>연락 담당자 Tonny Santoso가 언급되었습니다. 스니펫에서 직접적인 이메일이나 웹사이트를 찾을 수 없습니다.</t>
+          <t>The company website is the source, but no direct email or specific contact person is immediately visible on the product page.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PT CITA KARYA AGUNG</t>
+          <t>Hai Sang Hong Marine Foodstuffs Limited</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2934,65 +2918,61 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://variouseafood.com/</t>
+          <t>https://hshhongkong.com/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>인도네시아의 선도적인 신선 및 냉동 해산물 가공업체, 공급업체 및 수출업체. 전복과 같은 냉동 복족류를 포함하여 35가지 이상의 다양한 제품을 제공합니다. 어부 및 양식 전문가로부터 조달.</t>
+          <t>Importer, Wholesaler, Retailer of seafood and frozen products</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Belawan</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Belawan, Indonesia.</t>
+          <t>Physical store in the heart of the seafood district</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>달팽이 및 전복과 같은 프리미엄 냉동 복족류, 최적의 신선도를 유지하기 위해 신중하게 가공. GMP 표준 및 HACCP 인증.</t>
+          <t>Offers a diverse selection of high-quality seafood and frozen products, including premium abalone, imported from various countries.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>확고한 가공업체 및 공급업체, 지속 가능성 및 품질에 대한 약속, 광범위한 제품. 주로 수출업체이지만, 조달 및 가공 활동은 인도네시아 내 전복 공급망에서 관련 플레이어임을 나타냅니다.</t>
+          <t>A long-standing company (50 years) with a strong presence in the seafood industry, acting as an importer, wholesaler, and retailer of abalone.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://variouseafood.com/</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>스니펫에서 직접적인 이메일을 찾을 수 없습니다.</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGh6uStIBzLzAsQPFttX2GJZLjvdVhH_j6rNKY276Ws2aWnpTeepN3EbgMK5BDoqO-GcGdJxey9ZeE9xX409tT0l8nU_OMwCKb9Vctc1_8aFZzyEGdax3nndXci66nbTGN3AdDft4iDqZWF9BH4B_whX8xfT1P2tvVG6SQ0hqAuR4bHumg_La8w==</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pesca K &amp; M Co., Ltd.</t>
+          <t>I.FISH Company Limited</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3000,76 +2980,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>pescauno@nifty.com</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
-        </is>
-      </c>
+          <t>https://ifish.com.hk/</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>표2 (HS 160557)</t>
+          <t>Seafood importer and supplier for hotels and restaurants</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Yau Tong</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
+          <t>Unit D, 8/F, Wah Shun Industrial Building 4 Cho Yuen Street; Yau Tong, Hong Kong</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
+          <t>Supplies farm-raised and wild-caught abalone from South Africa, along with a wide range of premium seafood products.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
+          <t>Explicitly states they are a leading seafood importer in Hong Kong and supply abalone, targeting hotels and restaurants, suggesting a strong distribution network.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGtI-nmTK4njbRY2vG7POki0OZpPdXFRWnkI3Gz1qUh0rFzIJvfNJn9ZnDvOA6OKvciXsN8kXgc9qvoRnPpUstOg1juycMC5z2OmBS4jBc-TLkNamM5L1yX46syAg==</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
+          <t>Tel: +852 2775-9118, Fax: +852 2775-1118 are available on the source page but not requested in the schema.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>True World Japan Inc.</t>
+          <t>I.FISH Company Limited (挪威漁業有限公司)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3078,144 +3050,128 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>Seafood importer, supplier to hotels and restaurants</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Yau Tong</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
+          <t>Unit D, 8/F, Wah Shun Industrial Building 4 Cho Yuen Street; Yau Tong, Hong Kong</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
+          <t>Supplies farm-raised and wild-caught abalone from South Africa, also other premium seafood products.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
+          <t>Clearly states they are a 'leading seafood importer in Hong Kong' and specifically mention abalone.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcRjbz-xC-RPV6RGVTJ05l2UjEbLSt8kDpDc12F0Sm1vg_-NaPC3aeUMmGHbkmat_ULk4KF4Pmf3mvVCiKGZonDGF5PdgNfk5uSior-q3l3FMbE3ozjbMMgMPW</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
+          <t>Phone numbers +852 2775-9118 (Tel), +852 2775-1118 (Fax) are available.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tsukuino Co. Ltd.</t>
+          <t>Reign Abalone Limited</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>법인</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>tukuino@heart.ocn.ne.jp</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://www.tsukuino.com/english.html</t>
-        </is>
-      </c>
+          <t>개인 에이전트</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>Distributor, Import Agent, Importer, Retailer, Wholesaler, e-tailer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Wong Chuk Hang</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
+          <t>Unit 25, 16/F One Island South 2 Heung Yip Rd Wong Chuk Hang, Hong Kong</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
+          <t>Food &amp; Beverage, specifically abalone (implied by company name and listed categories). Major Markets: Chinese Mainland, Hong Kong, Japan, Other Asian Countries, Southeast Asia.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
+          <t>Explicitly listed as an 'Import Agent' and 'Importer' for abalone, indicating active sourcing and distribution capabilities.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.tsukuino.com/english.html</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEzd9GrR1nPI2g_BsUqKMi_cf_ixpqwM72aX91ZKNb2619ovggt6mFRRnmmWbFe8_bsvbtsBWZf9KPU60GRRqiz1gmsmTf4VwDg6uJkwdQrQnLpP127YH3Fv2npu146Xshfpm2rGNLpAynAU8vlM1SnKuc4ojkyWcTbH3H_KxNTyKRf3vDChmIHJqPWcVTZdy8=</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
+          <t>Contact person Mr Lawrence Kuoch, CEO.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Harmony Marine Products Sdn. Bhd.</t>
+          <t>Wing Tai Hong Marine Products Limited</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3224,46 +3180,42 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://www.harmonymarine.com.my/</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>전복, 해삼, 어류 부레를 포함한 프리미엄 해산물 진미 공급업체. 아시아 태평양, 남미 및 아프리카에서 제품 및 재료를 조달합니다.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Importing, wholesaling, retailing and exporting of dried marine products</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>본사는 현대적인 시설(전용 건조실, 3,000평방피트 냉동고, 5,000평방피트 보관 공간)을 갖추고 있으며 HACCP 인증을 받았습니다.</t>
-        </is>
-      </c>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>프리미엄 전복, 엄격한 품질 관리, 지속 가능한 조달, 30년 이상의 경험.</t>
+          <t>Dried marine products, including abalone and scallop.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>광범위한 경험을 가진 확고한 공급업체, 국제적으로 조달, HACCP 인증.</t>
+          <t>A well-established company involved in importing and wholesaling dried abalone, indicating a direct channel for distribution.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://www.harmonymarine.com.my/abalone-supplier-malaysia</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGJ1L2bIzrk2yA85itKs-Ijnva2yxVj9WV1_DK8czhqTtfES3ukaA7PcRVAQPil20Pjf9_BmyMTol0b1me42dKM_pGn7L3GCecfevtyZR-V_ptb6x1ux-wy20gy3jahAAyZ_cGrx9koIh-YEkg4h0UqNkI=</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>주로 공급업체이지만, 다양한 지역에서 조달하는 것은 수입 활동을 의미합니다.</t>
+          <t>Phone number +852 28150381 is available on the source page but not requested in the schema.</t>
         </is>
       </c>
     </row>
@@ -3275,12 +3227,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
+          <t>Bin Auf</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3289,50 +3241,38 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://oceanpacificonline.com/</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 해산물 및 냉동 식품을 도매 및 공급합니다.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Johor Bahru</t>
-        </is>
-      </c>
+          <t>인도네시아 수출업체, 수입업체, 해산물 무역업체. 제품에는 말린 해삼, 전복, 전갱이, 산호 송어, 말린 오징어, 황다랑어 등이 포함됩니다. 소량/대량 공급 가능.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia.</t>
-        </is>
-      </c>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>전복, 조개, 게, 생선, 고기, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 공급합니다. 해산물 및 냉동 식품의 선두 공급업체입니다.</t>
+          <t>전복을 포함한 다양한 해산물 거래, 소량/대량 공급 가능.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>다양한 국내 브랜드, 지속적인 트렌드 분석, 최고의 서비스와 제품 제공에 전념.</t>
+          <t>명시적으로 '수입업체' 역할을 명시, 다양한 제품 범위, 유연한 공급량.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://oceanpacificonline.com/abalone</t>
+          <t>https://www.trade-seafood.com/seafood-indonesia.htm</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>웹사이트에 전화번호가 있습니다.</t>
+          <t>스니펫에서 직접적인 웹사이트나 이메일을 찾을 수 없지만, 회사는 수입업체로 등재되어 있습니다.</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3284,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>V Top Frozen Food Sdn Bhd</t>
+          <t>CV Langgeng Sentosa Trade Indo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3357,137 +3297,133 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Vtopff@gmail.com</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://vtopfrozenfood.com/</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
+          <t>인도네시아 동부 자바의 냉동 해산물 수출업체, 조달업체 및 가공업체. 주요 생산품은 롤리고 오징어, 전복 고기, 문어, 갑오징어, 저서어류입니다. 냉동 삶은 전복 고기 'mata 7' 재고 보유.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>East Java</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
+          <t>East Java - Indonesia.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
+          <t>냉동 삶은 전복 고기, 즉시 선적 가능.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
+          <t>전복 고기의 직접 조달 및 가공업체, 즉시 선적 가능한 재고 보유. 주로 수출업체이지만, 조달 및 가공 역할은 국내에서 제품을 취급하며 수입을 위한 연락처가 될 수 있음을 시사합니다.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://vtopfrozenfood.com/abalone-slices</t>
+          <t>https://www.go4worldbusiness.com/find/products/frozen-abalone/indonesia.html</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>웹사이트에 전화번호가 있습니다.</t>
+          <t>연락 담당자 Tonny Santoso가 언급되었습니다. 스니펫에서 직접적인 이메일이나 웹사이트를 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bajamar Trading Group</t>
+          <t>PT CITA KARYA AGUNG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>개인 에이전트</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>artavilo@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://variouseafood.com/</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Producers, exporters, importers, wholesalers and agents of various seafood products including live and canned abalone, geoduck, lobster, fish, squid, scallops, shrimp, tuna, octopus.</t>
+          <t>인도네시아의 선도적인 신선 및 냉동 해산물 가공업체, 공급업체 및 수출업체. 전복과 같은 냉동 복족류를 포함하여 35가지 이상의 다양한 제품을 제공합니다. 어부 및 양식 전문가로부터 조달.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Guerrero Negro</t>
+          <t>Belawan</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Victoria Sanchez s/n, Col. Estado 30, Guerrero Negro, Baja California Sur, 23940</t>
+          <t>Belawan, Indonesia.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Live Red Abalone, Cultured Live Red Abalone, Blue and Yellow Canned Abalone, Yellow and Blue Abalone (frozen).</t>
+          <t>달팽이 및 전복과 같은 프리미엄 냉동 복족류, 최적의 신선도를 유지하기 위해 신중하게 가공. GMP 표준 및 HACCP 인증.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Explicitly imports and distributes abalone, acts as an agent, and deals with both live and canned abalone.</t>
+          <t>확고한 가공업체 및 공급업체, 지속 가능성 및 품질에 대한 약속, 광범위한 제품. 주로 수출업체이지만, 조달 및 가공 활동은 인도네시아 내 전복 공급망에서 관련 플레이어임을 나타냅니다.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEywKxEIyVlMNjfilH11VDswQqsLbyNCU7KB_sereg0oMd6MEBpTRLhahJSb5ITplmF-lGSCyPqmzVjEvIRUUGjTD8ks23jykrR0C5IlZx-us7Uhww1TkqIWDq3d_g75TtnWphZSRfxCKtdPR7qLt6KUMo6XIBaSHqS9NjgbTEworKmrpJVnpV6fm7Igv28sf0h</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>https://variouseafood.com/</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>스니펫에서 직접적인 이메일을 찾을 수 없습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 14:58:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GlobalPezk</t>
+          <t>Pesca K &amp; M Co., Ltd.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3497,74 +3433,74 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>info@globalpezk.com</t>
+          <t>pescauno@nifty.com</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>globalpezk.com</t>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+52 (669) 980 6440 (Whatsapp for Mazatlán)</t>
+          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Import and commercialization of premium seafood and exclusive supplies for oriental cuisine from the USA, China, Japan, and Canada. Wholesale and retail with national coverage in Mexico.</t>
+          <t>표2 (HS 160557)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Blvd. Fundadores 6119 Int. 11. El Rubí, C.P 22626, Tijuana, B.C. (Also operates in Mazatlán, Los Mochis, Culiacán, Guadalajara, and Mexico City)</t>
+          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Imported premium seafood, wagyu, and oriental cuisine supplies. Products mentioned include smoked eel, hamachi fillet, soft-shell crab, masago, langostino, tiger shrimp.</t>
+          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Explicitly imports seafood from various countries and specializes in supplies for oriental cuisine, where abalone is a key product. Possesses a strong distribution network across Mexico.</t>
+          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGZAJLAMkuIRT2SJZy4_LMCS0YEHBaLEV3uNNvyo_6qjuNukemFvTb2riRNlf6Y_eb0QOnBfUKIkNRGgwPQ0HRaFdsRwduGKkx8wQ2viuu2e4n2vMcwFmNdwBlZrdWJZg==</t>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Abalone is not explicitly listed in their product examples, but their focus on imported seafood and oriental cuisine supplies makes it highly probable.</t>
+          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 14:58:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Olanda Seafood Trading Inc.</t>
+          <t>True World Japan Inc.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3572,72 +3508,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ventas@olandaseafood.com</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>www.olandaseafood.com</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Commercialization of seafood products from different parts of the world, importing and distributing fresh and frozen seafood, including shellfish. Focus on quality and freshness, and supplies for the Oriental gastronomic sector.</t>
+          <t>표1 (HS 030781)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Boulevard Tercera Oeste 17503 Int 1 Garita de Otay, Otay, Tijuana, B.C., 22430</t>
+          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Import and commercialization of seafood, including shellfish. Products mentioned include salmon, octopus, shrimp, frozen fish, frozen noodles.</t>
+          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Explicitly imports and distributes seafood. While abalone is not explicitly listed in their product snippets, 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
+          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNYFpQ3-O5BAGOJXp-8-1MXgnYuTONmz1IeuKZ8cjTcQDFTiUIliVDTOUiVv-9Pmlv-_yFfxQMX7171TKmxWaTj2u0Zkeu7QCZma2SACK8gvTa_I4BkXwS3dQs</t>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Abalone is not explicitly listed in their product snippets, but 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
+          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 14:58:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Adri &amp; Zoon Schaal- en Schelpdierenhandel B.V.</t>
+          <t>Tsukuino Co. Ltd.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3647,66 +3583,70 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>info@adrienzoon.nl</t>
+          <t>tukuino@heart.ocn.ne.jp</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.adrienzoon.com</t>
+          <t>https://www.tsukuino.com/english.html</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>전 세계 25개 어시장에서 해산물을 조달하며, 생선, 조개류, 갑각류를 수입, 수출, 도매 및 유통합니다.</t>
+          <t>표1 (HS 030781)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yerseke</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Krab 17, 4401 PA Yerseke</t>
+          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>전복 (Abalone), 아만데스/도그 코클 (Amandes/Dog Cockles), 멸치 (Anchovies), 북극 곤들매기 (Arctic char), 홍합 (Blue Mussels), 갈색 게 (Brown Crab), 대구 (Cod), 가재 (Crayfish), 굴 (Oysters), 기타 조개류 및 갑각류, 신선 수입 생선, 북해 생선, 냉동 해산물, 해초, 비식품 품목. 맞춤형 필레 및 포장 서비스를 제공합니다.</t>
+          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1983년부터 운영된 가족 기업으로, 고객, 공급업체 및 직원과의 장기적인 파트너십에 중점을 둡니다. 고품질의 맞춤형 서비스를 제공하며, 친환경 어업 방식과 전기 트레일러 사용 등 지속 가능한 관행을 추구합니다. 자체 운송 차량을 통해 전 세계로 배송합니다.</t>
+          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://www.adrienzoon.com/contact</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>https://www.tsukuino.com/english.html</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Starco Foodstuff</t>
+          <t>Harmony Marine Products Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3717,65 +3657,61 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
+          <t>https://www.harmonymarine.com.my/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>냉동 전복 조개류를 포함한 다양한 제품의 공급업체 및 수출업체입니다. 보리, 목재 펠릿, 새우, 복사 용지, 금속 등도 취급합니다.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Heerlen</t>
-        </is>
-      </c>
+          <t>전복, 해삼, 어류 부레를 포함한 프리미엄 해산물 진미 공급업체. 아시아 태평양, 남미 및 아프리카에서 제품 및 재료를 조달합니다.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Hoofdstraat 208, Hoensbroek</t>
+          <t>본사는 현대적인 시설(전용 건조실, 3,000평방피트 냉동고, 5,000평방피트 보관 공간)을 갖추고 있으며 HACCP 인증을 받았습니다.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>냉동 전복 조개류 (Frozen Abalone Shellfish), 보리 (Barley), 목재 펠릿 (Wood Pellets), 새우 (Shrimps), 복사 용지 (Copy Paper), 폐철 (Used Rail Scrap), 구리 음극 (Copper Cathode), 아몬드 (Almond Nuts), 알루미늄 잉곳 (Aluminium Ingots), 냉동 닭고기 (Frozen Chicken), 양고기 (Lamb/Mutton Meat).</t>
+          <t>프리미엄 전복, 엄격한 품질 관리, 지속 가능한 조달, 30년 이상의 경험.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>B2B 플랫폼인 Tradewheel.com에 냉동 전복 조개류 공급업체로 등록되어 있습니다. 2019년에 설립되었습니다. 매우 다양한 제품군을 취급하는 일반 무역 회사일 수 있습니다.</t>
+          <t>광범위한 경험을 가진 확고한 공급업체, 국제적으로 조달, HACCP 인증.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
+          <t>https://www.harmonymarine.com.my/abalone-supplier-malaysia</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>이메일 주소는 Tradewheel.com 프로필에 직접 공개되어 있지 않습니다.</t>
+          <t>주로 공급업체이지만, 다양한 지역에서 조달하는 것은 수입 활동을 의미합니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kiwi Fish</t>
+          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3786,65 +3722,65 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://kiwifish.co.nz</t>
+          <t>https://oceanpacificonline.com/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Premium seafood wholesaler, supplying an extensive range of live, chilled, and frozen shellfish, including pāua (abalone), to various markets including superyachts.</t>
+          <t>전복을 포함한 다양한 해산물 및 냉동 식품을 도매 및 공급합니다.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Central Auckland</t>
+          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Offers the best of New Zealand's sustainably caught seafood harvest, custom processed and delivered. Operates a Risk Management Programme (RMP) approved and audited by the Ministry for Primary Industries (MPI).</t>
+          <t>전복, 조개, 게, 생선, 고기, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 공급합니다. 해산물 및 냉동 식품의 선두 공급업체입니다.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Established premium seafood wholesaler with a wide range of products and strong quality control, suggesting capability for distributing abalone within New Zealand.</t>
+          <t>다양한 국내 브랜드, 지속적인 트렌드 분석, 최고의 서비스와 제품 제공에 전념.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQET8rm6pD2fyT7blQHzUlDu1ArhqNzw8L5XOkDHPt6BbyoKTCVauxe6Oxsjy7ctVUvrR8vDBXtaw4VbGut7tDCnC3Pj4-1Xvaq0HCMnqW3hIuF82K8ePbg==</t>
+          <t>https://oceanpacificonline.com/abalone</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Distributes New Zealand-sourced abalone (pāua).</t>
+          <t>웹사이트에 전화번호가 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Waters Marine Limited</t>
+          <t>V Top Frozen Food Sdn Bhd</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3854,128 +3790,120 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>hello@northernwaters.co.nz</t>
+          <t>Vtopff@gmail.com</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://northernwaters.co.nz</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Facebook, TikTok, Instagram</t>
-        </is>
-      </c>
+          <t>https://vtopfrozenfood.com/</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sells whole pāua (abalone) for wholesale and retail.</t>
+          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Warkworth</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>182 State Highway 1, Warkworth 0981, New Zealand (AUK Dome Valley)</t>
+          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Sustainably harvested whole pāua (abalone) from the waters of Wairarapa and the South Island, offering authentic New Zealand flavor. Available for pickup or delivery.</t>
+          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Direct supplier and wholesaler of whole abalone, with clear contact information and a focus on sustainably harvested local product for the New Zealand market.</t>
+          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUTHdE_OizUFY_wnDheiVjs5gz8f6C2bi2M-kQnU8AHGUWDyfJfhJEeNJt5ZarxJzqydgApFymnTwOlFD3rW2VhMd-tPSVGo3JAsYEGcp40Nc3oTgS5tR5neHphsqorpRO59dq267d84rNGLqV6wH6d8HO7QE==</t>
+          <t>https://vtopfrozenfood.com/abalone-slices</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Distributes New Zealand-sourced abalone (pāua).</t>
+          <t>웹사이트에 전화번호가 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sunz Seafood</t>
+          <t>Bajamar Trading Group</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>법인</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://sunzseafood.co.nz</t>
-        </is>
-      </c>
+          <t>개인 에이전트</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>artavilo@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Wholesale and foodservice distribution of New Zealand minced pāua (abalone).</t>
+          <t>Producers, exporters, importers, wholesalers and agents of various seafood products including live and canned abalone, geoduck, lobster, fish, squid, scallops, shrimp, tuna, octopus.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Whitianga</t>
+          <t>Guerrero Negro</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>269 South Highway West Whitianga 3510</t>
+          <t>Victoria Sanchez s/n, Col. Estado 30, Guerrero Negro, Baja California Sur, 23940</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Premium New Zealand minced pāua (abalone), wild-caught and hand-harvested from Wairarapa and South Island, processed to export standards and frozen fresh. Offers meat-only pāua, ideal for patties, fritters, and commercial kitchen use.</t>
+          <t>Live Red Abalone, Cultured Live Red Abalone, Blue and Yellow Canned Abalone, Yellow and Blue Abalone (frozen).</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Established wholesaler and foodservice supplier of abalone meat within New Zealand, indicating a strong distribution network for locally sourced product.</t>
+          <t>Explicitly imports and distributes abalone, acts as an agent, and deals with both live and canned abalone.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6XLTPVgpag7xKK9QzbM_253BrUulevcWOCSV-khxpvqieFX7K7bO3HslNSPhfSIJySeYWXSDhgResGgoCJy1BNk6USQXQpWs7QU9S16CwXnw3H-JmFBse6B2Q6YReNBZXV8pjWQbq-KKVPcA-Zat9UCHvP7N6mtg50x-AO6e4Da1VnfLE</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Primarily distributes New Zealand-sourced abalone (pāua).</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEywKxEIyVlMNjfilH11VDswQqsLbyNCU7KB_sereg0oMd6MEBpTRLhahJSb5ITplmF-lGSCyPqmzVjEvIRUUGjTD8ks23jykrR0C5IlZx-us7Uhww1TkqIWDq3d_g75TtnWphZSRfxCKtdPR7qLt6KUMo6XIBaSHqS9NjgbTEworKmrpJVnpV6fm7Igv28sf0h</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3985,12 +3913,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FoodPhil Corporation</t>
+          <t>GlobalPezk</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3998,45 +3926,61 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>info@globalpezk.com</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://foodphil.com/</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>globalpezk.com</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>+52 (669) 980 6440 (Whatsapp for Mazatlán)</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Frozen and fresh seafood, including abalone, scallop, shrimps, lobsters, crabs, crablets, crabmeat.</t>
+          <t>Import and commercialization of premium seafood and exclusive supplies for oriental cuisine from the USA, China, Japan, and Canada. Wholesale and retail with national coverage in Mexico.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Blvd. Fundadores 6119 Int. 11. El Rubí, C.P 22626, Tijuana, B.C. (Also operates in Mazatlán, Los Mochis, Culiacán, Guadalajara, and Mexico City)</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Proven trader of frozen and fresh seafood, supplying to several restaurants, distributors, and malls around the Philippines.</t>
+          <t>Imported premium seafood, wagyu, and oriental cuisine supplies. Products mentioned include smoked eel, hamachi fillet, soft-shell crab, masago, langostino, tiger shrimp.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Established in 2007, they are a reliable supplier of frozen and fresh seafood to hotels, restaurants, and retailers.</t>
+          <t>Explicitly imports seafood from various countries and specializes in supplies for oriental cuisine, where abalone is a key product. Possesses a strong distribution network across Mexico.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://foodphil.com/</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGZAJLAMkuIRT2SJZy4_LMCS0YEHBaLEV3uNNvyo_6qjuNukemFvTb2riRNlf6Y_eb0QOnBfUKIkNRGgwPQ0HRaFdsRwduGKkx8wQ2viuu2e4n2vMcwFmNdwBlZrdWJZg==</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Abalone is not explicitly listed in their product examples, but their focus on imported seafood and oriental cuisine supplies makes it highly probable.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4046,12 +3990,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pancoastal International</t>
+          <t>Olanda Seafood Trading Inc.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4059,47 +4003,55 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ventas@olandaseafood.com</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://pancoastal.com/</t>
+          <t>www.olandaseafood.com</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Importation, distribution, wholesale, and retail of premium frozen seafood. Product range includes Atlantic Salmon, Coho Salmon, Barramundi, Pompano, Chilean Seabass, Tuna.</t>
+          <t>Commercialization of seafood products from different parts of the world, importing and distributing fresh and frozen seafood, including shellfish. Focus on quality and freshness, and supplies for the Oriental gastronomic sector.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Metro Manila</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Boulevard Tercera Oeste 17503 Int 1 Garita de Otay, Otay, Tijuana, B.C., 22430</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Specializes in premium frozen seafood, sourcing globally from Canada, Chile, Norway, EU, China, Vietnam, and USA. Serves restaurants, hotels, supermarkets, wholesalers, and retailers.</t>
+          <t>Import and commercialization of seafood, including shellfish. Products mentioned include salmon, octopus, shrimp, frozen fish, frozen noodles.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Dedicated to offering a diverse range of top-quality imported seafood and leading the market in high-quality seafood distribution.</t>
+          <t>Explicitly imports and distributes seafood. While abalone is not explicitly listed in their product snippets, 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://pancoastal.com/</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNYFpQ3-O5BAGOJXp-8-1MXgnYuTONmz1IeuKZ8cjTcQDFTiUIliVDTOUiVv-9Pmlv-_yFfxQMX7171TKmxWaTj2u0Zkeu7QCZma2SACK8gvTa_I4BkXwS3dQs</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Abalone is not explicitly listed in their product examples, but their general scope as a 'premium frozen seafood importer' and distributor makes them a strong potential partner for abalone. Contact details like email/LinkedIn/messenger not explicitly listed on the homepage, but a 'Contact' page is available on their website.</t>
+          <t>Abalone is not explicitly listed in their product snippets, but 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
         </is>
       </c>
     </row>
@@ -4111,12 +4063,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TC International Seafoods Provider Inc.</t>
+          <t>Adri &amp; Zoon Schaal- en Schelpdierenhandel B.V.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4124,41 +4076,53 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>info@adrienzoon.nl</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.adrienzoon.com</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Manufacturing, import and export of Fresh Frozen Marine products, including Frozen Boiled Abalone Meat.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>전 세계 25개 어시장에서 해산물을 조달하며, 생선, 조개류, 갑각류를 수입, 수출, 도매 및 유통합니다.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Yerseke</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Krab 17, 4401 PA Yerseke</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Actively trading in Taiwan, China, Hong Kong, Vietnam, USA and Canada.</t>
+          <t>전복 (Abalone), 아만데스/도그 코클 (Amandes/Dog Cockles), 멸치 (Anchovies), 북극 곤들매기 (Arctic char), 홍합 (Blue Mussels), 갈색 게 (Brown Crab), 대구 (Cod), 가재 (Crayfish), 굴 (Oysters), 기타 조개류 및 갑각류, 신선 수입 생선, 북해 생선, 냉동 해산물, 해초, 비식품 품목. 맞춤형 필레 및 포장 서비스를 제공합니다.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Engaged in both import and export of fresh frozen marine products, indicating a strong supply chain and market presence.</t>
+          <t>1983년부터 운영된 가족 기업으로, 고객, 공급업체 및 직원과의 장기적인 파트너십에 중점을 둡니다. 고품질의 맞춤형 서비스를 제공하며, 친환경 어업 방식과 전기 트레일러 사용 등 지속 가능한 관행을 추구합니다. 자체 운송 차량을 통해 전 세계로 배송합니다.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHuXKC2Pza8RjFQF46dD1k1qjUsZOZYpuhqP_IeQ9NAgxgU5WN--XiuJAdSYdV639ettOP0E8pmoUv3ePW26aNr17kXVLhBdJmbwcr7SiA7-K-5MOvza_DQsawn51Im7X9ksC7MtyPAsNMpSMlBQfligeiYlwfRTvQbojapfK_uRtBC</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Specific city within the Philippines not found in the provided snippets. Contact details like email/website not explicitly listed in the search results.</t>
-        </is>
-      </c>
+          <t>https://www.adrienzoon.com/contact</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4168,12 +4132,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>㈜제이에스코리아</t>
+          <t>Starco Foodstuff</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4184,65 +4148,65 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>js-korea.com</t>
+          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>전복, 굴 등 어패류 가공 및 수출 전문. 활어, 냉동, 통조림 등 다양한 형태로 가공하여 홍콩, 싱가포르, 베트남, 캐나다 등 세계 각지에 수출.</t>
+          <t>냉동 전복 조개류를 포함한 다양한 제품의 공급업체 및 수출업체입니다. 보리, 목재 펠릿, 새우, 복사 용지, 금속 등도 취급합니다.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>완도</t>
+          <t>Heerlen</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>완도에 본사 및 식품 가공 공장 위치.</t>
+          <t>Hoofdstraat 208, Hoensbroek</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>전복 가공식품 (통조림, 소스, 죽, 장 등), 굴 가공식품, 해외 수출. K·FISH 인증 보유.</t>
+          <t>냉동 전복 조개류 (Frozen Abalone Shellfish), 보리 (Barley), 목재 펠릿 (Wood Pellets), 새우 (Shrimps), 복사 용지 (Copy Paper), 폐철 (Used Rail Scrap), 구리 음극 (Copper Cathode), 아몬드 (Almond Nuts), 알루미늄 잉곳 (Aluminium Ingots), 냉동 닭고기 (Frozen Chicken), 양고기 (Lamb/Mutton Meat).</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>전복 가공 기술 및 수출 노하우가 뛰어나며, K·FISH 인증을 통해 품질 안정성을 확보하고 다양한 가공 제품으로 해외 시장에 진출하고 있습니다.</t>
+          <t>B2B 플랫폼인 Tradewheel.com에 냉동 전복 조개류 공급업체로 등록되어 있습니다. 2019년에 설립되었습니다. 매우 다양한 제품군을 취급하는 일반 무역 회사일 수 있습니다.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvnf2Abv7NqaI1pbEBcXg5_-hi89lZ5556iuwdFyRctwjXwyaEYhM901eVExey6vZHCLG2nr3C1Ds3UgxRZBC2l7XMO0V9Hwe2dSiv9Eiln8VAsVxufluTjNuYHTksoBQK1LF7NASp5z_cPjB03gfmajsqvetdJ_MZQMDDQHE_kel2J0KkBfswaCR-M4EiTiX4uJYtFdg5QL47Zt8rQ4DJ7Hke9DdDqsWHLKoplDUi9hbzGTMsS37FIrEp1_O71yNFk4e8cwEwaSAIU9C-xfFqHRF_cTbnsDkL515JE3vwHY6A2yA36BPJZHGFFp1QPwcNMRBp7ltExYN9-pcsBO_T3RPaRjmUxAKC0G3FnWNyoXPT7et58evQA0Rcp1h2iJK22EkfH4CpCY1dkQuXFfkbgr6h6KCIA==</t>
+          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+          <t>이메일 주소는 Tradewheel.com 프로필에 직접 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>㈜청산바다</t>
+          <t>Kiwi Fish</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4253,65 +4217,65 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>cheongsanbada.com</t>
+          <t>https://kiwifish.co.nz</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>전복 생산, 유통, 수출, 가공, 판매를 원스톱으로 진행하는 생산자 조합 회사. 일본, 홍콩, 유럽, 미국 등 해외 수출 및 국내 최고급 호텔, 백화점 거래.</t>
+          <t>Premium seafood wholesaler, supplying an extensive range of live, chilled, and frozen shellfish, including pāua (abalone), to various markets including superyachts.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>완도</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>전남 완도군 완도읍 농공단지4길 22-7</t>
+          <t>Central Auckland</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>활전복, 전복 가공식품, 아시아 최초 ASC 인증 보유.</t>
+          <t>Offers the best of New Zealand's sustainably caught seafood harvest, custom processed and delivered. Operates a Risk Management Programme (RMP) approved and audited by the Ministry for Primary Industries (MPI).</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>전복 생산부터 수출까지 전 과정을 직접 관리하며, 아시아 최초 ASC 인증을 통해 품질과 지속가능성을 인정받았습니다. 해외 시장에 대한 높은 이해도와 유통망을 보유하고 있습니다.</t>
+          <t>Established premium seafood wholesaler with a wide range of products and strong quality control, suggesting capability for distributing abalone within New Zealand.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVkzRFigxKCfhziKW_fKDfhJoYijxhubjB5tnFMmsV-sW4Hy7O47UY7PSizNwgsH9ltf3nlA7J_PcfmA2VN8TcatJD25HrYqVUA4eEVj5_as7jOPqqp9X38PI99eMFTx96G1kBBqatrgJmAqFLEwSfcCW_l6aPl4a7ueV0NkLYLdFEZltKfZAJ0nJdrlEcxLNzCY4xx-4CVxPPNRSUu8OA6l9jflRKq5crSvp4aoZzg8LOXK_2P7byIJdl-QxIVlAA5QWCiUfuaUts400REyvusr10ZahsNebaiZTaok3EDYrSY0J10Sq-yuiN34IlTHLWVfNEWYCVxkzX4Ix3EAkZWzRvYeJkFLlH3lZi7Po_Ul7QhAwasnpX0fHZVEtJ</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQET8rm6pD2fyT7blQHzUlDu1ArhqNzw8L5XOkDHPt6BbyoKTCVauxe6Oxsjy7ctVUvrR8vDBXtaw4VbGut7tDCnC3Pj4-1Xvaq0HCMnqW3hIuF82K8ePbg==</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>고객센터 전화번호는 061-553-5900이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+          <t>Distributes New Zealand-sourced abalone (pāua).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>완도전복주식회사</t>
+          <t>Northern Waters Marine Limited</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4319,68 +4283,76 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>hello@northernwaters.co.nz</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>wakorea.kr</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>https://northernwaters.co.nz</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Facebook, TikTok, Instagram</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>국내외 기업 및 개인 고객을 대상으로 활전복 및 가공전복 공급, 국내 최대 활전복 유통 및 가공전복 제품 생산, 롯데마트, 이마트, CJ프레시웨이 등 주요 거래처, 일본, 미국, 싱가포르 등 동남아 지역 수출.</t>
+          <t>Sells whole pāua (abalone) for wholesale and retail.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>완도</t>
+          <t>Warkworth</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>전라남도 완도군</t>
+          <t>182 State Highway 1, Warkworth 0981, New Zealand (AUK Dome Valley)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>활전복, 가공전복 (통조림, 동결제품), 국내 대형 유통망 공급, 해외 수출.</t>
+          <t>Sustainably harvested whole pāua (abalone) from the waters of Wairarapa and the South Island, offering authentic New Zealand flavor. Available for pickup or delivery.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>생산 어민과 완도군이 공동 출자하여 설립된 국내 최대 전복 전문 기업으로, 안정적인 공급망과 광범위한 국내외 유통망을 보유하고 있습니다.</t>
+          <t>Direct supplier and wholesaler of whole abalone, with clear contact information and a focus on sustainably harvested local product for the New Zealand market.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVUzQYPzka2YSdvtxrcdlEwnD9kMLBlEc0nUobdRmu7Sh6VCkqAI7XZdkeOmLwU4iXbob_FjOZxeI7_jSshQFyj4k2SrvUPYNeiS2umO4l</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUTHdE_OizUFY_wnDheiVjs5gz8f6C2bi2M-kQnU8AHGUWDyfJfhJEeNJt5ZarxJzqydgApFymnTwOlFD3rW2VhMd-tPSVGo3JAsYEGcp40Nc3oTgS5tR5neHphsqorpRO59dq267d84rNGLqV6wH6d8HO7QE==</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>고객센터 전화번호는 1577-8855이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+          <t>Distributes New Zealand-sourced abalone (pāua).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dakar Ice</t>
+          <t>Sunz Seafood</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4388,72 +4360,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>contact@dakarice.com</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>http://www.dakarice.com</t>
+          <t>https://sunzseafood.co.nz</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>수입/유통 (Import/Distribution)</t>
+          <t>Wholesale and foodservice distribution of New Zealand minced pāua (abalone).</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>Whitianga</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Hann plage, au km 5 boulevard de la commune de Dakar</t>
+          <t>269 South Highway West Whitianga 3510</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>다양한 어류 취급, 특히 전복(abalone)을 월 최소 1컨테이너 처리 가능.</t>
+          <t>Premium New Zealand minced pāua (abalone), wild-caught and hand-harvested from Wairarapa and South Island, processed to export standards and frozen fresh. Offers meat-only pāua, ideal for patties, fritters, and commercial kitchen use.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>전복(abalone)을 월 최소 1컨테이너 규모로 취급하며, 수산물 전반에 대한 경험이 풍부하여 협력 가능성이 높습니다.</t>
+          <t>Established wholesaler and foodservice supplier of abalone meat within New Zealand, indicating a strong distribution network for locally sourced product.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHyVlKRmRztQxojYk66kNXGxJrx8_JI93Lx6e0cD3eq6iNIdAXKWbzug3ERNopXTxQ4Xu-KFj5Nf0dusDVD1ygDla4N1Jmpqe5_Hq1joE8XvJ2ZD6iyhMQbnLgAWb_WAVShMpUIkg==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6XLTPVgpag7xKK9QzbM_253BrUulevcWOCSV-khxpvqieFX7K7bO3HslNSPhfSIJySeYWXSDhgResGgoCJy1BNk6USQXQpWs7QU9S16CwXnw3H-JmFBse6B2Q6YReNBZXV8pjWQbq-KKVPcA-Zat9UCHvP7N6mtg50x-AO6e4Da1VnfLE</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Fijin.com에 'Dakar Ice'가 전복을 취급하며 월 최소 1컨테이너를 처리할 수 있다고 명시되어 있습니다. 공식 웹사이트는 검색 결과에서 직접 확인되지 않았으나, 이메일 주소를 통해 도메인을 추정했습니다.</t>
+          <t>Primarily distributes New Zealand-sourced abalone (pāua).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Goh Joo Hin Pte Ltd</t>
+          <t>FoodPhil Corporation</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4461,72 +4429,60 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>food@gjh.com.sg</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>http://www.gjh.com.sg</t>
+          <t>https://foodphil.com/</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Wholesaler, Distributor</t>
+          <t>Frozen and fresh seafood, including abalone, scallop, shrimps, lobsters, crabs, crablets, crabmeat.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
-        </is>
-      </c>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
+          <t>Proven trader of frozen and fresh seafood, supplying to several restaurants, distributors, and malls around the Philippines.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
+          <t>Established in 2007, they are a reliable supplier of frozen and fresh seafood to hotels, restaurants, and retailers.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
-        </is>
-      </c>
+          <t>https://foodphil.com/</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oceanus Group Limited</t>
+          <t>Pancoastal International</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4534,72 +4490,64 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>contact@oceanus.com.sg</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>http://www.oceanus.com.sg</t>
+          <t>https://pancoastal.com/</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
+          <t>Importation, distribution, wholesale, and retail of premium frozen seafood. Product range includes Atlantic Salmon, Coho Salmon, Barramundi, Pompano, Chilean Seabass, Tuna.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Metro Manila</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
-        </is>
-      </c>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
+          <t>Specializes in premium frozen seafood, sourcing globally from Canada, Chile, Norway, EU, China, Vietnam, and USA. Serves restaurants, hotels, supermarkets, wholesalers, and retailers.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
+          <t>Dedicated to offering a diverse range of top-quality imported seafood and leading the market in high-quality seafood distribution.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
+          <t>https://pancoastal.com/</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
+          <t>Abalone is not explicitly listed in their product examples, but their general scope as a 'premium frozen seafood importer' and distributor makes them a strong potential partner for abalone. Contact details like email/LinkedIn/messenger not explicitly listed on the homepage, but a 'Contact' page is available on their website.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Teck Sang Pte Ltd</t>
+          <t>TC International Seafoods Provider Inc.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4607,55 +4555,39 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>local@tecksang.com</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>https://www.tecksang.com</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
+          <t>Manufacturing, import and export of Fresh Frozen Marine products, including Frozen Boiled Abalone Meat.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>11 Hongkong Street, Singapore 059654</t>
-        </is>
-      </c>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
+          <t>Actively trading in Taiwan, China, Hong Kong, Vietnam, USA and Canada.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
+          <t>Engaged in both import and export of fresh frozen marine products, indicating a strong supply chain and market presence.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHuXKC2Pza8RjFQF46dD1k1qjUsZOZYpuhqP_IeQ9NAgxgU5WN--XiuJAdSYdV639ettOP0E8pmoUv3ePW26aNr17kXVLhBdJmbwcr7SiA7-K-5MOvza_DQsawn51Im7X9ksC7MtyPAsNMpSMlBQfligeiYlwfRTvQbojapfK_uRtBC</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
+          <t>Specific city within the Philippines not found in the provided snippets. Contact details like email/website not explicitly listed in the search results.</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4599,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlantis Foods</t>
+          <t>㈜제이에스코리아</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4680,55 +4612,51 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>info@atlantisfoods.co.za</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.atlantisfoods.co.za/</t>
+          <t>js-korea.com</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>South Africa의 주요 해산물 유통 회사 중 하나로, 도매업체, 식품 서비스 제공업체 및 소매업체에 고품질 해산물 제품을 소싱, 가공 및 유통합니다. 과거 전무이사가 전복(Abalone) 및 냉장 보관을 담당했습니다.</t>
+          <t>전복, 굴 등 어패류 가공 및 수출 전문. 활어, 냉동, 통조림 등 다양한 형태로 가공하여 홍콩, 싱가포르, 베트남, 캐나다 등 세계 각지에 수출.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>완도</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8 Wessex Road Paarden Eiland Cape Town, South Africa, 7405 (Sales &amp; Marketing Office)</t>
+          <t>완도에 본사 및 식품 가공 공장 위치.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>다양한 신선, 냉동, 부가가치 및 즉석 해산물 제품을 취급하며, 전복을 포함한 해산물 유통 경험이 있습니다.</t>
+          <t>전복 가공식품 (통조림, 소스, 죽, 장 등), 굴 가공식품, 해외 수출. K·FISH 인증 보유.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>남아프리카 공화국 내에서 광범위한 유통망을 가진 대규모 해산물 유통업체로, 다양한 채널에 대량 공급이 가능합니다.</t>
+          <t>전복 가공 기술 및 수출 노하우가 뛰어나며, K·FISH 인증을 통해 품질 안정성을 확보하고 다양한 가공 제품으로 해외 시장에 진출하고 있습니다.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://www.atlantisfoods.co.za/contact-us/</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvnf2Abv7NqaI1pbEBcXg5_-hi89lZ5556iuwdFyRctwjXwyaEYhM901eVExey6vZHCLG2nr3C1Ds3UgxRZBC2l7XMO0V9Hwe2dSiv9Eiln8VAsVxufluTjNuYHTksoBQK1LF7NASp5z_cPjB03gfmajsqvetdJ_MZQMDDQHE_kel2J0KkBfswaCR-M4EiTiX4uJYtFdg5QL47Zt8rQ4DJ7Hke9DdDqsWHLKoplDUi9hbzGTMsS37FIrEp1_O71yNFk4e8cwEwaSAIU9C-xfFqHRF_cTbnsDkL515JE3vwHY6A2yA36BPJZHGFFp1QPwcNMRBp7ltExYN9-pcsBO_T3RPaRjmUxAKC0G3FnWNyoXPT7et58evQA0Rcp1h2iJK22EkfH4CpCY1dkQuXFfkbgr6h6KCIA==</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>BestFoodImporters.com에 따르면 'Importer, Distributor, Wholesaler, Supplier'로 분류됩니다. 이전 그룹 물류 관리자가 전복을 담당했다는 언급이 있습니다.</t>
+          <t>이메일은 웹사이트에 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4668,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Greenfish</t>
+          <t>㈜청산바다</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4753,59 +4681,51 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>ops@greenfish.co.za, Sales1@greenfish.co.za</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://greenfish.co.za/</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>063 666 2802 (Whatsapp)</t>
-        </is>
-      </c>
+          <t>cheongsanbada.com</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>온라인 및 도매 해산물 공급업체로, 양식 전복(perlemoen)을 포함한 신선한 해산물을 취급합니다.</t>
+          <t>전복 생산, 유통, 수출, 가공, 판매를 원스톱으로 진행하는 생산자 조합 회사. 일본, 홍콩, 유럽, 미국 등 해외 수출 및 국내 최고급 호텔, 백화점 거래.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>완도</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>온라인 전용 (소매점 없음), Cape Town 및 주변 지역(CBD, Southern Suburbs, Houtbay, Plattekloof, Deep South, Table View, Blouberg, Melkbos, Durbanville, Stellenbosch, Somerset West, Franschhoek, Paarl) 배송 가능.</t>
+          <t>전남 완도군 완도읍 농공단지4길 22-7</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>6개들이 라이브 양식 전복(perlemoen)을 판매하며, 노르웨이산 연어, 대구, 참치, 킹클립, 홍합, 굴, 옐로우테일, 카벨조우 등 다양한 신선 해산물을 제공합니다.</t>
+          <t>활전복, 전복 가공식품, 아시아 최초 ASC 인증 보유.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>양식 전복을 직접 공급하며, 개인 소비자 및 도매 고객 모두에게 서비스를 제공합니다. 소규모 또는 전문적인 주문, 레스토랑 직거래에 적합합니다.</t>
+          <t>전복 생산부터 수출까지 전 과정을 직접 관리하며, 아시아 최초 ASC 인증을 통해 품질과 지속가능성을 인정받았습니다. 해외 시장에 대한 높은 이해도와 유통망을 보유하고 있습니다.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://greenfish.co.za/products/abalone-perlemoen-live-box-cultivated-x6</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVkzRFigxKCfhziKW_fKDfhJoYijxhubjB5tnFMmsV-sW4Hy7O47UY7PSizNwgsH9ltf3nlA7J_PcfmA2VN8TcatJD25HrYqVUA4eEVj5_as7jOPqqp9X38PI99eMFTx96G1kBBqatrgJmAqFLEwSfcCW_l6aPl4a7ueV0NkLYLdFEZltKfZAJ0nJdrlEcxLNzCY4xx-4CVxPPNRSUu8OA6l9jflRKq5crSvp4aoZzg8LOXK_2P7byIJdl-QxIVlAA5QWCiUfuaUts400REyvusr10ZahsNebaiZTaok3EDYrSY0J10Sq-yuiN34IlTHLWVfNEWYCVxkzX4Ix3EAkZWzRvYeJkFLlH3lZi7Po_Ul7QhAwasnpX0fHZVEtJ</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>온라인 전용 업체이며, 소매점은 없습니다.</t>
+          <t>고객센터 전화번호는 061-553-5900이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -4817,12 +4737,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FRESHCADO RECIEN PESCADO SL</t>
+          <t>완도전복주식회사</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4830,53 +4750,53 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>contact@freshcado.es</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://freshcado.es</t>
+          <t>wakorea.kr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Wholesale and retail of fresh and frozen fish and seafood, including premium seafood. Operates as an online fishmonger and supplies professionals across Spain, sourcing from Mercamadrid and international ports.</t>
+          <t>국내외 기업 및 개인 고객을 대상으로 활전복 및 가공전복 공급, 국내 최대 활전복 유통 및 가공전복 제품 생산, 롯데마트, 이마트, CJ프레시웨이 등 주요 거래처, 일본, 미국, 싱가포르 등 동남아 지역 수출.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>완도</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>C/ de la Diputació, 256, 08007 Barcelona</t>
+          <t>전라남도 완도군</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Offers a wide selection of fresh and frozen seafood. Emphasizes maximum freshness, direct product from Mercamadrid, and 24/48h delivery. Committed to sustainability and responsible fishing.</t>
+          <t>활전복, 가공전복 (통조림, 동결제품), 국내 대형 유통망 공급, 해외 수출.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>As a large seafood wholesaler and online retailer with a wide range of fresh and frozen seafood, including a 'Premium Seafood' category, Freshcado is a strong prospect for importing and distributing abalone.</t>
+          <t>생산 어민과 완도군이 공동 출자하여 설립된 국내 최대 전복 전문 기업으로, 안정적인 공급망과 광범위한 국내외 유통망을 보유하고 있습니다.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://freshcado.es/legal-notice/, https://freshcado.es/accessibility-statement/, https://freshcado.es/general-terms-and-conditions/, https://freshcado.es/en/fish-and-seafood-wholesaler-in-spain/, https://freshcado.es/en/online-fishmonger-buy-fresh-fish-and-seafood/, https://freshcado.es/en/comprar-smoked-and-canned-products-online/</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVUzQYPzka2YSdvtxrcdlEwnD9kMLBlEc0nUobdRmu7Sh6VCkqAI7XZdkeOmLwU4iXbob_FjOZxeI7_jSshQFyj4k2SrvUPYNeiS2umO4l</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>고객센터 전화번호는 1577-8855이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4886,12 +4806,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Globalimar Europa, SL</t>
+          <t>Dakar Ice</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4901,66 +4821,70 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>info@globalimar.com</t>
+          <t>contact@dakarice.com</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.globalimar.com</t>
+          <t>http://www.dakarice.com</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Frozen seafood import, production, and commercialization for mass-market, including bivalves, cephalopods, crustaceans, surimi, and prepared fish. Serves Spain, Europe, USA, and Maghreb region.</t>
+          <t>수입/유통 (Import/Distribution)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Llagostera</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>C/ Jaume I, 2A, 17240 Llagostera, Girona</t>
+          <t>Hann plage, au km 5 boulevard de la commune de Dakar</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Specialists in frozen seafood products, with a focus on quality and sustainability. Offers a diversified range of frozen seafood. Explicitly states import and commercialization activities.</t>
+          <t>다양한 어류 취급, 특히 전복(abalone)을 월 최소 1컨테이너 처리 가능.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Explicitly states 'import, produce and commercialize' frozen seafood. Their broad range of seafood products, including bivalves, makes them a highly probable candidate for importing abalone.</t>
+          <t>전복(abalone)을 월 최소 1컨테이너 규모로 취급하며, 수산물 전반에 대한 경험이 풍부하여 협력 가능성이 높습니다.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://www.globalimar.com/contact/, https://www.conxemar.com/en/asociados/globalimar-europa-sl, https://www.conxemar.com/en/exhibitor/globalimar-europa-sl-conxemar-2024, https://www.globalimar.com/en/company/specialists-in-frozen-seafood/, https://www.bestfoodimporters.com/importer/globalimar-europa</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHyVlKRmRztQxojYk66kNXGxJrx8_JI93Lx6e0cD3eq6iNIdAXKWbzug3ERNopXTxQ4Xu-KFj5Nf0dusDVD1ygDla4N1Jmpqe5_Hq1joE8XvJ2ZD6iyhMQbnLgAWb_WAVShMpUIkg==</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Fijin.com에 'Dakar Ice'가 전복을 취급하며 월 최소 1컨테이너를 처리할 수 있다고 명시되어 있습니다. 공식 웹사이트는 검색 결과에서 직접 확인되지 않았으나, 이메일 주소를 통해 도메인을 추정했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>La Alondra Seafood (Pescados La Alondra Sl)</t>
+          <t>Goh Joo Hin Pte Ltd</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4970,66 +4894,70 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>hola@laalondraseafood.es</t>
+          <t>food@gjh.com.sg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.laalondraseafood.es</t>
+          <t>http://www.gjh.com.sg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Distribution of fresh and cryogenized seafood for retail, HORECA channel, and international markets. Focuses on premium seafood products from the best fishing grounds worldwide.</t>
+          <t>Importer, Exporter, Wholesaler, Distributor</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Avenida Euro núm. 24 Puesto 17 19 21, 47009 Valladolid, Castilla-león</t>
+          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Specializes in high-quality, fresh, and cryogenized seafood. Offers a catalog of seafood products from the best fishing grounds globally. Strong presence in HORECA and retail, with international distribution capabilities.</t>
+          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Their focus on premium seafood, international distribution, and the HORECA channel makes them a good prospect for importing and distributing abalone. Their advanced cryogenic preservation technology could be a suitable fit for abalone products.</t>
+          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://www.laalondraseafood.es/en/distribution/, https://www.laalondraseafood.es/en/fresh-fish-and-seafood/, https://www.laalondraseafood.es/en/cryogenized-seafood/, https://www.laalondraseafood.es/en/innovation/, https://www.empresite.com/PESCADOS-LA-ALONDRA-SL.html, https://www.laalondraseafood.es/en/contact/</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fresh Harvest (Pvt) Ltd</t>
+          <t>Hosen Group Ltd.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5038,59 +4966,63 @@
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://freshharvest.lk/</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Seafood Importer and Distributor</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Importer, Exporter, Distributor, Manufacture &amp; Trade</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>320 Jalan Boon Lay</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Leading seafood company in Sri Lanka, delivers high quality ready-to-cook seafood products. Caters to local market, supplies to top-class hotel chains, leading restaurants, and expanding in local retail market. Acts as an importer of high quality seafood.</t>
+          <t>Fast-moving consumer goods, including canned seafood. Distributes to Southeast Asia, Australia, Indian Sub-continent, Middle-East, North Asia, Pacific Islands.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>스리랑카 현지 시장에 고품질 해산물을 수입하여 호텔, 레스토랑 및 소매점에 공급하는 선도적인 회사입니다. 전복 수입 및 유통에 대한 협력 가능성이 높습니다.</t>
+          <t>A leading distributor in Singapore's dry goods sector, explicitly stating import and distribution of fast-moving consumer goods, including canned seafood, across Southeast Asia.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcQYNWYOJvFZ5465KMss_BHieKPxvrhT-oNHOi2KKwePbAueaXewTLSRdFvyC53bKsJB9SxBoH5hsVkTNWMHCaabHTVCeR0iPYsraHevFcJpFSX0n9</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHSaPnDkPMuPpMogVwbMshl1E9Nw6aZXhv9a1mjBlCE6ncCrnbj0op79iiQk2fqf2sGIpmnTi8wmK9UUUf37L46yOrLr3fVUEFLzOWZGYp5KtjCBvCptFndM3f7NYMvUxUxOhGHZxiezdgWxQ7JzeIYJXFkhZhMzQFpT6O7LA==</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>이메일/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다.</t>
+          <t>Website and email not publicly available in the snippet. They market their own brands and represent others.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Johnson Seafood Co., Ltd.</t>
+          <t>Oceanus Group Limited</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5098,64 +5030,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>contact@oceanus.com.sg</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.johnsonseafood.com.tw</t>
+          <t>http://www.oceanus.com.sg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Leading seafood importer in Taiwan. Imports live, frozen, and freshly chilled seafood, including abalone &amp; scallop. Sources from over 40 countries.</t>
+          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tainan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Based in Qigu coastal areas around Tainan, aquaculture in Tainan's Jiali Township.</t>
+          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Wide range of seafood products (fish, shrimps, crabs, shellfish, mollusk, processed seafood), regular SGS inspection, provides safe and tasty food materials. Product range covers live seafood, frozen seafood, and freshly chilled seafood.</t>
+          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Over 50 years of operation, excellent reputation, sizeable procurement volume, trusted partner by overseas suppliers, and commitment to food safety with SGS inspection.</t>
+          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://www.johnsonseafood.com.tw/about-us/company-profile</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ming Sheng Seafood Co., Ltd.</t>
+          <t>Teck Sang Pte Ltd</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5163,64 +5103,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>local@tecksang.com</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.mingsheng.com.tw</t>
+          <t>https://www.tecksang.com</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Importer of fresh frozen marine products, supplying diversified premium seafood to wholesalers across Taiwan. Imports over 300 premium frozen seafood products, sourcing from 4 oceans and 5 continents.</t>
+          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2F, 332 Zihyou 2nd Rd., Zuoying District, Kaohsiung City, Taiwan.</t>
+          <t>11 Hongkong Street, Singapore 059654</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Over 30 years of experience, strong relationships with manufacturers and customers, world-class logistic system. Offers a set of diversified premium seafood.</t>
+          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Long-standing importer with a wide global sourcing network and a focus on timely delivery to wholesalers. Strong reputation and trust from domestic and international suppliers.</t>
+          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://www.mingsheng.com.tw/about-ming-sheng</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YEN &amp; Brothers Enterprise CO.,LTD.</t>
+          <t>YL Enterprises (Yilai Abalone)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5228,68 +5176,64 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>service@mail.yens.com.tw</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://www.yens.com.tw</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Abalone importer and wholesaler, deals with frozen abalone meat, whole-cooked abalone, Australian abalone. Also handles other fish, crustacean, shellfish, mollusc, meat, soup, prepared foods.</t>
+          <t>Buyer, Importer, Manufacture</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>New Taipei City</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>14F, NO. 217,SEC. 2, NEW TAIPEI BLVD., XINZHUANG DIST., NEW TAIPEI CITY 242, TAIWAN (R.O.C.)</t>
+          <t>865 Mountbatten Road #03-02, Katong Shopping Centre</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Global purchasing, R&amp;D and production, food safety, logistic management. Importer and wholesaler of various seafood products, including abalone.</t>
+          <t>Canned abalone processing enterprise, larval nursing, abalone breeding, abalone processing. Exports to Singapore, South East Asia, Taiwan, Hong Kong, Macau.</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Established company with global purchasing capabilities and a strong focus on food safety and quality management. Handles a variety of abalone products (frozen, whole-cooked, Australian).</t>
+          <t>Directly identified as a Buyer and Importer of abalone in Singapore, with a focus on Southeast Asia and surrounding regions. They also manufacture.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://www.yens.com.tw/products/shellfish/abalone</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdXWn3sY9CX7JdfaAp4fQShQKS9VRARffKM3O8GOoBfVS1FEP6Hjsur3G3BqYsWUxlytZfFJy78jUCAJHY9defZhq-D_oI3S--AbgjcTdExdiUheXg73Q==</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Contact person: Mr. Lim. Phone and fax numbers are listed but incomplete in the snippet. Website not publicly available in the snippet.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
+          <t>Atlantis Foods</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5299,70 +5243,70 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>info@ruifuoilfood.com</t>
+          <t>info@atlantisfoods.co.za</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://ruifuoilfood.com/</t>
+          <t>https://www.atlantisfoods.co.za/</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
+          <t>South Africa의 주요 해산물 유통 회사 중 하나로, 도매업체, 식품 서비스 제공업체 및 소매업체에 고품질 해산물 제품을 소싱, 가공 및 유통합니다. 과거 전무이사가 전복(Abalone) 및 냉장 보관을 담당했습니다.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Si Maha Phot, Prachin Buri</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
+          <t>8 Wessex Road Paarden Eiland Cape Town, South Africa, 7405 (Sales &amp; Marketing Office)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
+          <t>다양한 신선, 냉동, 부가가치 및 즉석 해산물 제품을 취급하며, 전복을 포함한 해산물 유통 경험이 있습니다.</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
+          <t>남아프리카 공화국 내에서 광범위한 유통망을 가진 대규모 해산물 유통업체로, 다양한 채널에 대량 공급이 가능합니다.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
+          <t>https://www.atlantisfoods.co.za/contact-us/</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
+          <t>BestFoodImporters.com에 따르면 'Importer, Distributor, Wholesaler, Supplier'로 분류됩니다. 이전 그룹 물류 관리자가 전복을 담당했다는 언급이 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thai Abalone Co.,Ltd.</t>
+          <t>Greenfish</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5370,68 +5314,76 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ops@greenfish.co.za, Sales1@greenfish.co.za</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://m.ec21.com/company/thaiabalone/</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>https://greenfish.co.za/</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>063 666 2802 (Whatsapp)</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
+          <t>온라인 및 도매 해산물 공급업체로, 양식 전복(perlemoen)을 포함한 신선한 해산물을 취급합니다.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Pathiu, Chumphon</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
+          <t>온라인 전용 (소매점 없음), Cape Town 및 주변 지역(CBD, Southern Suburbs, Houtbay, Plattekloof, Deep South, Table View, Blouberg, Melkbos, Durbanville, Stellenbosch, Somerset West, Franschhoek, Paarl) 배송 가능.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
+          <t>6개들이 라이브 양식 전복(perlemoen)을 판매하며, 노르웨이산 연어, 대구, 참치, 킹클립, 홍합, 굴, 옐로우테일, 카벨조우 등 다양한 신선 해산물을 제공합니다.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
+          <t>양식 전복을 직접 공급하며, 개인 소비자 및 도매 고객 모두에게 서비스를 제공합니다. 소규모 또는 전문적인 주문, 레스토랑 직거래에 적합합니다.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://m.ec21.com/company/thaiabalone/</t>
+          <t>https://greenfish.co.za/products/abalone-perlemoen-live-box-cultivated-x6</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
+          <t>온라인 전용 업체이며, 소매점은 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Monterey Abalone Company</t>
+          <t>FRESHCADO RECIEN PESCADO SL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5439,68 +5391,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>contact@freshcado.es</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://montereyabalone.com</t>
+          <t>https://freshcado.es</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
+          <t>Wholesale and retail of fresh and frozen fish and seafood, including premium seafood. Operates as an online fishmonger and supplies professionals across Spain, sourcing from Mercamadrid and international ports.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Monterey</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
+          <t>C/ de la Diputació, 256, 08007 Barcelona</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
+          <t>Offers a wide selection of fresh and frozen seafood. Emphasizes maximum freshness, direct product from Mercamadrid, and 24/48h delivery. Committed to sustainability and responsible fishing.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
+          <t>As a large seafood wholesaler and online retailer with a wide range of fresh and frozen seafood, including a 'Premium Seafood' category, Freshcado is a strong prospect for importing and distributing abalone.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Email not found in provided snippets.</t>
-        </is>
-      </c>
+          <t>https://freshcado.es/legal-notice/, https://freshcado.es/accessibility-statement/, https://freshcado.es/general-terms-and-conditions/, https://freshcado.es/en/fish-and-seafood-wholesaler-in-spain/, https://freshcado.es/en/online-fishmonger-buy-fresh-fish-and-seafood/, https://freshcado.es/en/comprar-smoked-and-canned-products-online/</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ocean Floor Inc.</t>
+          <t>Globalimar Europa, SL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5508,56 +5460,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>info@globalimar.com</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.globalimar.com</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Frozen seafood import, production, and commercialization for mass-market, including bivalves, cephalopods, crustaceans, surimi, and prepared fish. Serves Spain, Europe, USA, and Maghreb region.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Llagostera</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>C/ Jaume I, 2A, 17240 Llagostera, Girona</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
+          <t>Specialists in frozen seafood products, with a focus on quality and sustainability. Offers a diversified range of frozen seafood. Explicitly states import and commercialization activities.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
+          <t>Explicitly states 'import, produce and commercialize' frozen seafood. Their broad range of seafood products, including bivalves, makes them a highly probable candidate for importing abalone.</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>City, email, and website not found in provided snippets.</t>
-        </is>
-      </c>
+          <t>https://www.globalimar.com/contact/, https://www.conxemar.com/en/asociados/globalimar-europa-sl, https://www.conxemar.com/en/exhibitor/globalimar-europa-sl-conxemar-2024, https://www.globalimar.com/en/company/specialists-in-frozen-seafood/, https://www.bestfoodimporters.com/importer/globalimar-europa</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seafarers Inc.</t>
+          <t>La Alondra Seafood (Pescados La Alondra Sl)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5565,56 +5529,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>hola@laalondraseafood.es</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://www.laalondraseafood.es</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Distribution of fresh and cryogenized seafood for retail, HORECA channel, and international markets. Focuses on premium seafood products from the best fishing grounds worldwide.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Avenida Euro núm. 24 Puesto 17 19 21, 47009 Valladolid, Castilla-león</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
+          <t>Specializes in high-quality, fresh, and cryogenized seafood. Offers a catalog of seafood products from the best fishing grounds globally. Strong presence in HORECA and retail, with international distribution capabilities.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
+          <t>Their focus on premium seafood, international distribution, and the HORECA channel makes them a good prospect for importing and distributing abalone. Their advanced cryogenic preservation technology could be a suitable fit for abalone products.</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>City, email, and website not found in provided snippets.</t>
-        </is>
-      </c>
+          <t>https://www.laalondraseafood.es/en/distribution/, https://www.laalondraseafood.es/en/fresh-fish-and-seafood/, https://www.laalondraseafood.es/en/cryogenized-seafood/, https://www.laalondraseafood.es/en/innovation/, https://www.empresite.com/PESCADOS-LA-ALONDRA-SL.html, https://www.laalondraseafood.es/en/contact/</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Abalone Fish Processing LLC</t>
+          <t>Fresh Harvest (Pvt) Ltd</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5623,46 +5599,42 @@
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://freshharvest.lk/</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Fish and Seafood Processors</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Ajman</t>
-        </is>
-      </c>
+          <t>Seafood Importer and Distributor</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Near Factory Mart, New Ind Area, Ajman / 78a, Amman street, Ajman Industrial 2</t>
-        </is>
-      </c>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Fish and Seafood Processors. The company name suggests a focus on abalone.</t>
+          <t>Leading seafood company in Sri Lanka, delivers high quality ready-to-cook seafood products. Caters to local market, supplies to top-class hotel chains, leading restaurants, and expanding in local retail market. Acts as an importer of high quality seafood.</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>A seafood processing company, likely involved in the import and distribution of various seafood, potentially including abalone, given its name. They are listed as 'Fish And Seafood Processors'.</t>
+          <t>스리랑카 현지 시장에 고품질 해산물을 수입하여 호텔, 레스토랑 및 소매점에 공급하는 선도적인 회사입니다. 전복 수입 및 유통에 대한 협력 가능성이 높습니다.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHFN1ioKMvAABGXDTz-XA2FisFHogtokbmSflhk3jbvA8p7zaDQFSZwrI0hdELPSZmK4Wc-LYdVkfx9Icf2bIlxGcy5n-3UNZ38yb-YhBVFHE0QP_48m00iz7KofFmbKySqsSnnKW3nKI_I128GTUIQfv-FTBuOaPRMuJfMDST_</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcQYNWYOJvFZ5465KMss_BHieKPxvrhT-oNHOi2KKwePbAueaXewTLSRdFvyC53bKsJB9SxBoH5hsVkTNWMHCaabHTVCeR0iPYsraHevFcJpFSX0n9</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Phone number: 06-7438606</t>
+          <t>이메일/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다.</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5646,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dior Fresh Fish</t>
+          <t>Johnson Seafood Co., Ltd.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5690,43 +5662,43 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://diorfreshfish.com/</t>
+          <t>https://www.johnsonseafood.com.tw</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fresh and frozen seafood, including Whole Shell Abalone. Delivery across UAE (Dubai, Abu Dhabi, Sharjah).</t>
+          <t>Leading seafood importer in Taiwan. Imports live, frozen, and freshly chilled seafood, including abalone &amp; scallop. Sources from over 40 countries.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Tainan</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Waterfront market Deira, Dubai.</t>
+          <t>Based in Qigu coastal areas around Tainan, aquaculture in Tainan's Jiali Township.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Sells 'Fresh Whole Shell Abalone' sourced from pristine cold-water regions (FAO Areas 27 and 81). Halal Compliant &amp; Hygienically Processed. Cold-Chain Delivery (0–4°C). Offers custom fish preparation and 2-hour/same-day delivery in Dubai, next-day across UAE.</t>
+          <t>Wide range of seafood products (fish, shrimps, crabs, shellfish, mollusk, processed seafood), regular SGS inspection, provides safe and tasty food materials. Product range covers live seafood, frozen seafood, and freshly chilled seafood.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Directly imports and distributes abalone, with a focus on quality and cold-chain logistics. They cater to households and high-end restaurants.</t>
+          <t>Over 50 years of operation, excellent reputation, sizeable procurement volume, trusted partner by overseas suppliers, and commitment to food safety with SGS inspection.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF1n6IrUDF_2UqEV1FcEcY_91lJj3LUZsTqcN2E-z6ynL2pmf6_SM1ymPQjnZMML_D3hhCHfVLVikDUjllk1QaU7pVCslFnbxRTPWXUF1y6MLjcD1m-IBi83-ovGxE8KZhXTNMo4yW_3PmnAFzpJ5O5jrf8_bcyfg==</t>
+          <t>https://www.johnsonseafood.com.tw/about-us/company-profile</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
@@ -5739,12 +5711,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sea World Fish Processing Llc</t>
+          <t>Ming Sheng Seafood Co., Ltd.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5753,52 +5725,48 @@
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>+971564117152 (WhatsApp)</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.mingsheng.com.tw</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Frozen Seafood, Shrimp, Salmon, Squid, Abalone, Lobster, Tuna, Trevally. Fish &amp; Seafood Importers, Exporters &amp; Processors.</t>
+          <t>Importer of fresh frozen marine products, supplying diversified premium seafood to wholesalers across Taiwan. Imports over 300 premium frozen seafood products, sourcing from 4 oceans and 5 continents.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Meena Rd, Nr Fish Market, Al Jurf Indl Area, Ajman. Also listed in Al Quoz Industrial 3, Dubai.</t>
+          <t>2F, 332 Zihyou 2nd Rd., Zuoying District, Kaohsiung City, Taiwan.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Supplier of Frozen Seafood including Abalone, Shrimp, Salmon, Squid, Lobster, Tuna, Trevally. Also lists Salmon, King Fish, Octopus.</t>
+          <t>Over 30 years of experience, strong relationships with manufacturers and customers, world-class logistic system. Offers a set of diversified premium seafood.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Explicitly listed as a supplier of 'Frozen Abalone' and 'Frozen Seafood'. They are also 'Fish &amp; Seafood Importers, Exporters &amp; Processors'.</t>
+          <t>Long-standing importer with a wide global sourcing network and a focus on timely delivery to wholesalers. Strong reputation and trust from domestic and international suppliers.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHilrZwc_-sVdE6bxfa_EuTM77Z-w7QcSFQExMjw8zLaBemFs7vOrXa3yrDTsx-7YDW4t9Z8Al_fRoC7fqyqD0LgQWijBKAJOUkaCbOVcgwqY3UASq9uRKwk3Qd-ag7ux7mmxmf1e26daaZRNlDWEd_2ZaKnwEDtz5oxNbZCL9OEVnyaMgh0ArAZFmnkodMlaIL</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Phone number: +971-6-7444559</t>
-        </is>
-      </c>
+          <t>https://www.mingsheng.com.tw/about-ming-sheng</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5808,12 +5776,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Direct Seafoods</t>
+          <t>YEN &amp; Brothers Enterprise CO.,LTD.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5823,70 +5791,66 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>sales@directseafoods.co.uk</t>
+          <t>service@mail.yens.com.tw</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.directseafoods.co.uk/</t>
+          <t>https://www.yens.com.tw</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Wholesale abalone, frozen wholesale abalone, supplying to restaurants, caterers, and distributors.</t>
+          <t>Abalone importer and wholesaler, deals with frozen abalone meat, whole-cooked abalone, Australian abalone. Also handles other fish, crustacean, shellfish, mollusc, meat, soup, prepared foods.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>New Taipei City</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Crown Court Severalls Business Park, Clough road, Colchester CO4 9TZ</t>
+          <t>14F, NO. 217,SEC. 2, NEW TAIPEI BLVD., XINZHUANG DIST., NEW TAIPEI CITY 242, TAIWAN (R.O.C.)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Expertly sourced wholesale abalone, premium quality, range of pack sizes, sustainably sourced options, frozen abalone.</t>
+          <t>Global purchasing, R&amp;D and production, food safety, logistic management. Importer and wholesaler of various seafood products, including abalone.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Clearly states they are suppliers of wholesale abalone for businesses, including caterers and distributors, indicating they import or source in bulk.</t>
+          <t>Established company with global purchasing capabilities and a strong focus on food safety and quality management. Handles a variety of abalone products (frozen, whole-cooked, Australian).</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHUIYsQ2UBPSBJ867GFx9lsSGgOScseBoH5kgVzDM4Z9FqfpgCuJOckuXoixQJWbbT--kaUWwRR_UzXIpjbk7uvQF9L8O0c_NRa3jAnZIPK8qH5hk4lkW-WX7hkiJFFlIanM64gCt86Rui4ofRFzhQfr-MHgQRPuI-tVU0=</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Part of Bidfresh Limited.</t>
-        </is>
-      </c>
+          <t>https://www.yens.com.tw/products/shellfish/abalone</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fine Food Specialist</t>
+          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5896,70 +5860,70 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>support@finefoodspecialist.co.uk</t>
+          <t>info@ruifuoilfood.com</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.finefoodspecialist.co.uk/</t>
+          <t>https://ruifuoilfood.com/</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sells large Australian abalone online, offers wholesale.</t>
+          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Si Maha Phot, Prachin Buri</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Not explicitly stated beyond 'London and the UK'.</t>
+          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Large Australian abalone, frozen, sashimi grade, offers next day delivery.</t>
+          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Explicitly states 'Wholesale available. Trusted UK fine food wholesaler,' indicating they are a distributor.</t>
+          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGMjhqPJpEsff_zAS7zQT4UIck_UEpFMw36Ap14taYnEELyVa1mAKjWqtFFwvjKYoZ6_VuZ37CEImyilNnDqE0avI5M1E1YyngtytpAY67YhY8ts-aoTS1FWZ3AtkuSrw-UyioUx9MMvlc6lidPdRqiatFTdXzrMlinyaaYKh0gqQ==</t>
+          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Offers both retail and wholesale.</t>
+          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seafood Australia</t>
+          <t>Thai Abalone Co.,Ltd.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5970,61 +5934,65 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://seafoodaustralia.co.uk/</t>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sells Premium Australian Canned Abalone and Wild Abalone, with 'Fast UK Shipping' and a 'Wholesale' section.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Pathiu, Chumphon</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Delivers to anywhere in the UK.</t>
+          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Premium Australian wild and farmed abalone, canned abalone, direct from farm to door, sustainably farmed or caught.</t>
+          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Has a 'Wholesale' section on their website and offers direct supply of Australian abalone, suggesting they are an importer/distributor.</t>
+          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHydvT7JMFhRuJb4p5iZBcaBABfGyX2tWoFEHuHnjJ_kqBq4Eb1I0ey6Ty7x2ua2-wI7FN6fuFx3syKl6sTP9xSL_oGe4JKYhCxMN3JZuetVzzTAo5vHoDUhwQt-44=</t>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Specializes in Australian abalone.</t>
+          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fishy Vietnam Co., Ltd.</t>
+          <t>Monterey Abalone Company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6032,68 +6000,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Fishy.vn@gmail.com</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://fishy.vn/</t>
+          <t>https://montereyabalone.com</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Importing and distributing top-class seafood, including various types of abalone (Frozen Abalone (Loco) Meat, Frozen Australian Greenlip Abalone, Frozen Abalone, Braised Abalone In Oyster Sauce, Abalone Seafood Soup).</t>
+          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Monterey</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City</t>
+          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Specializes in importing and distributing top-class seafood. Products include various types of abalone (frozen, Australian greenlip, loco meat, abalone seafood soup, braised abalone in oyster sauce). Focus on product quality, dedication, and customer satisfaction.</t>
+          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Direct importer and distributor, indicating a clear channel for cooperation. Emphasizes quality and customer satisfaction.</t>
+          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFnIbNcTSOzpm1rjxZKNdOXHZFHXPLvkR6w0O11uKwUJy88CBKHuqahAqg6N3_l-KqHBD9TlsdBOFLPPwARm092X_aBdYKa_w7CDxuB3MzJ4junbM6oKTpwaIgIt3W2fFE=</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Email not found in provided snippets.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sai Thanh Foods</t>
+          <t>Ocean Floor Inc.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6101,68 +6069,56 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>salesfreshfood@sacofoods.vn</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>https://saithanhfoods.com/</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Supplier of frozen abalone (Haliotis Diversicolor) from Vietnam. Also deals with other seafood like sea fish, river fish, octopus, squid, shellfish.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Ho Chi Minh City</t>
-        </is>
-      </c>
+          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Lot III-22, Street 19/5A, Tan Binh Industrial Park, Tay Thanh Ward, Ho Chi Minh City, Vietnam</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Specializes in frozen abalone (Haliotis Diversicolor) of Vietnamese origin. They also offer other seafood products.</t>
+          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Direct supplier of frozen abalone, indicating a potential for direct sourcing. They invite inquiries for specifications and pricing.</t>
+          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdzZHAIL6EJepETfinawUNWPxz-8vXV951xIFxRs0HZB32IxHGNPOCJKb_txdlYe0VZWWpejeThan1R4sfd3Pj_eg_ZzTpeCR9cmBU_meF-izlTZCbpQTD124H_zWN5Fe1iuEj6bD5iqxCJW8af6yMk-s=</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>City, email, and website not found in provided snippets.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Trọng Đức Seafood</t>
+          <t>Seafarers Inc.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6171,59 +6127,55 @@
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>https://trongduc.com/</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Imports abalone mainly from Korea, Japan, and neighboring countries. Also deals with other seafood like Japanese scallops, sea eel. Offers good prices for wholesalers, agents, and distributors.</t>
+          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Imports abalone from Korea, Japan, and neighboring countries. Offers various sizes of Korean abalone. Emphasizes product quality, reputation, and direct import for good prices for wholesalers/agents/distributors.</t>
+          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Explicitly states good prices for wholesalers, agents, and distributors, making them a direct potential partner. They also offer returns if not satisfied.</t>
+          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFNhjSu_CUVmGlZe8ulZHnui_rrcb9z2Gm9Dk4aJlf3YHrn288thuxtw0ARGxmu3uLnFb-7BIWKI_KEffIQPvRk0m3fct_IGwngL1ebQV7ngD9mdbqcdBnMHvE7US-xDV1Y9SOFz--R_tY6SDR-u-90jvs=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>City and location detail not explicitly mentioned in the provided source.</t>
+          <t>City, email, and website not found in provided snippets.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FGC JOINT STOCK COMPANY</t>
+          <t>Abalone Fish Processing LLC</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6231,72 +6183,64 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>fgc.seafoods@gmail.com</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>https://www.fgc-foods.com/</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>전복(살아있는, 열처리 및 냉동)을 포함한 고품질의 안전한 수입 식품을 제조 및 공급합니다.</t>
+          <t>Fish and Seafood Processors</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi.</t>
+          <t>Near Factory Mart, New Ind Area, Ajman / 78a, Amman street, Ajman Industrial 2</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>수입 전복(살아있는, 열처리 및 냉동), 1kg/봉지, 10kg/상자, -18°C 보관, 24개월 유통기한.</t>
+          <t>Fish and Seafood Processors. The company name suggests a focus on abalone.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>수입 전복 공급업체, 품질 및 안전에 중점, 다양한 맛과 스타일.</t>
+          <t>A seafood processing company, likely involved in the import and distribution of various seafood, potentially including abalone, given its name. They are listed as 'Fish And Seafood Processors'.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://www.fgc-foods.com/san-pham/thuc-pham-chat-luong-cho-kenh-nha-hang-va-ban-le/bao-ngu-nhap-khau</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHFN1ioKMvAABGXDTz-XA2FisFHogtokbmSflhk3jbvA8p7zaDQFSZwrI0hdELPSZmK4Wc-LYdVkfx9Icf2bIlxGcy5n-3UNZ38yb-YhBVFHE0QP_48m00iz7KofFmbKySqsSnnKW3nKI_I128GTUIQfv-FTBuOaPRMuJfMDST_</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>전화 및 Zalo 핫라인도 이용 가능합니다.</t>
+          <t>Phone number: 06-7438606</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fishy Vietnam Co., Ltd</t>
+          <t>Dior Fresh Fish</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6304,114 +6248,731 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Fishy.vn@gmail.com</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://fishy.vn/</t>
+          <t>https://diorfreshfish.com/</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>베트남에서 전복(냉동 전복(Loco) 고기, 냉동 호주산 그린립 전복 포함)을 포함한 최고급 해산물을 수입 및 유통합니다.</t>
+          <t>Fresh and frozen seafood, including Whole Shell Abalone. Delivery across UAE (Dubai, Abu Dhabi, Sharjah).</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City.</t>
+          <t>Waterfront market Deira, Dubai.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>최고급 해산물 수입 및 유통 전문, 헌신과 명성, 고객 만족 중시, 고품질 제품, 최고의 서비스.</t>
+          <t>Sells 'Fresh Whole Shell Abalone' sourced from pristine cold-water regions (FAO Areas 27 and 81). Halal Compliant &amp; Hygienically Processed. Cold-Chain Delivery (0–4°C). Offers custom fish preparation and 2-hour/same-day delivery in Dubai, next-day across UAE.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>프리미엄 해산물 수입 및 유통 선두 기업, 다양한 전복 제품, 품질 및 고객 서비스에 중점.</t>
+          <t>Directly imports and distributes abalone, with a focus on quality and cold-chain logistics. They cater to households and high-end restaurants.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://fishy.vn/san-pham/bao-ngu</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>세금 ID 및 핫라인도 이용 가능합니다.</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF1n6IrUDF_2UqEV1FcEcY_91lJj3LUZsTqcN2E-z6ynL2pmf6_SM1ymPQjnZMML_D3hhCHfVLVikDUjllk1QaU7pVCslFnbxRTPWXUF1y6MLjcD1m-IBi83-ovGxE8KZhXTNMo4yW_3PmnAFzpJ5O5jrf8_bcyfg==</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Sea World Fish Processing Llc</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>+971564117152 (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Frozen Seafood, Shrimp, Salmon, Squid, Abalone, Lobster, Tuna, Trevally. Fish &amp; Seafood Importers, Exporters &amp; Processors.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Ajman</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Meena Rd, Nr Fish Market, Al Jurf Indl Area, Ajman. Also listed in Al Quoz Industrial 3, Dubai.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Supplier of Frozen Seafood including Abalone, Shrimp, Salmon, Squid, Lobster, Tuna, Trevally. Also lists Salmon, King Fish, Octopus.</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Explicitly listed as a supplier of 'Frozen Abalone' and 'Frozen Seafood'. They are also 'Fish &amp; Seafood Importers, Exporters &amp; Processors'.</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHilrZwc_-sVdE6bxfa_EuTM77Z-w7QcSFQExMjw8zLaBemFs7vOrXa3yrDTsx-7YDW4t9Z8Al_fRoC7fqyqD0LgQWijBKAJOUkaCbOVcgwqY3UASq9uRKwk3Qd-ag7ux7mmxmf1e26daaZRNlDWEd_2ZaKnwEDtz5oxNbZCL9OEVnyaMgh0ArAZFmnkodMlaIL</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Phone number: +971-6-7444559</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Direct Seafoods</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>sales@directseafoods.co.uk</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.directseafoods.co.uk/</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Wholesale abalone, frozen wholesale abalone, supplying to restaurants, caterers, and distributors.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Colchester</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Crown Court Severalls Business Park, Clough road, Colchester CO4 9TZ</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Expertly sourced wholesale abalone, premium quality, range of pack sizes, sustainably sourced options, frozen abalone.</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Clearly states they are suppliers of wholesale abalone for businesses, including caterers and distributors, indicating they import or source in bulk.</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHUIYsQ2UBPSBJ867GFx9lsSGgOScseBoH5kgVzDM4Z9FqfpgCuJOckuXoixQJWbbT--kaUWwRR_UzXIpjbk7uvQF9L8O0c_NRa3jAnZIPK8qH5hk4lkW-WX7hkiJFFlIanM64gCt86Rui4ofRFzhQfr-MHgQRPuI-tVU0=</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Part of Bidfresh Limited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Fine Food Specialist</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>support@finefoodspecialist.co.uk</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.finefoodspecialist.co.uk/</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sells large Australian abalone online, offers wholesale.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Not explicitly stated beyond 'London and the UK'.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Large Australian abalone, frozen, sashimi grade, offers next day delivery.</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Explicitly states 'Wholesale available. Trusted UK fine food wholesaler,' indicating they are a distributor.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGMjhqPJpEsff_zAS7zQT4UIck_UEpFMw36Ap14taYnEELyVa1mAKjWqtFFwvjKYoZ6_VuZ37CEImyilNnDqE0avI5M1E1YyngtytpAY67YhY8ts-aoTS1FWZ3AtkuSrw-UyioUx9MMvlc6lidPdRqiatFTdXzrMlinyaaYKh0gqQ==</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Offers both retail and wholesale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Seafood Australia</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://seafoodaustralia.co.uk/</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sells Premium Australian Canned Abalone and Wild Abalone, with 'Fast UK Shipping' and a 'Wholesale' section.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Delivers to anywhere in the UK.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Premium Australian wild and farmed abalone, canned abalone, direct from farm to door, sustainably farmed or caught.</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Has a 'Wholesale' section on their website and offers direct supply of Australian abalone, suggesting they are an importer/distributor.</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHydvT7JMFhRuJb4p5iZBcaBABfGyX2tWoFEHuHnjJ_kqBq4Eb1I0ey6Ty7x2ua2-wI7FN6fuFx3syKl6sTP9xSL_oGe4JKYhCxMN3JZuetVzzTAo5vHoDUhwQt-44=</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Specializes in Australian abalone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Viet Nam</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Fishy Vietnam Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Fishy.vn@gmail.com</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Importing and distributing top-class seafood, including various types of abalone (Frozen Abalone (Loco) Meat, Frozen Australian Greenlip Abalone, Frozen Abalone, Braised Abalone In Oyster Sauce, Abalone Seafood Soup).</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Specializes in importing and distributing top-class seafood. Products include various types of abalone (frozen, Australian greenlip, loco meat, abalone seafood soup, braised abalone in oyster sauce). Focus on product quality, dedication, and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Direct importer and distributor, indicating a clear channel for cooperation. Emphasizes quality and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFnIbNcTSOzpm1rjxZKNdOXHZFHXPLvkR6w0O11uKwUJy88CBKHuqahAqg6N3_l-KqHBD9TlsdBOFLPPwARm092X_aBdYKa_w7CDxuB3MzJ4junbM6oKTpwaIgIt3W2fFE=</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Viet Nam</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sai Thanh Foods</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>salesfreshfood@sacofoods.vn</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://saithanhfoods.com/</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Supplier of frozen abalone (Haliotis Diversicolor) from Vietnam. Also deals with other seafood like sea fish, river fish, octopus, squid, shellfish.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Lot III-22, Street 19/5A, Tan Binh Industrial Park, Tay Thanh Ward, Ho Chi Minh City, Vietnam</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Specializes in frozen abalone (Haliotis Diversicolor) of Vietnamese origin. They also offer other seafood products.</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Direct supplier of frozen abalone, indicating a potential for direct sourcing. They invite inquiries for specifications and pricing.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdzZHAIL6EJepETfinawUNWPxz-8vXV951xIFxRs0HZB32IxHGNPOCJKb_txdlYe0VZWWpejeThan1R4sfd3Pj_eg_ZzTpeCR9cmBU_meF-izlTZCbpQTD124H_zWN5Fe1iuEj6bD5iqxCJW8af6yMk-s=</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Viet Nam</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Trọng Đức Seafood</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://trongduc.com/</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Imports abalone mainly from Korea, Japan, and neighboring countries. Also deals with other seafood like Japanese scallops, sea eel. Offers good prices for wholesalers, agents, and distributors.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Imports abalone from Korea, Japan, and neighboring countries. Offers various sizes of Korean abalone. Emphasizes product quality, reputation, and direct import for good prices for wholesalers/agents/distributors.</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Explicitly states good prices for wholesalers, agents, and distributors, making them a direct potential partner. They also offer returns if not satisfied.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFNhjSu_CUVmGlZe8ulZHnui_rrcb9z2Gm9Dk4aJlf3YHrn288thuxtw0ARGxmu3uLnFb-7BIWKI_KEffIQPvRk0m3fct_IGwngL1ebQV7ngD9mdbqcdBnMHvE7US-xDV1Y9SOFz--R_tY6SDR-u-90jvs=</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>City and location detail not explicitly mentioned in the provided source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>2026-07-31 19:31:29</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>FGC JOINT STOCK COMPANY</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>fgc.seafoods@gmail.com</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.fgc-foods.com/</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>전복(살아있는, 열처리 및 냉동)을 포함한 고품질의 안전한 수입 식품을 제조 및 공급합니다.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>수입 전복(살아있는, 열처리 및 냉동), 1kg/봉지, 10kg/상자, -18°C 보관, 24개월 유통기한.</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>수입 전복 공급업체, 품질 및 안전에 중점, 다양한 맛과 스타일.</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>https://www.fgc-foods.com/san-pham/thuc-pham-chat-luong-cho-kenh-nha-hang-va-ban-le/bao-ngu-nhap-khau</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>전화 및 Zalo 핫라인도 이용 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Fishy Vietnam Co., Ltd</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Fishy.vn@gmail.com</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>베트남에서 전복(냉동 전복(Loco) 고기, 냉동 호주산 그린립 전복 포함)을 포함한 최고급 해산물을 수입 및 유통합니다.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>최고급 해산물 수입 및 유통 전문, 헌신과 명성, 고객 만족 중시, 고품질 제품, 최고의 서비스.</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>프리미엄 해산물 수입 및 유통 선두 기업, 다양한 전복 제품, 품질 및 고객 서비스에 중점.</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/san-pham/bao-ngu</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>세금 ID 및 핫라인도 이용 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
         <is>
           <t>Trọng Đức Seafood</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>법인</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
         <is>
           <t>https://trongduc.vn/</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
         <is>
           <t>한국, 일본 및 인근 국가에서 전복을 수입하여 도매업체, 에이전트 및 유통업체에 공급합니다.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
         <is>
           <t>수입 전복 (한국, 일본 및 인근 국가산), 다양한 크기, 도매업체/에이전트/유통업체에 좋은 가격, 품질 명성, 완전한 문서 및 바코드.</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>직접 수입업체이며, 도매업체/에이전트/유통업체에 좋은 가격을 제공하고, 품질 및 문서화에 중점을 둡니다.</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>https://trongduc.vn/san-pham/bao-ngu-nhap-khau/</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>이메일/전화번호는 스니펫에 명시되어 있지 않지만 웹사이트가 제공됩니다.</t>
         </is>

--- a/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
+++ b/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
@@ -1191,12 +1191,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>🔍 조사 완료 (3개사 발견)</t>
+          <t>🔍 조사 완료 (4개사 발견)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Harmony Marine Products Sdn. Bhd., Ocean Pacific Seafood &amp; Meat Sdn Bhd 외 1개사</t>
+          <t>Harmony Marine Products Sdn. Bhd., Ocean Fresh Seafood Products Sdn. Bhd. 외 2개사</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1482,7 +1482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3636,7 +3636,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 19:11:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3663,7 +3663,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>전복, 해삼, 어류 부레를 포함한 프리미엄 해산물 진미 공급업체. 아시아 태평양, 남미 및 아프리카에서 제품 및 재료를 조달합니다.</t>
+          <t>전복, 해삼, 어교 등 고급 해산물 공급. 아시아-태평양, 남미, 아프리카에서 제품 및 원료를 조달하며, 국내 및 해외 시장에 해산물 가공품을 공급.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3672,36 +3672,32 @@
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>본사는 현대적인 시설(전용 건조실, 3,000평방피트 냉동고, 5,000평방피트 보관 공간)을 갖추고 있으며 HACCP 인증을 받았습니다.</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>프리미엄 전복, 엄격한 품질 관리, 지속 가능한 조달, 30년 이상의 경험.</t>
+          <t>수십 년의 경험, HACCP 인증, 품질 및 신선도에 중점.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>광범위한 경험을 가진 확고한 공급업체, 국제적으로 조달, HACCP 인증.</t>
+          <t>다양한 지역에서 제품을 조달(수입 의미)하고 전복을 공급한다고 명시함.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://www.harmonymarine.com.my/abalone-supplier-malaysia</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGKQgXr5Q4iTaMV90WWjiFHsNExBM3ehTQIDTdfCYMajRuPXZkSRDlYsz9E64GfunKJYV8gmDLSafgGNk03B95XPYogH5mILd87xWzkQDKcvP-Cu6MYCj0J8Vgx6TdvrA==</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>주로 공급업체이지만, 다양한 지역에서 조달하는 것은 수입 활동을 의미합니다.</t>
+          <t>이메일은 검색 결과에서 직접 확인되지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 19:11:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3711,7 +3707,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
+          <t>Ocean Fresh Seafood Products Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3722,18 +3718,18 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://oceanpacificonline.com/</t>
+          <t>https://oceanfresh.com.my/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 해산물 및 냉동 식품을 도매 및 공급합니다.</t>
+          <t>전복을 포함한 냉동 해산물 제품의 도매업자, 소매업자, 가공업자 및 수출업자. 다른 공급업체로부터 해산물을 수입한다고 언급함. 주요 시장은 말레이시아, 터키, 중국, 태국, 베트남, 일본, 인도네시아, 필리핀, 싱가포르, 한국, 이탈리아, 포르투갈, 미국, 호주 등.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Johor Bahru</t>
+          <t>Kuantan</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3743,34 +3739,34 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia.</t>
+          <t>Lot 19869, Kampung Baru Peramu, 26060 Kuantan, Pahang Darul Makmur</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>전복, 조개, 게, 생선, 고기, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 공급합니다. 해산물 및 냉동 식품의 선두 공급업체입니다.</t>
+          <t>최고 품질의 수확, 부드럽고 풍미 있는 전복, 지속 가능한 관행. HACCP, GMP, MeSTI, HALAL, EU Number 75, GACC, FDA 인증 보유.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>다양한 국내 브랜드, 지속적인 트렌드 분석, 최고의 서비스와 제품 제공에 전념.</t>
+          <t>해산물 수입을 명시하고 있으며, 말레이시아 내 전복 도매/소매업자임.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://oceanpacificonline.com/abalone</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGbSloXTHvXsEfMfZoED_KCIgU-oG2Jwgsx9TKqGtZCuQGKIEh3w4CGJJDHh5LJ89eHlzW1HMKiwtPzU_9Q2mNbzcxl5W_yeCSzWdZ1t2c0GO8RF4MT169-ZGNK7DdQg1-yK5l3</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>웹사이트에 전화번호가 있습니다.</t>
+          <t>이메일은 검색 결과에서 직접 확인되지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 19:11:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3780,7 +3776,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>V Top Frozen Food Sdn Bhd</t>
+          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3788,25 +3784,21 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Vtopff@gmail.com</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://vtopfrozenfood.com/</t>
+          <t>https://oceanpacificonline.com/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
+          <t>전복, 조개, 게, 생선, 육류, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 도매 및 공급.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3816,94 +3808,102 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
+          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
+          <t>다양한 해산물 및 육류 제품 취급.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
+          <t>말레이시아에서 전복을 도매 및 공급한다고 명시함. 이는 수입 또는 수입업자로부터의 구매를 의미하며, 유통 채널로서 협력 가능성이 높음.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://vtopfrozenfood.com/abalone-slices</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHwCZKluSSt7oYj7crdsFJGBYORnP7_17SuLRkDfcZvxASSQGO_bUsZZTa_jqnOoxGbtjsC8gzbYOQQwkxOBEzlDW6tfG8QCS6NY-Mspuoi1elIddpUydrGMAQKESf4Emdfedp57H0igxkoxxjOr6Vn8F4Amb4IXWxOV4W2zQgBjg==</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>웹사이트에 전화번호가 있습니다.</t>
+          <t>이메일은 검색 결과에서 직접 확인되지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bajamar Trading Group</t>
+          <t>V Top Frozen Food Sdn Bhd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>개인 에이전트</t>
+          <t>법인</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>artavilo@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>Vtopff@gmail.com</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://vtopfrozenfood.com/</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Producers, exporters, importers, wholesalers and agents of various seafood products including live and canned abalone, geoduck, lobster, fish, squid, scallops, shrimp, tuna, octopus.</t>
+          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Guerrero Negro</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Victoria Sanchez s/n, Col. Estado 30, Guerrero Negro, Baja California Sur, 23940</t>
+          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Live Red Abalone, Cultured Live Red Abalone, Blue and Yellow Canned Abalone, Yellow and Blue Abalone (frozen).</t>
+          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Explicitly imports and distributes abalone, acts as an agent, and deals with both live and canned abalone.</t>
+          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEywKxEIyVlMNjfilH11VDswQqsLbyNCU7KB_sereg0oMd6MEBpTRLhahJSb5ITplmF-lGSCyPqmzVjEvIRUUGjTD8ks23jykrR0C5IlZx-us7Uhww1TkqIWDq3d_g75TtnWphZSRfxCKtdPR7qLt6KUMo6XIBaSHqS9NjgbTEworKmrpJVnpV6fm7Igv28sf0h</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>https://vtopfrozenfood.com/abalone-slices</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>웹사이트에 전화번호가 있습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3918,37 +3918,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GlobalPezk</t>
+          <t>Bajamar Trading Group</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>법인</t>
+          <t>개인 에이전트</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>info@globalpezk.com</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>globalpezk.com</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>+52 (669) 980 6440 (Whatsapp for Mazatlán)</t>
-        </is>
-      </c>
+          <t>artavilo@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Import and commercialization of premium seafood and exclusive supplies for oriental cuisine from the USA, China, Japan, and Canada. Wholesale and retail with national coverage in Mexico.</t>
+          <t>Producers, exporters, importers, wholesalers and agents of various seafood products including live and canned abalone, geoduck, lobster, fish, squid, scallops, shrimp, tuna, octopus.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Guerrero Negro</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3958,29 +3950,25 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Blvd. Fundadores 6119 Int. 11. El Rubí, C.P 22626, Tijuana, B.C. (Also operates in Mazatlán, Los Mochis, Culiacán, Guadalajara, and Mexico City)</t>
+          <t>Victoria Sanchez s/n, Col. Estado 30, Guerrero Negro, Baja California Sur, 23940</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Imported premium seafood, wagyu, and oriental cuisine supplies. Products mentioned include smoked eel, hamachi fillet, soft-shell crab, masago, langostino, tiger shrimp.</t>
+          <t>Live Red Abalone, Cultured Live Red Abalone, Blue and Yellow Canned Abalone, Yellow and Blue Abalone (frozen).</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Explicitly imports seafood from various countries and specializes in supplies for oriental cuisine, where abalone is a key product. Possesses a strong distribution network across Mexico.</t>
+          <t>Explicitly imports and distributes abalone, acts as an agent, and deals with both live and canned abalone.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGZAJLAMkuIRT2SJZy4_LMCS0YEHBaLEV3uNNvyo_6qjuNukemFvTb2riRNlf6Y_eb0QOnBfUKIkNRGgwPQ0HRaFdsRwduGKkx8wQ2viuu2e4n2vMcwFmNdwBlZrdWJZg==</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Abalone is not explicitly listed in their product examples, but their focus on imported seafood and oriental cuisine supplies makes it highly probable.</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEywKxEIyVlMNjfilH11VDswQqsLbyNCU7KB_sereg0oMd6MEBpTRLhahJSb5ITplmF-lGSCyPqmzVjEvIRUUGjTD8ks23jykrR0C5IlZx-us7Uhww1TkqIWDq3d_g75TtnWphZSRfxCKtdPR7qLt6KUMo6XIBaSHqS9NjgbTEworKmrpJVnpV6fm7Igv28sf0h</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3995,7 +3983,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Olanda Seafood Trading Inc.</t>
+          <t>GlobalPezk</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4005,18 +3993,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ventas@olandaseafood.com</t>
+          <t>info@globalpezk.com</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>www.olandaseafood.com</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>globalpezk.com</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>+52 (669) 980 6440 (Whatsapp for Mazatlán)</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Commercialization of seafood products from different parts of the world, importing and distributing fresh and frozen seafood, including shellfish. Focus on quality and freshness, and supplies for the Oriental gastronomic sector.</t>
+          <t>Import and commercialization of premium seafood and exclusive supplies for oriental cuisine from the USA, China, Japan, and Canada. Wholesale and retail with national coverage in Mexico.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4031,27 +4023,27 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Boulevard Tercera Oeste 17503 Int 1 Garita de Otay, Otay, Tijuana, B.C., 22430</t>
+          <t>Blvd. Fundadores 6119 Int. 11. El Rubí, C.P 22626, Tijuana, B.C. (Also operates in Mazatlán, Los Mochis, Culiacán, Guadalajara, and Mexico City)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Import and commercialization of seafood, including shellfish. Products mentioned include salmon, octopus, shrimp, frozen fish, frozen noodles.</t>
+          <t>Imported premium seafood, wagyu, and oriental cuisine supplies. Products mentioned include smoked eel, hamachi fillet, soft-shell crab, masago, langostino, tiger shrimp.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Explicitly imports and distributes seafood. While abalone is not explicitly listed in their product snippets, 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
+          <t>Explicitly imports seafood from various countries and specializes in supplies for oriental cuisine, where abalone is a key product. Possesses a strong distribution network across Mexico.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNYFpQ3-O5BAGOJXp-8-1MXgnYuTONmz1IeuKZ8cjTcQDFTiUIliVDTOUiVv-9Pmlv-_yFfxQMX7171TKmxWaTj2u0Zkeu7QCZma2SACK8gvTa_I4BkXwS3dQs</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGZAJLAMkuIRT2SJZy4_LMCS0YEHBaLEV3uNNvyo_6qjuNukemFvTb2riRNlf6Y_eb0QOnBfUKIkNRGgwPQ0HRaFdsRwduGKkx8wQ2viuu2e4n2vMcwFmNdwBlZrdWJZg==</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Abalone is not explicitly listed in their product snippets, but 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
+          <t>Abalone is not explicitly listed in their product examples, but their focus on imported seafood and oriental cuisine supplies makes it highly probable.</t>
         </is>
       </c>
     </row>
@@ -4063,12 +4055,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Adri &amp; Zoon Schaal- en Schelpdierenhandel B.V.</t>
+          <t>Olanda Seafood Trading Inc.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4078,51 +4070,55 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>info@adrienzoon.nl</t>
+          <t>ventas@olandaseafood.com</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.adrienzoon.com</t>
+          <t>www.olandaseafood.com</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>전 세계 25개 어시장에서 해산물을 조달하며, 생선, 조개류, 갑각류를 수입, 수출, 도매 및 유통합니다.</t>
+          <t>Commercialization of seafood products from different parts of the world, importing and distributing fresh and frozen seafood, including shellfish. Focus on quality and freshness, and supplies for the Oriental gastronomic sector.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Yerseke</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Krab 17, 4401 PA Yerseke</t>
+          <t>Boulevard Tercera Oeste 17503 Int 1 Garita de Otay, Otay, Tijuana, B.C., 22430</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>전복 (Abalone), 아만데스/도그 코클 (Amandes/Dog Cockles), 멸치 (Anchovies), 북극 곤들매기 (Arctic char), 홍합 (Blue Mussels), 갈색 게 (Brown Crab), 대구 (Cod), 가재 (Crayfish), 굴 (Oysters), 기타 조개류 및 갑각류, 신선 수입 생선, 북해 생선, 냉동 해산물, 해초, 비식품 품목. 맞춤형 필레 및 포장 서비스를 제공합니다.</t>
+          <t>Import and commercialization of seafood, including shellfish. Products mentioned include salmon, octopus, shrimp, frozen fish, frozen noodles.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1983년부터 운영된 가족 기업으로, 고객, 공급업체 및 직원과의 장기적인 파트너십에 중점을 둡니다. 고품질의 맞춤형 서비스를 제공하며, 친환경 어업 방식과 전기 트레일러 사용 등 지속 가능한 관행을 추구합니다. 자체 운송 차량을 통해 전 세계로 배송합니다.</t>
+          <t>Explicitly imports and distributes seafood. While abalone is not explicitly listed in their product snippets, 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://www.adrienzoon.com/contact</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNYFpQ3-O5BAGOJXp-8-1MXgnYuTONmz1IeuKZ8cjTcQDFTiUIliVDTOUiVv-9Pmlv-_yFfxQMX7171TKmxWaTj2u0Zkeu7QCZma2SACK8gvTa_I4BkXwS3dQs</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Abalone is not explicitly listed in their product snippets, but 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4137,7 +4133,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Starco Foodstuff</t>
+          <t>Adri &amp; Zoon Schaal- en Schelpdierenhandel B.V.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4145,21 +4141,25 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>info@adrienzoon.nl</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
+          <t>https://www.adrienzoon.com</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>냉동 전복 조개류를 포함한 다양한 제품의 공급업체 및 수출업체입니다. 보리, 목재 펠릿, 새우, 복사 용지, 금속 등도 취급합니다.</t>
+          <t>전 세계 25개 어시장에서 해산물을 조달하며, 생선, 조개류, 갑각류를 수입, 수출, 도매 및 유통합니다.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Heerlen</t>
+          <t>Yerseke</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4169,44 +4169,40 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Hoofdstraat 208, Hoensbroek</t>
+          <t>Krab 17, 4401 PA Yerseke</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>냉동 전복 조개류 (Frozen Abalone Shellfish), 보리 (Barley), 목재 펠릿 (Wood Pellets), 새우 (Shrimps), 복사 용지 (Copy Paper), 폐철 (Used Rail Scrap), 구리 음극 (Copper Cathode), 아몬드 (Almond Nuts), 알루미늄 잉곳 (Aluminium Ingots), 냉동 닭고기 (Frozen Chicken), 양고기 (Lamb/Mutton Meat).</t>
+          <t>전복 (Abalone), 아만데스/도그 코클 (Amandes/Dog Cockles), 멸치 (Anchovies), 북극 곤들매기 (Arctic char), 홍합 (Blue Mussels), 갈색 게 (Brown Crab), 대구 (Cod), 가재 (Crayfish), 굴 (Oysters), 기타 조개류 및 갑각류, 신선 수입 생선, 북해 생선, 냉동 해산물, 해초, 비식품 품목. 맞춤형 필레 및 포장 서비스를 제공합니다.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>B2B 플랫폼인 Tradewheel.com에 냉동 전복 조개류 공급업체로 등록되어 있습니다. 2019년에 설립되었습니다. 매우 다양한 제품군을 취급하는 일반 무역 회사일 수 있습니다.</t>
+          <t>1983년부터 운영된 가족 기업으로, 고객, 공급업체 및 직원과의 장기적인 파트너십에 중점을 둡니다. 고품질의 맞춤형 서비스를 제공하며, 친환경 어업 방식과 전기 트레일러 사용 등 지속 가능한 관행을 추구합니다. 자체 운송 차량을 통해 전 세계로 배송합니다.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>이메일 주소는 Tradewheel.com 프로필에 직접 공개되어 있지 않습니다.</t>
-        </is>
-      </c>
+          <t>https://www.adrienzoon.com/contact</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kiwi Fish</t>
+          <t>Starco Foodstuff</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4217,48 +4213,48 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://kiwifish.co.nz</t>
+          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Premium seafood wholesaler, supplying an extensive range of live, chilled, and frozen shellfish, including pāua (abalone), to various markets including superyachts.</t>
+          <t>냉동 전복 조개류를 포함한 다양한 제품의 공급업체 및 수출업체입니다. 보리, 목재 펠릿, 새우, 복사 용지, 금속 등도 취급합니다.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Heerlen</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Central Auckland</t>
+          <t>Hoofdstraat 208, Hoensbroek</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Offers the best of New Zealand's sustainably caught seafood harvest, custom processed and delivered. Operates a Risk Management Programme (RMP) approved and audited by the Ministry for Primary Industries (MPI).</t>
+          <t>냉동 전복 조개류 (Frozen Abalone Shellfish), 보리 (Barley), 목재 펠릿 (Wood Pellets), 새우 (Shrimps), 복사 용지 (Copy Paper), 폐철 (Used Rail Scrap), 구리 음극 (Copper Cathode), 아몬드 (Almond Nuts), 알루미늄 잉곳 (Aluminium Ingots), 냉동 닭고기 (Frozen Chicken), 양고기 (Lamb/Mutton Meat).</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Established premium seafood wholesaler with a wide range of products and strong quality control, suggesting capability for distributing abalone within New Zealand.</t>
+          <t>B2B 플랫폼인 Tradewheel.com에 냉동 전복 조개류 공급업체로 등록되어 있습니다. 2019년에 설립되었습니다. 매우 다양한 제품군을 취급하는 일반 무역 회사일 수 있습니다.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQET8rm6pD2fyT7blQHzUlDu1ArhqNzw8L5XOkDHPt6BbyoKTCVauxe6Oxsjy7ctVUvrR8vDBXtaw4VbGut7tDCnC3Pj4-1Xvaq0HCMnqW3hIuF82K8ePbg==</t>
+          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Distributes New Zealand-sourced abalone (pāua).</t>
+          <t>이메일 주소는 Tradewheel.com 프로필에 직접 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4271,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Waters Marine Limited</t>
+          <t>Kiwi Fish</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4283,29 +4279,21 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>hello@northernwaters.co.nz</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://northernwaters.co.nz</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Facebook, TikTok, Instagram</t>
-        </is>
-      </c>
+          <t>https://kiwifish.co.nz</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sells whole pāua (abalone) for wholesale and retail.</t>
+          <t>Premium seafood wholesaler, supplying an extensive range of live, chilled, and frozen shellfish, including pāua (abalone), to various markets including superyachts.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Warkworth</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4315,22 +4303,22 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>182 State Highway 1, Warkworth 0981, New Zealand (AUK Dome Valley)</t>
+          <t>Central Auckland</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sustainably harvested whole pāua (abalone) from the waters of Wairarapa and the South Island, offering authentic New Zealand flavor. Available for pickup or delivery.</t>
+          <t>Offers the best of New Zealand's sustainably caught seafood harvest, custom processed and delivered. Operates a Risk Management Programme (RMP) approved and audited by the Ministry for Primary Industries (MPI).</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Direct supplier and wholesaler of whole abalone, with clear contact information and a focus on sustainably harvested local product for the New Zealand market.</t>
+          <t>Established premium seafood wholesaler with a wide range of products and strong quality control, suggesting capability for distributing abalone within New Zealand.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUTHdE_OizUFY_wnDheiVjs5gz8f6C2bi2M-kQnU8AHGUWDyfJfhJEeNJt5ZarxJzqydgApFymnTwOlFD3rW2VhMd-tPSVGo3JAsYEGcp40Nc3oTgS5tR5neHphsqorpRO59dq267d84rNGLqV6wH6d8HO7QE==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQET8rm6pD2fyT7blQHzUlDu1ArhqNzw8L5XOkDHPt6BbyoKTCVauxe6Oxsjy7ctVUvrR8vDBXtaw4VbGut7tDCnC3Pj4-1Xvaq0HCMnqW3hIuF82K8ePbg==</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4352,7 +4340,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sunz Seafood</t>
+          <t>Northern Waters Marine Limited</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4360,21 +4348,29 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>hello@northernwaters.co.nz</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://sunzseafood.co.nz</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>https://northernwaters.co.nz</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Facebook, TikTok, Instagram</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Wholesale and foodservice distribution of New Zealand minced pāua (abalone).</t>
+          <t>Sells whole pāua (abalone) for wholesale and retail.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Whitianga</t>
+          <t>Warkworth</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4384,44 +4380,44 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>269 South Highway West Whitianga 3510</t>
+          <t>182 State Highway 1, Warkworth 0981, New Zealand (AUK Dome Valley)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Premium New Zealand minced pāua (abalone), wild-caught and hand-harvested from Wairarapa and South Island, processed to export standards and frozen fresh. Offers meat-only pāua, ideal for patties, fritters, and commercial kitchen use.</t>
+          <t>Sustainably harvested whole pāua (abalone) from the waters of Wairarapa and the South Island, offering authentic New Zealand flavor. Available for pickup or delivery.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Established wholesaler and foodservice supplier of abalone meat within New Zealand, indicating a strong distribution network for locally sourced product.</t>
+          <t>Direct supplier and wholesaler of whole abalone, with clear contact information and a focus on sustainably harvested local product for the New Zealand market.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6XLTPVgpag7xKK9QzbM_253BrUulevcWOCSV-khxpvqieFX7K7bO3HslNSPhfSIJySeYWXSDhgResGgoCJy1BNk6USQXQpWs7QU9S16CwXnw3H-JmFBse6B2Q6YReNBZXV8pjWQbq-KKVPcA-Zat9UCHvP7N6mtg50x-AO6e4Da1VnfLE</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUTHdE_OizUFY_wnDheiVjs5gz8f6C2bi2M-kQnU8AHGUWDyfJfhJEeNJt5ZarxJzqydgApFymnTwOlFD3rW2VhMd-tPSVGo3JAsYEGcp40Nc3oTgS5tR5neHphsqorpRO59dq267d84rNGLqV6wH6d8HO7QE==</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Primarily distributes New Zealand-sourced abalone (pāua).</t>
+          <t>Distributes New Zealand-sourced abalone (pāua).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FoodPhil Corporation</t>
+          <t>Sunz Seafood</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4432,42 +4428,50 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://foodphil.com/</t>
+          <t>https://sunzseafood.co.nz</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Frozen and fresh seafood, including abalone, scallop, shrimps, lobsters, crabs, crablets, crabmeat.</t>
+          <t>Wholesale and foodservice distribution of New Zealand minced pāua (abalone).</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Whitianga</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>269 South Highway West Whitianga 3510</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Proven trader of frozen and fresh seafood, supplying to several restaurants, distributors, and malls around the Philippines.</t>
+          <t>Premium New Zealand minced pāua (abalone), wild-caught and hand-harvested from Wairarapa and South Island, processed to export standards and frozen fresh. Offers meat-only pāua, ideal for patties, fritters, and commercial kitchen use.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Established in 2007, they are a reliable supplier of frozen and fresh seafood to hotels, restaurants, and retailers.</t>
+          <t>Established wholesaler and foodservice supplier of abalone meat within New Zealand, indicating a strong distribution network for locally sourced product.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://foodphil.com/</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6XLTPVgpag7xKK9QzbM_253BrUulevcWOCSV-khxpvqieFX7K7bO3HslNSPhfSIJySeYWXSDhgResGgoCJy1BNk6USQXQpWs7QU9S16CwXnw3H-JmFBse6B2Q6YReNBZXV8pjWQbq-KKVPcA-Zat9UCHvP7N6mtg50x-AO6e4Da1VnfLE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Primarily distributes New Zealand-sourced abalone (pāua).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4482,7 +4486,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pancoastal International</t>
+          <t>FoodPhil Corporation</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4493,18 +4497,18 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://pancoastal.com/</t>
+          <t>https://foodphil.com/</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Importation, distribution, wholesale, and retail of premium frozen seafood. Product range includes Atlantic Salmon, Coho Salmon, Barramundi, Pompano, Chilean Seabass, Tuna.</t>
+          <t>Frozen and fresh seafood, including abalone, scallop, shrimps, lobsters, crabs, crablets, crabmeat.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Metro Manila</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4515,24 +4519,20 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Specializes in premium frozen seafood, sourcing globally from Canada, Chile, Norway, EU, China, Vietnam, and USA. Serves restaurants, hotels, supermarkets, wholesalers, and retailers.</t>
+          <t>Proven trader of frozen and fresh seafood, supplying to several restaurants, distributors, and malls around the Philippines.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Dedicated to offering a diverse range of top-quality imported seafood and leading the market in high-quality seafood distribution.</t>
+          <t>Established in 2007, they are a reliable supplier of frozen and fresh seafood to hotels, restaurants, and retailers.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://pancoastal.com/</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Abalone is not explicitly listed in their product examples, but their general scope as a 'premium frozen seafood importer' and distributor makes them a strong potential partner for abalone. Contact details like email/LinkedIn/messenger not explicitly listed on the homepage, but a 'Contact' page is available on their website.</t>
-        </is>
-      </c>
+          <t>https://foodphil.com/</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TC International Seafoods Provider Inc.</t>
+          <t>Pancoastal International</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4556,14 +4556,22 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://pancoastal.com/</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Manufacturing, import and export of Fresh Frozen Marine products, including Frozen Boiled Abalone Meat.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Importation, distribution, wholesale, and retail of premium frozen seafood. Product range includes Atlantic Salmon, Coho Salmon, Barramundi, Pompano, Chilean Seabass, Tuna.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Philippines</t>
@@ -4572,22 +4580,22 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Actively trading in Taiwan, China, Hong Kong, Vietnam, USA and Canada.</t>
+          <t>Specializes in premium frozen seafood, sourcing globally from Canada, Chile, Norway, EU, China, Vietnam, and USA. Serves restaurants, hotels, supermarkets, wholesalers, and retailers.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Engaged in both import and export of fresh frozen marine products, indicating a strong supply chain and market presence.</t>
+          <t>Dedicated to offering a diverse range of top-quality imported seafood and leading the market in high-quality seafood distribution.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHuXKC2Pza8RjFQF46dD1k1qjUsZOZYpuhqP_IeQ9NAgxgU5WN--XiuJAdSYdV639ettOP0E8pmoUv3ePW26aNr17kXVLhBdJmbwcr7SiA7-K-5MOvza_DQsawn51Im7X9ksC7MtyPAsNMpSMlBQfligeiYlwfRTvQbojapfK_uRtBC</t>
+          <t>https://pancoastal.com/</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Specific city within the Philippines not found in the provided snippets. Contact details like email/website not explicitly listed in the search results.</t>
+          <t>Abalone is not explicitly listed in their product examples, but their general scope as a 'premium frozen seafood importer' and distributor makes them a strong potential partner for abalone. Contact details like email/LinkedIn/messenger not explicitly listed on the homepage, but a 'Contact' page is available on their website.</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4607,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>㈜제이에스코리아</t>
+          <t>TC International Seafoods Provider Inc.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4613,50 +4621,38 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>js-korea.com</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>전복, 굴 등 어패류 가공 및 수출 전문. 활어, 냉동, 통조림 등 다양한 형태로 가공하여 홍콩, 싱가포르, 베트남, 캐나다 등 세계 각지에 수출.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>완도</t>
-        </is>
-      </c>
+          <t>Manufacturing, import and export of Fresh Frozen Marine products, including Frozen Boiled Abalone Meat.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>완도에 본사 및 식품 가공 공장 위치.</t>
-        </is>
-      </c>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>전복 가공식품 (통조림, 소스, 죽, 장 등), 굴 가공식품, 해외 수출. K·FISH 인증 보유.</t>
+          <t>Actively trading in Taiwan, China, Hong Kong, Vietnam, USA and Canada.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>전복 가공 기술 및 수출 노하우가 뛰어나며, K·FISH 인증을 통해 품질 안정성을 확보하고 다양한 가공 제품으로 해외 시장에 진출하고 있습니다.</t>
+          <t>Engaged in both import and export of fresh frozen marine products, indicating a strong supply chain and market presence.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvnf2Abv7NqaI1pbEBcXg5_-hi89lZ5556iuwdFyRctwjXwyaEYhM901eVExey6vZHCLG2nr3C1Ds3UgxRZBC2l7XMO0V9Hwe2dSiv9Eiln8VAsVxufluTjNuYHTksoBQK1LF7NASp5z_cPjB03gfmajsqvetdJ_MZQMDDQHE_kel2J0KkBfswaCR-M4EiTiX4uJYtFdg5QL47Zt8rQ4DJ7Hke9DdDqsWHLKoplDUi9hbzGTMsS37FIrEp1_O71yNFk4e8cwEwaSAIU9C-xfFqHRF_cTbnsDkL515JE3vwHY6A2yA36BPJZHGFFp1QPwcNMRBp7ltExYN9-pcsBO_T3RPaRjmUxAKC0G3FnWNyoXPT7et58evQA0Rcp1h2iJK22EkfH4CpCY1dkQuXFfkbgr6h6KCIA==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHuXKC2Pza8RjFQF46dD1k1qjUsZOZYpuhqP_IeQ9NAgxgU5WN--XiuJAdSYdV639ettOP0E8pmoUv3ePW26aNr17kXVLhBdJmbwcr7SiA7-K-5MOvza_DQsawn51Im7X9ksC7MtyPAsNMpSMlBQfligeiYlwfRTvQbojapfK_uRtBC</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+          <t>Specific city within the Philippines not found in the provided snippets. Contact details like email/website not explicitly listed in the search results.</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4669,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>㈜청산바다</t>
+          <t>㈜제이에스코리아</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4684,13 +4680,13 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>cheongsanbada.com</t>
+          <t>js-korea.com</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>전복 생산, 유통, 수출, 가공, 판매를 원스톱으로 진행하는 생산자 조합 회사. 일본, 홍콩, 유럽, 미국 등 해외 수출 및 국내 최고급 호텔, 백화점 거래.</t>
+          <t>전복, 굴 등 어패류 가공 및 수출 전문. 활어, 냉동, 통조림 등 다양한 형태로 가공하여 홍콩, 싱가포르, 베트남, 캐나다 등 세계 각지에 수출.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4705,27 +4701,27 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>전남 완도군 완도읍 농공단지4길 22-7</t>
+          <t>완도에 본사 및 식품 가공 공장 위치.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>활전복, 전복 가공식품, 아시아 최초 ASC 인증 보유.</t>
+          <t>전복 가공식품 (통조림, 소스, 죽, 장 등), 굴 가공식품, 해외 수출. K·FISH 인증 보유.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>전복 생산부터 수출까지 전 과정을 직접 관리하며, 아시아 최초 ASC 인증을 통해 품질과 지속가능성을 인정받았습니다. 해외 시장에 대한 높은 이해도와 유통망을 보유하고 있습니다.</t>
+          <t>전복 가공 기술 및 수출 노하우가 뛰어나며, K·FISH 인증을 통해 품질 안정성을 확보하고 다양한 가공 제품으로 해외 시장에 진출하고 있습니다.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVkzRFigxKCfhziKW_fKDfhJoYijxhubjB5tnFMmsV-sW4Hy7O47UY7PSizNwgsH9ltf3nlA7J_PcfmA2VN8TcatJD25HrYqVUA4eEVj5_as7jOPqqp9X38PI99eMFTx96G1kBBqatrgJmAqFLEwSfcCW_l6aPl4a7ueV0NkLYLdFEZltKfZAJ0nJdrlEcxLNzCY4xx-4CVxPPNRSUu8OA6l9jflRKq5crSvp4aoZzg8LOXK_2P7byIJdl-QxIVlAA5QWCiUfuaUts400REyvusr10ZahsNebaiZTaok3EDYrSY0J10Sq-yuiN34IlTHLWVfNEWYCVxkzX4Ix3EAkZWzRvYeJkFLlH3lZi7Po_Ul7QhAwasnpX0fHZVEtJ</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvnf2Abv7NqaI1pbEBcXg5_-hi89lZ5556iuwdFyRctwjXwyaEYhM901eVExey6vZHCLG2nr3C1Ds3UgxRZBC2l7XMO0V9Hwe2dSiv9Eiln8VAsVxufluTjNuYHTksoBQK1LF7NASp5z_cPjB03gfmajsqvetdJ_MZQMDDQHE_kel2J0KkBfswaCR-M4EiTiX4uJYtFdg5QL47Zt8rQ4DJ7Hke9DdDqsWHLKoplDUi9hbzGTMsS37FIrEp1_O71yNFk4e8cwEwaSAIU9C-xfFqHRF_cTbnsDkL515JE3vwHY6A2yA36BPJZHGFFp1QPwcNMRBp7ltExYN9-pcsBO_T3RPaRjmUxAKC0G3FnWNyoXPT7et58evQA0Rcp1h2iJK22EkfH4CpCY1dkQuXFfkbgr6h6KCIA==</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>고객센터 전화번호는 061-553-5900이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+          <t>이메일은 웹사이트에 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4738,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>완도전복주식회사</t>
+          <t>㈜청산바다</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4753,13 +4749,13 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>wakorea.kr</t>
+          <t>cheongsanbada.com</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>국내외 기업 및 개인 고객을 대상으로 활전복 및 가공전복 공급, 국내 최대 활전복 유통 및 가공전복 제품 생산, 롯데마트, 이마트, CJ프레시웨이 등 주요 거래처, 일본, 미국, 싱가포르 등 동남아 지역 수출.</t>
+          <t>전복 생산, 유통, 수출, 가공, 판매를 원스톱으로 진행하는 생산자 조합 회사. 일본, 홍콩, 유럽, 미국 등 해외 수출 및 국내 최고급 호텔, 백화점 거래.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4774,27 +4770,27 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>전라남도 완도군</t>
+          <t>전남 완도군 완도읍 농공단지4길 22-7</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>활전복, 가공전복 (통조림, 동결제품), 국내 대형 유통망 공급, 해외 수출.</t>
+          <t>활전복, 전복 가공식품, 아시아 최초 ASC 인증 보유.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>생산 어민과 완도군이 공동 출자하여 설립된 국내 최대 전복 전문 기업으로, 안정적인 공급망과 광범위한 국내외 유통망을 보유하고 있습니다.</t>
+          <t>전복 생산부터 수출까지 전 과정을 직접 관리하며, 아시아 최초 ASC 인증을 통해 품질과 지속가능성을 인정받았습니다. 해외 시장에 대한 높은 이해도와 유통망을 보유하고 있습니다.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVUzQYPzka2YSdvtxrcdlEwnD9kMLBlEc0nUobdRmu7Sh6VCkqAI7XZdkeOmLwU4iXbob_FjOZxeI7_jSshQFyj4k2SrvUPYNeiS2umO4l</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVkzRFigxKCfhziKW_fKDfhJoYijxhubjB5tnFMmsV-sW4Hy7O47UY7PSizNwgsH9ltf3nlA7J_PcfmA2VN8TcatJD25HrYqVUA4eEVj5_as7jOPqqp9X38PI99eMFTx96G1kBBqatrgJmAqFLEwSfcCW_l6aPl4a7ueV0NkLYLdFEZltKfZAJ0nJdrlEcxLNzCY4xx-4CVxPPNRSUu8OA6l9jflRKq5crSvp4aoZzg8LOXK_2P7byIJdl-QxIVlAA5QWCiUfuaUts400REyvusr10ZahsNebaiZTaok3EDYrSY0J10Sq-yuiN34IlTHLWVfNEWYCVxkzX4Ix3EAkZWzRvYeJkFLlH3lZi7Po_Ul7QhAwasnpX0fHZVEtJ</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>고객센터 전화번호는 1577-8855이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+          <t>고객센터 전화번호는 061-553-5900이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4802,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dakar Ice</t>
+          <t>완도전복주식회사</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4819,72 +4815,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>contact@dakarice.com</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>http://www.dakarice.com</t>
+          <t>wakorea.kr</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>수입/유통 (Import/Distribution)</t>
+          <t>국내외 기업 및 개인 고객을 대상으로 활전복 및 가공전복 공급, 국내 최대 활전복 유통 및 가공전복 제품 생산, 롯데마트, 이마트, CJ프레시웨이 등 주요 거래처, 일본, 미국, 싱가포르 등 동남아 지역 수출.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>완도</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Hann plage, au km 5 boulevard de la commune de Dakar</t>
+          <t>전라남도 완도군</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>다양한 어류 취급, 특히 전복(abalone)을 월 최소 1컨테이너 처리 가능.</t>
+          <t>활전복, 가공전복 (통조림, 동결제품), 국내 대형 유통망 공급, 해외 수출.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>전복(abalone)을 월 최소 1컨테이너 규모로 취급하며, 수산물 전반에 대한 경험이 풍부하여 협력 가능성이 높습니다.</t>
+          <t>생산 어민과 완도군이 공동 출자하여 설립된 국내 최대 전복 전문 기업으로, 안정적인 공급망과 광범위한 국내외 유통망을 보유하고 있습니다.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHyVlKRmRztQxojYk66kNXGxJrx8_JI93Lx6e0cD3eq6iNIdAXKWbzug3ERNopXTxQ4Xu-KFj5Nf0dusDVD1ygDla4N1Jmpqe5_Hq1joE8XvJ2ZD6iyhMQbnLgAWb_WAVShMpUIkg==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVUzQYPzka2YSdvtxrcdlEwnD9kMLBlEc0nUobdRmu7Sh6VCkqAI7XZdkeOmLwU4iXbob_FjOZxeI7_jSshQFyj4k2SrvUPYNeiS2umO4l</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Fijin.com에 'Dakar Ice'가 전복을 취급하며 월 최소 1컨테이너를 처리할 수 있다고 명시되어 있습니다. 공식 웹사이트는 검색 결과에서 직접 확인되지 않았으나, 이메일 주소를 통해 도메인을 추정했습니다.</t>
+          <t>고객센터 전화번호는 1577-8855이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Goh Joo Hin Pte Ltd</t>
+          <t>Dakar Ice</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4894,60 +4886,60 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>food@gjh.com.sg</t>
+          <t>contact@dakarice.com</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>http://www.gjh.com.sg</t>
+          <t>http://www.dakarice.com</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Wholesaler, Distributor</t>
+          <t>수입/유통 (Import/Distribution)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
+          <t>Hann plage, au km 5 boulevard de la commune de Dakar</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
+          <t>다양한 어류 취급, 특히 전복(abalone)을 월 최소 1컨테이너 처리 가능.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
+          <t>전복(abalone)을 월 최소 1컨테이너 규모로 취급하며, 수산물 전반에 대한 경험이 풍부하여 협력 가능성이 높습니다.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHyVlKRmRztQxojYk66kNXGxJrx8_JI93Lx6e0cD3eq6iNIdAXKWbzug3ERNopXTxQ4Xu-KFj5Nf0dusDVD1ygDla4N1Jmpqe5_Hq1joE8XvJ2ZD6iyhMQbnLgAWb_WAVShMpUIkg==</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
+          <t>Fijin.com에 'Dakar Ice'가 전복을 취급하며 월 최소 1컨테이너를 처리할 수 있다고 명시되어 있습니다. 공식 웹사이트는 검색 결과에서 직접 확인되지 않았으나, 이메일 주소를 통해 도메인을 추정했습니다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-01 13:25:05</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4957,7 +4949,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hosen Group Ltd.</t>
+          <t>Goh Joo Hin Pte Ltd</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4965,12 +4957,20 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>food@gjh.com.sg</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>http://www.gjh.com.sg</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Distributor, Manufacture &amp; Trade</t>
+          <t>Importer, Exporter, Wholesaler, Distributor</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4985,34 +4985,34 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>320 Jalan Boon Lay</t>
+          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Fast-moving consumer goods, including canned seafood. Distributes to Southeast Asia, Australia, Indian Sub-continent, Middle-East, North Asia, Pacific Islands.</t>
+          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>A leading distributor in Singapore's dry goods sector, explicitly stating import and distribution of fast-moving consumer goods, including canned seafood, across Southeast Asia.</t>
+          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHSaPnDkPMuPpMogVwbMshl1E9Nw6aZXhv9a1mjBlCE6ncCrnbj0op79iiQk2fqf2sGIpmnTi8wmK9UUUf37L46yOrLr3fVUEFLzOWZGYp5KtjCBvCptFndM3f7NYMvUxUxOhGHZxiezdgWxQ7JzeIYJXFkhZhMzQFpT6O7LA==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Website and email not publicly available in the snippet. They market their own brands and represent others.</t>
+          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oceanus Group Limited</t>
+          <t>Hosen Group Ltd.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5030,20 +5030,12 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>contact@oceanus.com.sg</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>http://www.oceanus.com.sg</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
+          <t>Importer, Exporter, Distributor, Manufacture &amp; Trade</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5058,27 +5050,27 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
+          <t>320 Jalan Boon Lay</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
+          <t>Fast-moving consumer goods, including canned seafood. Distributes to Southeast Asia, Australia, Indian Sub-continent, Middle-East, North Asia, Pacific Islands.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
+          <t>A leading distributor in Singapore's dry goods sector, explicitly stating import and distribution of fast-moving consumer goods, including canned seafood, across Southeast Asia.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHSaPnDkPMuPpMogVwbMshl1E9Nw6aZXhv9a1mjBlCE6ncCrnbj0op79iiQk2fqf2sGIpmnTi8wmK9UUUf37L46yOrLr3fVUEFLzOWZGYp5KtjCBvCptFndM3f7NYMvUxUxOhGHZxiezdgWxQ7JzeIYJXFkhZhMzQFpT6O7LA==</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
+          <t>Website and email not publicly available in the snippet. They market their own brands and represent others.</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5087,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Teck Sang Pte Ltd</t>
+          <t>Oceanus Group Limited</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5105,18 +5097,18 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>local@tecksang.com</t>
+          <t>contact@oceanus.com.sg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.tecksang.com</t>
+          <t>http://www.oceanus.com.sg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
+          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5131,34 +5123,34 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>11 Hongkong Street, Singapore 059654</t>
+          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
+          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
+          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
+          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-01 13:25:05</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5168,7 +5160,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YL Enterprises (Yilai Abalone)</t>
+          <t>Teck Sang Pte Ltd</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5176,12 +5168,20 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>local@tecksang.com</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.tecksang.com</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Buyer, Importer, Manufacture</t>
+          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5196,44 +5196,44 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>865 Mountbatten Road #03-02, Katong Shopping Centre</t>
+          <t>11 Hongkong Street, Singapore 059654</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Canned abalone processing enterprise, larval nursing, abalone breeding, abalone processing. Exports to Singapore, South East Asia, Taiwan, Hong Kong, Macau.</t>
+          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Directly identified as a Buyer and Importer of abalone in Singapore, with a focus on Southeast Asia and surrounding regions. They also manufacture.</t>
+          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdXWn3sY9CX7JdfaAp4fQShQKS9VRARffKM3O8GOoBfVS1FEP6Hjsur3G3BqYsWUxlytZfFJy78jUCAJHY9defZhq-D_oI3S--AbgjcTdExdiUheXg73Q==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Contact person: Mr. Lim. Phone and fax numbers are listed but incomplete in the snippet. Website not publicly available in the snippet.</t>
+          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlantis Foods</t>
+          <t>YL Enterprises (Yilai Abalone)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5241,55 +5241,47 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>info@atlantisfoods.co.za</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://www.atlantisfoods.co.za/</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>South Africa의 주요 해산물 유통 회사 중 하나로, 도매업체, 식품 서비스 제공업체 및 소매업체에 고품질 해산물 제품을 소싱, 가공 및 유통합니다. 과거 전무이사가 전복(Abalone) 및 냉장 보관을 담당했습니다.</t>
+          <t>Buyer, Importer, Manufacture</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8 Wessex Road Paarden Eiland Cape Town, South Africa, 7405 (Sales &amp; Marketing Office)</t>
+          <t>865 Mountbatten Road #03-02, Katong Shopping Centre</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>다양한 신선, 냉동, 부가가치 및 즉석 해산물 제품을 취급하며, 전복을 포함한 해산물 유통 경험이 있습니다.</t>
+          <t>Canned abalone processing enterprise, larval nursing, abalone breeding, abalone processing. Exports to Singapore, South East Asia, Taiwan, Hong Kong, Macau.</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>남아프리카 공화국 내에서 광범위한 유통망을 가진 대규모 해산물 유통업체로, 다양한 채널에 대량 공급이 가능합니다.</t>
+          <t>Directly identified as a Buyer and Importer of abalone in Singapore, with a focus on Southeast Asia and surrounding regions. They also manufacture.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://www.atlantisfoods.co.za/contact-us/</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdXWn3sY9CX7JdfaAp4fQShQKS9VRARffKM3O8GOoBfVS1FEP6Hjsur3G3BqYsWUxlytZfFJy78jUCAJHY9defZhq-D_oI3S--AbgjcTdExdiUheXg73Q==</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>BestFoodImporters.com에 따르면 'Importer, Distributor, Wholesaler, Supplier'로 분류됩니다. 이전 그룹 물류 관리자가 전복을 담당했다는 언급이 있습니다.</t>
+          <t>Contact person: Mr. Lim. Phone and fax numbers are listed but incomplete in the snippet. Website not publicly available in the snippet.</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5298,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Greenfish</t>
+          <t>Atlantis Foods</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5316,22 +5308,18 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ops@greenfish.co.za, Sales1@greenfish.co.za</t>
+          <t>info@atlantisfoods.co.za</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://greenfish.co.za/</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>063 666 2802 (Whatsapp)</t>
-        </is>
-      </c>
+          <t>https://www.atlantisfoods.co.za/</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>온라인 및 도매 해산물 공급업체로, 양식 전복(perlemoen)을 포함한 신선한 해산물을 취급합니다.</t>
+          <t>South Africa의 주요 해산물 유통 회사 중 하나로, 도매업체, 식품 서비스 제공업체 및 소매업체에 고품질 해산물 제품을 소싱, 가공 및 유통합니다. 과거 전무이사가 전복(Abalone) 및 냉장 보관을 담당했습니다.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5346,27 +5334,27 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>온라인 전용 (소매점 없음), Cape Town 및 주변 지역(CBD, Southern Suburbs, Houtbay, Plattekloof, Deep South, Table View, Blouberg, Melkbos, Durbanville, Stellenbosch, Somerset West, Franschhoek, Paarl) 배송 가능.</t>
+          <t>8 Wessex Road Paarden Eiland Cape Town, South Africa, 7405 (Sales &amp; Marketing Office)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>6개들이 라이브 양식 전복(perlemoen)을 판매하며, 노르웨이산 연어, 대구, 참치, 킹클립, 홍합, 굴, 옐로우테일, 카벨조우 등 다양한 신선 해산물을 제공합니다.</t>
+          <t>다양한 신선, 냉동, 부가가치 및 즉석 해산물 제품을 취급하며, 전복을 포함한 해산물 유통 경험이 있습니다.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>양식 전복을 직접 공급하며, 개인 소비자 및 도매 고객 모두에게 서비스를 제공합니다. 소규모 또는 전문적인 주문, 레스토랑 직거래에 적합합니다.</t>
+          <t>남아프리카 공화국 내에서 광범위한 유통망을 가진 대규모 해산물 유통업체로, 다양한 채널에 대량 공급이 가능합니다.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://greenfish.co.za/products/abalone-perlemoen-live-box-cultivated-x6</t>
+          <t>https://www.atlantisfoods.co.za/contact-us/</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>온라인 전용 업체이며, 소매점은 없습니다.</t>
+          <t>BestFoodImporters.com에 따르면 'Importer, Distributor, Wholesaler, Supplier'로 분류됩니다. 이전 그룹 물류 관리자가 전복을 담당했다는 언급이 있습니다.</t>
         </is>
       </c>
     </row>
@@ -5378,12 +5366,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FRESHCADO RECIEN PESCADO SL</t>
+          <t>Greenfish</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5393,51 +5381,59 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>contact@freshcado.es</t>
+          <t>ops@greenfish.co.za, Sales1@greenfish.co.za</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://freshcado.es</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>https://greenfish.co.za/</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>063 666 2802 (Whatsapp)</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Wholesale and retail of fresh and frozen fish and seafood, including premium seafood. Operates as an online fishmonger and supplies professionals across Spain, sourcing from Mercamadrid and international ports.</t>
+          <t>온라인 및 도매 해산물 공급업체로, 양식 전복(perlemoen)을 포함한 신선한 해산물을 취급합니다.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>C/ de la Diputació, 256, 08007 Barcelona</t>
+          <t>온라인 전용 (소매점 없음), Cape Town 및 주변 지역(CBD, Southern Suburbs, Houtbay, Plattekloof, Deep South, Table View, Blouberg, Melkbos, Durbanville, Stellenbosch, Somerset West, Franschhoek, Paarl) 배송 가능.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Offers a wide selection of fresh and frozen seafood. Emphasizes maximum freshness, direct product from Mercamadrid, and 24/48h delivery. Committed to sustainability and responsible fishing.</t>
+          <t>6개들이 라이브 양식 전복(perlemoen)을 판매하며, 노르웨이산 연어, 대구, 참치, 킹클립, 홍합, 굴, 옐로우테일, 카벨조우 등 다양한 신선 해산물을 제공합니다.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>As a large seafood wholesaler and online retailer with a wide range of fresh and frozen seafood, including a 'Premium Seafood' category, Freshcado is a strong prospect for importing and distributing abalone.</t>
+          <t>양식 전복을 직접 공급하며, 개인 소비자 및 도매 고객 모두에게 서비스를 제공합니다. 소규모 또는 전문적인 주문, 레스토랑 직거래에 적합합니다.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://freshcado.es/legal-notice/, https://freshcado.es/accessibility-statement/, https://freshcado.es/general-terms-and-conditions/, https://freshcado.es/en/fish-and-seafood-wholesaler-in-spain/, https://freshcado.es/en/online-fishmonger-buy-fresh-fish-and-seafood/, https://freshcado.es/en/comprar-smoked-and-canned-products-online/</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
+          <t>https://greenfish.co.za/products/abalone-perlemoen-live-box-cultivated-x6</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>온라인 전용 업체이며, 소매점은 없습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5452,7 +5448,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Globalimar Europa, SL</t>
+          <t>FRESHCADO RECIEN PESCADO SL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5462,23 +5458,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>info@globalimar.com</t>
+          <t>contact@freshcado.es</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.globalimar.com</t>
+          <t>https://freshcado.es</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Frozen seafood import, production, and commercialization for mass-market, including bivalves, cephalopods, crustaceans, surimi, and prepared fish. Serves Spain, Europe, USA, and Maghreb region.</t>
+          <t>Wholesale and retail of fresh and frozen fish and seafood, including premium seafood. Operates as an online fishmonger and supplies professionals across Spain, sourcing from Mercamadrid and international ports.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Llagostera</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5488,22 +5484,22 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>C/ Jaume I, 2A, 17240 Llagostera, Girona</t>
+          <t>C/ de la Diputació, 256, 08007 Barcelona</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Specialists in frozen seafood products, with a focus on quality and sustainability. Offers a diversified range of frozen seafood. Explicitly states import and commercialization activities.</t>
+          <t>Offers a wide selection of fresh and frozen seafood. Emphasizes maximum freshness, direct product from Mercamadrid, and 24/48h delivery. Committed to sustainability and responsible fishing.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Explicitly states 'import, produce and commercialize' frozen seafood. Their broad range of seafood products, including bivalves, makes them a highly probable candidate for importing abalone.</t>
+          <t>As a large seafood wholesaler and online retailer with a wide range of fresh and frozen seafood, including a 'Premium Seafood' category, Freshcado is a strong prospect for importing and distributing abalone.</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://www.globalimar.com/contact/, https://www.conxemar.com/en/asociados/globalimar-europa-sl, https://www.conxemar.com/en/exhibitor/globalimar-europa-sl-conxemar-2024, https://www.globalimar.com/en/company/specialists-in-frozen-seafood/, https://www.bestfoodimporters.com/importer/globalimar-europa</t>
+          <t>https://freshcado.es/legal-notice/, https://freshcado.es/accessibility-statement/, https://freshcado.es/general-terms-and-conditions/, https://freshcado.es/en/fish-and-seafood-wholesaler-in-spain/, https://freshcado.es/en/online-fishmonger-buy-fresh-fish-and-seafood/, https://freshcado.es/en/comprar-smoked-and-canned-products-online/</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
@@ -5521,7 +5517,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>La Alondra Seafood (Pescados La Alondra Sl)</t>
+          <t>Globalimar Europa, SL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5531,23 +5527,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>hola@laalondraseafood.es</t>
+          <t>info@globalimar.com</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.laalondraseafood.es</t>
+          <t>https://www.globalimar.com</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Distribution of fresh and cryogenized seafood for retail, HORECA channel, and international markets. Focuses on premium seafood products from the best fishing grounds worldwide.</t>
+          <t>Frozen seafood import, production, and commercialization for mass-market, including bivalves, cephalopods, crustaceans, surimi, and prepared fish. Serves Spain, Europe, USA, and Maghreb region.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Llagostera</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5557,22 +5553,22 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Avenida Euro núm. 24 Puesto 17 19 21, 47009 Valladolid, Castilla-león</t>
+          <t>C/ Jaume I, 2A, 17240 Llagostera, Girona</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Specializes in high-quality, fresh, and cryogenized seafood. Offers a catalog of seafood products from the best fishing grounds globally. Strong presence in HORECA and retail, with international distribution capabilities.</t>
+          <t>Specialists in frozen seafood products, with a focus on quality and sustainability. Offers a diversified range of frozen seafood. Explicitly states import and commercialization activities.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Their focus on premium seafood, international distribution, and the HORECA channel makes them a good prospect for importing and distributing abalone. Their advanced cryogenic preservation technology could be a suitable fit for abalone products.</t>
+          <t>Explicitly states 'import, produce and commercialize' frozen seafood. Their broad range of seafood products, including bivalves, makes them a highly probable candidate for importing abalone.</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://www.laalondraseafood.es/en/distribution/, https://www.laalondraseafood.es/en/fresh-fish-and-seafood/, https://www.laalondraseafood.es/en/cryogenized-seafood/, https://www.laalondraseafood.es/en/innovation/, https://www.empresite.com/PESCADOS-LA-ALONDRA-SL.html, https://www.laalondraseafood.es/en/contact/</t>
+          <t>https://www.globalimar.com/contact/, https://www.conxemar.com/en/asociados/globalimar-europa-sl, https://www.conxemar.com/en/exhibitor/globalimar-europa-sl-conxemar-2024, https://www.globalimar.com/en/company/specialists-in-frozen-seafood/, https://www.bestfoodimporters.com/importer/globalimar-europa</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
@@ -5580,17 +5576,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fresh Harvest (Pvt) Ltd</t>
+          <t>La Alondra Seafood (Pescados La Alondra Sl)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5598,60 +5594,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>hola@laalondraseafood.es</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://freshharvest.lk/</t>
+          <t>https://www.laalondraseafood.es</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Seafood Importer and Distributor</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Distribution of fresh and cryogenized seafood for retail, HORECA channel, and international markets. Focuses on premium seafood products from the best fishing grounds worldwide.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Avenida Euro núm. 24 Puesto 17 19 21, 47009 Valladolid, Castilla-león</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Leading seafood company in Sri Lanka, delivers high quality ready-to-cook seafood products. Caters to local market, supplies to top-class hotel chains, leading restaurants, and expanding in local retail market. Acts as an importer of high quality seafood.</t>
+          <t>Specializes in high-quality, fresh, and cryogenized seafood. Offers a catalog of seafood products from the best fishing grounds globally. Strong presence in HORECA and retail, with international distribution capabilities.</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>스리랑카 현지 시장에 고품질 해산물을 수입하여 호텔, 레스토랑 및 소매점에 공급하는 선도적인 회사입니다. 전복 수입 및 유통에 대한 협력 가능성이 높습니다.</t>
+          <t>Their focus on premium seafood, international distribution, and the HORECA channel makes them a good prospect for importing and distributing abalone. Their advanced cryogenic preservation technology could be a suitable fit for abalone products.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcQYNWYOJvFZ5465KMss_BHieKPxvrhT-oNHOi2KKwePbAueaXewTLSRdFvyC53bKsJB9SxBoH5hsVkTNWMHCaabHTVCeR0iPYsraHevFcJpFSX0n9</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>이메일/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다.</t>
-        </is>
-      </c>
+          <t>https://www.laalondraseafood.es/en/distribution/, https://www.laalondraseafood.es/en/fresh-fish-and-seafood/, https://www.laalondraseafood.es/en/cryogenized-seafood/, https://www.laalondraseafood.es/en/innovation/, https://www.empresite.com/PESCADOS-LA-ALONDRA-SL.html, https://www.laalondraseafood.es/en/contact/</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Johnson Seafood Co., Ltd.</t>
+          <t>Fresh Harvest (Pvt) Ltd</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5662,46 +5666,42 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.johnsonseafood.com.tw</t>
+          <t>https://freshharvest.lk/</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Leading seafood importer in Taiwan. Imports live, frozen, and freshly chilled seafood, including abalone &amp; scallop. Sources from over 40 countries.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Tainan</t>
-        </is>
-      </c>
+          <t>Seafood Importer and Distributor</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Based in Qigu coastal areas around Tainan, aquaculture in Tainan's Jiali Township.</t>
-        </is>
-      </c>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Wide range of seafood products (fish, shrimps, crabs, shellfish, mollusk, processed seafood), regular SGS inspection, provides safe and tasty food materials. Product range covers live seafood, frozen seafood, and freshly chilled seafood.</t>
+          <t>Leading seafood company in Sri Lanka, delivers high quality ready-to-cook seafood products. Caters to local market, supplies to top-class hotel chains, leading restaurants, and expanding in local retail market. Acts as an importer of high quality seafood.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Over 50 years of operation, excellent reputation, sizeable procurement volume, trusted partner by overseas suppliers, and commitment to food safety with SGS inspection.</t>
+          <t>스리랑카 현지 시장에 고품질 해산물을 수입하여 호텔, 레스토랑 및 소매점에 공급하는 선도적인 회사입니다. 전복 수입 및 유통에 대한 협력 가능성이 높습니다.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://www.johnsonseafood.com.tw/about-us/company-profile</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcQYNWYOJvFZ5465KMss_BHieKPxvrhT-oNHOi2KKwePbAueaXewTLSRdFvyC53bKsJB9SxBoH5hsVkTNWMHCaabHTVCeR0iPYsraHevFcJpFSX0n9</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>이메일/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ming Sheng Seafood Co., Ltd.</t>
+          <t>Johnson Seafood Co., Ltd.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5727,18 +5727,18 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.mingsheng.com.tw</t>
+          <t>https://www.johnsonseafood.com.tw</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Importer of fresh frozen marine products, supplying diversified premium seafood to wholesalers across Taiwan. Imports over 300 premium frozen seafood products, sourcing from 4 oceans and 5 continents.</t>
+          <t>Leading seafood importer in Taiwan. Imports live, frozen, and freshly chilled seafood, including abalone &amp; scallop. Sources from over 40 countries.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
+          <t>Tainan</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2F, 332 Zihyou 2nd Rd., Zuoying District, Kaohsiung City, Taiwan.</t>
+          <t>Based in Qigu coastal areas around Tainan, aquaculture in Tainan's Jiali Township.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Over 30 years of experience, strong relationships with manufacturers and customers, world-class logistic system. Offers a set of diversified premium seafood.</t>
+          <t>Wide range of seafood products (fish, shrimps, crabs, shellfish, mollusk, processed seafood), regular SGS inspection, provides safe and tasty food materials. Product range covers live seafood, frozen seafood, and freshly chilled seafood.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Long-standing importer with a wide global sourcing network and a focus on timely delivery to wholesalers. Strong reputation and trust from domestic and international suppliers.</t>
+          <t>Over 50 years of operation, excellent reputation, sizeable procurement volume, trusted partner by overseas suppliers, and commitment to food safety with SGS inspection.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://www.mingsheng.com.tw/about-ming-sheng</t>
+          <t>https://www.johnsonseafood.com.tw/about-us/company-profile</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YEN &amp; Brothers Enterprise CO.,LTD.</t>
+          <t>Ming Sheng Seafood Co., Ltd.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5789,25 +5789,21 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>service@mail.yens.com.tw</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.yens.com.tw</t>
+          <t>https://www.mingsheng.com.tw</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Abalone importer and wholesaler, deals with frozen abalone meat, whole-cooked abalone, Australian abalone. Also handles other fish, crustacean, shellfish, mollusc, meat, soup, prepared foods.</t>
+          <t>Importer of fresh frozen marine products, supplying diversified premium seafood to wholesalers across Taiwan. Imports over 300 premium frozen seafood products, sourcing from 4 oceans and 5 continents.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>New Taipei City</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5817,22 +5813,22 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>14F, NO. 217,SEC. 2, NEW TAIPEI BLVD., XINZHUANG DIST., NEW TAIPEI CITY 242, TAIWAN (R.O.C.)</t>
+          <t>2F, 332 Zihyou 2nd Rd., Zuoying District, Kaohsiung City, Taiwan.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Global purchasing, R&amp;D and production, food safety, logistic management. Importer and wholesaler of various seafood products, including abalone.</t>
+          <t>Over 30 years of experience, strong relationships with manufacturers and customers, world-class logistic system. Offers a set of diversified premium seafood.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Established company with global purchasing capabilities and a strong focus on food safety and quality management. Handles a variety of abalone products (frozen, whole-cooked, Australian).</t>
+          <t>Long-standing importer with a wide global sourcing network and a focus on timely delivery to wholesalers. Strong reputation and trust from domestic and international suppliers.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://www.yens.com.tw/products/shellfish/abalone</t>
+          <t>https://www.mingsheng.com.tw/about-ming-sheng</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
@@ -5840,17 +5836,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
+          <t>YEN &amp; Brothers Enterprise CO.,LTD.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5860,55 +5856,51 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>info@ruifuoilfood.com</t>
+          <t>service@mail.yens.com.tw</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://ruifuoilfood.com/</t>
+          <t>https://www.yens.com.tw</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
+          <t>Abalone importer and wholesaler, deals with frozen abalone meat, whole-cooked abalone, Australian abalone. Also handles other fish, crustacean, shellfish, mollusc, meat, soup, prepared foods.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Si Maha Phot, Prachin Buri</t>
+          <t>New Taipei City</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
+          <t>14F, NO. 217,SEC. 2, NEW TAIPEI BLVD., XINZHUANG DIST., NEW TAIPEI CITY 242, TAIWAN (R.O.C.)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
+          <t>Global purchasing, R&amp;D and production, food safety, logistic management. Importer and wholesaler of various seafood products, including abalone.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
+          <t>Established company with global purchasing capabilities and a strong focus on food safety and quality management. Handles a variety of abalone products (frozen, whole-cooked, Australian).</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
-        </is>
-      </c>
+          <t>https://www.yens.com.tw/products/shellfish/abalone</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5923,7 +5915,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thai Abalone Co.,Ltd.</t>
+          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5931,21 +5923,25 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>info@ruifuoilfood.com</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://m.ec21.com/company/thaiabalone/</t>
+          <t>https://ruifuoilfood.com/</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
+          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Pathiu, Chumphon</t>
+          <t>Si Maha Phot, Prachin Buri</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5955,44 +5951,44 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
+          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
+          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
+          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://m.ec21.com/company/thaiabalone/</t>
+          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
+          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monterey Abalone Company</t>
+          <t>Thai Abalone Co.,Ltd.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6003,48 +5999,48 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://montereyabalone.com</t>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
+          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Monterey</t>
+          <t>Pathiu, Chumphon</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
+          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
+          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
+          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Email not found in provided snippets.</t>
+          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6057,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ocean Floor Inc.</t>
+          <t>Monterey Abalone Company</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6070,38 +6066,50 @@
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://montereyabalone.com</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Monterey</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
+          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
+          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>City, email, and website not found in provided snippets.</t>
+          <t>Email not found in provided snippets.</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6126,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seafarers Inc.</t>
+          <t>Ocean Floor Inc.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6131,7 +6139,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
+          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -6143,12 +6151,12 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
+          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
+          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6165,17 +6173,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Abalone Fish Processing LLC</t>
+          <t>Seafarers Inc.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6188,42 +6196,34 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fish and Seafood Processors</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Ajman</t>
-        </is>
-      </c>
+          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Near Factory Mart, New Ind Area, Ajman / 78a, Amman street, Ajman Industrial 2</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Fish and Seafood Processors. The company name suggests a focus on abalone.</t>
+          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>A seafood processing company, likely involved in the import and distribution of various seafood, potentially including abalone, given its name. They are listed as 'Fish And Seafood Processors'.</t>
+          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHFN1ioKMvAABGXDTz-XA2FisFHogtokbmSflhk3jbvA8p7zaDQFSZwrI0hdELPSZmK4Wc-LYdVkfx9Icf2bIlxGcy5n-3UNZ38yb-YhBVFHE0QP_48m00iz7KofFmbKySqsSnnKW3nKI_I128GTUIQfv-FTBuOaPRMuJfMDST_</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Phone number: 06-7438606</t>
+          <t>City, email, and website not found in provided snippets.</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dior Fresh Fish</t>
+          <t>Abalone Fish Processing LLC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6249,20 +6249,16 @@
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>https://diorfreshfish.com/</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Fresh and frozen seafood, including Whole Shell Abalone. Delivery across UAE (Dubai, Abu Dhabi, Sharjah).</t>
+          <t>Fish and Seafood Processors</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6272,25 +6268,29 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Waterfront market Deira, Dubai.</t>
+          <t>Near Factory Mart, New Ind Area, Ajman / 78a, Amman street, Ajman Industrial 2</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Sells 'Fresh Whole Shell Abalone' sourced from pristine cold-water regions (FAO Areas 27 and 81). Halal Compliant &amp; Hygienically Processed. Cold-Chain Delivery (0–4°C). Offers custom fish preparation and 2-hour/same-day delivery in Dubai, next-day across UAE.</t>
+          <t>Fish and Seafood Processors. The company name suggests a focus on abalone.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Directly imports and distributes abalone, with a focus on quality and cold-chain logistics. They cater to households and high-end restaurants.</t>
+          <t>A seafood processing company, likely involved in the import and distribution of various seafood, potentially including abalone, given its name. They are listed as 'Fish And Seafood Processors'.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF1n6IrUDF_2UqEV1FcEcY_91lJj3LUZsTqcN2E-z6ynL2pmf6_SM1ymPQjnZMML_D3hhCHfVLVikDUjllk1QaU7pVCslFnbxRTPWXUF1y6MLjcD1m-IBi83-ovGxE8KZhXTNMo4yW_3PmnAFzpJ5O5jrf8_bcyfg==</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHFN1ioKMvAABGXDTz-XA2FisFHogtokbmSflhk3jbvA8p7zaDQFSZwrI0hdELPSZmK4Wc-LYdVkfx9Icf2bIlxGcy5n-3UNZ38yb-YhBVFHE0QP_48m00iz7KofFmbKySqsSnnKW3nKI_I128GTUIQfv-FTBuOaPRMuJfMDST_</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Phone number: 06-7438606</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sea World Fish Processing Llc</t>
+          <t>Dior Fresh Fish</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6314,20 +6314,20 @@
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>+971564117152 (WhatsApp)</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://diorfreshfish.com/</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Frozen Seafood, Shrimp, Salmon, Squid, Abalone, Lobster, Tuna, Trevally. Fish &amp; Seafood Importers, Exporters &amp; Processors.</t>
+          <t>Fresh and frozen seafood, including Whole Shell Abalone. Delivery across UAE (Dubai, Abu Dhabi, Sharjah).</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6337,29 +6337,25 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Meena Rd, Nr Fish Market, Al Jurf Indl Area, Ajman. Also listed in Al Quoz Industrial 3, Dubai.</t>
+          <t>Waterfront market Deira, Dubai.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Supplier of Frozen Seafood including Abalone, Shrimp, Salmon, Squid, Lobster, Tuna, Trevally. Also lists Salmon, King Fish, Octopus.</t>
+          <t>Sells 'Fresh Whole Shell Abalone' sourced from pristine cold-water regions (FAO Areas 27 and 81). Halal Compliant &amp; Hygienically Processed. Cold-Chain Delivery (0–4°C). Offers custom fish preparation and 2-hour/same-day delivery in Dubai, next-day across UAE.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Explicitly listed as a supplier of 'Frozen Abalone' and 'Frozen Seafood'. They are also 'Fish &amp; Seafood Importers, Exporters &amp; Processors'.</t>
+          <t>Directly imports and distributes abalone, with a focus on quality and cold-chain logistics. They cater to households and high-end restaurants.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHilrZwc_-sVdE6bxfa_EuTM77Z-w7QcSFQExMjw8zLaBemFs7vOrXa3yrDTsx-7YDW4t9Z8Al_fRoC7fqyqD0LgQWijBKAJOUkaCbOVcgwqY3UASq9uRKwk3Qd-ag7ux7mmxmf1e26daaZRNlDWEd_2ZaKnwEDtz5oxNbZCL9OEVnyaMgh0ArAZFmnkodMlaIL</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Phone number: +971-6-7444559</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF1n6IrUDF_2UqEV1FcEcY_91lJj3LUZsTqcN2E-z6ynL2pmf6_SM1ymPQjnZMML_D3hhCHfVLVikDUjllk1QaU7pVCslFnbxRTPWXUF1y6MLjcD1m-IBi83-ovGxE8KZhXTNMo4yW_3PmnAFzpJ5O5jrf8_bcyfg==</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6369,12 +6365,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Direct Seafoods</t>
+          <t>Sea World Fish Processing Llc</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6382,55 +6378,51 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>sales@directseafoods.co.uk</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://www.directseafoods.co.uk/</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>+971564117152 (WhatsApp)</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Wholesale abalone, frozen wholesale abalone, supplying to restaurants, caterers, and distributors.</t>
+          <t>Frozen Seafood, Shrimp, Salmon, Squid, Abalone, Lobster, Tuna, Trevally. Fish &amp; Seafood Importers, Exporters &amp; Processors.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Crown Court Severalls Business Park, Clough road, Colchester CO4 9TZ</t>
+          <t>Meena Rd, Nr Fish Market, Al Jurf Indl Area, Ajman. Also listed in Al Quoz Industrial 3, Dubai.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Expertly sourced wholesale abalone, premium quality, range of pack sizes, sustainably sourced options, frozen abalone.</t>
+          <t>Supplier of Frozen Seafood including Abalone, Shrimp, Salmon, Squid, Lobster, Tuna, Trevally. Also lists Salmon, King Fish, Octopus.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Clearly states they are suppliers of wholesale abalone for businesses, including caterers and distributors, indicating they import or source in bulk.</t>
+          <t>Explicitly listed as a supplier of 'Frozen Abalone' and 'Frozen Seafood'. They are also 'Fish &amp; Seafood Importers, Exporters &amp; Processors'.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHUIYsQ2UBPSBJ867GFx9lsSGgOScseBoH5kgVzDM4Z9FqfpgCuJOckuXoixQJWbbT--kaUWwRR_UzXIpjbk7uvQF9L8O0c_NRa3jAnZIPK8qH5hk4lkW-WX7hkiJFFlIanM64gCt86Rui4ofRFzhQfr-MHgQRPuI-tVU0=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHilrZwc_-sVdE6bxfa_EuTM77Z-w7QcSFQExMjw8zLaBemFs7vOrXa3yrDTsx-7YDW4t9Z8Al_fRoC7fqyqD0LgQWijBKAJOUkaCbOVcgwqY3UASq9uRKwk3Qd-ag7ux7mmxmf1e26daaZRNlDWEd_2ZaKnwEDtz5oxNbZCL9OEVnyaMgh0ArAZFmnkodMlaIL</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Part of Bidfresh Limited.</t>
+          <t>Phone number: +971-6-7444559</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6439,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fine Food Specialist</t>
+          <t>Direct Seafoods</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6457,23 +6449,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>support@finefoodspecialist.co.uk</t>
+          <t>sales@directseafoods.co.uk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.finefoodspecialist.co.uk/</t>
+          <t>https://www.directseafoods.co.uk/</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sells large Australian abalone online, offers wholesale.</t>
+          <t>Wholesale abalone, frozen wholesale abalone, supplying to restaurants, caterers, and distributors.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6483,27 +6475,27 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Not explicitly stated beyond 'London and the UK'.</t>
+          <t>Crown Court Severalls Business Park, Clough road, Colchester CO4 9TZ</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Large Australian abalone, frozen, sashimi grade, offers next day delivery.</t>
+          <t>Expertly sourced wholesale abalone, premium quality, range of pack sizes, sustainably sourced options, frozen abalone.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Explicitly states 'Wholesale available. Trusted UK fine food wholesaler,' indicating they are a distributor.</t>
+          <t>Clearly states they are suppliers of wholesale abalone for businesses, including caterers and distributors, indicating they import or source in bulk.</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGMjhqPJpEsff_zAS7zQT4UIck_UEpFMw36Ap14taYnEELyVa1mAKjWqtFFwvjKYoZ6_VuZ37CEImyilNnDqE0avI5M1E1YyngtytpAY67YhY8ts-aoTS1FWZ3AtkuSrw-UyioUx9MMvlc6lidPdRqiatFTdXzrMlinyaaYKh0gqQ==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHUIYsQ2UBPSBJ867GFx9lsSGgOScseBoH5kgVzDM4Z9FqfpgCuJOckuXoixQJWbbT--kaUWwRR_UzXIpjbk7uvQF9L8O0c_NRa3jAnZIPK8qH5hk4lkW-WX7hkiJFFlIanM64gCt86Rui4ofRFzhQfr-MHgQRPuI-tVU0=</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Offers both retail and wholesale.</t>
+          <t>Part of Bidfresh Limited.</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6512,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seafood Australia</t>
+          <t>Fine Food Specialist</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6528,19 +6520,27 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>support@finefoodspecialist.co.uk</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://seafoodaustralia.co.uk/</t>
+          <t>https://www.finefoodspecialist.co.uk/</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sells Premium Australian Canned Abalone and Wild Abalone, with 'Fast UK Shipping' and a 'Wholesale' section.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>Sells large Australian abalone online, offers wholesale.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -6548,27 +6548,27 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Delivers to anywhere in the UK.</t>
+          <t>Not explicitly stated beyond 'London and the UK'.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Premium Australian wild and farmed abalone, canned abalone, direct from farm to door, sustainably farmed or caught.</t>
+          <t>Large Australian abalone, frozen, sashimi grade, offers next day delivery.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Has a 'Wholesale' section on their website and offers direct supply of Australian abalone, suggesting they are an importer/distributor.</t>
+          <t>Explicitly states 'Wholesale available. Trusted UK fine food wholesaler,' indicating they are a distributor.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHydvT7JMFhRuJb4p5iZBcaBABfGyX2tWoFEHuHnjJ_kqBq4Eb1I0ey6Ty7x2ua2-wI7FN6fuFx3syKl6sTP9xSL_oGe4JKYhCxMN3JZuetVzzTAo5vHoDUhwQt-44=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGMjhqPJpEsff_zAS7zQT4UIck_UEpFMw36Ap14taYnEELyVa1mAKjWqtFFwvjKYoZ6_VuZ37CEImyilNnDqE0avI5M1E1YyngtytpAY67YhY8ts-aoTS1FWZ3AtkuSrw-UyioUx9MMvlc6lidPdRqiatFTdXzrMlinyaaYKh0gqQ==</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Specializes in Australian abalone.</t>
+          <t>Offers both retail and wholesale.</t>
         </is>
       </c>
     </row>
@@ -6580,12 +6580,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fishy Vietnam Co., Ltd.</t>
+          <t>Seafood Australia</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6593,53 +6593,49 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Fishy.vn@gmail.com</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://fishy.vn/</t>
+          <t>https://seafoodaustralia.co.uk/</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Importing and distributing top-class seafood, including various types of abalone (Frozen Abalone (Loco) Meat, Frozen Australian Greenlip Abalone, Frozen Abalone, Braised Abalone In Oyster Sauce, Abalone Seafood Soup).</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Ho Chi Minh City</t>
-        </is>
-      </c>
+          <t>Sells Premium Australian Canned Abalone and Wild Abalone, with 'Fast UK Shipping' and a 'Wholesale' section.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City</t>
+          <t>Delivers to anywhere in the UK.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Specializes in importing and distributing top-class seafood. Products include various types of abalone (frozen, Australian greenlip, loco meat, abalone seafood soup, braised abalone in oyster sauce). Focus on product quality, dedication, and customer satisfaction.</t>
+          <t>Premium Australian wild and farmed abalone, canned abalone, direct from farm to door, sustainably farmed or caught.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Direct importer and distributor, indicating a clear channel for cooperation. Emphasizes quality and customer satisfaction.</t>
+          <t>Has a 'Wholesale' section on their website and offers direct supply of Australian abalone, suggesting they are an importer/distributor.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFnIbNcTSOzpm1rjxZKNdOXHZFHXPLvkR6w0O11uKwUJy88CBKHuqahAqg6N3_l-KqHBD9TlsdBOFLPPwARm092X_aBdYKa_w7CDxuB3MzJ4junbM6oKTpwaIgIt3W2fFE=</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHydvT7JMFhRuJb4p5iZBcaBABfGyX2tWoFEHuHnjJ_kqBq4Eb1I0ey6Ty7x2ua2-wI7FN6fuFx3syKl6sTP9xSL_oGe4JKYhCxMN3JZuetVzzTAo5vHoDUhwQt-44=</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Specializes in Australian abalone.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6654,7 +6650,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sai Thanh Foods</t>
+          <t>Fishy Vietnam Co., Ltd.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6664,18 +6660,18 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>salesfreshfood@sacofoods.vn</t>
+          <t>Fishy.vn@gmail.com</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://saithanhfoods.com/</t>
+          <t>https://fishy.vn/</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Supplier of frozen abalone (Haliotis Diversicolor) from Vietnam. Also deals with other seafood like sea fish, river fish, octopus, squid, shellfish.</t>
+          <t>Importing and distributing top-class seafood, including various types of abalone (Frozen Abalone (Loco) Meat, Frozen Australian Greenlip Abalone, Frozen Abalone, Braised Abalone In Oyster Sauce, Abalone Seafood Soup).</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6690,22 +6686,22 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Lot III-22, Street 19/5A, Tan Binh Industrial Park, Tay Thanh Ward, Ho Chi Minh City, Vietnam</t>
+          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Specializes in frozen abalone (Haliotis Diversicolor) of Vietnamese origin. They also offer other seafood products.</t>
+          <t>Specializes in importing and distributing top-class seafood. Products include various types of abalone (frozen, Australian greenlip, loco meat, abalone seafood soup, braised abalone in oyster sauce). Focus on product quality, dedication, and customer satisfaction.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Direct supplier of frozen abalone, indicating a potential for direct sourcing. They invite inquiries for specifications and pricing.</t>
+          <t>Direct importer and distributor, indicating a clear channel for cooperation. Emphasizes quality and customer satisfaction.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdzZHAIL6EJepETfinawUNWPxz-8vXV951xIFxRs0HZB32IxHGNPOCJKb_txdlYe0VZWWpejeThan1R4sfd3Pj_eg_ZzTpeCR9cmBU_meF-izlTZCbpQTD124H_zWN5Fe1iuEj6bD5iqxCJW8af6yMk-s=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFnIbNcTSOzpm1rjxZKNdOXHZFHXPLvkR6w0O11uKwUJy88CBKHuqahAqg6N3_l-KqHBD9TlsdBOFLPPwARm092X_aBdYKa_w7CDxuB3MzJ4junbM6oKTpwaIgIt3W2fFE=</t>
         </is>
       </c>
       <c r="O77" t="inlineStr"/>
@@ -6723,7 +6719,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Trọng Đức Seafood</t>
+          <t>Sai Thanh Foods</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6731,60 +6727,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>salesfreshfood@sacofoods.vn</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trongduc.com/</t>
+          <t>https://saithanhfoods.com/</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Imports abalone mainly from Korea, Japan, and neighboring countries. Also deals with other seafood like Japanese scallops, sea eel. Offers good prices for wholesalers, agents, and distributors.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Supplier of frozen abalone (Haliotis Diversicolor) from Vietnam. Also deals with other seafood like sea fish, river fish, octopus, squid, shellfish.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Lot III-22, Street 19/5A, Tan Binh Industrial Park, Tay Thanh Ward, Ho Chi Minh City, Vietnam</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Imports abalone from Korea, Japan, and neighboring countries. Offers various sizes of Korean abalone. Emphasizes product quality, reputation, and direct import for good prices for wholesalers/agents/distributors.</t>
+          <t>Specializes in frozen abalone (Haliotis Diversicolor) of Vietnamese origin. They also offer other seafood products.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Explicitly states good prices for wholesalers, agents, and distributors, making them a direct potential partner. They also offer returns if not satisfied.</t>
+          <t>Direct supplier of frozen abalone, indicating a potential for direct sourcing. They invite inquiries for specifications and pricing.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFNhjSu_CUVmGlZe8ulZHnui_rrcb9z2Gm9Dk4aJlf3YHrn288thuxtw0ARGxmu3uLnFb-7BIWKI_KEffIQPvRk0m3fct_IGwngL1ebQV7ngD9mdbqcdBnMHvE7US-xDV1Y9SOFz--R_tY6SDR-u-90jvs=</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>City and location detail not explicitly mentioned in the provided source.</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdzZHAIL6EJepETfinawUNWPxz-8vXV951xIFxRs0HZB32IxHGNPOCJKb_txdlYe0VZWWpejeThan1R4sfd3Pj_eg_ZzTpeCR9cmBU_meF-izlTZCbpQTD124H_zWN5Fe1iuEj6bD5iqxCJW8af6yMk-s=</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FGC JOINT STOCK COMPANY</t>
+          <t>Trọng Đức Seafood</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6792,62 +6796,50 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>fgc.seafoods@gmail.com</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.fgc-foods.com/</t>
+          <t>https://trongduc.com/</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>전복(살아있는, 열처리 및 냉동)을 포함한 고품질의 안전한 수입 식품을 제조 및 공급합니다.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Hanoi</t>
-        </is>
-      </c>
+          <t>Imports abalone mainly from Korea, Japan, and neighboring countries. Also deals with other seafood like Japanese scallops, sea eel. Offers good prices for wholesalers, agents, and distributors.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi.</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>수입 전복(살아있는, 열처리 및 냉동), 1kg/봉지, 10kg/상자, -18°C 보관, 24개월 유통기한.</t>
+          <t>Imports abalone from Korea, Japan, and neighboring countries. Offers various sizes of Korean abalone. Emphasizes product quality, reputation, and direct import for good prices for wholesalers/agents/distributors.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>수입 전복 공급업체, 품질 및 안전에 중점, 다양한 맛과 스타일.</t>
+          <t>Explicitly states good prices for wholesalers, agents, and distributors, making them a direct potential partner. They also offer returns if not satisfied.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>https://www.fgc-foods.com/san-pham/thuc-pham-chat-luong-cho-kenh-nha-hang-va-ban-le/bao-ngu-nhap-khau</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFNhjSu_CUVmGlZe8ulZHnui_rrcb9z2Gm9Dk4aJlf3YHrn288thuxtw0ARGxmu3uLnFb-7BIWKI_KEffIQPvRk0m3fct_IGwngL1ebQV7ngD9mdbqcdBnMHvE7US-xDV1Y9SOFz--R_tY6SDR-u-90jvs=</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>전화 및 Zalo 핫라인도 이용 가능합니다.</t>
+          <t>City and location detail not explicitly mentioned in the provided source.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 19:11:01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6857,7 +6849,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fishy Vietnam Co., Ltd</t>
+          <t>FGC Joint Stock Company</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6867,23 +6859,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fishy.vn@gmail.com</t>
+          <t>fgc.seafoods@gmail.com</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://fishy.vn/</t>
+          <t>www.fgc-foods.com</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>베트남에서 전복(냉동 전복(Loco) 고기, 냉동 호주산 그린립 전복 포함)을 포함한 최고급 해산물을 수입 및 유통합니다.</t>
+          <t>수입 전복(고기술 냉동, 1kg/봉지, 10kg/상자)을 포함한 고품질의 안전한 수입 식품 제조 및 공급.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6893,34 +6885,30 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City.</t>
+          <t>No. Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>최고급 해산물 수입 및 유통 전문, 헌신과 명성, 고객 만족 중시, 고품질 제품, 최고의 서비스.</t>
+          <t>베트남 소비자를 위한 품질, 안전, 다양한 맛에 중점. 유통기한 24개월.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>프리미엄 해산물 수입 및 유통 선두 기업, 다양한 전복 제품, 품질 및 고객 서비스에 중점.</t>
+          <t>수입 전복 공급을 명시하고 있으며, 연락처 정보를 제공함.</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://fishy.vn/san-pham/bao-ngu</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>세금 ID 및 핫라인도 이용 가능합니다.</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHE6mcXntxILCL80ePf_RaMd8_2Q1VoZPmmcM2-Dcup5cbCvzqz-CNF3AtJgiZHZj5dHrRODpU085MAGySrx5zFHgCQCU8gHHdan8Z3Wb6s_AhMxdw26TkHvNYPM8Gq0QOKdFkrqPzEyKdEXFiEOWmuJHcoRfbQ==</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 19:11:01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6930,7 +6918,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Trọng Đức Seafood</t>
+          <t>Fishy Vietnam Co., Ltd</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6938,41 +6926,110 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Fishy.vn@gmail.com</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://trongduc.vn/</t>
+          <t>https://fishy.vn/</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
+          <t>베트남 내 최고급 해산물 수입 및 유통 전문. 냉동 전복(Loco) 고기, 호주산 그린립 전복, 전복 해산물 수프, 굴 소스 전복찜 등 전복 제품 취급.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>최고급 해산물 수입 및 유통 전문. 제품 품질, 헌신, 명성을 최우선으로 함.</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>전복 수입 및 유통을 명시하고 있으며, 명확한 연락처 정보를 제공함.</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHwAboISDt8AuptY7bnv5ph6VjqmmkpAPFOZk2JMVsRdGqtoCvPclbAo3ifjMuo6MaoY7vIgLjwlRUF1m8aehW6P6lXgS_HsmX9cInaCZgP16MKCnA5DwofX7ObFe2jdw==</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Trọng Đức Seafood</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://trongduc.vn/</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>한국, 일본 및 인근 국가에서 전복을 수입하여 도매업체, 에이전트 및 유통업체에 공급합니다.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
         <is>
           <t>수입 전복 (한국, 일본 및 인근 국가산), 다양한 크기, 도매업체/에이전트/유통업체에 좋은 가격, 품질 명성, 완전한 문서 및 바코드.</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>직접 수입업체이며, 도매업체/에이전트/유통업체에 좋은 가격을 제공하고, 품질 및 문서화에 중점을 둡니다.</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>https://trongduc.vn/san-pham/bao-ngu-nhap-khau/</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>이메일/전화번호는 스니펫에 명시되어 있지 않지만 웹사이트가 제공됩니다.</t>
         </is>

--- a/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
+++ b/BIZ-Jeonbok/data/abalone_buyers_leads.xlsx
@@ -1482,7 +1482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2641,7 +2641,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-02 08:27:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2662,13 +2662,13 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.ifish.com.hk</t>
+          <t>https://ifish.com.hk/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Leading seafood importer in Hong Kong. Supplies farm-raised and wild-caught abalone from South Africa. Provides a wide range of premium seafood products for Hong Kong hotels and restaurants.</t>
+          <t>Live, fresh, and frozen seafood import and distribution for hotels and restaurants.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2688,25 +2688,29 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Committed to sustainable practices, sources world's finest quality seafood, supplies to hotels and restaurants. Specializes in shellfish and prawns, including abalone.</t>
+          <t>Leading seafood importer in Hong Kong. Supplies farm-raised and wild-caught abalone from South Africa. Committed to sustainable practices. Wide range of premium seafood products.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Focus on premium quality and sustainable sourcing, strong network with hotels and restaurants in Hong Kong, and direct supply of abalone from South Africa.</t>
+          <t>Specializes in importing premium seafood, including abalone, for the HORECA sector in Hong Kong. Focus on quality and sustainable sourcing.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.ifish.com.hk/product/abalone</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEk_iCRzMecVPcK7gTqtRCPkbcqW70WiRE1f8PlFriDodSAbkv5avthwlb-dmtuWt6qovNjcFS41Sz2ORsz8n-OXwqKuDwhu3BhVW_fbQxnJSMUfPDBD13aM2OuQQ==</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Email not explicitly found on the provided page, only a contact number.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-01 13:25:05</t>
+          <t>2026-08-02 08:27:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2725,11 +2729,15 @@
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.hktdc.com/sourcing/company/reign-abalone-limited/114000005000000000000/</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Distributor, Import Agent, Importer, Retailer, Service Company, Wholesaler, e-tailer</t>
+          <t>Distributor, Import Agent, Importer, Retailer, Wholesaler of food and beverage, including abalone.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2744,34 +2752,34 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Unit 25, 16/F One Island South 2 Heung Yip Rd</t>
+          <t>Unit 25, 16/F One Island South 2 Heung Yip Rd Wong Chuk Hang, Hong Kong</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Food, Food &amp; Beverage. Major markets include Chinese Mainland, Hong Kong, Japan, Other Asian Countries, Southeast Asia.</t>
+          <t>Engages in import, distribution, retail, and wholesale of food products. Major markets include Chinese Mainland, Hong Kong, Japan, Other Asian Countries, Southeast Asia.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Explicitly listed as an Importer and Import Agent for food products, with a focus on Asian markets including 'Other Asian Countries' and Southeast Asia. Handles wholesale and distribution.</t>
+          <t>Acts as an import agent and distributor for abalone, with a broad market reach across Asia.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHs_UrjUiksMwMku5GxaRzu55tr9QYwMAOEcYCiPw30oxyfHgK5sfZtx3UKLELi2XcP5KEObX-z-4NhJkevT2vS4xG-YSmys9Pjpm9jYheokDR6dd4xEEpy_nu20WEoxqsU1xyGWmBFAMeINwttLkZxqSt3Lk0UDmWQ-MCFduSYpN5rchLVVd9cExTaIekJrdy8</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGG0Tfjl01uO35FxVAFWw36KC6E4zR0m-RO4g-k_4K3YZSNQ4YoYfHNYqTwLE8TOInbxbSUd01w_P3P3AbLsvQxAC6Ibeysu5kX5A3l0CQgt_2fUrFjaROQ4Oc0L-8Ftlhh8iKn5M69M315ppdFY_bIMMq7xRwsiYMmRsREI37f1p0PsNhgH47ElIqmPIjbnDgJ</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Contact person: Mr Lawrence Kuoch, CEO. Email and website not publicly available in the snippet.</t>
+          <t>Email not explicitly found on the provided page.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-02 08:27:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2796,13 +2804,13 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.seabo.co</t>
+          <t>https://www.seabo.co/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Leading Hong Kong-based company in the seafood industry, importer, wholesaler. Deals with frozen abalone, frozen molluscs, frozen fish, frozen pork.</t>
+          <t>Frozen abalone, frozen seafood, frozen molluscs, frozen crustaceans. Global sourcing and distribution.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2822,17 +2830,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Over 40 years of international reputation, global seafood network (sources from over 30 countries), offers Seabo brand line products, reliable and timely delivery.</t>
+          <t>Over 40 years of international reputation in the seafood industry. Sources from over 30 different countries. Offers exclusively packaged Seabo brand line products. Reliable and timely delivery.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Established company with extensive sourcing and distribution capabilities in Hong Kong, specializing in frozen seafood including abalone.</t>
+          <t>Leading Hong Kong-based seafood importer and wholesaler with extensive global network and experience in frozen abalone.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://www.seabo.co/contact-us</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGZh0nYnKzEAMCRIC4ar3DgbJbt_AXFxQyyrtQPe1iIqZNTeZMZMKjglvOj3G0e5vRiUf6OZirHnMSY4yZy0xxmbRdNnfh-K_gBo218YFmCRQ==</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -2962,7 +2970,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-02 08:27:13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2972,7 +2980,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>I.FISH Company Limited</t>
+          <t>Halbmond Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2980,21 +2988,29 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>info@halbmondco.com</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://ifish.com.hk/</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>https://halbmondco.com</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Whatsapp Mr.Adeel (+85267147757), Mr.Akber (+85262785720)</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Seafood importer and supplier for hotels and restaurants</t>
+          <t>Wholesaler Importer of Dried Seafood, specializing in quality dry seafood products. They are actively looking for more suppliers.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yau Tong</t>
+          <t>Tsim Sha Tsui</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3004,34 +3020,34 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Unit D, 8/F, Wah Shun Industrial Building 4 Cho Yuen Street; Yau Tong, Hong Kong</t>
+          <t>20 2/F Mirador Mansion, 54-56 Nathan Road, Tsim Sha Tsui 00852, Hong Kong</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Supplies farm-raised and wild-caught abalone from South Africa, along with a wide range of premium seafood products.</t>
+          <t>Dried abalone, dried fish maw, sea cucumber, shark fin, shark liver oil, lobster, sea horse, cordyceps, bird's nest. They purchase from Middle-East, The Indian ocean and Africa.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Explicitly states they are a leading seafood importer in Hong Kong and supply abalone, targeting hotels and restaurants, suggesting a strong distribution network.</t>
+          <t>Specialized in dried abalone and actively seeking new suppliers, indicating a clear interest in sourcing. Their expert team can handle various stages of seafood processing.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGtI-nmTK4njbRY2vG7POki0OZpPdXFRWnkI3Gz1qUh0rFzIJvfNJn9ZnDvOA6OKvciXsN8kXgc9qvoRnPpUstOg1juycMC5z2OmBS4jBc-TLkNamM5L1yX46syAg==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGWubmqpsrY0-9bJ_dULkbRfcdj5cizkI0L88msbnmR80Ntvwu57ktCfI30oYUE6aa74Z_57Jgb0YkNeuETizfEzCxxn2DbS8KUPfZGSAw4pBJfNMtEA-laHZXUniwZ0A==</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Tel: +852 2775-9118, Fax: +852 2775-1118 are available on the source page but not requested in the schema.</t>
+          <t>The company's website confirms their role as a wholesaler and importer of dried seafood.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-01 13:25:05</t>
+          <t>2026-08-02 08:27:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3041,7 +3057,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>I.FISH Company Limited (挪威漁業有限公司)</t>
+          <t>I.FISH Company Limited</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3050,11 +3066,15 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://ifish.com.hk</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Seafood importer, supplier to hotels and restaurants</t>
+          <t>Highly diversified seafood importer and distributor, providing supply solutions and customized design programs for wholesalers, retail chains, distributors, and food service companies throughout the Asia Pacific Region. They supply live, fresh, and frozen seafood.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3069,27 +3089,27 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Unit D, 8/F, Wah Shun Industrial Building 4 Cho Yuen Street; Yau Tong, Hong Kong</t>
+          <t>Unit D, 8/F, Wah Shun Industrial Building, No. 4 Cho Yuen Street, Yau Tong, Kowloon, Hong Kong</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Supplies farm-raised and wild-caught abalone from South Africa, also other premium seafood products.</t>
+          <t>Live, fresh, and frozen seafood, including abalone, geoducks, lobsters, oysters, salmons, conchs, whelks, and deep-sea fish. They supply farm-raised and wild-caught abalone from South Africa.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Clearly states they are a 'leading seafood importer in Hong Kong' and specifically mention abalone.</t>
+          <t>Established importer and distributor with a wide range of seafood and a broad distribution network in the Asia Pacific region, including Hong Kong hotels and restaurants. Actively sourcing from reputable suppliers.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcRjbz-xC-RPV6RGVTJ05l2UjEbLSt8kDpDc12F0Sm1vg_-NaPC3aeUMmGHbkmat_ULk4KF4Pmf3mvVCiKGZonDGF5PdgNfk5uSior-q3l3FMbE3ozjbMMgMPW</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFGqP_V9C8SXK10-bNs57OwGTBSd5H7bhyPmVPR3uHvlwQBuBKNIC5GDuAFsZI5q_Yvel16-W_B4GaFsqfteKB8WV9GNuhqeEP_VDefaj5RuuF0R4VscxZXiIJH0aQB3emireqhDlUM8GvfeH_r46NMfv3EiboPvL8o8wq7mc6UvoSwphwk7Hi3wml-ng==</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Phone numbers +852 2775-9118 (Tel), +852 2775-1118 (Fax) are available.</t>
+          <t>Contact Person: Ms. Bea Wong (Manager). Telephone: +852-2775-0505, +852-2775-9118. Fax: +852-2775-1118.</t>
         </is>
       </c>
     </row>
@@ -3106,12 +3126,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reign Abalone Limited</t>
+          <t>I.FISH Company Limited (挪威漁業有限公司)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>개인 에이전트</t>
+          <t>법인</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -3119,12 +3139,12 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Distributor, Import Agent, Importer, Retailer, Wholesaler, e-tailer</t>
+          <t>Seafood importer, supplier to hotels and restaurants</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Wong Chuk Hang</t>
+          <t>Yau Tong</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3134,34 +3154,34 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Unit 25, 16/F One Island South 2 Heung Yip Rd Wong Chuk Hang, Hong Kong</t>
+          <t>Unit D, 8/F, Wah Shun Industrial Building 4 Cho Yuen Street; Yau Tong, Hong Kong</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage, specifically abalone (implied by company name and listed categories). Major Markets: Chinese Mainland, Hong Kong, Japan, Other Asian Countries, Southeast Asia.</t>
+          <t>Supplies farm-raised and wild-caught abalone from South Africa, also other premium seafood products.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Explicitly listed as an 'Import Agent' and 'Importer' for abalone, indicating active sourcing and distribution capabilities.</t>
+          <t>Clearly states they are a 'leading seafood importer in Hong Kong' and specifically mention abalone.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEzd9GrR1nPI2g_BsUqKMi_cf_ixpqwM72aX91ZKNb2619ovggt6mFRRnmmWbFe8_bsvbtsBWZf9KPU60GRRqiz1gmsmTf4VwDg6uJkwdQrQnLpP127YH3Fv2npu146Xshfpm2rGNLpAynAU8vlM1SnKuc4ojkyWcTbH3H_KxNTyKRf3vDChmIHJqPWcVTZdy8=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcRjbz-xC-RPV6RGVTJ05l2UjEbLSt8kDpDc12F0Sm1vg_-NaPC3aeUMmGHbkmat_ULk4KF4Pmf3mvVCiKGZonDGF5PdgNfk5uSior-q3l3FMbE3ozjbMMgMPW</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Contact person Mr Lawrence Kuoch, CEO.</t>
+          <t>Phone numbers +852 2775-9118 (Tel), +852 2775-1118 (Fax) are available.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3171,12 +3191,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wing Tai Hong Marine Products Limited</t>
+          <t>Reign Abalone Limited</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>법인</t>
+          <t>개인 에이전트</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -3184,12 +3204,12 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Importing, wholesaling, retailing and exporting of dried marine products</t>
+          <t>Distributor, Import Agent, Importer, Retailer, Wholesaler, e-tailer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Wong Chuk Hang</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3197,42 +3217,46 @@
           <t>Hong Kong SAR</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Unit 25, 16/F One Island South 2 Heung Yip Rd Wong Chuk Hang, Hong Kong</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Dried marine products, including abalone and scallop.</t>
+          <t>Food &amp; Beverage, specifically abalone (implied by company name and listed categories). Major Markets: Chinese Mainland, Hong Kong, Japan, Other Asian Countries, Southeast Asia.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>A well-established company involved in importing and wholesaling dried abalone, indicating a direct channel for distribution.</t>
+          <t>Explicitly listed as an 'Import Agent' and 'Importer' for abalone, indicating active sourcing and distribution capabilities.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGJ1L2bIzrk2yA85itKs-Ijnva2yxVj9WV1_DK8czhqTtfES3ukaA7PcRVAQPil20Pjf9_BmyMTol0b1me42dKM_pGn7L3GCecfevtyZR-V_ptb6x1ux-wy20gy3jahAAyZ_cGrx9koIh-YEkg4h0UqNkI=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEzd9GrR1nPI2g_BsUqKMi_cf_ixpqwM72aX91ZKNb2619ovggt6mFRRnmmWbFe8_bsvbtsBWZf9KPU60GRRqiz1gmsmTf4VwDg6uJkwdQrQnLpP127YH3Fv2npu146Xshfpm2rGNLpAynAU8vlM1SnKuc4ojkyWcTbH3H_KxNTyKRf3vDChmIHJqPWcVTZdy8=</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Phone number +852 28150381 is available on the source page but not requested in the schema.</t>
+          <t>Contact person Mr Lawrence Kuoch, CEO.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-02 08:27:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bin Auf</t>
+          <t>Source Natural Store (Sonatural.hk)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3240,56 +3264,76 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>cs@sonatural.hk</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.sonatural.hk</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>whatsapp +852-66129937</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>인도네시아 수출업체, 수입업체, 해산물 무역업체. 제품에는 말린 해삼, 전복, 전갱이, 산호 송어, 말린 오징어, 황다랑어 등이 포함됩니다. 소량/대량 공급 가능.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Hong Kong based Live &amp; Fresh Seafood specialist, providing the world's finest, freshest, healthiest and highest quality live seafood directly to customers' doors or restaurants. Offers wholesale services.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Delivers to Kowloon, Hong Kong Island, New Territories.</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 해산물 거래, 소량/대량 공급 가능.</t>
+          <t>Live &amp; fresh seafood, including abalone. Focus on quality, health, and sustainability.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>명시적으로 '수입업체' 역할을 명시, 다양한 제품 범위, 유연한 공급량.</t>
+          <t>Specializes in live and fresh seafood, offers wholesale services to retailers and restaurants, and is committed to supplying high-quality, sustainable products.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/seafood-indonesia.htm</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEG8fT2sRRJrUgFbFOfrZpOkDH4PaAC1aa-5oej0GTRf-72X2MGm_vh1qStyxGn5Et4-QLJgij4JOTUGoRSsgsfJ0gZUyHhOVZQEgynSaBBeKq21TajbvO8yB41Ihr_cuoN4CQ8dy-z58QYpPS</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>스니펫에서 직접적인 웹사이트나 이메일을 찾을 수 없지만, 회사는 수입업체로 등재되어 있습니다.</t>
+          <t>The company's website and contact page confirm their role and services.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CV Langgeng Sentosa Trade Indo</t>
+          <t>Wing Tai Hong Marine Products Limited</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3302,42 +3346,38 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>인도네시아 동부 자바의 냉동 해산물 수출업체, 조달업체 및 가공업체. 주요 생산품은 롤리고 오징어, 전복 고기, 문어, 갑오징어, 저서어류입니다. 냉동 삶은 전복 고기 'mata 7' 재고 보유.</t>
+          <t>Importing, wholesaling, retailing and exporting of dried marine products</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>East Java</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>East Java - Indonesia.</t>
-        </is>
-      </c>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>냉동 삶은 전복 고기, 즉시 선적 가능.</t>
+          <t>Dried marine products, including abalone and scallop.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>전복 고기의 직접 조달 및 가공업체, 즉시 선적 가능한 재고 보유. 주로 수출업체이지만, 조달 및 가공 역할은 국내에서 제품을 취급하며 수입을 위한 연락처가 될 수 있음을 시사합니다.</t>
+          <t>A well-established company involved in importing and wholesaling dried abalone, indicating a direct channel for distribution.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://www.go4worldbusiness.com/find/products/frozen-abalone/indonesia.html</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGJ1L2bIzrk2yA85itKs-Ijnva2yxVj9WV1_DK8czhqTtfES3ukaA7PcRVAQPil20Pjf9_BmyMTol0b1me42dKM_pGn7L3GCecfevtyZR-V_ptb6x1ux-wy20gy3jahAAyZ_cGrx9koIh-YEkg4h0UqNkI=</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>연락 담당자 Tonny Santoso가 언급되었습니다. 스니펫에서 직접적인 이메일이나 웹사이트를 찾을 수 없습니다.</t>
+          <t>Phone number +852 28150381 is available on the source page but not requested in the schema.</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3394,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PT CITA KARYA AGUNG</t>
+          <t>Bin Auf</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3363,67 +3403,55 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://variouseafood.com/</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>인도네시아의 선도적인 신선 및 냉동 해산물 가공업체, 공급업체 및 수출업체. 전복과 같은 냉동 복족류를 포함하여 35가지 이상의 다양한 제품을 제공합니다. 어부 및 양식 전문가로부터 조달.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Belawan</t>
-        </is>
-      </c>
+          <t>인도네시아 수출업체, 수입업체, 해산물 무역업체. 제품에는 말린 해삼, 전복, 전갱이, 산호 송어, 말린 오징어, 황다랑어 등이 포함됩니다. 소량/대량 공급 가능.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Belawan, Indonesia.</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>달팽이 및 전복과 같은 프리미엄 냉동 복족류, 최적의 신선도를 유지하기 위해 신중하게 가공. GMP 표준 및 HACCP 인증.</t>
+          <t>전복을 포함한 다양한 해산물 거래, 소량/대량 공급 가능.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>확고한 가공업체 및 공급업체, 지속 가능성 및 품질에 대한 약속, 광범위한 제품. 주로 수출업체이지만, 조달 및 가공 활동은 인도네시아 내 전복 공급망에서 관련 플레이어임을 나타냅니다.</t>
+          <t>명시적으로 '수입업체' 역할을 명시, 다양한 제품 범위, 유연한 공급량.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://variouseafood.com/</t>
+          <t>https://www.trade-seafood.com/seafood-indonesia.htm</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>스니펫에서 직접적인 이메일을 찾을 수 없습니다.</t>
+          <t>스니펫에서 직접적인 웹사이트나 이메일을 찾을 수 없지만, 회사는 수입업체로 등재되어 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pesca K &amp; M Co., Ltd.</t>
+          <t>CV Langgeng Sentosa Trade Indo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3431,76 +3459,64 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>pescauno@nifty.com</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>표2 (HS 160557)</t>
+          <t>인도네시아 동부 자바의 냉동 해산물 수출업체, 조달업체 및 가공업체. 주요 생산품은 롤리고 오징어, 전복 고기, 문어, 갑오징어, 저서어류입니다. 냉동 삶은 전복 고기 'mata 7' 재고 보유.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>East Java</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
+          <t>East Java - Indonesia.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
+          <t>냉동 삶은 전복 고기, 즉시 선적 가능.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
+          <t>전복 고기의 직접 조달 및 가공업체, 즉시 선적 가능한 재고 보유. 주로 수출업체이지만, 조달 및 가공 역할은 국내에서 제품을 취급하며 수입을 위한 연락처가 될 수 있음을 시사합니다.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+          <t>https://www.go4worldbusiness.com/find/products/frozen-abalone/indonesia.html</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
+          <t>연락 담당자 Tonny Santoso가 언급되었습니다. 스니펫에서 직접적인 이메일이나 웹사이트를 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31 14:58:21</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>True World Japan Inc.</t>
+          <t>PT CITA KARYA AGUNG</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3511,52 +3527,48 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
-        </is>
-      </c>
+          <t>https://variouseafood.com/</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>인도네시아의 선도적인 신선 및 냉동 해산물 가공업체, 공급업체 및 수출업체. 전복과 같은 냉동 복족류를 포함하여 35가지 이상의 다양한 제품을 제공합니다. 어부 및 양식 전문가로부터 조달.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Belawan</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
+          <t>Belawan, Indonesia.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
+          <t>달팽이 및 전복과 같은 프리미엄 냉동 복족류, 최적의 신선도를 유지하기 위해 신중하게 가공. GMP 표준 및 HACCP 인증.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
+          <t>확고한 가공업체 및 공급업체, 지속 가능성 및 품질에 대한 약속, 광범위한 제품. 주로 수출업체이지만, 조달 및 가공 활동은 인도네시아 내 전복 공급망에서 관련 플레이어임을 나타냅니다.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+          <t>https://variouseafood.com/</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
+          <t>스니펫에서 직접적인 이메일을 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3585,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tsukuino Co. Ltd.</t>
+          <t>Pesca K &amp; M Co., Ltd.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3583,18 +3595,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>tukuino@heart.ocn.ne.jp</t>
+          <t>pescauno@nifty.com</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.tsukuino.com/english.html</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tel: +81 3 5633 8765 / Fax: +81 3 5633 8766 (담당자: Hiro Kikuchi, Manager)</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>표1 (HS 030781)</t>
+          <t>표2 (HS 160557)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3609,44 +3625,44 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
+          <t>Sun East Bldg. 3F, 3-14-17 Toyo, Koto-Ku, 135-0016 (칠레/페루 지사보유)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
+          <t>칠레/페루산 수산물 수입업체. 칠레산 냉동 대하(각질포함), 통조림 대하(4-10조각/tin 213g), 건조 대하를 다룴. 브랜드: Pesca Uno, Don Jorge, Compomar.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
+          <t>통조림/건조 전복 가공품 유통 실적이 있는 수입상 — 한국산 가공품(HS160557) 종류 확장 제안 가능성.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://www.tsukuino.com/english.html</t>
+          <t>https://www.trade-seafood.com/directory/seafood/exporters/pesca-k-m-co-japan.htm</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
+          <t>페이지에 표시된 이메일은 JS 난독화(자동 추출 불가) 처리되어 있어 실제 주소로 기록하지 않음. 전화/팩스로 연락 권장.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-01 19:11:01</t>
+          <t>2026-07-31 14:58:21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Harmony Marine Products Sdn. Bhd.</t>
+          <t>True World Japan Inc.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3657,57 +3673,69 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.harmonymarine.com.my/</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tel: 03-6859-0881 (본사) / 03-6204-9532 (도쿄 지사)</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>전복, 해삼, 어교 등 고급 해산물 공급. 아시아-태평양, 남미, 아프리카에서 제품 및 원료를 조달하며, 국내 및 해외 시장에 해산물 가공품을 공급.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>표1 (HS 030781)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Shinmei Bldg. 3F, 3-3 Akashi-cho, Chuo-ku 104-0044 (본사); 후쿠오카 지사도 보유</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>수십 년의 경험, HACCP 인증, 품질 및 신선도에 중점.</t>
+          <t>한국 완도산 전복(Wando abalone)을 명시적으로 취급 중 — Live/Boiled/Frozen 규격별(50g~110g) 판매.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>다양한 지역에서 제품을 조달(수입 의미)하고 전복을 공급한다고 명시함.</t>
+          <t>이미 한국산(완도) 전복을 수입·판매 중인 실적이 있는 트레이딩 회사 — 신규 한국 공급처로서 가장 직접적인 협력 가능성.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGKQgXr5Q4iTaMV90WWjiFHsNExBM3ehTQIDTdfCYMajRuPXZkSRDlYsz9E64GfunKJYV8gmDLSafgGNk03B95XPYogH5mILd87xWzkQDKcvP-Cu6MYCj0J8Vgx6TdvrA==</t>
+          <t>https://www.trueworld-jp.com/en/product/awabi/index.html</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>이메일은 검색 결과에서 직접 확인되지 않았습니다.</t>
+          <t>공개 이메일 없음, 웹사이트 문의폼/대표번호를 통한 컸택 권장.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-01 19:11:01</t>
+          <t>2026-07-31 14:58:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ocean Fresh Seafood Products Sdn. Bhd.</t>
+          <t>Tsukuino Co. Ltd.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3715,51 +3743,55 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>tukuino@heart.ocn.ne.jp</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://oceanfresh.com.my/</t>
+          <t>https://www.tsukuino.com/english.html</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>전복을 포함한 냉동 해산물 제품의 도매업자, 소매업자, 가공업자 및 수출업자. 다른 공급업체로부터 해산물을 수입한다고 언급함. 주요 시장은 말레이시아, 터키, 중국, 태국, 베트남, 일본, 인도네시아, 필리핀, 싱가포르, 한국, 이탈리아, 포르투갈, 미국, 호주 등.</t>
+          <t>표1 (HS 030781)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Kuantan</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Lot 19869, Kampung Baru Peramu, 26060 Kuantan, Pahang Darul Makmur</t>
+          <t>Toyosu Market, store 1065-1068, Koto-ku</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>최고 품질의 수확, 부드럽고 풍미 있는 전복, 지속 가능한 관행. HACCP, GMP, MeSTI, HALAL, EU Number 75, GACC, FDA 인증 보유.</t>
+          <t>1965년 설립. Toyosu Market 소재 수산물 도매상. 활어, 전복(abalone), 신선어, 냉동품, 가공품, 건어물 등 취급.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>해산물 수입을 명시하고 있으며, 말레이시아 내 전복 도매/소매업자임.</t>
+          <t>전복을 포함한 다양한 수산물을 이미 취급 중인 도매상 — 국가/희망 어종/예상 물량을 포함해 연락 요망.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGbSloXTHvXsEfMfZoED_KCIgU-oG2Jwgsx9TKqGtZCuQGKIEh3w4CGJJDHh5LJ89eHlzW1HMKiwtPzU_9Q2mNbzcxl5W_yeCSzWdZ1t2c0GO8RF4MT169-ZGNK7DdQg1-yK5l3</t>
+          <t>https://www.tsukuino.com/english.html</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>이메일은 검색 결과에서 직접 확인되지 않았습니다.</t>
+          <t>이메일만 공개, 전화번호/문의폼 없음.</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3808,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
+          <t>Harmony Marine Products Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3787,43 +3819,35 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://oceanpacificonline.com/</t>
+          <t>https://www.harmonymarine.com.my/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>전복, 조개, 게, 생선, 육류, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 도매 및 공급.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Johor Bahru</t>
-        </is>
-      </c>
+          <t>전복, 해삼, 어교 등 고급 해산물 공급. 아시아-태평양, 남미, 아프리카에서 제품 및 원료를 조달하며, 국내 및 해외 시장에 해산물 가공품을 공급.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>다양한 해산물 및 육류 제품 취급.</t>
+          <t>수십 년의 경험, HACCP 인증, 품질 및 신선도에 중점.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>말레이시아에서 전복을 도매 및 공급한다고 명시함. 이는 수입 또는 수입업자로부터의 구매를 의미하며, 유통 채널로서 협력 가능성이 높음.</t>
+          <t>다양한 지역에서 제품을 조달(수입 의미)하고 전복을 공급한다고 명시함.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHwCZKluSSt7oYj7crdsFJGBYORnP7_17SuLRkDfcZvxASSQGO_bUsZZTa_jqnOoxGbtjsC8gzbYOQQwkxOBEzlDW6tfG8QCS6NY-Mspuoi1elIddpUydrGMAQKESf4Emdfedp57H0igxkoxxjOr6Vn8F4Amb4IXWxOV4W2zQgBjg==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGKQgXr5Q4iTaMV90WWjiFHsNExBM3ehTQIDTdfCYMajRuPXZkSRDlYsz9E64GfunKJYV8gmDLSafgGNk03B95XPYogH5mILd87xWzkQDKcvP-Cu6MYCj0J8Vgx6TdvrA==</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3835,7 +3859,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 19:11:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3845,7 +3869,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>V Top Frozen Food Sdn Bhd</t>
+          <t>Ocean Fresh Seafood Products Sdn. Bhd.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3853,25 +3877,21 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Vtopff@gmail.com</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://vtopfrozenfood.com/</t>
+          <t>https://oceanfresh.com.my/</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
+          <t>전복을 포함한 냉동 해산물 제품의 도매업자, 소매업자, 가공업자 및 수출업자. 다른 공급업체로부터 해산물을 수입한다고 언급함. 주요 시장은 말레이시아, 터키, 중국, 태국, 베트남, 일본, 인도네시아, 필리핀, 싱가포르, 한국, 이탈리아, 포르투갈, 미국, 호주 등.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Kuantan</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3881,109 +3901,113 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
+          <t>Lot 19869, Kampung Baru Peramu, 26060 Kuantan, Pahang Darul Makmur</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
+          <t>최고 품질의 수확, 부드럽고 풍미 있는 전복, 지속 가능한 관행. HACCP, GMP, MeSTI, HALAL, EU Number 75, GACC, FDA 인증 보유.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
+          <t>해산물 수입을 명시하고 있으며, 말레이시아 내 전복 도매/소매업자임.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://vtopfrozenfood.com/abalone-slices</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGbSloXTHvXsEfMfZoED_KCIgU-oG2Jwgsx9TKqGtZCuQGKIEh3w4CGJJDHh5LJ89eHlzW1HMKiwtPzU_9Q2mNbzcxl5W_yeCSzWdZ1t2c0GO8RF4MT169-ZGNK7DdQg1-yK5l3</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>웹사이트에 전화번호가 있습니다.</t>
+          <t>이메일은 검색 결과에서 직접 확인되지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 19:11:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bajamar Trading Group</t>
+          <t>Ocean Pacific Seafood &amp; Meat Sdn Bhd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>개인 에이전트</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>artavilo@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://oceanpacificonline.com/</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Producers, exporters, importers, wholesalers and agents of various seafood products including live and canned abalone, geoduck, lobster, fish, squid, scallops, shrimp, tuna, octopus.</t>
+          <t>전복, 조개, 게, 생선, 육류, 새우, 사시미, 소스, 소시지, 조미료, 스낵 등을 도매 및 공급.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Guerrero Negro</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Victoria Sanchez s/n, Col. Estado 30, Guerrero Negro, Baja California Sur, 23940</t>
+          <t>29, Jalan Perniagaan Setia 1/1, Taman Perniagaan Setia, 81100 Johor Bahru, Johor, Malaysia</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Live Red Abalone, Cultured Live Red Abalone, Blue and Yellow Canned Abalone, Yellow and Blue Abalone (frozen).</t>
+          <t>다양한 해산물 및 육류 제품 취급.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Explicitly imports and distributes abalone, acts as an agent, and deals with both live and canned abalone.</t>
+          <t>말레이시아에서 전복을 도매 및 공급한다고 명시함. 이는 수입 또는 수입업자로부터의 구매를 의미하며, 유통 채널로서 협력 가능성이 높음.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEywKxEIyVlMNjfilH11VDswQqsLbyNCU7KB_sereg0oMd6MEBpTRLhahJSb5ITplmF-lGSCyPqmzVjEvIRUUGjTD8ks23jykrR0C5IlZx-us7Uhww1TkqIWDq3d_g75TtnWphZSRfxCKtdPR7qLt6KUMo6XIBaSHqS9NjgbTEworKmrpJVnpV6fm7Igv28sf0h</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHwCZKluSSt7oYj7crdsFJGBYORnP7_17SuLRkDfcZvxASSQGO_bUsZZTa_jqnOoxGbtjsC8gzbYOQQwkxOBEzlDW6tfG8QCS6NY-Mspuoi1elIddpUydrGMAQKESf4Emdfedp57H0igxkoxxjOr6Vn8F4Amb4IXWxOV4W2zQgBjg==</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>이메일은 검색 결과에서 직접 확인되지 않았습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GlobalPezk</t>
+          <t>V Top Frozen Food Sdn Bhd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3993,57 +4017,53 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>info@globalpezk.com</t>
+          <t>Vtopff@gmail.com</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>globalpezk.com</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>+52 (669) 980 6440 (Whatsapp for Mazatlán)</t>
-        </is>
-      </c>
+          <t>https://vtopfrozenfood.com/</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Import and commercialization of premium seafood and exclusive supplies for oriental cuisine from the USA, China, Japan, and Canada. Wholesale and retail with national coverage in Mexico.</t>
+          <t>전복 슬라이스 및 기타 냉동 식품의 도매업체 및 공급업체.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Blvd. Fundadores 6119 Int. 11. El Rubí, C.P 22626, Tijuana, B.C. (Also operates in Mazatlán, Los Mochis, Culiacán, Guadalajara, and Mexico City)</t>
+          <t>21, Ground Floor, Lorong Bunga Melati 2A, Taman Maju Jaya, 56100 Kuala Lumpur, Malaysia.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Imported premium seafood, wagyu, and oriental cuisine supplies. Products mentioned include smoked eel, hamachi fillet, soft-shell crab, masago, langostino, tiger shrimp.</t>
+          <t>부드러운 전복 슬라이스, 풍부한 맛과 단단한 식감, 수프나 볶음 요리에 적합.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Explicitly imports seafood from various countries and specializes in supplies for oriental cuisine, where abalone is a key product. Possesses a strong distribution network across Mexico.</t>
+          <t>신선도와 품질에 중점, 전복 슬라이스 공급.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGZAJLAMkuIRT2SJZy4_LMCS0YEHBaLEV3uNNvyo_6qjuNukemFvTb2riRNlf6Y_eb0QOnBfUKIkNRGgwPQ0HRaFdsRwduGKkx8wQ2viuu2e4n2vMcwFmNdwBlZrdWJZg==</t>
+          <t>https://vtopfrozenfood.com/abalone-slices</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Abalone is not explicitly listed in their product examples, but their focus on imported seafood and oriental cuisine supplies makes it highly probable.</t>
+          <t>웹사이트에 전화번호가 있습니다.</t>
         </is>
       </c>
     </row>
@@ -4060,33 +4080,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Olanda Seafood Trading Inc.</t>
+          <t>Bajamar Trading Group</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>법인</t>
+          <t>개인 에이전트</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ventas@olandaseafood.com</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>www.olandaseafood.com</t>
-        </is>
-      </c>
+          <t>artavilo@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Commercialization of seafood products from different parts of the world, importing and distributing fresh and frozen seafood, including shellfish. Focus on quality and freshness, and supplies for the Oriental gastronomic sector.</t>
+          <t>Producers, exporters, importers, wholesalers and agents of various seafood products including live and canned abalone, geoduck, lobster, fish, squid, scallops, shrimp, tuna, octopus.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Guerrero Negro</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4096,29 +4112,25 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Boulevard Tercera Oeste 17503 Int 1 Garita de Otay, Otay, Tijuana, B.C., 22430</t>
+          <t>Victoria Sanchez s/n, Col. Estado 30, Guerrero Negro, Baja California Sur, 23940</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Import and commercialization of seafood, including shellfish. Products mentioned include salmon, octopus, shrimp, frozen fish, frozen noodles.</t>
+          <t>Live Red Abalone, Cultured Live Red Abalone, Blue and Yellow Canned Abalone, Yellow and Blue Abalone (frozen).</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Explicitly imports and distributes seafood. While abalone is not explicitly listed in their product snippets, 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
+          <t>Explicitly imports and distributes abalone, acts as an agent, and deals with both live and canned abalone.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNYFpQ3-O5BAGOJXp-8-1MXgnYuTONmz1IeuKZ8cjTcQDFTiUIliVDTOUiVv-9Pmlv-_yFfxQMX7171TKmxWaTj2u0Zkeu7QCZma2SACK8gvTa_I4BkXwS3dQs</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Abalone is not explicitly listed in their product snippets, but 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEywKxEIyVlMNjfilH11VDswQqsLbyNCU7KB_sereg0oMd6MEBpTRLhahJSb5ITplmF-lGSCyPqmzVjEvIRUUGjTD8ks23jykrR0C5IlZx-us7Uhww1TkqIWDq3d_g75TtnWphZSRfxCKtdPR7qLt6KUMo6XIBaSHqS9NjgbTEworKmrpJVnpV6fm7Igv28sf0h</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4128,12 +4140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Adri &amp; Zoon Schaal- en Schelpdierenhandel B.V.</t>
+          <t>GlobalPezk</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4143,51 +4155,59 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>info@adrienzoon.nl</t>
+          <t>info@globalpezk.com</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.adrienzoon.com</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>globalpezk.com</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>+52 (669) 980 6440 (Whatsapp for Mazatlán)</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>전 세계 25개 어시장에서 해산물을 조달하며, 생선, 조개류, 갑각류를 수입, 수출, 도매 및 유통합니다.</t>
+          <t>Import and commercialization of premium seafood and exclusive supplies for oriental cuisine from the USA, China, Japan, and Canada. Wholesale and retail with national coverage in Mexico.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Yerseke</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Krab 17, 4401 PA Yerseke</t>
+          <t>Blvd. Fundadores 6119 Int. 11. El Rubí, C.P 22626, Tijuana, B.C. (Also operates in Mazatlán, Los Mochis, Culiacán, Guadalajara, and Mexico City)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>전복 (Abalone), 아만데스/도그 코클 (Amandes/Dog Cockles), 멸치 (Anchovies), 북극 곤들매기 (Arctic char), 홍합 (Blue Mussels), 갈색 게 (Brown Crab), 대구 (Cod), 가재 (Crayfish), 굴 (Oysters), 기타 조개류 및 갑각류, 신선 수입 생선, 북해 생선, 냉동 해산물, 해초, 비식품 품목. 맞춤형 필레 및 포장 서비스를 제공합니다.</t>
+          <t>Imported premium seafood, wagyu, and oriental cuisine supplies. Products mentioned include smoked eel, hamachi fillet, soft-shell crab, masago, langostino, tiger shrimp.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1983년부터 운영된 가족 기업으로, 고객, 공급업체 및 직원과의 장기적인 파트너십에 중점을 둡니다. 고품질의 맞춤형 서비스를 제공하며, 친환경 어업 방식과 전기 트레일러 사용 등 지속 가능한 관행을 추구합니다. 자체 운송 차량을 통해 전 세계로 배송합니다.</t>
+          <t>Explicitly imports seafood from various countries and specializes in supplies for oriental cuisine, where abalone is a key product. Possesses a strong distribution network across Mexico.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://www.adrienzoon.com/contact</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGZAJLAMkuIRT2SJZy4_LMCS0YEHBaLEV3uNNvyo_6qjuNukemFvTb2riRNlf6Y_eb0QOnBfUKIkNRGgwPQ0HRaFdsRwduGKkx8wQ2viuu2e4n2vMcwFmNdwBlZrdWJZg==</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Abalone is not explicitly listed in their product examples, but their focus on imported seafood and oriental cuisine supplies makes it highly probable.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4197,12 +4217,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Starco Foodstuff</t>
+          <t>Olanda Seafood Trading Inc.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4210,68 +4230,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ventas@olandaseafood.com</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
+          <t>www.olandaseafood.com</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>냉동 전복 조개류를 포함한 다양한 제품의 공급업체 및 수출업체입니다. 보리, 목재 펠릿, 새우, 복사 용지, 금속 등도 취급합니다.</t>
+          <t>Commercialization of seafood products from different parts of the world, importing and distributing fresh and frozen seafood, including shellfish. Focus on quality and freshness, and supplies for the Oriental gastronomic sector.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Heerlen</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Hoofdstraat 208, Hoensbroek</t>
+          <t>Boulevard Tercera Oeste 17503 Int 1 Garita de Otay, Otay, Tijuana, B.C., 22430</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>냉동 전복 조개류 (Frozen Abalone Shellfish), 보리 (Barley), 목재 펠릿 (Wood Pellets), 새우 (Shrimps), 복사 용지 (Copy Paper), 폐철 (Used Rail Scrap), 구리 음극 (Copper Cathode), 아몬드 (Almond Nuts), 알루미늄 잉곳 (Aluminium Ingots), 냉동 닭고기 (Frozen Chicken), 양고기 (Lamb/Mutton Meat).</t>
+          <t>Import and commercialization of seafood, including shellfish. Products mentioned include salmon, octopus, shrimp, frozen fish, frozen noodles.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>B2B 플랫폼인 Tradewheel.com에 냉동 전복 조개류 공급업체로 등록되어 있습니다. 2019년에 설립되었습니다. 매우 다양한 제품군을 취급하는 일반 무역 회사일 수 있습니다.</t>
+          <t>Explicitly imports and distributes seafood. While abalone is not explicitly listed in their product snippets, 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNYFpQ3-O5BAGOJXp-8-1MXgnYuTONmz1IeuKZ8cjTcQDFTiUIliVDTOUiVv-9Pmlv-_yFfxQMX7171TKmxWaTj2u0Zkeu7QCZma2SACK8gvTa_I4BkXwS3dQs</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>이메일 주소는 Tradewheel.com 프로필에 직접 공개되어 있지 않습니다.</t>
+          <t>Abalone is not explicitly listed in their product snippets, but 'shellfish' is, and they import for the Oriental gastronomic sector where abalone is highly valued.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kiwi Fish</t>
+          <t>Adri &amp; Zoon Schaal- en Schelpdierenhandel B.V.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4279,68 +4303,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>info@adrienzoon.nl</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://kiwifish.co.nz</t>
+          <t>https://www.adrienzoon.com</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Premium seafood wholesaler, supplying an extensive range of live, chilled, and frozen shellfish, including pāua (abalone), to various markets including superyachts.</t>
+          <t>전 세계 25개 어시장에서 해산물을 조달하며, 생선, 조개류, 갑각류를 수입, 수출, 도매 및 유통합니다.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Yerseke</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Central Auckland</t>
+          <t>Krab 17, 4401 PA Yerseke</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Offers the best of New Zealand's sustainably caught seafood harvest, custom processed and delivered. Operates a Risk Management Programme (RMP) approved and audited by the Ministry for Primary Industries (MPI).</t>
+          <t>전복 (Abalone), 아만데스/도그 코클 (Amandes/Dog Cockles), 멸치 (Anchovies), 북극 곤들매기 (Arctic char), 홍합 (Blue Mussels), 갈색 게 (Brown Crab), 대구 (Cod), 가재 (Crayfish), 굴 (Oysters), 기타 조개류 및 갑각류, 신선 수입 생선, 북해 생선, 냉동 해산물, 해초, 비식품 품목. 맞춤형 필레 및 포장 서비스를 제공합니다.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Established premium seafood wholesaler with a wide range of products and strong quality control, suggesting capability for distributing abalone within New Zealand.</t>
+          <t>1983년부터 운영된 가족 기업으로, 고객, 공급업체 및 직원과의 장기적인 파트너십에 중점을 둡니다. 고품질의 맞춤형 서비스를 제공하며, 친환경 어업 방식과 전기 트레일러 사용 등 지속 가능한 관행을 추구합니다. 자체 운송 차량을 통해 전 세계로 배송합니다.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQET8rm6pD2fyT7blQHzUlDu1ArhqNzw8L5XOkDHPt6BbyoKTCVauxe6Oxsjy7ctVUvrR8vDBXtaw4VbGut7tDCnC3Pj4-1Xvaq0HCMnqW3hIuF82K8ePbg==</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Distributes New Zealand-sourced abalone (pāua).</t>
-        </is>
-      </c>
+          <t>https://www.adrienzoon.com/contact</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Waters Marine Limited</t>
+          <t>Starco Foodstuff</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4348,59 +4372,51 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>hello@northernwaters.co.nz</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://northernwaters.co.nz</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Facebook, TikTok, Instagram</t>
-        </is>
-      </c>
+          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sells whole pāua (abalone) for wholesale and retail.</t>
+          <t>냉동 전복 조개류를 포함한 다양한 제품의 공급업체 및 수출업체입니다. 보리, 목재 펠릿, 새우, 복사 용지, 금속 등도 취급합니다.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Warkworth</t>
+          <t>Heerlen</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>182 State Highway 1, Warkworth 0981, New Zealand (AUK Dome Valley)</t>
+          <t>Hoofdstraat 208, Hoensbroek</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sustainably harvested whole pāua (abalone) from the waters of Wairarapa and the South Island, offering authentic New Zealand flavor. Available for pickup or delivery.</t>
+          <t>냉동 전복 조개류 (Frozen Abalone Shellfish), 보리 (Barley), 목재 펠릿 (Wood Pellets), 새우 (Shrimps), 복사 용지 (Copy Paper), 폐철 (Used Rail Scrap), 구리 음극 (Copper Cathode), 아몬드 (Almond Nuts), 알루미늄 잉곳 (Aluminium Ingots), 냉동 닭고기 (Frozen Chicken), 양고기 (Lamb/Mutton Meat).</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Direct supplier and wholesaler of whole abalone, with clear contact information and a focus on sustainably harvested local product for the New Zealand market.</t>
+          <t>B2B 플랫폼인 Tradewheel.com에 냉동 전복 조개류 공급업체로 등록되어 있습니다. 2019년에 설립되었습니다. 매우 다양한 제품군을 취급하는 일반 무역 회사일 수 있습니다.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUTHdE_OizUFY_wnDheiVjs5gz8f6C2bi2M-kQnU8AHGUWDyfJfhJEeNJt5ZarxJzqydgApFymnTwOlFD3rW2VhMd-tPSVGo3JAsYEGcp40Nc3oTgS5tR5neHphsqorpRO59dq267d84rNGLqV6wH6d8HO7QE==</t>
+          <t>https://www.tradewheel.com/supplier/starco-foodstuff/</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Distributes New Zealand-sourced abalone (pāua).</t>
+          <t>이메일 주소는 Tradewheel.com 프로필에 직접 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4433,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sunz Seafood</t>
+          <t>Kiwi Fish</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4428,18 +4444,18 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://sunzseafood.co.nz</t>
+          <t>https://kiwifish.co.nz</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Wholesale and foodservice distribution of New Zealand minced pāua (abalone).</t>
+          <t>Premium seafood wholesaler, supplying an extensive range of live, chilled, and frozen shellfish, including pāua (abalone), to various markets including superyachts.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Whitianga</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4449,44 +4465,44 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>269 South Highway West Whitianga 3510</t>
+          <t>Central Auckland</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Premium New Zealand minced pāua (abalone), wild-caught and hand-harvested from Wairarapa and South Island, processed to export standards and frozen fresh. Offers meat-only pāua, ideal for patties, fritters, and commercial kitchen use.</t>
+          <t>Offers the best of New Zealand's sustainably caught seafood harvest, custom processed and delivered. Operates a Risk Management Programme (RMP) approved and audited by the Ministry for Primary Industries (MPI).</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Established wholesaler and foodservice supplier of abalone meat within New Zealand, indicating a strong distribution network for locally sourced product.</t>
+          <t>Established premium seafood wholesaler with a wide range of products and strong quality control, suggesting capability for distributing abalone within New Zealand.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6XLTPVgpag7xKK9QzbM_253BrUulevcWOCSV-khxpvqieFX7K7bO3HslNSPhfSIJySeYWXSDhgResGgoCJy1BNk6USQXQpWs7QU9S16CwXnw3H-JmFBse6B2Q6YReNBZXV8pjWQbq-KKVPcA-Zat9UCHvP7N6mtg50x-AO6e4Da1VnfLE</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQET8rm6pD2fyT7blQHzUlDu1ArhqNzw8L5XOkDHPt6BbyoKTCVauxe6Oxsjy7ctVUvrR8vDBXtaw4VbGut7tDCnC3Pj4-1Xvaq0HCMnqW3hIuF82K8ePbg==</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Primarily distributes New Zealand-sourced abalone (pāua).</t>
+          <t>Distributes New Zealand-sourced abalone (pāua).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FoodPhil Corporation</t>
+          <t>Northern Waters Marine Limited</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4494,60 +4510,76 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>hello@northernwaters.co.nz</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://foodphil.com/</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>https://northernwaters.co.nz</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Facebook, TikTok, Instagram</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Frozen and fresh seafood, including abalone, scallop, shrimps, lobsters, crabs, crablets, crabmeat.</t>
+          <t>Sells whole pāua (abalone) for wholesale and retail.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Warkworth</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>182 State Highway 1, Warkworth 0981, New Zealand (AUK Dome Valley)</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Proven trader of frozen and fresh seafood, supplying to several restaurants, distributors, and malls around the Philippines.</t>
+          <t>Sustainably harvested whole pāua (abalone) from the waters of Wairarapa and the South Island, offering authentic New Zealand flavor. Available for pickup or delivery.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Established in 2007, they are a reliable supplier of frozen and fresh seafood to hotels, restaurants, and retailers.</t>
+          <t>Direct supplier and wholesaler of whole abalone, with clear contact information and a focus on sustainably harvested local product for the New Zealand market.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://foodphil.com/</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUTHdE_OizUFY_wnDheiVjs5gz8f6C2bi2M-kQnU8AHGUWDyfJfhJEeNJt5ZarxJzqydgApFymnTwOlFD3rW2VhMd-tPSVGo3JAsYEGcp40Nc3oTgS5tR5neHphsqorpRO59dq267d84rNGLqV6wH6d8HO7QE==</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Distributes New Zealand-sourced abalone (pāua).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pancoastal International</t>
+          <t>Sunz Seafood</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4558,44 +4590,48 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://pancoastal.com/</t>
+          <t>https://sunzseafood.co.nz</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Importation, distribution, wholesale, and retail of premium frozen seafood. Product range includes Atlantic Salmon, Coho Salmon, Barramundi, Pompano, Chilean Seabass, Tuna.</t>
+          <t>Wholesale and foodservice distribution of New Zealand minced pāua (abalone).</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Metro Manila</t>
+          <t>Whitianga</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>269 South Highway West Whitianga 3510</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Specializes in premium frozen seafood, sourcing globally from Canada, Chile, Norway, EU, China, Vietnam, and USA. Serves restaurants, hotels, supermarkets, wholesalers, and retailers.</t>
+          <t>Premium New Zealand minced pāua (abalone), wild-caught and hand-harvested from Wairarapa and South Island, processed to export standards and frozen fresh. Offers meat-only pāua, ideal for patties, fritters, and commercial kitchen use.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Dedicated to offering a diverse range of top-quality imported seafood and leading the market in high-quality seafood distribution.</t>
+          <t>Established wholesaler and foodservice supplier of abalone meat within New Zealand, indicating a strong distribution network for locally sourced product.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://pancoastal.com/</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6XLTPVgpag7xKK9QzbM_253BrUulevcWOCSV-khxpvqieFX7K7bO3HslNSPhfSIJySeYWXSDhgResGgoCJy1BNk6USQXQpWs7QU9S16CwXnw3H-JmFBse6B2Q6YReNBZXV8pjWQbq-KKVPcA-Zat9UCHvP7N6mtg50x-AO6e4Da1VnfLE</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Abalone is not explicitly listed in their product examples, but their general scope as a 'premium frozen seafood importer' and distributor makes them a strong potential partner for abalone. Contact details like email/LinkedIn/messenger not explicitly listed on the homepage, but a 'Contact' page is available on their website.</t>
+          <t>Primarily distributes New Zealand-sourced abalone (pāua).</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4648,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TC International Seafoods Provider Inc.</t>
+          <t>FoodPhil Corporation</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4621,14 +4657,22 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://foodphil.com/</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Manufacturing, import and export of Fresh Frozen Marine products, including Frozen Boiled Abalone Meat.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Frozen and fresh seafood, including abalone, scallop, shrimps, lobsters, crabs, crablets, crabmeat.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Cebu</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>Philippines</t>
@@ -4637,24 +4681,20 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Actively trading in Taiwan, China, Hong Kong, Vietnam, USA and Canada.</t>
+          <t>Proven trader of frozen and fresh seafood, supplying to several restaurants, distributors, and malls around the Philippines.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Engaged in both import and export of fresh frozen marine products, indicating a strong supply chain and market presence.</t>
+          <t>Established in 2007, they are a reliable supplier of frozen and fresh seafood to hotels, restaurants, and retailers.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHuXKC2Pza8RjFQF46dD1k1qjUsZOZYpuhqP_IeQ9NAgxgU5WN--XiuJAdSYdV639ettOP0E8pmoUv3ePW26aNr17kXVLhBdJmbwcr7SiA7-K-5MOvza_DQsawn51Im7X9ksC7MtyPAsNMpSMlBQfligeiYlwfRTvQbojapfK_uRtBC</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Specific city within the Philippines not found in the provided snippets. Contact details like email/website not explicitly listed in the search results.</t>
-        </is>
-      </c>
+          <t>https://foodphil.com/</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4664,12 +4704,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>㈜제이에스코리아</t>
+          <t>Pancoastal International</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4680,48 +4720,44 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>js-korea.com</t>
+          <t>https://pancoastal.com/</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>전복, 굴 등 어패류 가공 및 수출 전문. 활어, 냉동, 통조림 등 다양한 형태로 가공하여 홍콩, 싱가포르, 베트남, 캐나다 등 세계 각지에 수출.</t>
+          <t>Importation, distribution, wholesale, and retail of premium frozen seafood. Product range includes Atlantic Salmon, Coho Salmon, Barramundi, Pompano, Chilean Seabass, Tuna.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>완도</t>
+          <t>Metro Manila</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>완도에 본사 및 식품 가공 공장 위치.</t>
-        </is>
-      </c>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>전복 가공식품 (통조림, 소스, 죽, 장 등), 굴 가공식품, 해외 수출. K·FISH 인증 보유.</t>
+          <t>Specializes in premium frozen seafood, sourcing globally from Canada, Chile, Norway, EU, China, Vietnam, and USA. Serves restaurants, hotels, supermarkets, wholesalers, and retailers.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>전복 가공 기술 및 수출 노하우가 뛰어나며, K·FISH 인증을 통해 품질 안정성을 확보하고 다양한 가공 제품으로 해외 시장에 진출하고 있습니다.</t>
+          <t>Dedicated to offering a diverse range of top-quality imported seafood and leading the market in high-quality seafood distribution.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvnf2Abv7NqaI1pbEBcXg5_-hi89lZ5556iuwdFyRctwjXwyaEYhM901eVExey6vZHCLG2nr3C1Ds3UgxRZBC2l7XMO0V9Hwe2dSiv9Eiln8VAsVxufluTjNuYHTksoBQK1LF7NASp5z_cPjB03gfmajsqvetdJ_MZQMDDQHE_kel2J0KkBfswaCR-M4EiTiX4uJYtFdg5QL47Zt8rQ4DJ7Hke9DdDqsWHLKoplDUi9hbzGTMsS37FIrEp1_O71yNFk4e8cwEwaSAIU9C-xfFqHRF_cTbnsDkL515JE3vwHY6A2yA36BPJZHGFFp1QPwcNMRBp7ltExYN9-pcsBO_T3RPaRjmUxAKC0G3FnWNyoXPT7et58evQA0Rcp1h2iJK22EkfH4CpCY1dkQuXFfkbgr6h6KCIA==</t>
+          <t>https://pancoastal.com/</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+          <t>Abalone is not explicitly listed in their product examples, but their general scope as a 'premium frozen seafood importer' and distributor makes them a strong potential partner for abalone. Contact details like email/LinkedIn/messenger not explicitly listed on the homepage, but a 'Contact' page is available on their website.</t>
         </is>
       </c>
     </row>
@@ -4733,12 +4769,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>㈜청산바다</t>
+          <t>TC International Seafoods Provider Inc.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4747,50 +4783,38 @@
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>cheongsanbada.com</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>전복 생산, 유통, 수출, 가공, 판매를 원스톱으로 진행하는 생산자 조합 회사. 일본, 홍콩, 유럽, 미국 등 해외 수출 및 국내 최고급 호텔, 백화점 거래.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>완도</t>
-        </is>
-      </c>
+          <t>Manufacturing, import and export of Fresh Frozen Marine products, including Frozen Boiled Abalone Meat.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>전남 완도군 완도읍 농공단지4길 22-7</t>
-        </is>
-      </c>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>활전복, 전복 가공식품, 아시아 최초 ASC 인증 보유.</t>
+          <t>Actively trading in Taiwan, China, Hong Kong, Vietnam, USA and Canada.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>전복 생산부터 수출까지 전 과정을 직접 관리하며, 아시아 최초 ASC 인증을 통해 품질과 지속가능성을 인정받았습니다. 해외 시장에 대한 높은 이해도와 유통망을 보유하고 있습니다.</t>
+          <t>Engaged in both import and export of fresh frozen marine products, indicating a strong supply chain and market presence.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVkzRFigxKCfhziKW_fKDfhJoYijxhubjB5tnFMmsV-sW4Hy7O47UY7PSizNwgsH9ltf3nlA7J_PcfmA2VN8TcatJD25HrYqVUA4eEVj5_as7jOPqqp9X38PI99eMFTx96G1kBBqatrgJmAqFLEwSfcCW_l6aPl4a7ueV0NkLYLdFEZltKfZAJ0nJdrlEcxLNzCY4xx-4CVxPPNRSUu8OA6l9jflRKq5crSvp4aoZzg8LOXK_2P7byIJdl-QxIVlAA5QWCiUfuaUts400REyvusr10ZahsNebaiZTaok3EDYrSY0J10Sq-yuiN34IlTHLWVfNEWYCVxkzX4Ix3EAkZWzRvYeJkFLlH3lZi7Po_Ul7QhAwasnpX0fHZVEtJ</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHuXKC2Pza8RjFQF46dD1k1qjUsZOZYpuhqP_IeQ9NAgxgU5WN--XiuJAdSYdV639ettOP0E8pmoUv3ePW26aNr17kXVLhBdJmbwcr7SiA7-K-5MOvza_DQsawn51Im7X9ksC7MtyPAsNMpSMlBQfligeiYlwfRTvQbojapfK_uRtBC</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>고객센터 전화번호는 061-553-5900이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+          <t>Specific city within the Philippines not found in the provided snippets. Contact details like email/website not explicitly listed in the search results.</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4831,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>완도전복주식회사</t>
+          <t>㈜제이에스코리아</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4818,13 +4842,13 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>wakorea.kr</t>
+          <t>js-korea.com</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>국내외 기업 및 개인 고객을 대상으로 활전복 및 가공전복 공급, 국내 최대 활전복 유통 및 가공전복 제품 생산, 롯데마트, 이마트, CJ프레시웨이 등 주요 거래처, 일본, 미국, 싱가포르 등 동남아 지역 수출.</t>
+          <t>전복, 굴 등 어패류 가공 및 수출 전문. 활어, 냉동, 통조림 등 다양한 형태로 가공하여 홍콩, 싱가포르, 베트남, 캐나다 등 세계 각지에 수출.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4839,27 +4863,27 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>전라남도 완도군</t>
+          <t>완도에 본사 및 식품 가공 공장 위치.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>활전복, 가공전복 (통조림, 동결제품), 국내 대형 유통망 공급, 해외 수출.</t>
+          <t>전복 가공식품 (통조림, 소스, 죽, 장 등), 굴 가공식품, 해외 수출. K·FISH 인증 보유.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>생산 어민과 완도군이 공동 출자하여 설립된 국내 최대 전복 전문 기업으로, 안정적인 공급망과 광범위한 국내외 유통망을 보유하고 있습니다.</t>
+          <t>전복 가공 기술 및 수출 노하우가 뛰어나며, K·FISH 인증을 통해 품질 안정성을 확보하고 다양한 가공 제품으로 해외 시장에 진출하고 있습니다.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVUzQYPzka2YSdvtxrcdlEwnD9kMLBlEc0nUobdRmu7Sh6VCkqAI7XZdkeOmLwU4iXbob_FjOZxeI7_jSshQFyj4k2SrvUPYNeiS2umO4l</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvnf2Abv7NqaI1pbEBcXg5_-hi89lZ5556iuwdFyRctwjXwyaEYhM901eVExey6vZHCLG2nr3C1Ds3UgxRZBC2l7XMO0V9Hwe2dSiv9Eiln8VAsVxufluTjNuYHTksoBQK1LF7NASp5z_cPjB03gfmajsqvetdJ_MZQMDDQHE_kel2J0KkBfswaCR-M4EiTiX4uJYtFdg5QL47Zt8rQ4DJ7Hke9DdDqsWHLKoplDUi9hbzGTMsS37FIrEp1_O71yNFk4e8cwEwaSAIU9C-xfFqHRF_cTbnsDkL515JE3vwHY6A2yA36BPJZHGFFp1QPwcNMRBp7ltExYN9-pcsBO_T3RPaRjmUxAKC0G3FnWNyoXPT7et58evQA0Rcp1h2iJK22EkfH4CpCY1dkQuXFfkbgr6h6KCIA==</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>고객센터 전화번호는 1577-8855이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
+          <t>이메일은 웹사이트에 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -4871,12 +4895,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dakar Ice</t>
+          <t>㈜청산바다</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4884,72 +4908,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>contact@dakarice.com</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>http://www.dakarice.com</t>
+          <t>cheongsanbada.com</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>수입/유통 (Import/Distribution)</t>
+          <t>전복 생산, 유통, 수출, 가공, 판매를 원스톱으로 진행하는 생산자 조합 회사. 일본, 홍콩, 유럽, 미국 등 해외 수출 및 국내 최고급 호텔, 백화점 거래.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>완도</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Hann plage, au km 5 boulevard de la commune de Dakar</t>
+          <t>전남 완도군 완도읍 농공단지4길 22-7</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>다양한 어류 취급, 특히 전복(abalone)을 월 최소 1컨테이너 처리 가능.</t>
+          <t>활전복, 전복 가공식품, 아시아 최초 ASC 인증 보유.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>전복(abalone)을 월 최소 1컨테이너 규모로 취급하며, 수산물 전반에 대한 경험이 풍부하여 협력 가능성이 높습니다.</t>
+          <t>전복 생산부터 수출까지 전 과정을 직접 관리하며, 아시아 최초 ASC 인증을 통해 품질과 지속가능성을 인정받았습니다. 해외 시장에 대한 높은 이해도와 유통망을 보유하고 있습니다.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHyVlKRmRztQxojYk66kNXGxJrx8_JI93Lx6e0cD3eq6iNIdAXKWbzug3ERNopXTxQ4Xu-KFj5Nf0dusDVD1ygDla4N1Jmpqe5_Hq1joE8XvJ2ZD6iyhMQbnLgAWb_WAVShMpUIkg==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVkzRFigxKCfhziKW_fKDfhJoYijxhubjB5tnFMmsV-sW4Hy7O47UY7PSizNwgsH9ltf3nlA7J_PcfmA2VN8TcatJD25HrYqVUA4eEVj5_as7jOPqqp9X38PI99eMFTx96G1kBBqatrgJmAqFLEwSfcCW_l6aPl4a7ueV0NkLYLdFEZltKfZAJ0nJdrlEcxLNzCY4xx-4CVxPPNRSUu8OA6l9jflRKq5crSvp4aoZzg8LOXK_2P7byIJdl-QxIVlAA5QWCiUfuaUts400REyvusr10ZahsNebaiZTaok3EDYrSY0J10Sq-yuiN34IlTHLWVfNEWYCVxkzX4Ix3EAkZWzRvYeJkFLlH3lZi7Po_Ul7QhAwasnpX0fHZVEtJ</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Fijin.com에 'Dakar Ice'가 전복을 취급하며 월 최소 1컨테이너를 처리할 수 있다고 명시되어 있습니다. 공식 웹사이트는 검색 결과에서 직접 확인되지 않았으나, 이메일 주소를 통해 도메인을 추정했습니다.</t>
+          <t>고객센터 전화번호는 061-553-5900이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Goh Joo Hin Pte Ltd</t>
+          <t>완도전복주식회사</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4957,72 +4977,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>food@gjh.com.sg</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>http://www.gjh.com.sg</t>
+          <t>wakorea.kr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Wholesaler, Distributor</t>
+          <t>국내외 기업 및 개인 고객을 대상으로 활전복 및 가공전복 공급, 국내 최대 활전복 유통 및 가공전복 제품 생산, 롯데마트, 이마트, CJ프레시웨이 등 주요 거래처, 일본, 미국, 싱가포르 등 동남아 지역 수출.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>완도</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Rep. of Korea</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
+          <t>전라남도 완도군</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
+          <t>활전복, 가공전복 (통조림, 동결제품), 국내 대형 유통망 공급, 해외 수출.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
+          <t>생산 어민과 완도군이 공동 출자하여 설립된 국내 최대 전복 전문 기업으로, 안정적인 공급망과 광범위한 국내외 유통망을 보유하고 있습니다.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVUzQYPzka2YSdvtxrcdlEwnD9kMLBlEc0nUobdRmu7Sh6VCkqAI7XZdkeOmLwU4iXbob_FjOZxeI7_jSshQFyj4k2SrvUPYNeiS2umO4l</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
+          <t>고객센터 전화번호는 1577-8855이나, 이메일은 웹사이트에 공개되어 있지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-01 13:25:05</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hosen Group Ltd.</t>
+          <t>Dakar Ice</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5030,47 +5046,55 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>contact@dakarice.com</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>http://www.dakarice.com</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Distributor, Manufacture &amp; Trade</t>
+          <t>수입/유통 (Import/Distribution)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>320 Jalan Boon Lay</t>
+          <t>Hann plage, au km 5 boulevard de la commune de Dakar</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Fast-moving consumer goods, including canned seafood. Distributes to Southeast Asia, Australia, Indian Sub-continent, Middle-East, North Asia, Pacific Islands.</t>
+          <t>다양한 어류 취급, 특히 전복(abalone)을 월 최소 1컨테이너 처리 가능.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>A leading distributor in Singapore's dry goods sector, explicitly stating import and distribution of fast-moving consumer goods, including canned seafood, across Southeast Asia.</t>
+          <t>전복(abalone)을 월 최소 1컨테이너 규모로 취급하며, 수산물 전반에 대한 경험이 풍부하여 협력 가능성이 높습니다.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHSaPnDkPMuPpMogVwbMshl1E9Nw6aZXhv9a1mjBlCE6ncCrnbj0op79iiQk2fqf2sGIpmnTi8wmK9UUUf37L46yOrLr3fVUEFLzOWZGYp5KtjCBvCptFndM3f7NYMvUxUxOhGHZxiezdgWxQ7JzeIYJXFkhZhMzQFpT6O7LA==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHyVlKRmRztQxojYk66kNXGxJrx8_JI93Lx6e0cD3eq6iNIdAXKWbzug3ERNopXTxQ4Xu-KFj5Nf0dusDVD1ygDla4N1Jmpqe5_Hq1joE8XvJ2ZD6iyhMQbnLgAWb_WAVShMpUIkg==</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Website and email not publicly available in the snippet. They market their own brands and represent others.</t>
+          <t>Fijin.com에 'Dakar Ice'가 전복을 취급하며 월 최소 1컨테이너를 처리할 수 있다고 명시되어 있습니다. 공식 웹사이트는 검색 결과에서 직접 확인되지 않았으나, 이메일 주소를 통해 도메인을 추정했습니다.</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5111,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oceanus Group Limited</t>
+          <t>Goh Joo Hin Pte Ltd</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5097,18 +5121,18 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>contact@oceanus.com.sg</t>
+          <t>food@gjh.com.sg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>http://www.oceanus.com.sg</t>
+          <t>http://www.gjh.com.sg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
+          <t>Importer, Exporter, Wholesaler, Distributor</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5123,34 +5147,34 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
+          <t>8 Gul Avenue, Singapore 629652 (Operating Hours: Mon-Fri 8:00am-5:00pm)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
+          <t>Fresh, frozen, and dried abalone products from premium brands; also deals in canned food and sundry goods. Distributes the 'New Moon' abalone brand.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
+          <t>Singapore's leading abalone supplier, wholesaler, and distributor with an extensive warehousing and distribution system, distributing to numerous countries. Handles a wide range of abalone products.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpYd7gUYobfEBiApu1siS2zf4dArjGWIlsG1j-73HIK8PqMFiI3fWCfHAhOGz2KBePMkcbjJaxDGjN61_HWN9JpBT5B6zJXz8wK_JNWuAvxX8qtSRafeSowQ0lDA==</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
+          <t>Multiple addresses found, prioritizing the one with operating hours for general contact. Email and website confirmed.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5160,7 +5184,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Teck Sang Pte Ltd</t>
+          <t>Hosen Group Ltd.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5168,20 +5192,12 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>local@tecksang.com</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://www.tecksang.com</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
+          <t>Importer, Exporter, Distributor, Manufacture &amp; Trade</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5196,34 +5212,34 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>11 Hongkong Street, Singapore 059654</t>
+          <t>320 Jalan Boon Lay</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
+          <t>Fast-moving consumer goods, including canned seafood. Distributes to Southeast Asia, Australia, Indian Sub-continent, Middle-East, North Asia, Pacific Islands.</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
+          <t>A leading distributor in Singapore's dry goods sector, explicitly stating import and distribution of fast-moving consumer goods, including canned seafood, across Southeast Asia.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHSaPnDkPMuPpMogVwbMshl1E9Nw6aZXhv9a1mjBlCE6ncCrnbj0op79iiQk2fqf2sGIpmnTi8wmK9UUUf37L46yOrLr3fVUEFLzOWZGYp5KtjCBvCptFndM3f7NYMvUxUxOhGHZxiezdgWxQ7JzeIYJXFkhZhMzQFpT6O7LA==</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
+          <t>Website and email not publicly available in the snippet. They market their own brands and represent others.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-01 13:25:05</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5233,7 +5249,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>YL Enterprises (Yilai Abalone)</t>
+          <t>Oceanus Group Limited</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5241,12 +5257,20 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>contact@oceanus.com.sg</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>http://www.oceanus.com.sg</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Buyer, Importer, Manufacture</t>
+          <t>Aquaculture Production, Abalone Processing &amp; Distribution, Food &amp; Beverage</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5261,44 +5285,44 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>865 Mountbatten Road #03-02, Katong Shopping Centre</t>
+          <t>25 Ubi Road 4, #03-05 UBIX, Singapore 408621</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Canned abalone processing enterprise, larval nursing, abalone breeding, abalone processing. Exports to Singapore, South East Asia, Taiwan, Hong Kong, Macau.</t>
+          <t>Land-based abalone producer, engaged in vacuum packing, canning, drying, and curing abalone for worldwide distribution. Focuses on premium quality Japanese breed abalones.</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Directly identified as a Buyer and Importer of abalone in Singapore, with a focus on Southeast Asia and surrounding regions. They also manufacture.</t>
+          <t>A vertically integrated abalone group, from aquaculture production to processing and global distribution. Known as the largest land-based abalone producer.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdXWn3sY9CX7JdfaAp4fQShQKS9VRARffKM3O8GOoBfVS1FEP6Hjsur3G3BqYsWUxlytZfFJy78jUCAJHY9defZhq-D_oI3S--AbgjcTdExdiUheXg73Q==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCX-0MjMTDz9Wy0X9Uq-4yTpi24cffD8REg5DyAqmEFTlEbB5kRLVZ16tjB4RLORJ6OBfvPoTdgnJNeGL_KbbpwOcOD9TZLBnbwcLQw0-qFeLyMn1ZOSNchEb1tgoeClqYAyWCv89P7mHzyBDrYaGjaFVn9oTxcvolWvuVu0S745tMVIA=</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Contact person: Mr. Lim. Phone and fax numbers are listed but incomplete in the snippet. Website not publicly available in the snippet.</t>
+          <t>LinkedIn link found is for Instagram. Email and website confirmed.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlantis Foods</t>
+          <t>Teck Sang Pte Ltd</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5308,70 +5332,70 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>info@atlantisfoods.co.za</t>
+          <t>local@tecksang.com</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.atlantisfoods.co.za/</t>
+          <t>https://www.tecksang.com</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>South Africa의 주요 해산물 유통 회사 중 하나로, 도매업체, 식품 서비스 제공업체 및 소매업체에 고품질 해산물 제품을 소싱, 가공 및 유통합니다. 과거 전무이사가 전복(Abalone) 및 냉장 보관을 담당했습니다.</t>
+          <t>Importer, Exporter, Wholesale Distributor, Retailer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8 Wessex Road Paarden Eiland Cape Town, South Africa, 7405 (Sales &amp; Marketing Office)</t>
+          <t>11 Hongkong Street, Singapore 059654</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>다양한 신선, 냉동, 부가가치 및 즉석 해산물 제품을 취급하며, 전복을 포함한 해산물 유통 경험이 있습니다.</t>
+          <t>Canned abalone (various brands including Calmex, Jade Tiger, Golden Ocean, On Hing, Lighthouse, Goldstar), dried seafood, nuts, beans, pulses, grains, spices, dried fruits, and other Chinese food ingredients.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>남아프리카 공화국 내에서 광범위한 유통망을 가진 대규모 해산물 유통업체로, 다양한 채널에 대량 공급이 가능합니다.</t>
+          <t>One of Singapore's most established food ingredients importers, exporters, and wholesale distributors. Described as the country's largest supplier of canned abalone, offering a wide range of options for B2B and B2C segments.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://www.atlantisfoods.co.za/contact-us/</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1mtWsTZTnldFGCIXnIggY2WmRJ5Xx6XNpeO5iWWTJcecHwFYzW3XyrN5az4cqYfBpBZCaHjW0y5nhTkal0oI7UeKB5Dn16d4jL5ZHXR5e3BJgcMoHx3WfAeJxJzND5M_3nRw4JAUBI_zBkbb9GRpISHXBpHI9sM=</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>BestFoodImporters.com에 따르면 'Importer, Distributor, Wholesaler, Supplier'로 분류됩니다. 이전 그룹 물류 관리자가 전복을 담당했다는 언급이 있습니다.</t>
+          <t>Website also referred to as tecksangonline.com. Email and website confirmed.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 13:25:05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Greenfish</t>
+          <t>YL Enterprises (Yilai Abalone)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5379,59 +5403,47 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ops@greenfish.co.za, Sales1@greenfish.co.za</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://greenfish.co.za/</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>063 666 2802 (Whatsapp)</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>온라인 및 도매 해산물 공급업체로, 양식 전복(perlemoen)을 포함한 신선한 해산물을 취급합니다.</t>
+          <t>Buyer, Importer, Manufacture</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>온라인 전용 (소매점 없음), Cape Town 및 주변 지역(CBD, Southern Suburbs, Houtbay, Plattekloof, Deep South, Table View, Blouberg, Melkbos, Durbanville, Stellenbosch, Somerset West, Franschhoek, Paarl) 배송 가능.</t>
+          <t>865 Mountbatten Road #03-02, Katong Shopping Centre</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>6개들이 라이브 양식 전복(perlemoen)을 판매하며, 노르웨이산 연어, 대구, 참치, 킹클립, 홍합, 굴, 옐로우테일, 카벨조우 등 다양한 신선 해산물을 제공합니다.</t>
+          <t>Canned abalone processing enterprise, larval nursing, abalone breeding, abalone processing. Exports to Singapore, South East Asia, Taiwan, Hong Kong, Macau.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>양식 전복을 직접 공급하며, 개인 소비자 및 도매 고객 모두에게 서비스를 제공합니다. 소규모 또는 전문적인 주문, 레스토랑 직거래에 적합합니다.</t>
+          <t>Directly identified as a Buyer and Importer of abalone in Singapore, with a focus on Southeast Asia and surrounding regions. They also manufacture.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://greenfish.co.za/products/abalone-perlemoen-live-box-cultivated-x6</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdXWn3sY9CX7JdfaAp4fQShQKS9VRARffKM3O8GOoBfVS1FEP6Hjsur3G3BqYsWUxlytZfFJy78jUCAJHY9defZhq-D_oI3S--AbgjcTdExdiUheXg73Q==</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>온라인 전용 업체이며, 소매점은 없습니다.</t>
+          <t>Contact person: Mr. Lim. Phone and fax numbers are listed but incomplete in the snippet. Website not publicly available in the snippet.</t>
         </is>
       </c>
     </row>
@@ -5443,12 +5455,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FRESHCADO RECIEN PESCADO SL</t>
+          <t>Atlantis Foods</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5458,51 +5470,55 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>contact@freshcado.es</t>
+          <t>info@atlantisfoods.co.za</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://freshcado.es</t>
+          <t>https://www.atlantisfoods.co.za/</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Wholesale and retail of fresh and frozen fish and seafood, including premium seafood. Operates as an online fishmonger and supplies professionals across Spain, sourcing from Mercamadrid and international ports.</t>
+          <t>South Africa의 주요 해산물 유통 회사 중 하나로, 도매업체, 식품 서비스 제공업체 및 소매업체에 고품질 해산물 제품을 소싱, 가공 및 유통합니다. 과거 전무이사가 전복(Abalone) 및 냉장 보관을 담당했습니다.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>C/ de la Diputació, 256, 08007 Barcelona</t>
+          <t>8 Wessex Road Paarden Eiland Cape Town, South Africa, 7405 (Sales &amp; Marketing Office)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Offers a wide selection of fresh and frozen seafood. Emphasizes maximum freshness, direct product from Mercamadrid, and 24/48h delivery. Committed to sustainability and responsible fishing.</t>
+          <t>다양한 신선, 냉동, 부가가치 및 즉석 해산물 제품을 취급하며, 전복을 포함한 해산물 유통 경험이 있습니다.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>As a large seafood wholesaler and online retailer with a wide range of fresh and frozen seafood, including a 'Premium Seafood' category, Freshcado is a strong prospect for importing and distributing abalone.</t>
+          <t>남아프리카 공화국 내에서 광범위한 유통망을 가진 대규모 해산물 유통업체로, 다양한 채널에 대량 공급이 가능합니다.</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://freshcado.es/legal-notice/, https://freshcado.es/accessibility-statement/, https://freshcado.es/general-terms-and-conditions/, https://freshcado.es/en/fish-and-seafood-wholesaler-in-spain/, https://freshcado.es/en/online-fishmonger-buy-fresh-fish-and-seafood/, https://freshcado.es/en/comprar-smoked-and-canned-products-online/</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+          <t>https://www.atlantisfoods.co.za/contact-us/</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>BestFoodImporters.com에 따르면 'Importer, Distributor, Wholesaler, Supplier'로 분류됩니다. 이전 그룹 물류 관리자가 전복을 담당했다는 언급이 있습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5512,12 +5528,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Globalimar Europa, SL</t>
+          <t>Greenfish</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5527,51 +5543,59 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>info@globalimar.com</t>
+          <t>ops@greenfish.co.za, Sales1@greenfish.co.za</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.globalimar.com</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>https://greenfish.co.za/</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>063 666 2802 (Whatsapp)</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Frozen seafood import, production, and commercialization for mass-market, including bivalves, cephalopods, crustaceans, surimi, and prepared fish. Serves Spain, Europe, USA, and Maghreb region.</t>
+          <t>온라인 및 도매 해산물 공급업체로, 양식 전복(perlemoen)을 포함한 신선한 해산물을 취급합니다.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Llagostera</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>C/ Jaume I, 2A, 17240 Llagostera, Girona</t>
+          <t>온라인 전용 (소매점 없음), Cape Town 및 주변 지역(CBD, Southern Suburbs, Houtbay, Plattekloof, Deep South, Table View, Blouberg, Melkbos, Durbanville, Stellenbosch, Somerset West, Franschhoek, Paarl) 배송 가능.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Specialists in frozen seafood products, with a focus on quality and sustainability. Offers a diversified range of frozen seafood. Explicitly states import and commercialization activities.</t>
+          <t>6개들이 라이브 양식 전복(perlemoen)을 판매하며, 노르웨이산 연어, 대구, 참치, 킹클립, 홍합, 굴, 옐로우테일, 카벨조우 등 다양한 신선 해산물을 제공합니다.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Explicitly states 'import, produce and commercialize' frozen seafood. Their broad range of seafood products, including bivalves, makes them a highly probable candidate for importing abalone.</t>
+          <t>양식 전복을 직접 공급하며, 개인 소비자 및 도매 고객 모두에게 서비스를 제공합니다. 소규모 또는 전문적인 주문, 레스토랑 직거래에 적합합니다.</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://www.globalimar.com/contact/, https://www.conxemar.com/en/asociados/globalimar-europa-sl, https://www.conxemar.com/en/exhibitor/globalimar-europa-sl-conxemar-2024, https://www.globalimar.com/en/company/specialists-in-frozen-seafood/, https://www.bestfoodimporters.com/importer/globalimar-europa</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
+          <t>https://greenfish.co.za/products/abalone-perlemoen-live-box-cultivated-x6</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>온라인 전용 업체이며, 소매점은 없습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5586,7 +5610,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>La Alondra Seafood (Pescados La Alondra Sl)</t>
+          <t>FRESHCADO RECIEN PESCADO SL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5596,23 +5620,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>hola@laalondraseafood.es</t>
+          <t>contact@freshcado.es</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.laalondraseafood.es</t>
+          <t>https://freshcado.es</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Distribution of fresh and cryogenized seafood for retail, HORECA channel, and international markets. Focuses on premium seafood products from the best fishing grounds worldwide.</t>
+          <t>Wholesale and retail of fresh and frozen fish and seafood, including premium seafood. Operates as an online fishmonger and supplies professionals across Spain, sourcing from Mercamadrid and international ports.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5622,22 +5646,22 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Avenida Euro núm. 24 Puesto 17 19 21, 47009 Valladolid, Castilla-león</t>
+          <t>C/ de la Diputació, 256, 08007 Barcelona</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Specializes in high-quality, fresh, and cryogenized seafood. Offers a catalog of seafood products from the best fishing grounds globally. Strong presence in HORECA and retail, with international distribution capabilities.</t>
+          <t>Offers a wide selection of fresh and frozen seafood. Emphasizes maximum freshness, direct product from Mercamadrid, and 24/48h delivery. Committed to sustainability and responsible fishing.</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Their focus on premium seafood, international distribution, and the HORECA channel makes them a good prospect for importing and distributing abalone. Their advanced cryogenic preservation technology could be a suitable fit for abalone products.</t>
+          <t>As a large seafood wholesaler and online retailer with a wide range of fresh and frozen seafood, including a 'Premium Seafood' category, Freshcado is a strong prospect for importing and distributing abalone.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://www.laalondraseafood.es/en/distribution/, https://www.laalondraseafood.es/en/fresh-fish-and-seafood/, https://www.laalondraseafood.es/en/cryogenized-seafood/, https://www.laalondraseafood.es/en/innovation/, https://www.empresite.com/PESCADOS-LA-ALONDRA-SL.html, https://www.laalondraseafood.es/en/contact/</t>
+          <t>https://freshcado.es/legal-notice/, https://freshcado.es/accessibility-statement/, https://freshcado.es/general-terms-and-conditions/, https://freshcado.es/en/fish-and-seafood-wholesaler-in-spain/, https://freshcado.es/en/online-fishmonger-buy-fresh-fish-and-seafood/, https://freshcado.es/en/comprar-smoked-and-canned-products-online/</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
@@ -5645,17 +5669,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-01 02:57:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fresh Harvest (Pvt) Ltd</t>
+          <t>Globalimar Europa, SL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5663,45 +5687,53 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>info@globalimar.com</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://freshharvest.lk/</t>
+          <t>https://www.globalimar.com</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Seafood Importer and Distributor</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Frozen seafood import, production, and commercialization for mass-market, including bivalves, cephalopods, crustaceans, surimi, and prepared fish. Serves Spain, Europe, USA, and Maghreb region.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Llagostera</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>C/ Jaume I, 2A, 17240 Llagostera, Girona</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Leading seafood company in Sri Lanka, delivers high quality ready-to-cook seafood products. Caters to local market, supplies to top-class hotel chains, leading restaurants, and expanding in local retail market. Acts as an importer of high quality seafood.</t>
+          <t>Specialists in frozen seafood products, with a focus on quality and sustainability. Offers a diversified range of frozen seafood. Explicitly states import and commercialization activities.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>스리랑카 현지 시장에 고품질 해산물을 수입하여 호텔, 레스토랑 및 소매점에 공급하는 선도적인 회사입니다. 전복 수입 및 유통에 대한 협력 가능성이 높습니다.</t>
+          <t>Explicitly states 'import, produce and commercialize' frozen seafood. Their broad range of seafood products, including bivalves, makes them a highly probable candidate for importing abalone.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcQYNWYOJvFZ5465KMss_BHieKPxvrhT-oNHOi2KKwePbAueaXewTLSRdFvyC53bKsJB9SxBoH5hsVkTNWMHCaabHTVCeR0iPYsraHevFcJpFSX0n9</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>이메일/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다.</t>
-        </is>
-      </c>
+          <t>https://www.globalimar.com/contact/, https://www.conxemar.com/en/asociados/globalimar-europa-sl, https://www.conxemar.com/en/exhibitor/globalimar-europa-sl-conxemar-2024, https://www.globalimar.com/en/company/specialists-in-frozen-seafood/, https://www.bestfoodimporters.com/importer/globalimar-europa</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5711,12 +5743,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Johnson Seafood Co., Ltd.</t>
+          <t>La Alondra Seafood (Pescados La Alondra Sl)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5724,46 +5756,50 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>hola@laalondraseafood.es</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.johnsonseafood.com.tw</t>
+          <t>https://www.laalondraseafood.es</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Leading seafood importer in Taiwan. Imports live, frozen, and freshly chilled seafood, including abalone &amp; scallop. Sources from over 40 countries.</t>
+          <t>Distribution of fresh and cryogenized seafood for retail, HORECA channel, and international markets. Focuses on premium seafood products from the best fishing grounds worldwide.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Tainan</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Based in Qigu coastal areas around Tainan, aquaculture in Tainan's Jiali Township.</t>
+          <t>Avenida Euro núm. 24 Puesto 17 19 21, 47009 Valladolid, Castilla-león</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Wide range of seafood products (fish, shrimps, crabs, shellfish, mollusk, processed seafood), regular SGS inspection, provides safe and tasty food materials. Product range covers live seafood, frozen seafood, and freshly chilled seafood.</t>
+          <t>Specializes in high-quality, fresh, and cryogenized seafood. Offers a catalog of seafood products from the best fishing grounds globally. Strong presence in HORECA and retail, with international distribution capabilities.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Over 50 years of operation, excellent reputation, sizeable procurement volume, trusted partner by overseas suppliers, and commitment to food safety with SGS inspection.</t>
+          <t>Their focus on premium seafood, international distribution, and the HORECA channel makes them a good prospect for importing and distributing abalone. Their advanced cryogenic preservation technology could be a suitable fit for abalone products.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://www.johnsonseafood.com.tw/about-us/company-profile</t>
+          <t>https://www.laalondraseafood.es/en/distribution/, https://www.laalondraseafood.es/en/fresh-fish-and-seafood/, https://www.laalondraseafood.es/en/cryogenized-seafood/, https://www.laalondraseafood.es/en/innovation/, https://www.empresite.com/PESCADOS-LA-ALONDRA-SL.html, https://www.laalondraseafood.es/en/contact/</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -5771,17 +5807,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-01 02:57:29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ming Sheng Seafood Co., Ltd.</t>
+          <t>Fresh Harvest (Pvt) Ltd</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5792,51 +5828,47 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.mingsheng.com.tw</t>
+          <t>https://freshharvest.lk/</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Importer of fresh frozen marine products, supplying diversified premium seafood to wholesalers across Taiwan. Imports over 300 premium frozen seafood products, sourcing from 4 oceans and 5 continents.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Kaohsiung City</t>
-        </is>
-      </c>
+          <t>Seafood Importer and Distributor</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>2F, 332 Zihyou 2nd Rd., Zuoying District, Kaohsiung City, Taiwan.</t>
-        </is>
-      </c>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Over 30 years of experience, strong relationships with manufacturers and customers, world-class logistic system. Offers a set of diversified premium seafood.</t>
+          <t>Leading seafood company in Sri Lanka, delivers high quality ready-to-cook seafood products. Caters to local market, supplies to top-class hotel chains, leading restaurants, and expanding in local retail market. Acts as an importer of high quality seafood.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Long-standing importer with a wide global sourcing network and a focus on timely delivery to wholesalers. Strong reputation and trust from domestic and international suppliers.</t>
+          <t>스리랑카 현지 시장에 고품질 해산물을 수입하여 호텔, 레스토랑 및 소매점에 공급하는 선도적인 회사입니다. 전복 수입 및 유통에 대한 협력 가능성이 높습니다.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://www.mingsheng.com.tw/about-ming-sheng</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcQYNWYOJvFZ5465KMss_BHieKPxvrhT-oNHOi2KKwePbAueaXewTLSRdFvyC53bKsJB9SxBoH5hsVkTNWMHCaabHTVCeR0iPYsraHevFcJpFSX0n9</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>이메일/링크드인/메신저 정보는 검색 결과에서 직접 확인되지 않았습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-08-02 08:27:13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5846,7 +5878,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YEN &amp; Brothers Enterprise CO.,LTD.</t>
+          <t>Johnson Seafood Co., Ltd.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5854,25 +5886,21 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>service@mail.yens.com.tw</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.yens.com.tw</t>
+          <t>https://www.johnsonseafood.com.tw/en/about/company-profile.html</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Abalone importer and wholesaler, deals with frozen abalone meat, whole-cooked abalone, Australian abalone. Also handles other fish, crustacean, shellfish, mollusc, meat, soup, prepared foods.</t>
+          <t>Import and sale of live, frozen, and freshly chilled seafood, including abalone, from over 40 countries.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>New Taipei City</t>
+          <t>Tainan</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5882,40 +5910,44 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>14F, NO. 217,SEC. 2, NEW TAIPEI BLVD., XINZHUANG DIST., NEW TAIPEI CITY 242, TAIWAN (R.O.C.)</t>
+          <t>Based in the Qigu coastal areas around Tainan, Taiwan</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Global purchasing, R&amp;D and production, food safety, logistic management. Importer and wholesaler of various seafood products, including abalone.</t>
+          <t>One of Taiwan's leading seafood importers with over 50 years of operation. Strong reputation and procurement volume. Products undergo regular SGS inspection and relevant certification.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Established company with global purchasing capabilities and a strong focus on food safety and quality management. Handles a variety of abalone products (frozen, whole-cooked, Australian).</t>
+          <t>A major and experienced seafood importer in Taiwan with a broad global sourcing network and a focus on food safety.</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://www.yens.com.tw/products/shellfish/abalone</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG9UshjI0ExfCNf4d2-z2zMUmUQ4KjwkQBoPR9j4CVFscKWxurEnAX8Zev2bR-USrOXwu7BP8d0ycZraUrJH1yYryuy2LgT3owJe3kjUIEpVgK7ZUFbia4M9kotC8lLhcJjj3OSuNoiVPZApPpCNF81_uOW8OdUqzwpBmA=</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Email not explicitly found on the provided page.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
+          <t>Ming Sheng Seafood Co., Ltd.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5923,72 +5955,64 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>info@ruifuoilfood.com</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://ruifuoilfood.com/</t>
+          <t>https://www.mingsheng.com.tw</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
+          <t>Importer of fresh frozen marine products, supplying diversified premium seafood to wholesalers across Taiwan. Imports over 300 premium frozen seafood products, sourcing from 4 oceans and 5 continents.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Si Maha Phot, Prachin Buri</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
+          <t>2F, 332 Zihyou 2nd Rd., Zuoying District, Kaohsiung City, Taiwan.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
+          <t>Over 30 years of experience, strong relationships with manufacturers and customers, world-class logistic system. Offers a set of diversified premium seafood.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
+          <t>Long-standing importer with a wide global sourcing network and a focus on timely delivery to wholesalers. Strong reputation and trust from domestic and international suppliers.</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
-        </is>
-      </c>
+          <t>https://www.mingsheng.com.tw/about-ming-sheng</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-02 08:27:13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thai Abalone Co.,Ltd.</t>
+          <t>YEN &amp; Brothers Enterprise CO., LTD.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5999,65 +6023,65 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://m.ec21.com/company/thaiabalone/</t>
+          <t>https://www.yens.com.tw/en/products/abalone.html</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
+          <t>Abalone importer and wholesaler, dealing with various seafood including fish, crustacean, shellfish, mollusc, meat, soup, prepared foods.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Pathiu, Chumphon</t>
+          <t>New Taipei City</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
+          <t>14 F, No. 219, Sec.2, New Taipei Blvd., Xinzhuang Dist., New Taipei City 242, Taiwan (R.O.C.)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
+          <t>Global purchasing, R&amp;D and production, food safety, logistic management. Offers a wide range of seafood products.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
+          <t>Directly states being an abalone importer and wholesaler with a focus on global purchasing and food safety.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://m.ec21.com/company/thaiabalone/</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGqvswlkQS9desdzVtSWw-6WVSciUh2MlF0BnPLCzbYSdt8fhamWXUtT0Ec-f5nY2se8UeCEjVv12AUFphkZNl0rbXGpIvRDcKKYwENREO5F5UFB7QszlRuF6re-ucRDShNuSQYm-Sxc9nHvjh5H2roXtkbNn_8DgRlh9U0v_OoAqpSCiETN0z-rwjq</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
+          <t>Email not explicitly found on the provided page, only phone numbers.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Monterey Abalone Company</t>
+          <t>YEN &amp; Brothers Enterprise CO.,LTD.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6065,68 +6089,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>service@mail.yens.com.tw</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://montereyabalone.com</t>
+          <t>https://www.yens.com.tw</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
+          <t>Abalone importer and wholesaler, deals with frozen abalone meat, whole-cooked abalone, Australian abalone. Also handles other fish, crustacean, shellfish, mollusc, meat, soup, prepared foods.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Monterey</t>
+          <t>New Taipei City</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
+          <t>14F, NO. 217,SEC. 2, NEW TAIPEI BLVD., XINZHUANG DIST., NEW TAIPEI CITY 242, TAIWAN (R.O.C.)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
+          <t>Global purchasing, R&amp;D and production, food safety, logistic management. Importer and wholesaler of various seafood products, including abalone.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
+          <t>Established company with global purchasing capabilities and a strong focus on food safety and quality management. Handles a variety of abalone products (frozen, whole-cooked, Australian).</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Email not found in provided snippets.</t>
-        </is>
-      </c>
+          <t>https://www.yens.com.tw/products/shellfish/abalone</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-08-02 08:27:13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ocean Floor Inc.</t>
+          <t>日芳牌 (Lian Hung Food Co., Ltd.)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6134,56 +6158,68 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>yun@lianhung.com.tw</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.lianhung.com.tw/en/product-category/abalone-seafood/</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Supplier of abalone seafood, including Chilean Abalone Slices, and other shellfish ingredients, pre-cooked food, sushi topping, stock &amp; sauce. Offers food OEM services.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Tainan City</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>No. 22, Gongye 5th Rd., Annan District, Tainan City, Taiwan (Tainan Technology Industrial Park)</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
+          <t>Specializes in various seafood products and offers OEM services. Products include Chilean Abalone Slices.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
+          <t>A Taiwanese company dealing with abalone seafood products, including imported Chilean abalone, and offering OEM services.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>City, email, and website not found in provided snippets.</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGHJ3pDMxlV_AYBtDy4bS4aV3N-1CDnCwWBRhmkKv-YZXDW4enWR7xSOfEV78X7YnzmSyerAADI7r1sF87N1yaZLwk87g4VMj8x_AgbsI3ETtOAsA2HGTeVaP8CedMvjAj54m-6EP8N8psdalpbsKAwoeWG9Rgu</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-31 12:22:35</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seafarers Inc.</t>
+          <t>RUIFU EDIBLE OIL (THAILAND) CO., LTD</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6191,56 +6227,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>info@ruifuoilfood.com</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://ruifuoilfood.com/</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>자사 '생선' 카테고리에서 '껍질이 있는 전복'을 포함한 다양한 제품 공급업체.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Si Maha Phot, Prachin Buri</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>106, MOO 7, THA TUM, SI MAHA PHOT, PRACHIN BURI 25140.</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
+          <t>껍질이 있는 전복, 냉동 식품, 12개월 유통기한.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
+          <t>전복 공급업체, 직접 이메일 및 WhatsApp 연락처 이용 가능.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
+          <t>https://ruifuoilfood.com/product/abalone-with-shelled/</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>City, email, and website not found in provided snippets.</t>
+          <t>주로 식용유 회사이지만 다른 식품도 공급합니다.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 19:31:29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Abalone Fish Processing LLC</t>
+          <t>Thai Abalone Co.,Ltd.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6249,63 +6301,67 @@
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Fish and Seafood Processors</t>
+          <t>전복, 살아있는 전복, 냉동 전복, 조미 소스, 전복 소스 공급업체.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Pathiu, Chumphon</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Near Factory Mart, New Ind Area, Ajman / 78a, Amman street, Ajman Industrial 2</t>
+          <t>42 Moo 1, Bangson Subdistrict, Pathiu, Chumphon.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Fish and Seafood Processors. The company name suggests a focus on abalone.</t>
+          <t>주요 제품은 전복, 살아있는 전복, IQF 냉동 전복입니다.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>A seafood processing company, likely involved in the import and distribution of various seafood, potentially including abalone, given its name. They are listed as 'Fish And Seafood Processors'.</t>
+          <t>다양한 형태의 전복을 직접 공급하는 업체. 명시적으로 '수입업체'는 아니지만, 태국 내 전복 공급업체는 무역에 있어 관련 연락처가 될 수 있습니다.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHFN1ioKMvAABGXDTz-XA2FisFHogtokbmSflhk3jbvA8p7zaDQFSZwrI0hdELPSZmK4Wc-LYdVkfx9Icf2bIlxGcy5n-3UNZ38yb-YhBVFHE0QP_48m00iz7KofFmbKySqsSnnKW3nKI_I128GTUIQfv-FTBuOaPRMuJfMDST_</t>
+          <t>https://m.ec21.com/company/thaiabalone/</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Phone number: 06-7438606</t>
+          <t>EC21의 마지막 로그인 날짜는 2007년 1월 27일로, 정보가 오래되었을 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dior Fresh Fish</t>
+          <t>Monterey Abalone Company</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6316,61 +6372,65 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://diorfreshfish.com/</t>
+          <t>https://montereyabalone.com</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Fresh and frozen seafood, including Whole Shell Abalone. Delivery across UAE (Dubai, Abu Dhabi, Sharjah).</t>
+          <t>Wholesale and direct-to-consumer sales of live abalone.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Monterey</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Waterfront market Deira, Dubai.</t>
+          <t>160 Municipal Wharf #2, Monterey, CA 93940</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Sells 'Fresh Whole Shell Abalone' sourced from pristine cold-water regions (FAO Areas 27 and 81). Halal Compliant &amp; Hygienically Processed. Cold-Chain Delivery (0–4°C). Offers custom fish preparation and 2-hour/same-day delivery in Dubai, next-day across UAE.</t>
+          <t>Ocean-grown, sustainably raised California Red Abalone. Sells live abalone in various sizes. Offers wholesale terms to chefs and restaurateurs.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Directly imports and distributes abalone, with a focus on quality and cold-chain logistics. They cater to households and high-end restaurants.</t>
+          <t>Direct source of high-quality, sustainably farmed live abalone in the USA. Ideal for partners seeking fresh, locally sourced product.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF1n6IrUDF_2UqEV1FcEcY_91lJj3LUZsTqcN2E-z6ynL2pmf6_SM1ymPQjnZMML_D3hhCHfVLVikDUjllk1QaU7pVCslFnbxRTPWXUF1y6MLjcD1m-IBi83-ovGxE8KZhXTNMo4yW_3PmnAFzpJ5O5jrf8_bcyfg==</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoi1ct3RsBchNrjKeIKEL4MUNj2iYQ-LgrmXoQULCgc3rEBC2MSFNH1uvRVV4tKKtjzCCNP0tOofPRV83YfuF0yyL-fY_xsAVe973oClT3k7WM7l9SsB_pG6N3wEIIdXTomva2</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Email not found in provided snippets.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sea World Fish Processing Llc</t>
+          <t>Ocean Floor Inc.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6380,66 +6440,54 @@
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>+971564117152 (WhatsApp)</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Frozen Seafood, Shrimp, Salmon, Squid, Abalone, Lobster, Tuna, Trevally. Fish &amp; Seafood Importers, Exporters &amp; Processors.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Ajman</t>
-        </is>
-      </c>
+          <t>Imports seafood from Baja California, Mexico, and distributes to restaurants and wholesalers in the USA.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Meena Rd, Nr Fish Market, Al Jurf Indl Area, Ajman. Also listed in Al Quoz Industrial 3, Dubai.</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Supplier of Frozen Seafood including Abalone, Shrimp, Salmon, Squid, Lobster, Tuna, Trevally. Also lists Salmon, King Fish, Octopus.</t>
+          <t>Specializes in whole fresh frozen wild abalone from Baja California, Mexico. Also imports Diver Jumbo Scallops, Blue Crab, and Diver Bay Scallops.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Explicitly listed as a supplier of 'Frozen Abalone' and 'Frozen Seafood'. They are also 'Fish &amp; Seafood Importers, Exporters &amp; Processors'.</t>
+          <t>Established importer and distributor of wild abalone from Mexico, serving restaurants and wholesalers in the US market. Good for suppliers of Mexican abalone.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHilrZwc_-sVdE6bxfa_EuTM77Z-w7QcSFQExMjw8zLaBemFs7vOrXa3yrDTsx-7YDW4t9Z8Al_fRoC7fqyqD0LgQWijBKAJOUkaCbOVcgwqY3UASq9uRKwk3Qd-ag7ux7mmxmf1e26daaZRNlDWEd_2ZaKnwEDtz5oxNbZCL9OEVnyaMgh0ArAZFmnkodMlaIL</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Phone number: +971-6-7444559</t>
+          <t>City, email, and website not found in provided snippets.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-01 08:27:44</t>
+          <t>2026-07-31 12:22:35</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Direct Seafoods</t>
+          <t>Seafarers Inc.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6447,55 +6495,39 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>sales@directseafoods.co.uk</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>https://www.directseafoods.co.uk/</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Wholesale abalone, frozen wholesale abalone, supplying to restaurants, caterers, and distributors.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Colchester</t>
-        </is>
-      </c>
+          <t>Imports and distributes fresh and frozen fish in USA, Canada, Caribbean, and Central America since 1999.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Crown Court Severalls Business Park, Clough road, Colchester CO4 9TZ</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Expertly sourced wholesale abalone, premium quality, range of pack sizes, sustainably sourced options, frozen abalone.</t>
+          <t>A fresh and frozen fish importer. Imports and distributes various seafood including abalone, tunas, snappers, groupers, oil fish, escolar, mahi mahi, king fish, cobia, corvina, turbot, wahoo, swordfish, mussels, smelt, squid.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Clearly states they are suppliers of wholesale abalone for businesses, including caterers and distributors, indicating they import or source in bulk.</t>
+          <t>Long-standing importer and distributor with a wide distribution network across North and Central America, including the Caribbean. Suitable for abalone suppliers seeking broad market access.</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHUIYsQ2UBPSBJ867GFx9lsSGgOScseBoH5kgVzDM4Z9FqfpgCuJOckuXoixQJWbbT--kaUWwRR_UzXIpjbk7uvQF9L8O0c_NRa3jAnZIPK8qH5hk4lkW-WX7hkiJFFlIanM64gCt86Rui4ofRFzhQfr-MHgQRPuI-tVU0=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBHnm704bueVNrlUu4QfISp-Hjx2SY6jMA19X6H_TBnXvQkVfmcRWecCg6Uwm-0mQUMdTjegM7zjAxj8lqzJCtlhXsahxxjfuBCArrrw-jdzpopTHc1wlK5qIn32FsKIUu5e7pju6YGEhs2WH2MsN6YPxcC9bQyMEBz_xHyOmLw==</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Part of Bidfresh Limited.</t>
+          <t>City, email, and website not found in provided snippets.</t>
         </is>
       </c>
     </row>
@@ -6507,12 +6539,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fine Food Specialist</t>
+          <t>Abalone Fish Processing LLC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6520,55 +6552,47 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>support@finefoodspecialist.co.uk</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://www.finefoodspecialist.co.uk/</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sells large Australian abalone online, offers wholesale.</t>
+          <t>Fish and Seafood Processors</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Not explicitly stated beyond 'London and the UK'.</t>
+          <t>Near Factory Mart, New Ind Area, Ajman / 78a, Amman street, Ajman Industrial 2</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Large Australian abalone, frozen, sashimi grade, offers next day delivery.</t>
+          <t>Fish and Seafood Processors. The company name suggests a focus on abalone.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Explicitly states 'Wholesale available. Trusted UK fine food wholesaler,' indicating they are a distributor.</t>
+          <t>A seafood processing company, likely involved in the import and distribution of various seafood, potentially including abalone, given its name. They are listed as 'Fish And Seafood Processors'.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGMjhqPJpEsff_zAS7zQT4UIck_UEpFMw36Ap14taYnEELyVa1mAKjWqtFFwvjKYoZ6_VuZ37CEImyilNnDqE0avI5M1E1YyngtytpAY67YhY8ts-aoTS1FWZ3AtkuSrw-UyioUx9MMvlc6lidPdRqiatFTdXzrMlinyaaYKh0gqQ==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHFN1ioKMvAABGXDTz-XA2FisFHogtokbmSflhk3jbvA8p7zaDQFSZwrI0hdELPSZmK4Wc-LYdVkfx9Icf2bIlxGcy5n-3UNZ38yb-YhBVFHE0QP_48m00iz7KofFmbKySqsSnnKW3nKI_I128GTUIQfv-FTBuOaPRMuJfMDST_</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Offers both retail and wholesale.</t>
+          <t>Phone number: 06-7438606</t>
         </is>
       </c>
     </row>
@@ -6580,12 +6604,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seafood Australia</t>
+          <t>Dior Fresh Fish</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6596,46 +6620,46 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://seafoodaustralia.co.uk/</t>
+          <t>https://diorfreshfish.com/</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sells Premium Australian Canned Abalone and Wild Abalone, with 'Fast UK Shipping' and a 'Wholesale' section.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Fresh and frozen seafood, including Whole Shell Abalone. Delivery across UAE (Dubai, Abu Dhabi, Sharjah).</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Delivers to anywhere in the UK.</t>
+          <t>Waterfront market Deira, Dubai.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Premium Australian wild and farmed abalone, canned abalone, direct from farm to door, sustainably farmed or caught.</t>
+          <t>Sells 'Fresh Whole Shell Abalone' sourced from pristine cold-water regions (FAO Areas 27 and 81). Halal Compliant &amp; Hygienically Processed. Cold-Chain Delivery (0–4°C). Offers custom fish preparation and 2-hour/same-day delivery in Dubai, next-day across UAE.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Has a 'Wholesale' section on their website and offers direct supply of Australian abalone, suggesting they are an importer/distributor.</t>
+          <t>Directly imports and distributes abalone, with a focus on quality and cold-chain logistics. They cater to households and high-end restaurants.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHydvT7JMFhRuJb4p5iZBcaBABfGyX2tWoFEHuHnjJ_kqBq4Eb1I0ey6Ty7x2ua2-wI7FN6fuFx3syKl6sTP9xSL_oGe4JKYhCxMN3JZuetVzzTAo5vHoDUhwQt-44=</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Specializes in Australian abalone.</t>
-        </is>
-      </c>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF1n6IrUDF_2UqEV1FcEcY_91lJj3LUZsTqcN2E-z6ynL2pmf6_SM1ymPQjnZMML_D3hhCHfVLVikDUjllk1QaU7pVCslFnbxRTPWXUF1y6MLjcD1m-IBi83-ovGxE8KZhXTNMo4yW_3PmnAFzpJ5O5jrf8_bcyfg==</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6645,12 +6669,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fishy Vietnam Co., Ltd.</t>
+          <t>Sea World Fish Processing Llc</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6658,53 +6682,53 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Fishy.vn@gmail.com</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>https://fishy.vn/</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>+971564117152 (WhatsApp)</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Importing and distributing top-class seafood, including various types of abalone (Frozen Abalone (Loco) Meat, Frozen Australian Greenlip Abalone, Frozen Abalone, Braised Abalone In Oyster Sauce, Abalone Seafood Soup).</t>
+          <t>Frozen Seafood, Shrimp, Salmon, Squid, Abalone, Lobster, Tuna, Trevally. Fish &amp; Seafood Importers, Exporters &amp; Processors.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City</t>
+          <t>Meena Rd, Nr Fish Market, Al Jurf Indl Area, Ajman. Also listed in Al Quoz Industrial 3, Dubai.</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Specializes in importing and distributing top-class seafood. Products include various types of abalone (frozen, Australian greenlip, loco meat, abalone seafood soup, braised abalone in oyster sauce). Focus on product quality, dedication, and customer satisfaction.</t>
+          <t>Supplier of Frozen Seafood including Abalone, Shrimp, Salmon, Squid, Lobster, Tuna, Trevally. Also lists Salmon, King Fish, Octopus.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Direct importer and distributor, indicating a clear channel for cooperation. Emphasizes quality and customer satisfaction.</t>
+          <t>Explicitly listed as a supplier of 'Frozen Abalone' and 'Frozen Seafood'. They are also 'Fish &amp; Seafood Importers, Exporters &amp; Processors'.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFnIbNcTSOzpm1rjxZKNdOXHZFHXPLvkR6w0O11uKwUJy88CBKHuqahAqg6N3_l-KqHBD9TlsdBOFLPPwARm092X_aBdYKa_w7CDxuB3MzJ4junbM6oKTpwaIgIt3W2fFE=</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHilrZwc_-sVdE6bxfa_EuTM77Z-w7QcSFQExMjw8zLaBemFs7vOrXa3yrDTsx-7YDW4t9Z8Al_fRoC7fqyqD0LgQWijBKAJOUkaCbOVcgwqY3UASq9uRKwk3Qd-ag7ux7mmxmf1e26daaZRNlDWEd_2ZaKnwEDtz5oxNbZCL9OEVnyaMgh0ArAZFmnkodMlaIL</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Phone number: +971-6-7444559</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6714,12 +6738,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sai Thanh Foods</t>
+          <t>Direct Seafoods</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6729,51 +6753,55 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>salesfreshfood@sacofoods.vn</t>
+          <t>sales@directseafoods.co.uk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://saithanhfoods.com/</t>
+          <t>https://www.directseafoods.co.uk/</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Supplier of frozen abalone (Haliotis Diversicolor) from Vietnam. Also deals with other seafood like sea fish, river fish, octopus, squid, shellfish.</t>
+          <t>Wholesale abalone, frozen wholesale abalone, supplying to restaurants, caterers, and distributors.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Lot III-22, Street 19/5A, Tan Binh Industrial Park, Tay Thanh Ward, Ho Chi Minh City, Vietnam</t>
+          <t>Crown Court Severalls Business Park, Clough road, Colchester CO4 9TZ</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Specializes in frozen abalone (Haliotis Diversicolor) of Vietnamese origin. They also offer other seafood products.</t>
+          <t>Expertly sourced wholesale abalone, premium quality, range of pack sizes, sustainably sourced options, frozen abalone.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Direct supplier of frozen abalone, indicating a potential for direct sourcing. They invite inquiries for specifications and pricing.</t>
+          <t>Clearly states they are suppliers of wholesale abalone for businesses, including caterers and distributors, indicating they import or source in bulk.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdzZHAIL6EJepETfinawUNWPxz-8vXV951xIFxRs0HZB32IxHGNPOCJKb_txdlYe0VZWWpejeThan1R4sfd3Pj_eg_ZzTpeCR9cmBU_meF-izlTZCbpQTD124H_zWN5Fe1iuEj6bD5iqxCJW8af6yMk-s=</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHUIYsQ2UBPSBJ867GFx9lsSGgOScseBoH5kgVzDM4Z9FqfpgCuJOckuXoixQJWbbT--kaUWwRR_UzXIpjbk7uvQF9L8O0c_NRa3jAnZIPK8qH5hk4lkW-WX7hkiJFFlIanM64gCt86Rui4ofRFzhQfr-MHgQRPuI-tVU0=</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Part of Bidfresh Limited.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6783,12 +6811,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Viet Nam</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Trọng Đức Seafood</t>
+          <t>Fine Food Specialist</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6796,60 +6824,72 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>support@finefoodspecialist.co.uk</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://trongduc.com/</t>
+          <t>https://www.finefoodspecialist.co.uk/</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Imports abalone mainly from Korea, Japan, and neighboring countries. Also deals with other seafood like Japanese scallops, sea eel. Offers good prices for wholesalers, agents, and distributors.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>Sells large Australian abalone online, offers wholesale.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Not explicitly stated beyond 'London and the UK'.</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Imports abalone from Korea, Japan, and neighboring countries. Offers various sizes of Korean abalone. Emphasizes product quality, reputation, and direct import for good prices for wholesalers/agents/distributors.</t>
+          <t>Large Australian abalone, frozen, sashimi grade, offers next day delivery.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Explicitly states good prices for wholesalers, agents, and distributors, making them a direct potential partner. They also offer returns if not satisfied.</t>
+          <t>Explicitly states 'Wholesale available. Trusted UK fine food wholesaler,' indicating they are a distributor.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFNhjSu_CUVmGlZe8ulZHnui_rrcb9z2Gm9Dk4aJlf3YHrn288thuxtw0ARGxmu3uLnFb-7BIWKI_KEffIQPvRk0m3fct_IGwngL1ebQV7ngD9mdbqcdBnMHvE7US-xDV1Y9SOFz--R_tY6SDR-u-90jvs=</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGMjhqPJpEsff_zAS7zQT4UIck_UEpFMw36Ap14taYnEELyVa1mAKjWqtFFwvjKYoZ6_VuZ37CEImyilNnDqE0avI5M1E1YyngtytpAY67YhY8ts-aoTS1FWZ3AtkuSrw-UyioUx9MMvlc6lidPdRqiatFTdXzrMlinyaaYKh0gqQ==</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>City and location detail not explicitly mentioned in the provided source.</t>
+          <t>Offers both retail and wholesale.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-01 19:11:01</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FGC Joint Stock Company</t>
+          <t>Seafood Australia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6857,68 +6897,64 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>fgc.seafoods@gmail.com</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>www.fgc-foods.com</t>
+          <t>https://seafoodaustralia.co.uk/</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>수입 전복(고기술 냉동, 1kg/봉지, 10kg/상자)을 포함한 고품질의 안전한 수입 식품 제조 및 공급.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Hanoi</t>
-        </is>
-      </c>
+          <t>Sells Premium Australian Canned Abalone and Wild Abalone, with 'Fast UK Shipping' and a 'Wholesale' section.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>No. Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi, Vietnam</t>
+          <t>Delivers to anywhere in the UK.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>베트남 소비자를 위한 품질, 안전, 다양한 맛에 중점. 유통기한 24개월.</t>
+          <t>Premium Australian wild and farmed abalone, canned abalone, direct from farm to door, sustainably farmed or caught.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>수입 전복 공급을 명시하고 있으며, 연락처 정보를 제공함.</t>
+          <t>Has a 'Wholesale' section on their website and offers direct supply of Australian abalone, suggesting they are an importer/distributor.</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHE6mcXntxILCL80ePf_RaMd8_2Q1VoZPmmcM2-Dcup5cbCvzqz-CNF3AtJgiZHZj5dHrRODpU085MAGySrx5zFHgCQCU8gHHdan8Z3Wb6s_AhMxdw26TkHvNYPM8Gq0QOKdFkrqPzEyKdEXFiEOWmuJHcoRfbQ==</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHydvT7JMFhRuJb4p5iZBcaBABfGyX2tWoFEHuHnjJ_kqBq4Eb1I0ey6Ty7x2ua2-wI7FN6fuFx3syKl6sTP9xSL_oGe4JKYhCxMN3JZuetVzzTAo5vHoDUhwQt-44=</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Specializes in Australian abalone.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-01 19:11:01</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fishy Vietnam Co., Ltd</t>
+          <t>Fishy Vietnam Co., Ltd.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6939,7 +6975,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>베트남 내 최고급 해산물 수입 및 유통 전문. 냉동 전복(Loco) 고기, 호주산 그린립 전복, 전복 해산물 수프, 굴 소스 전복찜 등 전복 제품 취급.</t>
+          <t>Importing and distributing top-class seafood, including various types of abalone (Frozen Abalone (Loco) Meat, Frozen Australian Greenlip Abalone, Frozen Abalone, Braised Abalone In Oyster Sauce, Abalone Seafood Soup).</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6959,17 +6995,17 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>최고급 해산물 수입 및 유통 전문. 제품 품질, 헌신, 명성을 최우선으로 함.</t>
+          <t>Specializes in importing and distributing top-class seafood. Products include various types of abalone (frozen, Australian greenlip, loco meat, abalone seafood soup, braised abalone in oyster sauce). Focus on product quality, dedication, and customer satisfaction.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>전복 수입 및 유통을 명시하고 있으며, 명확한 연락처 정보를 제공함.</t>
+          <t>Direct importer and distributor, indicating a clear channel for cooperation. Emphasizes quality and customer satisfaction.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHwAboISDt8AuptY7bnv5ph6VjqmmkpAPFOZk2JMVsRdGqtoCvPclbAo3ifjMuo6MaoY7vIgLjwlRUF1m8aehW6P6lXgS_HsmX9cInaCZgP16MKCnA5DwofX7ObFe2jdw==</t>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFnIbNcTSOzpm1rjxZKNdOXHZFHXPLvkR6w0O11uKwUJy88CBKHuqahAqg6N3_l-KqHBD9TlsdBOFLPPwARm092X_aBdYKa_w7CDxuB3MzJ4junbM6oKTpwaIgIt3W2fFE=</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
@@ -6977,17 +7013,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-31 19:31:29</t>
+          <t>2026-08-01 08:27:44</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Trọng Đức Seafood</t>
+          <t>Sai Thanh Foods</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6995,41 +7031,309 @@
           <t>법인</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>salesfreshfood@sacofoods.vn</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trongduc.vn/</t>
+          <t>https://saithanhfoods.com/</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
+          <t>Supplier of frozen abalone (Haliotis Diversicolor) from Vietnam. Also deals with other seafood like sea fish, river fish, octopus, squid, shellfish.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Lot III-22, Street 19/5A, Tan Binh Industrial Park, Tay Thanh Ward, Ho Chi Minh City, Vietnam</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Specializes in frozen abalone (Haliotis Diversicolor) of Vietnamese origin. They also offer other seafood products.</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Direct supplier of frozen abalone, indicating a potential for direct sourcing. They invite inquiries for specifications and pricing.</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFdzZHAIL6EJepETfinawUNWPxz-8vXV951xIFxRs0HZB32IxHGNPOCJKb_txdlYe0VZWWpejeThan1R4sfd3Pj_eg_ZzTpeCR9cmBU_meF-izlTZCbpQTD124H_zWN5Fe1iuEj6bD5iqxCJW8af6yMk-s=</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:27:44</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Viet Nam</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Trọng Đức Seafood</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://trongduc.com/</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Imports abalone mainly from Korea, Japan, and neighboring countries. Also deals with other seafood like Japanese scallops, sea eel. Offers good prices for wholesalers, agents, and distributors.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Imports abalone from Korea, Japan, and neighboring countries. Offers various sizes of Korean abalone. Emphasizes product quality, reputation, and direct import for good prices for wholesalers/agents/distributors.</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Explicitly states good prices for wholesalers, agents, and distributors, making them a direct potential partner. They also offer returns if not satisfied.</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFNhjSu_CUVmGlZe8ulZHnui_rrcb9z2Gm9Dk4aJlf3YHrn288thuxtw0ARGxmu3uLnFb-7BIWKI_KEffIQPvRk0m3fct_IGwngL1ebQV7ngD9mdbqcdBnMHvE7US-xDV1Y9SOFz--R_tY6SDR-u-90jvs=</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>City and location detail not explicitly mentioned in the provided source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:11:01</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FGC Joint Stock Company</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>fgc.seafoods@gmail.com</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>www.fgc-foods.com</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>수입 전복(고기술 냉동, 1kg/봉지, 10kg/상자)을 포함한 고품질의 안전한 수입 식품 제조 및 공급.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>No. Louis XII-LK45, Hoang Van Thu New Urban Area, Louis XII Street, Yen So Ward, Hoang Mai District, Hanoi, Vietnam</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>베트남 소비자를 위한 품질, 안전, 다양한 맛에 중점. 유통기한 24개월.</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>수입 전복 공급을 명시하고 있으며, 연락처 정보를 제공함.</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHE6mcXntxILCL80ePf_RaMd8_2Q1VoZPmmcM2-Dcup5cbCvzqz-CNF3AtJgiZHZj5dHrRODpU085MAGySrx5zFHgCQCU8gHHdan8Z3Wb6s_AhMxdw26TkHvNYPM8Gq0QOKdFkrqPzEyKdEXFiEOWmuJHcoRfbQ==</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:11:01</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Fishy Vietnam Co., Ltd</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Fishy.vn@gmail.com</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://fishy.vn/</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>베트남 내 최고급 해산물 수입 및 유통 전문. 냉동 전복(Loco) 고기, 호주산 그린립 전복, 전복 해산물 수프, 굴 소스 전복찜 등 전복 제품 취급.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>No. 621/1 National Highway 1A, KP3, Linh Xuan Ward, Thu Duc City, Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>최고급 해산물 수입 및 유통 전문. 제품 품질, 헌신, 명성을 최우선으로 함.</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>전복 수입 및 유통을 명시하고 있으며, 명확한 연락처 정보를 제공함.</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHwAboISDt8AuptY7bnv5ph6VjqmmkpAPFOZk2JMVsRdGqtoCvPclbAo3ifjMuo6MaoY7vIgLjwlRUF1m8aehW6P6lXgS_HsmX9cInaCZgP16MKCnA5DwofX7ObFe2jdw==</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-31 19:31:29</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Trọng Đức Seafood</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://trongduc.vn/</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>한국, 일본 및 인근 국가에서 전복을 수입하여 도매업체, 에이전트 및 유통업체에 공급합니다.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
         <is>
           <t>수입 전복 (한국, 일본 및 인근 국가산), 다양한 크기, 도매업체/에이전트/유통업체에 좋은 가격, 품질 명성, 완전한 문서 및 바코드.</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>직접 수입업체이며, 도매업체/에이전트/유통업체에 좋은 가격을 제공하고, 품질 및 문서화에 중점을 둡니다.</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>https://trongduc.vn/san-pham/bao-ngu-nhap-khau/</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>이메일/전화번호는 스니펫에 명시되어 있지 않지만 웹사이트가 제공됩니다.</t>
         </is>
